--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -11121,7 +11121,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:36</t>
+          <t>2026-08-18 15:57:02</t>
         </is>
       </c>
     </row>

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -11121,7 +11121,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:57:02</t>
+          <t>2026-08-18 16:25:25</t>
         </is>
       </c>
     </row>

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ145"/>
+  <dimension ref="A1:AJ152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="AH20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="AH21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
@@ -2380,13 +2380,13 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
       </c>
       <c r="AG26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" t="b">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3065,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA37" t="n">
         <v>10.15</v>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4091,13 +4091,13 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
       </c>
       <c r="AG51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH51" t="b">
         <v>0</v>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4307,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="AH54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4498,7 +4498,10 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-0.28</v>
       </c>
       <c r="AG57" t="b">
         <v>0</v>
@@ -4564,7 +4567,10 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-8.779999999999999</v>
       </c>
       <c r="AG58" t="b">
         <v>0</v>
@@ -4630,7 +4636,10 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-4.05</v>
       </c>
       <c r="AG59" t="b">
         <v>0</v>
@@ -4696,7 +4705,10 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-9.26</v>
       </c>
       <c r="AG60" t="b">
         <v>0</v>
@@ -4762,7 +4774,10 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>8.57</v>
       </c>
       <c r="AG61" t="b">
         <v>1</v>
@@ -4828,7 +4843,10 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-3.42</v>
       </c>
       <c r="AG62" t="b">
         <v>0</v>
@@ -4894,7 +4912,10 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>2.62</v>
       </c>
       <c r="AG63" t="b">
         <v>0</v>
@@ -4960,7 +4981,10 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1.17</v>
       </c>
       <c r="AG64" t="b">
         <v>0</v>
@@ -5026,7 +5050,10 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>12.12</v>
       </c>
       <c r="AG65" t="b">
         <v>0</v>
@@ -5092,7 +5119,10 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>-1.13</v>
       </c>
       <c r="AG66" t="b">
         <v>0</v>
@@ -5158,10 +5188,13 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>21.05</v>
       </c>
       <c r="AG67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH67" t="b">
         <v>0</v>
@@ -5224,7 +5257,10 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>6.36</v>
       </c>
       <c r="AG68" t="b">
         <v>0</v>
@@ -5290,7 +5326,10 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>-5.94</v>
       </c>
       <c r="AG69" t="b">
         <v>0</v>
@@ -5418,7 +5457,10 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>3.22</v>
       </c>
       <c r="AG71" t="b">
         <v>0</v>
@@ -5484,7 +5526,10 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>-2.78</v>
       </c>
       <c r="AG72" t="b">
         <v>0</v>
@@ -5550,7 +5595,10 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>5.81</v>
       </c>
       <c r="AG73" t="b">
         <v>0</v>
@@ -5616,7 +5664,10 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>-5.04</v>
       </c>
       <c r="AG74" t="b">
         <v>0</v>
@@ -5682,7 +5733,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG75" t="b">
         <v>0</v>
@@ -5748,7 +5799,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -5814,7 +5865,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG77" t="b">
         <v>0</v>
@@ -5880,7 +5931,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
@@ -5946,7 +5997,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG79" t="b">
         <v>0</v>
@@ -6012,7 +6063,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG80" t="b">
         <v>0</v>
@@ -6078,7 +6129,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG81" t="b">
         <v>0</v>
@@ -6144,7 +6195,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG82" t="b">
         <v>1</v>
@@ -6210,7 +6261,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -6276,10 +6327,10 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH84" t="b">
         <v>0</v>
@@ -6342,7 +6393,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG85" t="b">
         <v>0</v>
@@ -6408,7 +6459,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG86" t="b">
         <v>0</v>
@@ -6474,7 +6525,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG87" t="b">
         <v>0</v>
@@ -6540,7 +6591,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG88" t="b">
         <v>0</v>
@@ -6606,7 +6657,7 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -6734,7 +6785,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG91" t="b">
         <v>0</v>
@@ -6800,7 +6851,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG92" t="b">
         <v>0</v>
@@ -6866,7 +6917,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG93" t="b">
         <v>0</v>
@@ -6932,7 +6983,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG94" t="b">
         <v>0</v>
@@ -6998,7 +7049,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG95" t="b">
         <v>0</v>
@@ -7064,7 +7115,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG96" t="b">
         <v>0</v>
@@ -7130,7 +7181,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG97" t="b">
         <v>0</v>
@@ -7196,7 +7247,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG98" t="b">
         <v>0</v>
@@ -7262,7 +7313,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG99" t="b">
         <v>0</v>
@@ -7328,7 +7379,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG100" t="b">
         <v>0</v>
@@ -7394,7 +7445,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG101" t="b">
         <v>1</v>
@@ -7460,7 +7511,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG102" t="b">
         <v>1</v>
@@ -7526,7 +7577,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG103" t="b">
         <v>0</v>
@@ -7592,7 +7643,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG104" t="b">
         <v>0</v>
@@ -7658,10 +7709,10 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH105" t="b">
         <v>0</v>
@@ -7724,7 +7775,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG106" t="b">
         <v>0</v>
@@ -7790,7 +7841,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG107" t="b">
         <v>0</v>
@@ -7856,7 +7907,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG108" t="b">
         <v>0</v>
@@ -7922,7 +7973,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG109" t="b">
         <v>0</v>
@@ -7988,7 +8039,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG110" t="b">
         <v>0</v>
@@ -8054,7 +8105,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG111" t="b">
         <v>0</v>
@@ -8120,7 +8171,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG112" t="b">
         <v>0</v>
@@ -8186,7 +8237,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG113" t="b">
         <v>0</v>
@@ -8252,7 +8303,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG114" t="b">
         <v>0</v>
@@ -8318,13 +8369,13 @@
         </is>
       </c>
       <c r="Z115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH115" t="b">
         <v>1</v>
-      </c>
-      <c r="AG115" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH115" t="b">
-        <v>0</v>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
@@ -8384,7 +8435,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG116" t="b">
         <v>0</v>
@@ -8450,7 +8501,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG117" t="b">
         <v>0</v>
@@ -8516,13 +8567,13 @@
         </is>
       </c>
       <c r="Z118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="b">
         <v>1</v>
-      </c>
-      <c r="AG118" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH118" t="b">
-        <v>0</v>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
@@ -8582,13 +8633,13 @@
         </is>
       </c>
       <c r="Z119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="b">
         <v>1</v>
-      </c>
-      <c r="AG119" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH119" t="b">
-        <v>0</v>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
@@ -8648,13 +8699,13 @@
         </is>
       </c>
       <c r="Z120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="b">
         <v>1</v>
-      </c>
-      <c r="AG120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH120" t="b">
-        <v>0</v>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
@@ -8714,7 +8765,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG121" t="b">
         <v>0</v>
@@ -8780,7 +8831,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG122" t="b">
         <v>0</v>
@@ -8846,7 +8897,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG123" t="b">
         <v>0</v>
@@ -8912,7 +8963,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG124" t="b">
         <v>0</v>
@@ -8978,7 +9029,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG125" t="b">
         <v>0</v>
@@ -9044,13 +9095,13 @@
         </is>
       </c>
       <c r="Z126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="b">
         <v>1</v>
-      </c>
-      <c r="AG126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="b">
-        <v>0</v>
       </c>
       <c r="AI126" t="inlineStr">
         <is>
@@ -9110,7 +9161,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG127" t="b">
         <v>0</v>
@@ -9176,13 +9227,13 @@
         </is>
       </c>
       <c r="Z128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="b">
         <v>1</v>
-      </c>
-      <c r="AG128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="b">
-        <v>0</v>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
@@ -9242,7 +9293,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG129" t="b">
         <v>0</v>
@@ -9357,7 +9408,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG130" t="b">
         <v>0</v>
@@ -9472,7 +9523,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG131" t="b">
         <v>0</v>
@@ -9587,7 +9638,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG132" t="b">
         <v>0</v>
@@ -9702,7 +9753,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG133" t="b">
         <v>0</v>
@@ -9817,7 +9868,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG134" t="b">
         <v>0</v>
@@ -9932,7 +9983,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG135" t="b">
         <v>0</v>
@@ -10047,7 +10098,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG136" t="b">
         <v>0</v>
@@ -10159,7 +10210,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG137" t="b">
         <v>0</v>
@@ -10274,7 +10325,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG138" t="b">
         <v>0</v>
@@ -10389,7 +10440,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG139" t="b">
         <v>0</v>
@@ -10504,7 +10555,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG140" t="b">
         <v>0</v>
@@ -10619,7 +10670,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG141" t="b">
         <v>0</v>
@@ -10734,7 +10785,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG142" t="b">
         <v>0</v>
@@ -10849,7 +10900,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG143" t="b">
         <v>0</v>
@@ -10964,7 +11015,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG144" t="b">
         <v>0</v>
@@ -11079,7 +11130,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG145" t="b">
         <v>0</v>
@@ -11093,8 +11144,813 @@
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>72.81999999999999</v>
+      </c>
+      <c r="F146" t="n">
+        <v>43.53</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I146" t="b">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="K146" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M146" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="N146" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S146" t="n">
+        <v>5.5283</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V146" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="W146" t="n">
+        <v>37.2953</v>
+      </c>
+      <c r="X146" t="n">
+        <v>31.9314</v>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="F147" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I147" t="b">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="K147" t="n">
+        <v>79.29000000000001</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M147" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N147" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>74.95</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S147" t="n">
+        <v>6.1977</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V147" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="W147" t="n">
+        <v>85.5526</v>
+      </c>
+      <c r="X147" t="n">
+        <v>72.6968</v>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>72.48999999999999</v>
+      </c>
+      <c r="F148" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I148" t="b">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>10</v>
+      </c>
+      <c r="K148" t="n">
+        <v>789.8</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M148" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N148" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>676.3099999999999</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S148" t="n">
+        <v>7</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="V148" t="n">
+        <v>718</v>
+      </c>
+      <c r="W148" t="n">
+        <v>861.6</v>
+      </c>
+      <c r="X148" t="n">
+        <v>667.74</v>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="F149" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I149" t="b">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>10</v>
+      </c>
+      <c r="K149" t="n">
+        <v>300.85</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M149" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N149" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>257.38</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S149" t="n">
+        <v>7</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V149" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="W149" t="n">
+        <v>328.2</v>
+      </c>
+      <c r="X149" t="n">
+        <v>254.355</v>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>84.33</v>
+      </c>
+      <c r="F150" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I150" t="b">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="K150" t="n">
+        <v>244</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M150" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="N150" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>222</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S150" t="n">
+        <v>7</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V150" t="n">
+        <v>240.5</v>
+      </c>
+      <c r="W150" t="n">
+        <v>288.6</v>
+      </c>
+      <c r="X150" t="n">
+        <v>223.665</v>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="F151" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I151" t="b">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>10</v>
+      </c>
+      <c r="K151" t="n">
+        <v>6105</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M151" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N151" t="n">
+        <v>3</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>4846.85</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>84.36</v>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S151" t="n">
+        <v>7</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V151" t="n">
+        <v>5550</v>
+      </c>
+      <c r="W151" t="n">
+        <v>6660</v>
+      </c>
+      <c r="X151" t="n">
+        <v>5161.5</v>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>77.18000000000001</v>
+      </c>
+      <c r="F152" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I152" t="b">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>10</v>
+      </c>
+      <c r="K152" t="n">
+        <v>1243</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M152" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N152" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>1036.5</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>74.81999999999999</v>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S152" t="n">
+        <v>7</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V152" t="n">
+        <v>1130</v>
+      </c>
+      <c r="W152" t="n">
+        <v>1356</v>
+      </c>
+      <c r="X152" t="n">
+        <v>1050.9</v>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ145"/>
+  <autoFilter ref="A1:AJ152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11334,7 +12190,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-18 17:58:12</t>
+          <t>2026-08-19 14:24:13</t>
         </is>
       </c>
     </row>
@@ -11381,7 +12237,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7">
@@ -11401,7 +12257,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$163</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ152"/>
+  <dimension ref="A1:AJ163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
       </c>
       <c r="AG25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH25" t="b">
         <v>0</v>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA37" t="n">
         <v>10.15</v>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5050,13 +5050,13 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
       </c>
       <c r="AG65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH65" t="b">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA73" t="n">
         <v>5.81</v>
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -5733,7 +5733,10 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.53</v>
       </c>
       <c r="AG75" t="b">
         <v>0</v>
@@ -5799,7 +5802,10 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>-1.02</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -5865,7 +5871,10 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0.37</v>
       </c>
       <c r="AG77" t="b">
         <v>0</v>
@@ -5931,7 +5940,10 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>-11.94</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
@@ -5997,7 +6009,10 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>-2.44</v>
       </c>
       <c r="AG79" t="b">
         <v>0</v>
@@ -6063,7 +6078,10 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0.58</v>
       </c>
       <c r="AG80" t="b">
         <v>0</v>
@@ -6129,10 +6147,13 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>12.3</v>
       </c>
       <c r="AG81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH81" t="b">
         <v>0</v>
@@ -6195,7 +6216,10 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>23.43</v>
       </c>
       <c r="AG82" t="b">
         <v>1</v>
@@ -6261,7 +6285,10 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>-1.63</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -6327,7 +6354,10 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>17.81</v>
       </c>
       <c r="AG84" t="b">
         <v>1</v>
@@ -6393,7 +6423,10 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>-8.880000000000001</v>
       </c>
       <c r="AG85" t="b">
         <v>0</v>
@@ -6459,7 +6492,10 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>-3.34</v>
       </c>
       <c r="AG86" t="b">
         <v>0</v>
@@ -6525,7 +6561,10 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>-11.46</v>
       </c>
       <c r="AG87" t="b">
         <v>0</v>
@@ -6591,7 +6630,10 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>-3.81</v>
       </c>
       <c r="AG88" t="b">
         <v>0</v>
@@ -6657,7 +6699,10 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>4.61</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -6785,7 +6830,10 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0</v>
       </c>
       <c r="AG91" t="b">
         <v>0</v>
@@ -6851,7 +6899,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG92" t="b">
         <v>0</v>
@@ -6917,7 +6965,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG93" t="b">
         <v>0</v>
@@ -6983,7 +7031,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG94" t="b">
         <v>0</v>
@@ -7049,7 +7097,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG95" t="b">
         <v>0</v>
@@ -7115,7 +7163,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG96" t="b">
         <v>0</v>
@@ -7181,7 +7229,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG97" t="b">
         <v>0</v>
@@ -7247,7 +7295,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG98" t="b">
         <v>0</v>
@@ -7313,7 +7361,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG99" t="b">
         <v>0</v>
@@ -7379,7 +7427,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG100" t="b">
         <v>0</v>
@@ -7445,7 +7493,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG101" t="b">
         <v>1</v>
@@ -7511,7 +7559,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG102" t="b">
         <v>1</v>
@@ -7577,7 +7625,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG103" t="b">
         <v>0</v>
@@ -7643,7 +7691,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG104" t="b">
         <v>0</v>
@@ -7709,7 +7757,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG105" t="b">
         <v>1</v>
@@ -7775,7 +7823,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG106" t="b">
         <v>0</v>
@@ -7841,7 +7889,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG107" t="b">
         <v>0</v>
@@ -7907,7 +7955,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG108" t="b">
         <v>0</v>
@@ -7973,7 +8021,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG109" t="b">
         <v>0</v>
@@ -8039,7 +8087,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG110" t="b">
         <v>0</v>
@@ -8105,7 +8153,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG111" t="b">
         <v>0</v>
@@ -8171,7 +8219,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG112" t="b">
         <v>0</v>
@@ -8237,7 +8285,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG113" t="b">
         <v>0</v>
@@ -8303,7 +8351,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG114" t="b">
         <v>0</v>
@@ -8369,7 +8417,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG115" t="b">
         <v>0</v>
@@ -8435,7 +8483,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG116" t="b">
         <v>0</v>
@@ -8501,7 +8549,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG117" t="b">
         <v>0</v>
@@ -8567,7 +8615,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG118" t="b">
         <v>0</v>
@@ -8633,7 +8681,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG119" t="b">
         <v>0</v>
@@ -8699,7 +8747,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG120" t="b">
         <v>0</v>
@@ -8765,7 +8813,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG121" t="b">
         <v>0</v>
@@ -8831,7 +8879,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG122" t="b">
         <v>0</v>
@@ -8897,7 +8945,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG123" t="b">
         <v>0</v>
@@ -8963,7 +9011,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG124" t="b">
         <v>0</v>
@@ -9029,7 +9077,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG125" t="b">
         <v>0</v>
@@ -9095,7 +9143,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG126" t="b">
         <v>0</v>
@@ -9161,7 +9209,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG127" t="b">
         <v>0</v>
@@ -9227,7 +9275,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG128" t="b">
         <v>0</v>
@@ -9293,7 +9341,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG129" t="b">
         <v>0</v>
@@ -9408,7 +9456,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG130" t="b">
         <v>0</v>
@@ -9523,7 +9571,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG131" t="b">
         <v>0</v>
@@ -9638,7 +9686,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG132" t="b">
         <v>0</v>
@@ -9753,7 +9801,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG133" t="b">
         <v>0</v>
@@ -9868,7 +9916,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG134" t="b">
         <v>0</v>
@@ -9983,7 +10031,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG135" t="b">
         <v>0</v>
@@ -10098,7 +10146,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG136" t="b">
         <v>0</v>
@@ -10210,7 +10258,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG137" t="b">
         <v>0</v>
@@ -10325,7 +10373,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG138" t="b">
         <v>0</v>
@@ -10440,7 +10488,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG139" t="b">
         <v>0</v>
@@ -10555,7 +10603,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG140" t="b">
         <v>0</v>
@@ -10670,7 +10718,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG141" t="b">
         <v>0</v>
@@ -10785,7 +10833,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG142" t="b">
         <v>0</v>
@@ -10900,7 +10948,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG143" t="b">
         <v>0</v>
@@ -11015,7 +11063,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG144" t="b">
         <v>0</v>
@@ -11130,7 +11178,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG145" t="b">
         <v>0</v>
@@ -11245,7 +11293,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG146" t="b">
         <v>0</v>
@@ -11360,7 +11408,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG147" t="b">
         <v>0</v>
@@ -11475,7 +11523,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG148" t="b">
         <v>0</v>
@@ -11590,7 +11638,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG149" t="b">
         <v>0</v>
@@ -11705,7 +11753,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG150" t="b">
         <v>0</v>
@@ -11820,7 +11868,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG151" t="b">
         <v>0</v>
@@ -11935,7 +11983,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG152" t="b">
         <v>0</v>
@@ -11949,8 +11997,1273 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>73.31</v>
+      </c>
+      <c r="F153" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I153" t="b">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K153" t="n">
+        <v>36</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M153" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N153" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>63.56</v>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S153" t="n">
+        <v>7</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V153" t="n">
+        <v>34.85</v>
+      </c>
+      <c r="W153" t="n">
+        <v>39.1688</v>
+      </c>
+      <c r="X153" t="n">
+        <v>32.4105</v>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>上銀</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>76.09</v>
+      </c>
+      <c r="F154" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I154" t="b">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>10</v>
+      </c>
+      <c r="K154" t="n">
+        <v>427.35</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M154" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N154" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S154" t="n">
+        <v>7</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="V154" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="W154" t="n">
+        <v>466.2</v>
+      </c>
+      <c r="X154" t="n">
+        <v>361.305</v>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>72.55</v>
+      </c>
+      <c r="F155" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I155" t="b">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>10</v>
+      </c>
+      <c r="K155" t="n">
+        <v>298.1</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M155" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N155" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>262.83</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S155" t="n">
+        <v>7</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V155" t="n">
+        <v>271</v>
+      </c>
+      <c r="W155" t="n">
+        <v>325.2</v>
+      </c>
+      <c r="X155" t="n">
+        <v>252.03</v>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>70.29000000000001</v>
+      </c>
+      <c r="F156" t="n">
+        <v>47.11</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I156" t="b">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>10</v>
+      </c>
+      <c r="K156" t="n">
+        <v>750.2</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M156" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N156" t="n">
+        <v>5</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>649.5</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S156" t="n">
+        <v>7</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V156" t="n">
+        <v>682</v>
+      </c>
+      <c r="W156" t="n">
+        <v>818.4</v>
+      </c>
+      <c r="X156" t="n">
+        <v>634.26</v>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>73.59</v>
+      </c>
+      <c r="F157" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I157" t="b">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>10</v>
+      </c>
+      <c r="K157" t="n">
+        <v>572</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M157" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N157" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>494.5</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>54.36</v>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S157" t="n">
+        <v>7</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V157" t="n">
+        <v>520</v>
+      </c>
+      <c r="W157" t="n">
+        <v>624</v>
+      </c>
+      <c r="X157" t="n">
+        <v>483.6</v>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>77.81999999999999</v>
+      </c>
+      <c r="F158" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I158" t="b">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="K158" t="n">
+        <v>266</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M158" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N158" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S158" t="n">
+        <v>7</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V158" t="n">
+        <v>243.5</v>
+      </c>
+      <c r="W158" t="n">
+        <v>292.2</v>
+      </c>
+      <c r="X158" t="n">
+        <v>226.455</v>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2609</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>陽明</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>76.16</v>
+      </c>
+      <c r="F159" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I159" t="b">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K159" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M159" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S159" t="n">
+        <v>7</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V159" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="W159" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="X159" t="n">
+        <v>55.521</v>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="F160" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I160" t="b">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="K160" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M160" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N160" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S160" t="n">
+        <v>7</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V160" t="n">
+        <v>108</v>
+      </c>
+      <c r="W160" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="X160" t="n">
+        <v>100.44</v>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>77.73</v>
+      </c>
+      <c r="F161" t="n">
+        <v>42.98</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I161" t="b">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>10</v>
+      </c>
+      <c r="K161" t="n">
+        <v>6028</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M161" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N161" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>4955.86</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>69.89</v>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S161" t="n">
+        <v>7</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V161" t="n">
+        <v>5480</v>
+      </c>
+      <c r="W161" t="n">
+        <v>6576</v>
+      </c>
+      <c r="X161" t="n">
+        <v>5096.4</v>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>70.59</v>
+      </c>
+      <c r="F162" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I162" t="b">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>10</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1210</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M162" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>1064</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>60.28</v>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S162" t="n">
+        <v>7</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V162" t="n">
+        <v>1100</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1320</v>
+      </c>
+      <c r="X162" t="n">
+        <v>1023</v>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="F163" t="n">
+        <v>54.53</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I163" t="b">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>10</v>
+      </c>
+      <c r="K163" t="n">
+        <v>6990.5</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M163" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N163" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>6297.5</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>53.52</v>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S163" t="n">
+        <v>7</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V163" t="n">
+        <v>6355</v>
+      </c>
+      <c r="W163" t="n">
+        <v>7626</v>
+      </c>
+      <c r="X163" t="n">
+        <v>5910.15</v>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ152"/>
+  <autoFilter ref="A1:AJ163"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12190,7 +13503,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-19 14:24:13</t>
+          <t>2026-08-20 09:51:49</t>
         </is>
       </c>
     </row>
@@ -12237,7 +13550,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
@@ -12257,7 +13570,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ163"/>
+  <dimension ref="A1:AJ171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="AH49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>5</v>
       </c>
       <c r="AA75" t="n">
-        <v>-1.53</v>
+        <v>0.97</v>
       </c>
       <c r="AG75" t="b">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         <v>5</v>
       </c>
       <c r="AA76" t="n">
-        <v>-1.02</v>
+        <v>-3.4</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -5874,7 +5874,7 @@
         <v>5</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.37</v>
+        <v>-0.93</v>
       </c>
       <c r="AG77" t="b">
         <v>0</v>
@@ -5943,7 +5943,7 @@
         <v>5</v>
       </c>
       <c r="AA78" t="n">
-        <v>-11.94</v>
+        <v>-12.58</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
@@ -6012,7 +6012,7 @@
         <v>5</v>
       </c>
       <c r="AA79" t="n">
-        <v>-2.44</v>
+        <v>-3.58</v>
       </c>
       <c r="AG79" t="b">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>5</v>
       </c>
       <c r="AA81" t="n">
-        <v>12.3</v>
+        <v>14.15</v>
       </c>
       <c r="AG81" t="b">
         <v>1</v>
@@ -6219,7 +6219,7 @@
         <v>5</v>
       </c>
       <c r="AA82" t="n">
-        <v>23.43</v>
+        <v>29.71</v>
       </c>
       <c r="AG82" t="b">
         <v>1</v>
@@ -6288,7 +6288,7 @@
         <v>5</v>
       </c>
       <c r="AA83" t="n">
-        <v>-1.63</v>
+        <v>-1.5</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -6357,7 +6357,7 @@
         <v>5</v>
       </c>
       <c r="AA84" t="n">
-        <v>17.81</v>
+        <v>18.35</v>
       </c>
       <c r="AG84" t="b">
         <v>1</v>
@@ -6426,7 +6426,7 @@
         <v>5</v>
       </c>
       <c r="AA85" t="n">
-        <v>-8.880000000000001</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="AG85" t="b">
         <v>0</v>
@@ -6495,7 +6495,7 @@
         <v>5</v>
       </c>
       <c r="AA86" t="n">
-        <v>-3.34</v>
+        <v>1.62</v>
       </c>
       <c r="AG86" t="b">
         <v>0</v>
@@ -6564,7 +6564,7 @@
         <v>5</v>
       </c>
       <c r="AA87" t="n">
-        <v>-11.46</v>
+        <v>-10.5</v>
       </c>
       <c r="AG87" t="b">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>5</v>
       </c>
       <c r="AA88" t="n">
-        <v>-3.81</v>
+        <v>-4.84</v>
       </c>
       <c r="AG88" t="b">
         <v>0</v>
@@ -6702,7 +6702,7 @@
         <v>5</v>
       </c>
       <c r="AA89" t="n">
-        <v>4.61</v>
+        <v>4.2</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -6833,7 +6833,7 @@
         <v>5</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AG91" t="b">
         <v>0</v>
@@ -12005,12 +12005,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -12019,10 +12019,10 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>73.31</v>
+        <v>79.08</v>
       </c>
       <c r="F153" t="n">
-        <v>36.03</v>
+        <v>40.69</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -12038,40 +12038,40 @@
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>3.3</v>
+        <v>3.83</v>
       </c>
       <c r="K153" t="n">
-        <v>36</v>
+        <v>25.75</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>measured_move_target_up</t>
+          <t>gap_MM_Target_Up</t>
         </is>
       </c>
       <c r="M153" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="N153" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>33.22</v>
+        <v>24.27</v>
       </c>
       <c r="Q153" t="n">
-        <v>63.56</v>
+        <v>57.96</v>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="S153" t="n">
-        <v>7</v>
+        <v>4.3115</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -12084,13 +12084,13 @@
         </is>
       </c>
       <c r="V153" t="n">
-        <v>34.85</v>
+        <v>24.8</v>
       </c>
       <c r="W153" t="n">
-        <v>39.1688</v>
+        <v>27.0889</v>
       </c>
       <c r="X153" t="n">
-        <v>32.4105</v>
+        <v>23.7308</v>
       </c>
       <c r="Y153" t="inlineStr">
         <is>
@@ -12120,12 +12120,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -12134,10 +12134,10 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>76.09</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="F154" t="n">
-        <v>48.61</v>
+        <v>36.73</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -12146,17 +12146,17 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>WaitPullback</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="I154" t="b">
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="K154" t="n">
-        <v>427.35</v>
+        <v>36</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -12164,10 +12164,10 @@
         </is>
       </c>
       <c r="M154" t="n">
-        <v>1.43</v>
+        <v>0.54</v>
       </c>
       <c r="N154" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -12175,10 +12175,10 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>372.5</v>
+        <v>33.25</v>
       </c>
       <c r="Q154" t="n">
-        <v>60.7</v>
+        <v>68.17</v>
       </c>
       <c r="R154" t="inlineStr">
         <is>
@@ -12195,17 +12195,17 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>industrial</t>
+          <t>materials</t>
         </is>
       </c>
       <c r="V154" t="n">
-        <v>388.5</v>
+        <v>34.7</v>
       </c>
       <c r="W154" t="n">
-        <v>466.2</v>
+        <v>39.0431</v>
       </c>
       <c r="X154" t="n">
-        <v>361.305</v>
+        <v>32.271</v>
       </c>
       <c r="Y154" t="inlineStr">
         <is>
@@ -12235,12 +12235,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -12249,10 +12249,10 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>72.55</v>
+        <v>74.12</v>
       </c>
       <c r="F155" t="n">
-        <v>45.83</v>
+        <v>42.35</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -12261,47 +12261,47 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>WaitPullback</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="I155" t="b">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>10</v>
+        <v>1.39</v>
       </c>
       <c r="K155" t="n">
-        <v>298.1</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>measured_move_target_up</t>
+          <t>gap_MM_Target_Up</t>
         </is>
       </c>
       <c r="M155" t="n">
-        <v>1.43</v>
+        <v>0.21</v>
       </c>
       <c r="N155" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>262.83</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="Q155" t="n">
-        <v>48.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="S155" t="n">
-        <v>7</v>
+        <v>6.4802</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -12310,17 +12310,17 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>ai_hardware</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="V155" t="n">
-        <v>271</v>
+        <v>78.2</v>
       </c>
       <c r="W155" t="n">
-        <v>325.2</v>
+        <v>86.5274</v>
       </c>
       <c r="X155" t="n">
-        <v>252.03</v>
+        <v>73.13249999999999</v>
       </c>
       <c r="Y155" t="inlineStr">
         <is>
@@ -12350,12 +12350,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -12364,10 +12364,10 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>70.29000000000001</v>
+        <v>76.83</v>
       </c>
       <c r="F156" t="n">
-        <v>47.11</v>
+        <v>50.2</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -12383,21 +12383,21 @@
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>10</v>
+        <v>9.76</v>
       </c>
       <c r="K156" t="n">
-        <v>750.2</v>
+        <v>32.05</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>measured_move_target_up</t>
+          <t>wedge_failure_measured_move_target</t>
         </is>
       </c>
       <c r="M156" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="N156" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -12405,14 +12405,14 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>649.5</v>
+        <v>28.03</v>
       </c>
       <c r="Q156" t="n">
-        <v>54.08</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="S156" t="n">
@@ -12425,17 +12425,17 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>ai_hardware</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="V156" t="n">
-        <v>682</v>
+        <v>29.2</v>
       </c>
       <c r="W156" t="n">
-        <v>818.4</v>
+        <v>33.2614</v>
       </c>
       <c r="X156" t="n">
-        <v>634.26</v>
+        <v>27.156</v>
       </c>
       <c r="Y156" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -12479,10 +12479,10 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>73.59</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F157" t="n">
-        <v>42.65</v>
+        <v>55.46</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>10</v>
       </c>
       <c r="K157" t="n">
-        <v>572</v>
+        <v>799.7</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -12512,22 +12512,22 @@
         <v>1.43</v>
       </c>
       <c r="N157" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>494.5</v>
+        <v>693</v>
       </c>
       <c r="Q157" t="n">
-        <v>54.36</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="S157" t="n">
@@ -12540,17 +12540,17 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>semiconductor</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="V157" t="n">
-        <v>520</v>
+        <v>727</v>
       </c>
       <c r="W157" t="n">
-        <v>624</v>
+        <v>872.4</v>
       </c>
       <c r="X157" t="n">
-        <v>483.6</v>
+        <v>676.11</v>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
@@ -12580,12 +12580,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -12594,10 +12594,10 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>77.81999999999999</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F158" t="n">
-        <v>40.03</v>
+        <v>51.68</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -12613,40 +12613,40 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>9.24</v>
+        <v>8.32</v>
       </c>
       <c r="K158" t="n">
-        <v>266</v>
+        <v>397</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>measured_move_target_up</t>
+          <t>gap_MM_Target_Up</t>
         </is>
       </c>
       <c r="M158" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="N158" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P158" t="n">
-        <v>225.5</v>
+        <v>372.5</v>
       </c>
       <c r="Q158" t="n">
-        <v>70.2</v>
+        <v>44.52</v>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S158" t="n">
-        <v>7</v>
+        <v>4.9795</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -12655,17 +12655,17 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="V158" t="n">
-        <v>243.5</v>
+        <v>366.5</v>
       </c>
       <c r="W158" t="n">
-        <v>292.2</v>
+        <v>439.8</v>
       </c>
       <c r="X158" t="n">
-        <v>226.455</v>
+        <v>348.25</v>
       </c>
       <c r="Y158" t="inlineStr">
         <is>
@@ -12695,12 +12695,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -12709,10 +12709,10 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>76.16</v>
+        <v>72.55</v>
       </c>
       <c r="F159" t="n">
-        <v>25.69</v>
+        <v>45.83</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -12721,17 +12721,17 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>WaitPullback</t>
         </is>
       </c>
       <c r="I159" t="b">
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>0.67</v>
+        <v>10</v>
       </c>
       <c r="K159" t="n">
-        <v>60.1</v>
+        <v>298.1</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         </is>
       </c>
       <c r="M159" t="n">
-        <v>0.1</v>
+        <v>1.43</v>
       </c>
       <c r="N159" t="n">
         <v>4.5</v>
@@ -12750,14 +12750,14 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>55.3</v>
+        <v>262.83</v>
       </c>
       <c r="Q159" t="n">
-        <v>67.93000000000001</v>
+        <v>48.84</v>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S159" t="n">
@@ -12770,17 +12770,17 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>ai_hardware</t>
         </is>
       </c>
       <c r="V159" t="n">
-        <v>59.7</v>
+        <v>271</v>
       </c>
       <c r="W159" t="n">
-        <v>71.64</v>
+        <v>325.2</v>
       </c>
       <c r="X159" t="n">
-        <v>55.521</v>
+        <v>252.03</v>
       </c>
       <c r="Y159" t="inlineStr">
         <is>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -12824,10 +12824,10 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>84.39</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="F160" t="n">
-        <v>39.6</v>
+        <v>49.32</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -12843,10 +12843,10 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>8.890000000000001</v>
+        <v>10</v>
       </c>
       <c r="K160" t="n">
-        <v>117.6</v>
+        <v>6583.5</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         </is>
       </c>
       <c r="M160" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="N160" t="n">
         <v>4.5</v>
@@ -12865,14 +12865,14 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>96.40000000000001</v>
+        <v>5787.5</v>
       </c>
       <c r="Q160" t="n">
-        <v>80.68000000000001</v>
+        <v>65.48</v>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="S160" t="n">
@@ -12885,17 +12885,17 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>electronic_components</t>
         </is>
       </c>
       <c r="V160" t="n">
-        <v>108</v>
+        <v>5985</v>
       </c>
       <c r="W160" t="n">
-        <v>129.6</v>
+        <v>7182</v>
       </c>
       <c r="X160" t="n">
-        <v>100.44</v>
+        <v>5566.05</v>
       </c>
       <c r="Y160" t="inlineStr">
         <is>
@@ -12925,12 +12925,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -12939,10 +12939,10 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>77.73</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="F161" t="n">
-        <v>42.98</v>
+        <v>47.11</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>10</v>
       </c>
       <c r="K161" t="n">
-        <v>6028</v>
+        <v>750.2</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -12972,22 +12972,22 @@
         <v>1.43</v>
       </c>
       <c r="N161" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="P161" t="n">
-        <v>4955.86</v>
+        <v>649.5</v>
       </c>
       <c r="Q161" t="n">
-        <v>69.89</v>
+        <v>54.08</v>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S161" t="n">
@@ -13000,17 +13000,17 @@
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>electronic_components</t>
+          <t>ai_hardware</t>
         </is>
       </c>
       <c r="V161" t="n">
-        <v>5480</v>
+        <v>682</v>
       </c>
       <c r="W161" t="n">
-        <v>6576</v>
+        <v>818.4</v>
       </c>
       <c r="X161" t="n">
-        <v>5096.4</v>
+        <v>634.26</v>
       </c>
       <c r="Y161" t="inlineStr">
         <is>
@@ -13040,12 +13040,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>70.59</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="F162" t="n">
-        <v>43.04</v>
+        <v>43.38</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>10</v>
       </c>
       <c r="K162" t="n">
-        <v>1210</v>
+        <v>568.7</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>1.43</v>
       </c>
       <c r="N162" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -13095,14 +13095,14 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>1064</v>
+        <v>494.5</v>
       </c>
       <c r="Q162" t="n">
-        <v>60.28</v>
+        <v>59.2</v>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S162" t="n">
@@ -13115,17 +13115,17 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>electronic_components</t>
+          <t>semiconductor</t>
         </is>
       </c>
       <c r="V162" t="n">
-        <v>1100</v>
+        <v>517</v>
       </c>
       <c r="W162" t="n">
-        <v>1320</v>
+        <v>620.4</v>
       </c>
       <c r="X162" t="n">
-        <v>1023</v>
+        <v>480.81</v>
       </c>
       <c r="Y162" t="inlineStr">
         <is>
@@ -13155,115 +13155,1031 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>77.81999999999999</v>
+      </c>
+      <c r="F163" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I163" t="b">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="K163" t="n">
+        <v>266</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M163" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N163" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S163" t="n">
+        <v>7</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V163" t="n">
+        <v>243.5</v>
+      </c>
+      <c r="W163" t="n">
+        <v>292.2</v>
+      </c>
+      <c r="X163" t="n">
+        <v>226.455</v>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2609</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>陽明</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>76.16</v>
+      </c>
+      <c r="F164" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I164" t="b">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K164" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M164" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N164" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S164" t="n">
+        <v>7</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V164" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="W164" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="X164" t="n">
+        <v>55.521</v>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="F165" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I165" t="b">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="K165" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M165" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N165" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S165" t="n">
+        <v>7</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V165" t="n">
+        <v>108</v>
+      </c>
+      <c r="W165" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="X165" t="n">
+        <v>100.44</v>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>81.23</v>
+      </c>
+      <c r="F166" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I166" t="b">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>10</v>
+      </c>
+      <c r="K166" t="n">
+        <v>6066.5</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M166" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N166" t="n">
+        <v>3</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>4955.86</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>74.89</v>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S166" t="n">
+        <v>7</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V166" t="n">
+        <v>5515</v>
+      </c>
+      <c r="W166" t="n">
+        <v>6618</v>
+      </c>
+      <c r="X166" t="n">
+        <v>5128.95</v>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>78.62</v>
+      </c>
+      <c r="F167" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I167" t="b">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>10</v>
+      </c>
+      <c r="K167" t="n">
+        <v>1254</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M167" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N167" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>1064</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S167" t="n">
+        <v>7</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V167" t="n">
+        <v>1140</v>
+      </c>
+      <c r="W167" t="n">
+        <v>1368</v>
+      </c>
+      <c r="X167" t="n">
+        <v>1060.2</v>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="F168" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I168" t="b">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>10</v>
+      </c>
+      <c r="K168" t="n">
+        <v>3058</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M168" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N168" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>2612.5</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S168" t="n">
+        <v>7</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V168" t="n">
+        <v>2780</v>
+      </c>
+      <c r="W168" t="n">
+        <v>3336</v>
+      </c>
+      <c r="X168" t="n">
+        <v>2585.4</v>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>72.84999999999999</v>
+      </c>
+      <c r="F169" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I169" t="b">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>10</v>
+      </c>
+      <c r="K169" t="n">
+        <v>936.1</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M169" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N169" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>869</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S169" t="n">
+        <v>5.6445</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V169" t="n">
+        <v>851</v>
+      </c>
+      <c r="W169" t="n">
+        <v>1021.2</v>
+      </c>
+      <c r="X169" t="n">
+        <v>802.965</v>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>78.89</v>
+      </c>
+      <c r="F170" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I170" t="b">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>10</v>
+      </c>
+      <c r="K170" t="n">
+        <v>6193</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M170" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N170" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>5120</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>59.84</v>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S170" t="n">
+        <v>7</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V170" t="n">
+        <v>5630</v>
+      </c>
+      <c r="W170" t="n">
+        <v>6756</v>
+      </c>
+      <c r="X170" t="n">
+        <v>5235.9</v>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
           <t>6669</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>swing_accumulation_ready</t>
-        </is>
-      </c>
-      <c r="E163" t="n">
-        <v>74.44</v>
-      </c>
-      <c r="F163" t="n">
-        <v>54.53</v>
-      </c>
-      <c r="G163" t="inlineStr">
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="F171" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="G171" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H171" t="inlineStr">
         <is>
           <t>WaitPullback</t>
         </is>
       </c>
-      <c r="I163" t="b">
-        <v>0</v>
-      </c>
-      <c r="J163" t="n">
+      <c r="I171" t="b">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
         <v>10</v>
       </c>
-      <c r="K163" t="n">
-        <v>6990.5</v>
-      </c>
-      <c r="L163" t="inlineStr">
+      <c r="K171" t="n">
+        <v>6957.5</v>
+      </c>
+      <c r="L171" t="inlineStr">
         <is>
           <t>measured_move_target_up</t>
         </is>
       </c>
-      <c r="M163" t="n">
+      <c r="M171" t="n">
         <v>1.43</v>
       </c>
-      <c r="N163" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O163" t="inlineStr">
+      <c r="N171" t="n">
+        <v>7</v>
+      </c>
+      <c r="O171" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="P163" t="n">
+      <c r="P171" t="n">
         <v>6297.5</v>
       </c>
-      <c r="Q163" t="n">
-        <v>53.52</v>
-      </c>
-      <c r="R163" t="inlineStr">
+      <c r="Q171" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="R171" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="S163" t="n">
-        <v>7</v>
-      </c>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>RangeRotation</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
+      <c r="S171" t="n">
+        <v>7</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
         <is>
           <t>semiconductor</t>
         </is>
       </c>
-      <c r="V163" t="n">
-        <v>6355</v>
-      </c>
-      <c r="W163" t="n">
-        <v>7626</v>
-      </c>
-      <c r="X163" t="n">
-        <v>5910.15</v>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>Tracking</t>
-        </is>
-      </c>
-      <c r="Z163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG163" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH163" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI163" t="inlineStr">
+      <c r="V171" t="n">
+        <v>6325</v>
+      </c>
+      <c r="W171" t="n">
+        <v>7590</v>
+      </c>
+      <c r="X171" t="n">
+        <v>5882.25</v>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI171" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ163"/>
+  <autoFilter ref="A1:AJ171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13370,7 +14286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13458,10 +14374,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13503,7 +14429,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20 09:51:49</t>
+          <t>2026-08-20 14:22:09</t>
         </is>
       </c>
     </row>
@@ -13550,7 +14476,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7">
@@ -13570,7 +14496,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ171"/>
+  <dimension ref="A1:AJ180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -731,13 +731,16 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
       </c>
+      <c r="AB2" t="n">
+        <v>10.36</v>
+      </c>
       <c r="AG2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="b">
         <v>0</v>
@@ -800,11 +803,14 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
       </c>
+      <c r="AB3" t="n">
+        <v>-7.12</v>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,11 +875,14 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
       </c>
+      <c r="AB4" t="n">
+        <v>12.73</v>
+      </c>
       <c r="AG4" t="b">
         <v>1</v>
       </c>
@@ -938,11 +947,14 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
       </c>
+      <c r="AB5" t="n">
+        <v>-7.52</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1007,11 +1019,14 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
       </c>
+      <c r="AB6" t="n">
+        <v>2.37</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1076,11 +1091,14 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
       </c>
+      <c r="AB7" t="n">
+        <v>21.2</v>
+      </c>
       <c r="AG7" t="b">
         <v>1</v>
       </c>
@@ -1145,11 +1163,14 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
       </c>
+      <c r="AB8" t="n">
+        <v>-9.33</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1214,11 +1235,14 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
       </c>
+      <c r="AB9" t="n">
+        <v>-4.05</v>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1283,11 +1307,14 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
       </c>
+      <c r="AB10" t="n">
+        <v>-10.81</v>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1352,11 +1379,14 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
       </c>
+      <c r="AB11" t="n">
+        <v>-7.76</v>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1421,11 +1451,14 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
       </c>
+      <c r="AB12" t="n">
+        <v>27.94</v>
+      </c>
       <c r="AG12" t="b">
         <v>1</v>
       </c>
@@ -1490,11 +1523,14 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
       </c>
+      <c r="AB13" t="n">
+        <v>-2.21</v>
+      </c>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1621,11 +1657,14 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
       </c>
+      <c r="AB15" t="n">
+        <v>8.66</v>
+      </c>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -1690,11 +1729,14 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
       </c>
+      <c r="AB16" t="n">
+        <v>16.34</v>
+      </c>
       <c r="AG16" t="b">
         <v>1</v>
       </c>
@@ -1759,7 +1801,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1828,7 +1870,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -1897,7 +1939,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -1966,7 +2008,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -2035,7 +2077,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2104,7 +2146,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2173,7 +2215,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2242,7 +2284,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2311,7 +2353,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
@@ -2380,7 +2422,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
@@ -2449,7 +2491,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2518,7 +2560,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2587,7 +2629,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2656,7 +2698,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2725,7 +2767,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -2794,7 +2836,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -2863,7 +2905,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3056,7 +3098,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3125,7 +3167,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA37" t="n">
         <v>10.15</v>
@@ -3194,7 +3236,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3263,7 +3305,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3332,7 +3374,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3401,7 +3443,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3470,7 +3512,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3539,7 +3581,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3608,7 +3650,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -3677,7 +3719,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -3746,7 +3788,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -3815,7 +3857,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -3884,7 +3926,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -3953,7 +3995,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4022,13 +4064,13 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
       </c>
       <c r="AG50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH50" t="b">
         <v>0</v>
@@ -4091,7 +4133,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4160,7 +4202,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4229,7 +4271,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4298,7 +4340,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4429,7 +4471,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4498,7 +4540,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -4567,7 +4609,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -4636,7 +4678,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -4705,7 +4747,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -4774,7 +4816,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -4843,7 +4885,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -4912,7 +4954,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -4981,7 +5023,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5050,7 +5092,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5119,7 +5161,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5188,7 +5230,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5257,7 +5299,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -5326,7 +5368,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -5457,7 +5499,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -5526,7 +5568,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -5595,7 +5637,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA73" t="n">
         <v>5.81</v>
@@ -5664,7 +5706,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -5733,7 +5775,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -5802,7 +5844,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -5871,7 +5913,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -5940,7 +5982,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6009,7 +6051,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6018,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="AH79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
@@ -6078,7 +6120,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6147,7 +6189,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -6216,7 +6258,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -6285,7 +6327,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -6354,7 +6396,7 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -6423,7 +6465,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -6492,7 +6534,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -6561,7 +6603,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -6630,7 +6672,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -6699,7 +6741,7 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA89" t="n">
         <v>4.2</v>
@@ -6830,7 +6872,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -6899,7 +6941,10 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>1.83</v>
       </c>
       <c r="AG92" t="b">
         <v>0</v>
@@ -6965,7 +7010,10 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>-1.71</v>
       </c>
       <c r="AG93" t="b">
         <v>0</v>
@@ -7031,7 +7079,10 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>-2.25</v>
       </c>
       <c r="AG94" t="b">
         <v>0</v>
@@ -7097,7 +7148,10 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>-14.59</v>
       </c>
       <c r="AG95" t="b">
         <v>0</v>
@@ -7163,7 +7217,10 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>-11.01</v>
       </c>
       <c r="AG96" t="b">
         <v>0</v>
@@ -7229,13 +7286,16 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>-7.87</v>
       </c>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AH97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
@@ -7295,7 +7355,10 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>3.12</v>
       </c>
       <c r="AG98" t="b">
         <v>0</v>
@@ -7361,7 +7424,10 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>-9.98</v>
       </c>
       <c r="AG99" t="b">
         <v>0</v>
@@ -7427,10 +7493,13 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>14.84</v>
       </c>
       <c r="AG100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH100" t="b">
         <v>0</v>
@@ -7493,7 +7562,10 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>24.03</v>
       </c>
       <c r="AG101" t="b">
         <v>1</v>
@@ -7559,7 +7631,10 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>37.42</v>
       </c>
       <c r="AG102" t="b">
         <v>1</v>
@@ -7625,7 +7700,10 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>-0.32</v>
       </c>
       <c r="AG103" t="b">
         <v>0</v>
@@ -7691,7 +7769,10 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>-1.32</v>
       </c>
       <c r="AG104" t="b">
         <v>0</v>
@@ -7757,7 +7838,10 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>21.69</v>
       </c>
       <c r="AG105" t="b">
         <v>1</v>
@@ -7823,7 +7907,10 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>-11.44</v>
       </c>
       <c r="AG106" t="b">
         <v>0</v>
@@ -7889,7 +7976,10 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>6.37</v>
       </c>
       <c r="AG107" t="b">
         <v>0</v>
@@ -7955,13 +8045,16 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>-5.92</v>
       </c>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AH108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
@@ -8021,7 +8114,10 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>-9.300000000000001</v>
       </c>
       <c r="AG109" t="b">
         <v>0</v>
@@ -8087,7 +8183,10 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>2.47</v>
       </c>
       <c r="AG110" t="b">
         <v>0</v>
@@ -8153,7 +8252,10 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>-6.67</v>
       </c>
       <c r="AG111" t="b">
         <v>0</v>
@@ -8219,7 +8321,10 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>-2.8</v>
       </c>
       <c r="AG112" t="b">
         <v>0</v>
@@ -8285,7 +8390,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG113" t="b">
         <v>0</v>
@@ -8351,7 +8456,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG114" t="b">
         <v>0</v>
@@ -8417,7 +8522,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG115" t="b">
         <v>0</v>
@@ -8483,7 +8588,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG116" t="b">
         <v>0</v>
@@ -8549,7 +8654,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG117" t="b">
         <v>0</v>
@@ -8615,7 +8720,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG118" t="b">
         <v>0</v>
@@ -8681,7 +8786,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG119" t="b">
         <v>0</v>
@@ -8747,7 +8852,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG120" t="b">
         <v>0</v>
@@ -8813,7 +8918,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG121" t="b">
         <v>0</v>
@@ -8879,10 +8984,10 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH122" t="b">
         <v>0</v>
@@ -8945,7 +9050,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG123" t="b">
         <v>0</v>
@@ -9011,7 +9116,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG124" t="b">
         <v>0</v>
@@ -9077,7 +9182,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG125" t="b">
         <v>0</v>
@@ -9143,7 +9248,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG126" t="b">
         <v>0</v>
@@ -9209,7 +9314,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG127" t="b">
         <v>0</v>
@@ -9275,7 +9380,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG128" t="b">
         <v>0</v>
@@ -9341,7 +9446,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG129" t="b">
         <v>0</v>
@@ -9456,7 +9561,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG130" t="b">
         <v>0</v>
@@ -9571,13 +9676,13 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AH131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
@@ -9686,7 +9791,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG132" t="b">
         <v>0</v>
@@ -9801,13 +9906,13 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AH133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
@@ -9916,13 +10021,13 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AH134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
@@ -10031,7 +10136,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG135" t="b">
         <v>0</v>
@@ -10146,7 +10251,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG136" t="b">
         <v>0</v>
@@ -10258,7 +10363,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG137" t="b">
         <v>0</v>
@@ -10373,7 +10478,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG138" t="b">
         <v>0</v>
@@ -10488,7 +10593,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG139" t="b">
         <v>0</v>
@@ -10603,7 +10708,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG140" t="b">
         <v>0</v>
@@ -10718,13 +10823,13 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AH141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
@@ -10833,13 +10938,13 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AH142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
@@ -10948,7 +11053,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG143" t="b">
         <v>0</v>
@@ -11063,7 +11168,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG144" t="b">
         <v>0</v>
@@ -11178,7 +11283,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG145" t="b">
         <v>0</v>
@@ -11293,7 +11398,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG146" t="b">
         <v>0</v>
@@ -11408,7 +11513,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG147" t="b">
         <v>0</v>
@@ -11523,7 +11628,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG148" t="b">
         <v>0</v>
@@ -11638,13 +11743,13 @@
         </is>
       </c>
       <c r="Z149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH149" t="b">
         <v>1</v>
-      </c>
-      <c r="AG149" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH149" t="b">
-        <v>0</v>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
@@ -11753,7 +11858,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG150" t="b">
         <v>0</v>
@@ -11868,7 +11973,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG151" t="b">
         <v>0</v>
@@ -11983,13 +12088,13 @@
         </is>
       </c>
       <c r="Z152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH152" t="b">
         <v>1</v>
-      </c>
-      <c r="AG152" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH152" t="b">
-        <v>0</v>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
@@ -12098,7 +12203,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG153" t="b">
         <v>0</v>
@@ -12213,7 +12318,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG154" t="b">
         <v>0</v>
@@ -12328,7 +12433,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG155" t="b">
         <v>0</v>
@@ -12443,7 +12548,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG156" t="b">
         <v>0</v>
@@ -12558,7 +12663,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG157" t="b">
         <v>0</v>
@@ -12673,13 +12778,13 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AH158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI158" t="inlineStr">
         <is>
@@ -12788,13 +12893,13 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AH159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI159" t="inlineStr">
         <is>
@@ -12903,7 +13008,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG160" t="b">
         <v>0</v>
@@ -13018,7 +13123,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG161" t="b">
         <v>0</v>
@@ -13133,7 +13238,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG162" t="b">
         <v>0</v>
@@ -13248,7 +13353,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG163" t="b">
         <v>0</v>
@@ -13363,7 +13468,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG164" t="b">
         <v>0</v>
@@ -13478,7 +13583,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG165" t="b">
         <v>0</v>
@@ -13593,7 +13698,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG166" t="b">
         <v>0</v>
@@ -13708,13 +13813,13 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AH167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
@@ -13934,13 +14039,13 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AH169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI169" t="inlineStr">
         <is>
@@ -14049,7 +14154,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG170" t="b">
         <v>0</v>
@@ -14164,7 +14269,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG171" t="b">
         <v>0</v>
@@ -14178,8 +14283,1039 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>72.77</v>
+      </c>
+      <c r="F172" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I172" t="b">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="K172" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M172" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N172" t="n">
+        <v>10</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S172" t="n">
+        <v>4.504</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V172" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="W172" t="n">
+        <v>27.108</v>
+      </c>
+      <c r="X172" t="n">
+        <v>23.7308</v>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>80.47</v>
+      </c>
+      <c r="F173" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I173" t="b">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" t="n">
+        <v>36</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M173" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N173" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>79.17</v>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S173" t="n">
+        <v>7</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V173" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="W173" t="n">
+        <v>39.0268</v>
+      </c>
+      <c r="X173" t="n">
+        <v>32.5035</v>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>遠東新</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>76.19</v>
+      </c>
+      <c r="F174" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I174" t="b">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="K174" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M174" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N174" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>73.31999999999999</v>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S174" t="n">
+        <v>7</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V174" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="W174" t="n">
+        <v>35.5963</v>
+      </c>
+      <c r="X174" t="n">
+        <v>28.2255</v>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>75.04000000000001</v>
+      </c>
+      <c r="F175" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I175" t="b">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>10</v>
+      </c>
+      <c r="K175" t="n">
+        <v>580.8</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M175" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N175" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>494.5</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S175" t="n">
+        <v>7</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V175" t="n">
+        <v>528</v>
+      </c>
+      <c r="W175" t="n">
+        <v>633.6</v>
+      </c>
+      <c r="X175" t="n">
+        <v>491.04</v>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>74.78</v>
+      </c>
+      <c r="F176" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I176" t="b">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="K176" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M176" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N176" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S176" t="n">
+        <v>7</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V176" t="n">
+        <v>134</v>
+      </c>
+      <c r="W176" t="n">
+        <v>151.2218</v>
+      </c>
+      <c r="X176" t="n">
+        <v>124.62</v>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="F177" t="n">
+        <v>52.96</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I177" t="b">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K177" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M177" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N177" t="n">
+        <v>7</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S177" t="n">
+        <v>7</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V177" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="W177" t="n">
+        <v>42.8264</v>
+      </c>
+      <c r="X177" t="n">
+        <v>34.6425</v>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>86.58</v>
+      </c>
+      <c r="F178" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I178" t="b">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>10</v>
+      </c>
+      <c r="K178" t="n">
+        <v>6171</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M178" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N178" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>4970.86</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>77.81999999999999</v>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S178" t="n">
+        <v>7</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V178" t="n">
+        <v>5610</v>
+      </c>
+      <c r="W178" t="n">
+        <v>6732</v>
+      </c>
+      <c r="X178" t="n">
+        <v>5217.3</v>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>74.95</v>
+      </c>
+      <c r="F179" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I179" t="b">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>10</v>
+      </c>
+      <c r="K179" t="n">
+        <v>3212</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M179" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N179" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>2622.5</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S179" t="n">
+        <v>7</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V179" t="n">
+        <v>2920</v>
+      </c>
+      <c r="W179" t="n">
+        <v>3504</v>
+      </c>
+      <c r="X179" t="n">
+        <v>2715.6</v>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="F180" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I180" t="b">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>10</v>
+      </c>
+      <c r="K180" t="n">
+        <v>6160</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M180" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N180" t="n">
+        <v>3</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>5120</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>53</v>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S180" t="n">
+        <v>7</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V180" t="n">
+        <v>5600</v>
+      </c>
+      <c r="W180" t="n">
+        <v>6720</v>
+      </c>
+      <c r="X180" t="n">
+        <v>5208</v>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ171"/>
+  <autoFilter ref="A1:AJ180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14429,7 +15565,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20 14:22:09</t>
+          <t>2026-08-21 14:23:57</t>
         </is>
       </c>
     </row>
@@ -14476,7 +15612,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7">
@@ -14496,7 +15632,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ180"/>
+  <dimension ref="A1:AJ186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
@@ -1801,11 +1801,14 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
       </c>
+      <c r="AB17" t="n">
+        <v>0.61</v>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -1870,11 +1873,14 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
       </c>
+      <c r="AB18" t="n">
+        <v>-8.6</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -1939,11 +1945,14 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
       </c>
+      <c r="AB19" t="n">
+        <v>-2.29</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2008,11 +2017,14 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
       </c>
+      <c r="AB20" t="n">
+        <v>-11.24</v>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2077,11 +2089,14 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
       </c>
+      <c r="AB21" t="n">
+        <v>-7.94</v>
+      </c>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2146,11 +2161,14 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
       </c>
+      <c r="AB22" t="n">
+        <v>12.84</v>
+      </c>
       <c r="AG22" t="b">
         <v>1</v>
       </c>
@@ -2215,11 +2233,14 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
       </c>
+      <c r="AB23" t="n">
+        <v>-2.43</v>
+      </c>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2284,11 +2305,14 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
       </c>
+      <c r="AB24" t="n">
+        <v>-1.35</v>
+      </c>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2353,11 +2377,14 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
       </c>
+      <c r="AB25" t="n">
+        <v>17.06</v>
+      </c>
       <c r="AG25" t="b">
         <v>1</v>
       </c>
@@ -2422,11 +2449,14 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
       </c>
+      <c r="AB26" t="n">
+        <v>25</v>
+      </c>
       <c r="AG26" t="b">
         <v>1</v>
       </c>
@@ -2491,11 +2521,14 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
       </c>
+      <c r="AB27" t="n">
+        <v>42.29</v>
+      </c>
       <c r="AG27" t="b">
         <v>1</v>
       </c>
@@ -2560,11 +2593,14 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
       </c>
+      <c r="AB28" t="n">
+        <v>-10.8</v>
+      </c>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -2629,11 +2665,14 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
       </c>
+      <c r="AB29" t="n">
+        <v>-2.08</v>
+      </c>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -2698,11 +2737,14 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
       </c>
+      <c r="AB30" t="n">
+        <v>-8.140000000000001</v>
+      </c>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -2767,11 +2809,14 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
       </c>
+      <c r="AB31" t="n">
+        <v>2.36</v>
+      </c>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -2836,11 +2881,14 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
       </c>
+      <c r="AB32" t="n">
+        <v>-0.37</v>
+      </c>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -2905,11 +2953,14 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
       </c>
+      <c r="AB33" t="n">
+        <v>-9.07</v>
+      </c>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3098,11 +3149,14 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
       </c>
+      <c r="AB36" t="n">
+        <v>5.1</v>
+      </c>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -3167,11 +3221,14 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA37" t="n">
         <v>10.15</v>
       </c>
+      <c r="AB37" t="n">
+        <v>4.83</v>
+      </c>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -3236,11 +3293,14 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
       </c>
+      <c r="AB38" t="n">
+        <v>-1.74</v>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -3305,7 +3365,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3374,7 +3434,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3443,7 +3503,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3512,7 +3572,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3581,7 +3641,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3650,7 +3710,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -3719,7 +3779,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -3788,7 +3848,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -3857,7 +3917,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -3926,7 +3986,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -3995,7 +4055,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4064,7 +4124,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4133,7 +4193,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4202,7 +4262,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4271,7 +4331,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4340,7 +4400,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4471,7 +4531,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4540,7 +4600,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -4609,7 +4669,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -4678,7 +4738,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -4747,7 +4807,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -4816,7 +4876,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -4885,7 +4945,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -4954,7 +5014,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -5023,7 +5083,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5092,7 +5152,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5161,7 +5221,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5230,7 +5290,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5299,7 +5359,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -5368,7 +5428,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -5499,7 +5559,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -5568,7 +5628,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -5637,7 +5697,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA73" t="n">
         <v>5.81</v>
@@ -5706,7 +5766,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -5775,7 +5835,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -5844,7 +5904,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -5913,7 +5973,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -5982,7 +6042,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6051,7 +6111,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6120,7 +6180,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6189,7 +6249,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -6258,7 +6318,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -6327,7 +6387,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -6396,7 +6456,7 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -6465,7 +6525,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -6534,7 +6594,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -6603,7 +6663,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -6672,7 +6732,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -6741,7 +6801,7 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA89" t="n">
         <v>4.2</v>
@@ -6872,7 +6932,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -6941,7 +7001,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -7010,7 +7070,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -7079,7 +7139,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -7148,7 +7208,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -7217,7 +7277,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -7286,7 +7346,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -7355,7 +7415,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -7424,7 +7484,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -7493,7 +7553,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -7562,7 +7622,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -7631,7 +7691,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -7700,7 +7760,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -7769,7 +7829,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -7838,7 +7898,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -7907,7 +7967,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -7976,7 +8036,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -8045,7 +8105,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -8114,7 +8174,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -8183,7 +8243,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -8252,7 +8312,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -8321,7 +8381,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA112" t="n">
         <v>-2.8</v>
@@ -8390,7 +8450,10 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>-1.11</v>
       </c>
       <c r="AG113" t="b">
         <v>0</v>
@@ -8456,7 +8519,10 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>-2.05</v>
       </c>
       <c r="AG114" t="b">
         <v>0</v>
@@ -8522,7 +8588,10 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>-9.960000000000001</v>
       </c>
       <c r="AG115" t="b">
         <v>0</v>
@@ -8588,7 +8657,10 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>8.92</v>
       </c>
       <c r="AG116" t="b">
         <v>0</v>
@@ -8654,7 +8726,10 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>-1.6</v>
       </c>
       <c r="AG117" t="b">
         <v>0</v>
@@ -8720,7 +8795,10 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>-12.29</v>
       </c>
       <c r="AG118" t="b">
         <v>0</v>
@@ -8786,7 +8864,10 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>-14.49</v>
       </c>
       <c r="AG119" t="b">
         <v>0</v>
@@ -8852,7 +8933,10 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>-4.39</v>
       </c>
       <c r="AG120" t="b">
         <v>0</v>
@@ -8918,7 +9002,10 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>8.210000000000001</v>
       </c>
       <c r="AG121" t="b">
         <v>0</v>
@@ -8984,7 +9071,10 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>17.92</v>
       </c>
       <c r="AG122" t="b">
         <v>1</v>
@@ -9050,7 +9140,10 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>-1.27</v>
       </c>
       <c r="AG123" t="b">
         <v>0</v>
@@ -9116,7 +9209,10 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>-8.640000000000001</v>
       </c>
       <c r="AG124" t="b">
         <v>0</v>
@@ -9182,7 +9278,10 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>-1.75</v>
       </c>
       <c r="AG125" t="b">
         <v>0</v>
@@ -9248,7 +9347,10 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>-9.369999999999999</v>
       </c>
       <c r="AG126" t="b">
         <v>0</v>
@@ -9314,7 +9416,10 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>-6.15</v>
       </c>
       <c r="AG127" t="b">
         <v>0</v>
@@ -9380,7 +9485,10 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-8.289999999999999</v>
       </c>
       <c r="AG128" t="b">
         <v>0</v>
@@ -9446,7 +9554,10 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>-4.83</v>
       </c>
       <c r="AG129" t="b">
         <v>0</v>
@@ -9561,7 +9672,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG130" t="b">
         <v>0</v>
@@ -9676,7 +9787,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG131" t="b">
         <v>0</v>
@@ -9791,7 +9902,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG132" t="b">
         <v>0</v>
@@ -9906,7 +10017,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG133" t="b">
         <v>0</v>
@@ -10021,7 +10132,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG134" t="b">
         <v>0</v>
@@ -10136,7 +10247,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG135" t="b">
         <v>0</v>
@@ -10251,10 +10362,10 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH136" t="b">
         <v>0</v>
@@ -10363,7 +10474,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG137" t="b">
         <v>0</v>
@@ -10478,7 +10589,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG138" t="b">
         <v>0</v>
@@ -10593,7 +10704,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG139" t="b">
         <v>0</v>
@@ -10708,7 +10819,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG140" t="b">
         <v>0</v>
@@ -10823,7 +10934,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG141" t="b">
         <v>0</v>
@@ -10938,7 +11049,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG142" t="b">
         <v>0</v>
@@ -11053,7 +11164,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG143" t="b">
         <v>0</v>
@@ -11168,7 +11279,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG144" t="b">
         <v>0</v>
@@ -11283,7 +11394,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG145" t="b">
         <v>0</v>
@@ -11398,7 +11509,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG146" t="b">
         <v>0</v>
@@ -11513,7 +11624,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG147" t="b">
         <v>0</v>
@@ -11628,7 +11739,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG148" t="b">
         <v>0</v>
@@ -11743,7 +11854,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG149" t="b">
         <v>0</v>
@@ -11858,7 +11969,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG150" t="b">
         <v>0</v>
@@ -11973,7 +12084,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG151" t="b">
         <v>0</v>
@@ -12088,7 +12199,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG152" t="b">
         <v>0</v>
@@ -12203,7 +12314,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG153" t="b">
         <v>0</v>
@@ -12318,7 +12429,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG154" t="b">
         <v>0</v>
@@ -12433,7 +12544,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG155" t="b">
         <v>0</v>
@@ -12548,7 +12659,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG156" t="b">
         <v>0</v>
@@ -12663,7 +12774,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG157" t="b">
         <v>0</v>
@@ -12778,7 +12889,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG158" t="b">
         <v>0</v>
@@ -12893,7 +13004,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG159" t="b">
         <v>0</v>
@@ -13008,13 +13119,13 @@
         </is>
       </c>
       <c r="Z160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH160" t="b">
         <v>1</v>
-      </c>
-      <c r="AG160" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH160" t="b">
-        <v>0</v>
       </c>
       <c r="AI160" t="inlineStr">
         <is>
@@ -13123,7 +13234,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG161" t="b">
         <v>0</v>
@@ -13238,7 +13349,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG162" t="b">
         <v>0</v>
@@ -13353,7 +13464,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG163" t="b">
         <v>0</v>
@@ -13468,7 +13579,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG164" t="b">
         <v>0</v>
@@ -13583,10 +13694,10 @@
         </is>
       </c>
       <c r="Z165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG165" t="b">
         <v>1</v>
-      </c>
-      <c r="AG165" t="b">
-        <v>0</v>
       </c>
       <c r="AH165" t="b">
         <v>0</v>
@@ -13698,7 +13809,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG166" t="b">
         <v>0</v>
@@ -13813,7 +13924,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG167" t="b">
         <v>0</v>
@@ -14039,7 +14150,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG169" t="b">
         <v>0</v>
@@ -14154,7 +14265,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG170" t="b">
         <v>0</v>
@@ -14269,7 +14380,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG171" t="b">
         <v>0</v>
@@ -14384,7 +14495,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG172" t="b">
         <v>0</v>
@@ -14499,7 +14610,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG173" t="b">
         <v>0</v>
@@ -14614,7 +14725,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG174" t="b">
         <v>0</v>
@@ -14729,7 +14840,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG175" t="b">
         <v>0</v>
@@ -14844,7 +14955,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG176" t="b">
         <v>0</v>
@@ -14959,7 +15070,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG177" t="b">
         <v>0</v>
@@ -15074,7 +15185,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG178" t="b">
         <v>0</v>
@@ -15300,7 +15411,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG180" t="b">
         <v>0</v>
@@ -15314,8 +15425,698 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>遠東新</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>72.39</v>
+      </c>
+      <c r="F181" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I181" t="b">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K181" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M181" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N181" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>71.03</v>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S181" t="n">
+        <v>7</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V181" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="W181" t="n">
+        <v>33.8455</v>
+      </c>
+      <c r="X181" t="n">
+        <v>27.3885</v>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="F182" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I182" t="b">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="K182" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M182" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N182" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>59.86</v>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S182" t="n">
+        <v>7</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V182" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="W182" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="X182" t="n">
+        <v>38.688</v>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>74.61</v>
+      </c>
+      <c r="F183" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I183" t="b">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>10</v>
+      </c>
+      <c r="K183" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M183" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N183" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>230.25</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S183" t="n">
+        <v>7</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V183" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="W183" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="X183" t="n">
+        <v>232.965</v>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>73.04000000000001</v>
+      </c>
+      <c r="F184" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I184" t="b">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>10</v>
+      </c>
+      <c r="K184" t="n">
+        <v>5923.5</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M184" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N184" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>4970.86</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S184" t="n">
+        <v>7</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V184" t="n">
+        <v>5385</v>
+      </c>
+      <c r="W184" t="n">
+        <v>6462</v>
+      </c>
+      <c r="X184" t="n">
+        <v>5008.05</v>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>6472</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>保瑞</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>80.95999999999999</v>
+      </c>
+      <c r="F185" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I185" t="b">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>10</v>
+      </c>
+      <c r="K185" t="n">
+        <v>498.3</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M185" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N185" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>431</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>66.45999999999999</v>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S185" t="n">
+        <v>7</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V185" t="n">
+        <v>453</v>
+      </c>
+      <c r="W185" t="n">
+        <v>543.6</v>
+      </c>
+      <c r="X185" t="n">
+        <v>421.29</v>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="F186" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I186" t="b">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>10</v>
+      </c>
+      <c r="K186" t="n">
+        <v>6930</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M186" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N186" t="n">
+        <v>7</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>6297.5</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S186" t="n">
+        <v>7</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V186" t="n">
+        <v>6300</v>
+      </c>
+      <c r="W186" t="n">
+        <v>7489.4557</v>
+      </c>
+      <c r="X186" t="n">
+        <v>5859</v>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ180"/>
+  <autoFilter ref="A1:AJ186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15565,7 +16366,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:23:57</t>
+          <t>2026-08-24 14:50:49</t>
         </is>
       </c>
     </row>
@@ -15612,7 +16413,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7">
@@ -15632,7 +16433,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ186"/>
+  <dimension ref="A1:AJ202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA37" t="n">
         <v>10.15</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3365,11 +3365,14 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
       </c>
+      <c r="AB39" t="n">
+        <v>-6.41</v>
+      </c>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -3434,11 +3437,14 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
       </c>
+      <c r="AB40" t="n">
+        <v>0.39</v>
+      </c>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -3503,11 +3509,14 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
       </c>
+      <c r="AB41" t="n">
+        <v>-3.54</v>
+      </c>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -3572,11 +3581,14 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
       </c>
+      <c r="AB42" t="n">
+        <v>10.24</v>
+      </c>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -3641,11 +3653,14 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
       </c>
+      <c r="AB43" t="n">
+        <v>10.25</v>
+      </c>
       <c r="AG43" t="b">
         <v>1</v>
       </c>
@@ -3710,16 +3725,19 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
       </c>
+      <c r="AB44" t="n">
+        <v>-5.53</v>
+      </c>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
@@ -3779,11 +3797,14 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
       </c>
+      <c r="AB45" t="n">
+        <v>-0.86</v>
+      </c>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -3848,11 +3869,14 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
       </c>
+      <c r="AB46" t="n">
+        <v>1.08</v>
+      </c>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -3917,11 +3941,14 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
       </c>
+      <c r="AB47" t="n">
+        <v>1.36</v>
+      </c>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -3986,11 +4013,14 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
       </c>
+      <c r="AB48" t="n">
+        <v>4.29</v>
+      </c>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -4055,11 +4085,14 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
       </c>
+      <c r="AB49" t="n">
+        <v>-7.09</v>
+      </c>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -4124,11 +4157,14 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
       </c>
+      <c r="AB50" t="n">
+        <v>12.84</v>
+      </c>
       <c r="AG50" t="b">
         <v>1</v>
       </c>
@@ -4193,11 +4229,14 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
       </c>
+      <c r="AB51" t="n">
+        <v>22.31</v>
+      </c>
       <c r="AG51" t="b">
         <v>1</v>
       </c>
@@ -4262,11 +4301,14 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
       </c>
+      <c r="AB52" t="n">
+        <v>45.24</v>
+      </c>
       <c r="AG52" t="b">
         <v>1</v>
       </c>
@@ -4331,11 +4373,14 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
       </c>
+      <c r="AB53" t="n">
+        <v>2.09</v>
+      </c>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -4400,11 +4445,14 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
       </c>
+      <c r="AB54" t="n">
+        <v>-6.54</v>
+      </c>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -4531,11 +4579,14 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
       </c>
+      <c r="AB56" t="n">
+        <v>10.98</v>
+      </c>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -4600,7 +4651,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -4669,7 +4720,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -4738,7 +4789,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -4807,7 +4858,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -4876,7 +4927,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -4945,7 +4996,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -4954,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AH62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
@@ -5014,7 +5065,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -5023,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="AH63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
@@ -5083,7 +5134,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5152,7 +5203,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5221,7 +5272,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5290,7 +5341,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5359,7 +5410,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -5428,7 +5479,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -5559,7 +5610,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -5628,7 +5679,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -5697,7 +5748,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA73" t="n">
         <v>5.81</v>
@@ -5766,7 +5817,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -5835,7 +5886,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -5904,7 +5955,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -5973,7 +6024,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -6042,7 +6093,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6111,7 +6162,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6180,7 +6231,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6249,7 +6300,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -6318,7 +6369,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -6387,7 +6438,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -6456,7 +6507,7 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -6525,7 +6576,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -6594,7 +6645,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -6663,7 +6714,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -6732,7 +6783,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -6801,7 +6852,7 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA89" t="n">
         <v>4.2</v>
@@ -6932,7 +6983,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -7001,7 +7052,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -7070,7 +7121,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -7139,7 +7190,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -7208,7 +7259,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -7277,7 +7328,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -7346,7 +7397,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -7415,7 +7466,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -7484,7 +7535,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -7553,7 +7604,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -7622,7 +7673,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -7691,7 +7742,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -7760,7 +7811,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -7829,7 +7880,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -7898,7 +7949,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -7967,7 +8018,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -8036,7 +8087,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -8105,7 +8156,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -8174,7 +8225,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -8243,7 +8294,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -8312,7 +8363,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -8381,7 +8432,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA112" t="n">
         <v>-2.8</v>
@@ -8450,7 +8501,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
@@ -8519,7 +8570,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
@@ -8588,7 +8639,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
@@ -8657,7 +8708,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
@@ -8726,7 +8777,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
@@ -8795,7 +8846,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
@@ -8864,7 +8915,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
@@ -8933,7 +8984,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
@@ -9002,7 +9053,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
@@ -9071,7 +9122,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
@@ -9140,7 +9191,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
@@ -9209,7 +9260,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
@@ -9278,7 +9329,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
@@ -9347,7 +9398,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
@@ -9416,7 +9467,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
@@ -9485,7 +9536,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
@@ -9554,7 +9605,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA129" t="n">
         <v>-4.83</v>
@@ -9563,7 +9614,7 @@
         <v>0</v>
       </c>
       <c r="AH129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
@@ -9672,7 +9723,10 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.42</v>
       </c>
       <c r="AG130" t="b">
         <v>0</v>
@@ -9787,7 +9841,10 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>8.23</v>
       </c>
       <c r="AG131" t="b">
         <v>0</v>
@@ -9902,7 +9959,10 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.49</v>
       </c>
       <c r="AG132" t="b">
         <v>0</v>
@@ -10017,7 +10077,10 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>-9.25</v>
       </c>
       <c r="AG133" t="b">
         <v>0</v>
@@ -10132,7 +10195,10 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>-9.83</v>
       </c>
       <c r="AG134" t="b">
         <v>0</v>
@@ -10247,7 +10313,10 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>-0.97</v>
       </c>
       <c r="AG135" t="b">
         <v>0</v>
@@ -10362,7 +10431,10 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>13.17</v>
       </c>
       <c r="AG136" t="b">
         <v>1</v>
@@ -10474,7 +10546,10 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>9.27</v>
       </c>
       <c r="AG137" t="b">
         <v>0</v>
@@ -10589,7 +10664,10 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>2.36</v>
       </c>
       <c r="AG138" t="b">
         <v>0</v>
@@ -10704,7 +10782,10 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.68</v>
       </c>
       <c r="AG139" t="b">
         <v>0</v>
@@ -10819,7 +10900,10 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>8.130000000000001</v>
       </c>
       <c r="AG140" t="b">
         <v>0</v>
@@ -10934,7 +11018,10 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>-4.37</v>
       </c>
       <c r="AG141" t="b">
         <v>0</v>
@@ -11049,7 +11136,10 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>-3.47</v>
       </c>
       <c r="AG142" t="b">
         <v>0</v>
@@ -11164,7 +11254,10 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.63</v>
       </c>
       <c r="AG143" t="b">
         <v>0</v>
@@ -11279,7 +11372,10 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>6.43</v>
       </c>
       <c r="AG144" t="b">
         <v>0</v>
@@ -11394,7 +11490,10 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>0.63</v>
       </c>
       <c r="AG145" t="b">
         <v>0</v>
@@ -11509,7 +11608,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG146" t="b">
         <v>0</v>
@@ -11624,7 +11723,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG147" t="b">
         <v>0</v>
@@ -11739,7 +11838,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG148" t="b">
         <v>0</v>
@@ -11854,7 +11953,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG149" t="b">
         <v>0</v>
@@ -11969,7 +12068,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG150" t="b">
         <v>0</v>
@@ -12084,7 +12183,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG151" t="b">
         <v>0</v>
@@ -12199,7 +12298,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG152" t="b">
         <v>0</v>
@@ -12314,7 +12413,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG153" t="b">
         <v>0</v>
@@ -12429,7 +12528,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG154" t="b">
         <v>0</v>
@@ -12544,7 +12643,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG155" t="b">
         <v>0</v>
@@ -12659,7 +12758,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG156" t="b">
         <v>0</v>
@@ -12774,7 +12873,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG157" t="b">
         <v>0</v>
@@ -12889,7 +12988,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG158" t="b">
         <v>0</v>
@@ -13004,7 +13103,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG159" t="b">
         <v>0</v>
@@ -13119,7 +13218,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG160" t="b">
         <v>0</v>
@@ -13234,7 +13333,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG161" t="b">
         <v>0</v>
@@ -13349,13 +13448,13 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AH162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
@@ -13464,7 +13563,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG163" t="b">
         <v>0</v>
@@ -13579,7 +13678,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG164" t="b">
         <v>0</v>
@@ -13694,7 +13793,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG165" t="b">
         <v>1</v>
@@ -13809,7 +13908,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG166" t="b">
         <v>0</v>
@@ -13924,7 +14023,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG167" t="b">
         <v>0</v>
@@ -14150,7 +14249,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG169" t="b">
         <v>0</v>
@@ -14265,13 +14364,13 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AH170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI170" t="inlineStr">
         <is>
@@ -14380,7 +14479,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG171" t="b">
         <v>0</v>
@@ -14495,7 +14594,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG172" t="b">
         <v>0</v>
@@ -14610,7 +14709,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG173" t="b">
         <v>0</v>
@@ -14725,7 +14824,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG174" t="b">
         <v>0</v>
@@ -14840,13 +14939,13 @@
         </is>
       </c>
       <c r="Z175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH175" t="b">
         <v>1</v>
-      </c>
-      <c r="AG175" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH175" t="b">
-        <v>0</v>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
@@ -14955,7 +15054,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG176" t="b">
         <v>0</v>
@@ -15070,7 +15169,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG177" t="b">
         <v>0</v>
@@ -15185,7 +15284,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG178" t="b">
         <v>0</v>
@@ -15411,13 +15510,13 @@
         </is>
       </c>
       <c r="Z180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH180" t="b">
         <v>1</v>
-      </c>
-      <c r="AG180" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH180" t="b">
-        <v>0</v>
       </c>
       <c r="AI180" t="inlineStr">
         <is>
@@ -15526,7 +15625,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG181" t="b">
         <v>0</v>
@@ -15641,7 +15740,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG182" t="b">
         <v>0</v>
@@ -15756,7 +15855,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG183" t="b">
         <v>0</v>
@@ -15871,7 +15970,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG184" t="b">
         <v>0</v>
@@ -15986,7 +16085,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG185" t="b">
         <v>0</v>
@@ -16101,7 +16200,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG186" t="b">
         <v>0</v>
@@ -16115,8 +16214,1840 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>77.54000000000001</v>
+      </c>
+      <c r="F187" t="n">
+        <v>76.72</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I187" t="b">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
+        <v>10</v>
+      </c>
+      <c r="K187" t="n">
+        <v>788.7</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M187" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N187" t="n">
+        <v>10</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>697</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S187" t="n">
+        <v>3.2755</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="V187" t="n">
+        <v>717</v>
+      </c>
+      <c r="W187" t="n">
+        <v>860.4</v>
+      </c>
+      <c r="X187" t="n">
+        <v>693.515</v>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>84.66</v>
+      </c>
+      <c r="F188" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I188" t="b">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>10</v>
+      </c>
+      <c r="K188" t="n">
+        <v>325.6</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M188" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N188" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>69.45999999999999</v>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S188" t="n">
+        <v>7</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V188" t="n">
+        <v>296</v>
+      </c>
+      <c r="W188" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="X188" t="n">
+        <v>275.28</v>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>77.16</v>
+      </c>
+      <c r="F189" t="n">
+        <v>55.97</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I189" t="b">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>10</v>
+      </c>
+      <c r="K189" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M189" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N189" t="n">
+        <v>7</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S189" t="n">
+        <v>7</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V189" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="W189" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="X189" t="n">
+        <v>37.944</v>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>77.59</v>
+      </c>
+      <c r="F190" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I190" t="b">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>10</v>
+      </c>
+      <c r="K190" t="n">
+        <v>561</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M190" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N190" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>513</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S190" t="n">
+        <v>6.3529</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V190" t="n">
+        <v>510</v>
+      </c>
+      <c r="W190" t="n">
+        <v>612</v>
+      </c>
+      <c r="X190" t="n">
+        <v>477.6</v>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>72.04000000000001</v>
+      </c>
+      <c r="F191" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I191" t="b">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>10</v>
+      </c>
+      <c r="K191" t="n">
+        <v>270.6</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M191" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N191" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>232.25</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>56.23</v>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S191" t="n">
+        <v>7</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V191" t="n">
+        <v>246</v>
+      </c>
+      <c r="W191" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="X191" t="n">
+        <v>228.78</v>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>76.98</v>
+      </c>
+      <c r="F192" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I192" t="b">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K192" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M192" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N192" t="n">
+        <v>3</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S192" t="n">
+        <v>7</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V192" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="W192" t="n">
+        <v>169.6014</v>
+      </c>
+      <c r="X192" t="n">
+        <v>131.595</v>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="F193" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I193" t="b">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="K193" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M193" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="N193" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S193" t="n">
+        <v>6.2961</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V193" t="n">
+        <v>103</v>
+      </c>
+      <c r="W193" t="n">
+        <v>116.398</v>
+      </c>
+      <c r="X193" t="n">
+        <v>96.515</v>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="F194" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I194" t="b">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K194" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M194" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="N194" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S194" t="n">
+        <v>5.9906</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V194" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="W194" t="n">
+        <v>42.44</v>
+      </c>
+      <c r="X194" t="n">
+        <v>34.9245</v>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>晶豪科</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>71.47</v>
+      </c>
+      <c r="F195" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I195" t="b">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>10</v>
+      </c>
+      <c r="K195" t="n">
+        <v>297</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M195" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N195" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>260.75</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S195" t="n">
+        <v>7</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V195" t="n">
+        <v>270</v>
+      </c>
+      <c r="W195" t="n">
+        <v>324</v>
+      </c>
+      <c r="X195" t="n">
+        <v>251.1</v>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>78.18000000000001</v>
+      </c>
+      <c r="F196" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I196" t="b">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>10</v>
+      </c>
+      <c r="K196" t="n">
+        <v>6292</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M196" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N196" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>4970.86</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>64.31</v>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S196" t="n">
+        <v>7</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V196" t="n">
+        <v>5720</v>
+      </c>
+      <c r="W196" t="n">
+        <v>6864</v>
+      </c>
+      <c r="X196" t="n">
+        <v>5319.6</v>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>3034</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>聯詠</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>74.81</v>
+      </c>
+      <c r="F197" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I197" t="b">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>10</v>
+      </c>
+      <c r="K197" t="n">
+        <v>610.5</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M197" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N197" t="n">
+        <v>7</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>530.25</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S197" t="n">
+        <v>7</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V197" t="n">
+        <v>555</v>
+      </c>
+      <c r="W197" t="n">
+        <v>657.3330999999999</v>
+      </c>
+      <c r="X197" t="n">
+        <v>516.15</v>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>76.13</v>
+      </c>
+      <c r="F198" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I198" t="b">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>10</v>
+      </c>
+      <c r="K198" t="n">
+        <v>3256</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M198" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N198" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>2740</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S198" t="n">
+        <v>7</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V198" t="n">
+        <v>2960</v>
+      </c>
+      <c r="W198" t="n">
+        <v>3552</v>
+      </c>
+      <c r="X198" t="n">
+        <v>2752.8</v>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="F199" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I199" t="b">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="K199" t="n">
+        <v>1105</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M199" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N199" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>1017.5</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>57</v>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S199" t="n">
+        <v>7</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V199" t="n">
+        <v>1065</v>
+      </c>
+      <c r="W199" t="n">
+        <v>1278</v>
+      </c>
+      <c r="X199" t="n">
+        <v>990.45</v>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>76.09</v>
+      </c>
+      <c r="F200" t="n">
+        <v>47.11</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I200" t="b">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>10</v>
+      </c>
+      <c r="K200" t="n">
+        <v>6127</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M200" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N200" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>5250</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S200" t="n">
+        <v>7</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V200" t="n">
+        <v>5570</v>
+      </c>
+      <c r="W200" t="n">
+        <v>6684</v>
+      </c>
+      <c r="X200" t="n">
+        <v>5180.1</v>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>藥華藥</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="F201" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I201" t="b">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>10</v>
+      </c>
+      <c r="K201" t="n">
+        <v>1639</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M201" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N201" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>1370</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S201" t="n">
+        <v>7</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V201" t="n">
+        <v>1490</v>
+      </c>
+      <c r="W201" t="n">
+        <v>1788</v>
+      </c>
+      <c r="X201" t="n">
+        <v>1385.7</v>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="F202" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I202" t="b">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>10</v>
+      </c>
+      <c r="K202" t="n">
+        <v>7084</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M202" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N202" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>6297.5</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S202" t="n">
+        <v>7</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V202" t="n">
+        <v>6440</v>
+      </c>
+      <c r="W202" t="n">
+        <v>7728</v>
+      </c>
+      <c r="X202" t="n">
+        <v>5989.2</v>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ186"/>
+  <autoFilter ref="A1:AJ202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16366,7 +18297,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-24 14:50:49</t>
+          <t>2026-08-25 14:23:08</t>
         </is>
       </c>
     </row>
@@ -16413,7 +18344,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7">
@@ -16433,7 +18364,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$217</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ202"/>
+  <dimension ref="A1:AJ217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA37" t="n">
         <v>10.15</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4651,11 +4651,14 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
       </c>
+      <c r="AB57" t="n">
+        <v>-0.42</v>
+      </c>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -4720,11 +4723,14 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
       </c>
+      <c r="AB58" t="n">
+        <v>-7.84</v>
+      </c>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -4789,11 +4795,14 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
       </c>
+      <c r="AB59" t="n">
+        <v>-2.03</v>
+      </c>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -4858,11 +4867,14 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
       </c>
+      <c r="AB60" t="n">
+        <v>-8.699999999999999</v>
+      </c>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -4927,11 +4939,14 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
       </c>
+      <c r="AB61" t="n">
+        <v>13.97</v>
+      </c>
       <c r="AG61" t="b">
         <v>1</v>
       </c>
@@ -4996,11 +5011,14 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
       </c>
+      <c r="AB62" t="n">
+        <v>-9.789999999999999</v>
+      </c>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -5065,11 +5083,14 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
       </c>
+      <c r="AB63" t="n">
+        <v>2.88</v>
+      </c>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -5134,11 +5155,14 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
       </c>
+      <c r="AB64" t="n">
+        <v>0.29</v>
+      </c>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -5203,11 +5227,14 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
       </c>
+      <c r="AB65" t="n">
+        <v>7.69</v>
+      </c>
       <c r="AG65" t="b">
         <v>1</v>
       </c>
@@ -5272,11 +5299,14 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
       </c>
+      <c r="AB66" t="n">
+        <v>-1.76</v>
+      </c>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -5341,11 +5371,14 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
       </c>
+      <c r="AB67" t="n">
+        <v>37.19</v>
+      </c>
       <c r="AG67" t="b">
         <v>1</v>
       </c>
@@ -5410,11 +5443,14 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
       </c>
+      <c r="AB68" t="n">
+        <v>8.42</v>
+      </c>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -5479,11 +5515,14 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
       </c>
+      <c r="AB69" t="n">
+        <v>-5.94</v>
+      </c>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -5610,11 +5649,14 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
       </c>
+      <c r="AB71" t="n">
+        <v>19.4</v>
+      </c>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -5679,11 +5721,14 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
       </c>
+      <c r="AB72" t="n">
+        <v>10.07</v>
+      </c>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -5748,11 +5793,14 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA73" t="n">
         <v>5.81</v>
       </c>
+      <c r="AB73" t="n">
+        <v>12.61</v>
+      </c>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -5817,11 +5865,14 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
       </c>
+      <c r="AB74" t="n">
+        <v>-9</v>
+      </c>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -5886,7 +5937,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -5955,7 +6006,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -6024,7 +6075,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -6093,7 +6144,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6162,7 +6213,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6231,7 +6282,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6300,7 +6351,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -6369,7 +6420,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -6438,7 +6489,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -6507,7 +6558,7 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -6576,7 +6627,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -6645,7 +6696,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -6714,7 +6765,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -6783,7 +6834,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -6852,7 +6903,7 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA89" t="n">
         <v>4.2</v>
@@ -6983,7 +7034,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -7052,7 +7103,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -7121,7 +7172,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -7190,7 +7241,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -7259,7 +7310,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -7328,7 +7379,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -7397,7 +7448,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -7466,7 +7517,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -7535,7 +7586,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -7604,7 +7655,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -7673,7 +7724,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -7742,7 +7793,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -7811,7 +7862,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -7880,7 +7931,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -7949,7 +8000,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -8018,7 +8069,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -8087,7 +8138,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -8156,7 +8207,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -8225,7 +8276,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -8294,7 +8345,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -8363,7 +8414,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -8432,7 +8483,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA112" t="n">
         <v>-2.8</v>
@@ -8501,7 +8552,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
@@ -8570,7 +8621,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
@@ -8639,7 +8690,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
@@ -8708,7 +8759,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
@@ -8777,7 +8828,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
@@ -8846,7 +8897,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
@@ -8915,7 +8966,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
@@ -8984,7 +9035,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
@@ -9053,7 +9104,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
@@ -9122,7 +9173,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
@@ -9191,7 +9242,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
@@ -9260,7 +9311,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
@@ -9329,7 +9380,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
@@ -9398,7 +9449,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
@@ -9467,7 +9518,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
@@ -9536,7 +9587,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
@@ -9605,7 +9656,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA129" t="n">
         <v>-4.83</v>
@@ -9723,7 +9774,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
@@ -9841,7 +9892,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
@@ -9959,7 +10010,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
@@ -10077,7 +10128,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
@@ -10195,7 +10246,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
@@ -10313,7 +10364,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
@@ -10431,7 +10482,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
@@ -10546,7 +10597,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
@@ -10664,7 +10715,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
@@ -10782,7 +10833,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
@@ -10900,7 +10951,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
@@ -11018,7 +11069,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
@@ -11136,7 +11187,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
@@ -11254,7 +11305,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
@@ -11372,7 +11423,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
@@ -11490,7 +11541,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA145" t="n">
         <v>0.63</v>
@@ -11608,7 +11659,10 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>4.14</v>
       </c>
       <c r="AG146" t="b">
         <v>0</v>
@@ -11723,7 +11777,10 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>0.26</v>
       </c>
       <c r="AG147" t="b">
         <v>0</v>
@@ -11838,7 +11895,10 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>-0.14</v>
       </c>
       <c r="AG148" t="b">
         <v>0</v>
@@ -11953,7 +12013,10 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>12.25</v>
       </c>
       <c r="AG149" t="b">
         <v>0</v>
@@ -12068,7 +12131,10 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>-3.95</v>
       </c>
       <c r="AG150" t="b">
         <v>0</v>
@@ -12183,7 +12249,10 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>13.33</v>
       </c>
       <c r="AG151" t="b">
         <v>0</v>
@@ -12298,7 +12367,10 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>2.65</v>
       </c>
       <c r="AG152" t="b">
         <v>0</v>
@@ -12413,7 +12485,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG153" t="b">
         <v>0</v>
@@ -12528,7 +12600,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG154" t="b">
         <v>0</v>
@@ -12643,7 +12715,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG155" t="b">
         <v>0</v>
@@ -12758,7 +12830,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG156" t="b">
         <v>0</v>
@@ -12873,7 +12945,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG157" t="b">
         <v>0</v>
@@ -12988,7 +13060,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG158" t="b">
         <v>0</v>
@@ -13103,7 +13175,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG159" t="b">
         <v>0</v>
@@ -13218,7 +13290,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG160" t="b">
         <v>0</v>
@@ -13333,7 +13405,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG161" t="b">
         <v>0</v>
@@ -13448,7 +13520,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG162" t="b">
         <v>0</v>
@@ -13563,7 +13635,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG163" t="b">
         <v>0</v>
@@ -13678,7 +13750,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG164" t="b">
         <v>0</v>
@@ -13793,7 +13865,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG165" t="b">
         <v>1</v>
@@ -13908,7 +13980,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG166" t="b">
         <v>0</v>
@@ -14023,7 +14095,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG167" t="b">
         <v>0</v>
@@ -14249,7 +14321,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG169" t="b">
         <v>0</v>
@@ -14364,7 +14436,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG170" t="b">
         <v>0</v>
@@ -14479,7 +14551,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG171" t="b">
         <v>0</v>
@@ -14594,7 +14666,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG172" t="b">
         <v>0</v>
@@ -14709,7 +14781,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG173" t="b">
         <v>0</v>
@@ -14824,7 +14896,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG174" t="b">
         <v>0</v>
@@ -14939,7 +15011,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG175" t="b">
         <v>0</v>
@@ -15054,7 +15126,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG176" t="b">
         <v>0</v>
@@ -15169,7 +15241,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG177" t="b">
         <v>0</v>
@@ -15284,7 +15356,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG178" t="b">
         <v>0</v>
@@ -15510,7 +15582,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG180" t="b">
         <v>0</v>
@@ -15625,7 +15697,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG181" t="b">
         <v>0</v>
@@ -15740,7 +15812,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG182" t="b">
         <v>0</v>
@@ -15855,13 +15927,13 @@
         </is>
       </c>
       <c r="Z183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH183" t="b">
         <v>1</v>
-      </c>
-      <c r="AG183" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH183" t="b">
-        <v>0</v>
       </c>
       <c r="AI183" t="inlineStr">
         <is>
@@ -15970,7 +16042,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG184" t="b">
         <v>0</v>
@@ -16085,7 +16157,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG185" t="b">
         <v>0</v>
@@ -16200,7 +16272,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG186" t="b">
         <v>0</v>
@@ -16315,7 +16387,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG187" t="b">
         <v>0</v>
@@ -16430,7 +16502,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG188" t="b">
         <v>0</v>
@@ -16545,7 +16617,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG189" t="b">
         <v>0</v>
@@ -16660,7 +16732,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG190" t="b">
         <v>0</v>
@@ -16775,13 +16847,13 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AH191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI191" t="inlineStr">
         <is>
@@ -16890,7 +16962,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG192" t="b">
         <v>0</v>
@@ -17005,7 +17077,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG193" t="b">
         <v>0</v>
@@ -17120,7 +17192,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG194" t="b">
         <v>0</v>
@@ -17235,7 +17307,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG195" t="b">
         <v>0</v>
@@ -17350,7 +17422,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG196" t="b">
         <v>0</v>
@@ -17465,7 +17537,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG197" t="b">
         <v>0</v>
@@ -17802,7 +17874,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG200" t="b">
         <v>0</v>
@@ -17917,7 +17989,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG201" t="b">
         <v>0</v>
@@ -18032,7 +18104,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG202" t="b">
         <v>0</v>
@@ -18046,8 +18118,1729 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>70.38</v>
+      </c>
+      <c r="F203" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I203" t="b">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>10</v>
+      </c>
+      <c r="K203" t="n">
+        <v>43.34</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M203" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N203" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P203" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S203" t="n">
+        <v>7</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V203" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="W203" t="n">
+        <v>47.28</v>
+      </c>
+      <c r="X203" t="n">
+        <v>36.642</v>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>85.06999999999999</v>
+      </c>
+      <c r="F204" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I204" t="b">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="K204" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M204" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N204" t="n">
+        <v>3</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S204" t="n">
+        <v>7</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V204" t="n">
+        <v>307</v>
+      </c>
+      <c r="W204" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="X204" t="n">
+        <v>285.51</v>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>72.44</v>
+      </c>
+      <c r="F205" t="n">
+        <v>53.31</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I205" t="b">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>10</v>
+      </c>
+      <c r="K205" t="n">
+        <v>244.2</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M205" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N205" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S205" t="n">
+        <v>7</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V205" t="n">
+        <v>222</v>
+      </c>
+      <c r="W205" t="n">
+        <v>266.4</v>
+      </c>
+      <c r="X205" t="n">
+        <v>206.46</v>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>76.70999999999999</v>
+      </c>
+      <c r="F206" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I206" t="b">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K206" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M206" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N206" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S206" t="n">
+        <v>7</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V206" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="W206" t="n">
+        <v>49.14</v>
+      </c>
+      <c r="X206" t="n">
+        <v>38.0835</v>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="F207" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I207" t="b">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>10</v>
+      </c>
+      <c r="K207" t="n">
+        <v>1068.1</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M207" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N207" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>918.5</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>64.27</v>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S207" t="n">
+        <v>7</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V207" t="n">
+        <v>971</v>
+      </c>
+      <c r="W207" t="n">
+        <v>1165.2</v>
+      </c>
+      <c r="X207" t="n">
+        <v>903.03</v>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>77.69</v>
+      </c>
+      <c r="F208" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I208" t="b">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>10</v>
+      </c>
+      <c r="K208" t="n">
+        <v>756.8</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M208" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N208" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>676</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S208" t="n">
+        <v>7</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V208" t="n">
+        <v>688</v>
+      </c>
+      <c r="W208" t="n">
+        <v>825.6</v>
+      </c>
+      <c r="X208" t="n">
+        <v>639.84</v>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>77.19</v>
+      </c>
+      <c r="F209" t="n">
+        <v>53.77</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I209" t="b">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>10</v>
+      </c>
+      <c r="K209" t="n">
+        <v>568.7</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M209" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N209" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>513.5</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S209" t="n">
+        <v>7</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V209" t="n">
+        <v>517</v>
+      </c>
+      <c r="W209" t="n">
+        <v>620.4</v>
+      </c>
+      <c r="X209" t="n">
+        <v>480.81</v>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>73.09</v>
+      </c>
+      <c r="F210" t="n">
+        <v>63.62</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I210" t="b">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>10</v>
+      </c>
+      <c r="K210" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M210" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="N210" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>54.16</v>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S210" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V210" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="W210" t="n">
+        <v>44.0657</v>
+      </c>
+      <c r="X210" t="n">
+        <v>35.0737</v>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>76.44</v>
+      </c>
+      <c r="F211" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I211" t="b">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>10</v>
+      </c>
+      <c r="K211" t="n">
+        <v>1276</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M211" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N211" t="n">
+        <v>1</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>1086</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S211" t="n">
+        <v>7</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V211" t="n">
+        <v>1160</v>
+      </c>
+      <c r="W211" t="n">
+        <v>1392</v>
+      </c>
+      <c r="X211" t="n">
+        <v>1078.8</v>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>77.69</v>
+      </c>
+      <c r="F212" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I212" t="b">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>10</v>
+      </c>
+      <c r="K212" t="n">
+        <v>969.1</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M212" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N212" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>851.5</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S212" t="n">
+        <v>7</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V212" t="n">
+        <v>881</v>
+      </c>
+      <c r="W212" t="n">
+        <v>1057.2</v>
+      </c>
+      <c r="X212" t="n">
+        <v>819.33</v>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>75.58</v>
+      </c>
+      <c r="F213" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I213" t="b">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>10</v>
+      </c>
+      <c r="K213" t="n">
+        <v>1182.5</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M213" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N213" t="n">
+        <v>5</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>1020</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S213" t="n">
+        <v>7</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V213" t="n">
+        <v>1075</v>
+      </c>
+      <c r="W213" t="n">
+        <v>1290</v>
+      </c>
+      <c r="X213" t="n">
+        <v>999.75</v>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="F214" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I214" t="b">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>10</v>
+      </c>
+      <c r="K214" t="n">
+        <v>4356</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M214" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N214" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>4057.5</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>59.71</v>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S214" t="n">
+        <v>7</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V214" t="n">
+        <v>3960</v>
+      </c>
+      <c r="W214" t="n">
+        <v>4752</v>
+      </c>
+      <c r="X214" t="n">
+        <v>3682.8</v>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>藥華藥</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="F215" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I215" t="b">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>10</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1743.5</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M215" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N215" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>1465</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>58.88</v>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S215" t="n">
+        <v>7</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V215" t="n">
+        <v>1585</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1902</v>
+      </c>
+      <c r="X215" t="n">
+        <v>1474.05</v>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>6472</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>保瑞</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="F216" t="n">
+        <v>46.63</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I216" t="b">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>10</v>
+      </c>
+      <c r="K216" t="n">
+        <v>502.7</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M216" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N216" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>438</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>60.89</v>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S216" t="n">
+        <v>7</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V216" t="n">
+        <v>457</v>
+      </c>
+      <c r="W216" t="n">
+        <v>548.4</v>
+      </c>
+      <c r="X216" t="n">
+        <v>425.01</v>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>82.37</v>
+      </c>
+      <c r="F217" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I217" t="b">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>10</v>
+      </c>
+      <c r="K217" t="n">
+        <v>7463.5</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M217" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N217" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P217" t="n">
+        <v>6390</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>77.11</v>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S217" t="n">
+        <v>7</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V217" t="n">
+        <v>6785</v>
+      </c>
+      <c r="W217" t="n">
+        <v>8142</v>
+      </c>
+      <c r="X217" t="n">
+        <v>6310.05</v>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ202"/>
+  <autoFilter ref="A1:AJ217"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18297,7 +20090,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-25 14:23:08</t>
+          <t>2026-08-26 14:24:03</t>
         </is>
       </c>
     </row>
@@ -18344,7 +20137,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>201</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7">
@@ -18364,7 +20157,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>201</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$242</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ217"/>
+  <dimension ref="A1:AJ242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA37" t="n">
         <v>10.15</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -5658,7 +5658,7 @@
         <v>19.4</v>
       </c>
       <c r="AG71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH71" t="b">
         <v>0</v>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA73" t="n">
         <v>5.81</v>
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -5937,11 +5937,14 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
       </c>
+      <c r="AB75" t="n">
+        <v>6.94</v>
+      </c>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -6006,11 +6009,14 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
       </c>
+      <c r="AB76" t="n">
+        <v>0.68</v>
+      </c>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -6075,11 +6081,14 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
       </c>
+      <c r="AB77" t="n">
+        <v>11.69</v>
+      </c>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -6144,11 +6153,14 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
       </c>
+      <c r="AB78" t="n">
+        <v>-12.33</v>
+      </c>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -6213,11 +6225,14 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
       </c>
+      <c r="AB79" t="n">
+        <v>-3.3</v>
+      </c>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -6282,11 +6297,14 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
       </c>
+      <c r="AB80" t="n">
+        <v>5.25</v>
+      </c>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -6351,11 +6369,14 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
       </c>
+      <c r="AB81" t="n">
+        <v>7.89</v>
+      </c>
       <c r="AG81" t="b">
         <v>1</v>
       </c>
@@ -6420,11 +6441,14 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
       </c>
+      <c r="AB82" t="n">
+        <v>29.71</v>
+      </c>
       <c r="AG82" t="b">
         <v>1</v>
       </c>
@@ -6489,11 +6513,14 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
       </c>
+      <c r="AB83" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -6558,11 +6585,14 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
       </c>
+      <c r="AB84" t="n">
+        <v>48.39</v>
+      </c>
       <c r="AG84" t="b">
         <v>1</v>
       </c>
@@ -6627,11 +6657,14 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
       </c>
+      <c r="AB85" t="n">
+        <v>-8.880000000000001</v>
+      </c>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -6696,11 +6729,14 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
       </c>
+      <c r="AB86" t="n">
+        <v>6.86</v>
+      </c>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -6765,11 +6801,14 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
       </c>
+      <c r="AB87" t="n">
+        <v>-7.64</v>
+      </c>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -6834,11 +6873,14 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
       </c>
+      <c r="AB88" t="n">
+        <v>7.96</v>
+      </c>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -6903,11 +6945,14 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA89" t="n">
         <v>4.2</v>
       </c>
+      <c r="AB89" t="n">
+        <v>12.27</v>
+      </c>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -7034,11 +7079,14 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
       </c>
+      <c r="AB91" t="n">
+        <v>0</v>
+      </c>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -7103,7 +7151,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -7172,7 +7220,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -7241,7 +7289,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -7310,7 +7358,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -7379,7 +7427,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -7448,7 +7496,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -7517,7 +7565,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -7586,7 +7634,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -7655,7 +7703,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -7724,7 +7772,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -7793,7 +7841,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -7862,7 +7910,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -7931,7 +7979,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -8000,7 +8048,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -8069,7 +8117,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -8138,7 +8186,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -8207,7 +8255,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -8276,7 +8324,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -8345,7 +8393,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -8414,7 +8462,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -8483,7 +8531,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA112" t="n">
         <v>-2.8</v>
@@ -8552,7 +8600,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
@@ -8621,7 +8669,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
@@ -8690,7 +8738,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
@@ -8759,7 +8807,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
@@ -8828,7 +8876,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
@@ -8897,7 +8945,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
@@ -8966,7 +9014,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
@@ -9035,7 +9083,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
@@ -9104,7 +9152,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
@@ -9173,7 +9221,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
@@ -9242,7 +9290,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
@@ -9311,7 +9359,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
@@ -9380,7 +9428,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
@@ -9449,7 +9497,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
@@ -9518,7 +9566,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
@@ -9587,7 +9635,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
@@ -9656,7 +9704,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA129" t="n">
         <v>-4.83</v>
@@ -9774,7 +9822,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
@@ -9892,7 +9940,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
@@ -10010,7 +10058,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
@@ -10128,7 +10176,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
@@ -10246,7 +10294,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
@@ -10364,7 +10412,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
@@ -10482,7 +10530,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
@@ -10597,7 +10645,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
@@ -10715,7 +10763,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
@@ -10833,7 +10881,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
@@ -10951,13 +10999,13 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="AG140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH140" t="b">
         <v>0</v>
@@ -11069,7 +11117,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
@@ -11187,7 +11235,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
@@ -11305,7 +11353,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
@@ -11423,7 +11471,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
@@ -11541,7 +11589,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA145" t="n">
         <v>0.63</v>
@@ -11659,7 +11707,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
@@ -11777,7 +11825,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
@@ -11895,7 +11943,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
@@ -12013,7 +12061,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
@@ -12131,7 +12179,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
@@ -12249,13 +12297,13 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
       </c>
       <c r="AG151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH151" t="b">
         <v>0</v>
@@ -12367,7 +12415,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
@@ -12485,7 +12533,10 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>-2.82</v>
       </c>
       <c r="AG153" t="b">
         <v>0</v>
@@ -12600,7 +12651,10 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>1.15</v>
       </c>
       <c r="AG154" t="b">
         <v>0</v>
@@ -12715,7 +12769,10 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>-1.41</v>
       </c>
       <c r="AG155" t="b">
         <v>0</v>
@@ -12830,7 +12887,10 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>-2.74</v>
       </c>
       <c r="AG156" t="b">
         <v>0</v>
@@ -12945,7 +13005,10 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>5.91</v>
       </c>
       <c r="AG157" t="b">
         <v>0</v>
@@ -13060,7 +13123,10 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>-1.91</v>
       </c>
       <c r="AG158" t="b">
         <v>0</v>
@@ -13175,7 +13241,10 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>11.07</v>
       </c>
       <c r="AG159" t="b">
         <v>0</v>
@@ -13290,7 +13359,10 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>-8.1</v>
       </c>
       <c r="AG160" t="b">
         <v>0</v>
@@ -13405,7 +13477,10 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>-1.03</v>
       </c>
       <c r="AG161" t="b">
         <v>0</v>
@@ -13520,7 +13595,10 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>4.64</v>
       </c>
       <c r="AG162" t="b">
         <v>0</v>
@@ -13635,13 +13713,16 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>-4.52</v>
       </c>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AH163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI163" t="inlineStr">
         <is>
@@ -13750,7 +13831,10 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>-3.02</v>
       </c>
       <c r="AG164" t="b">
         <v>0</v>
@@ -13865,7 +13949,10 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>5.09</v>
       </c>
       <c r="AG165" t="b">
         <v>1</v>
@@ -13980,10 +14067,13 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>25.39</v>
       </c>
       <c r="AG166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH166" t="b">
         <v>0</v>
@@ -14095,7 +14185,10 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>3.51</v>
       </c>
       <c r="AG167" t="b">
         <v>0</v>
@@ -14321,7 +14414,10 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>7.4</v>
       </c>
       <c r="AG169" t="b">
         <v>0</v>
@@ -14436,7 +14532,10 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>5.15</v>
       </c>
       <c r="AG170" t="b">
         <v>0</v>
@@ -14551,7 +14650,10 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>7.75</v>
       </c>
       <c r="AG171" t="b">
         <v>0</v>
@@ -14666,7 +14768,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG172" t="b">
         <v>0</v>
@@ -14781,7 +14883,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG173" t="b">
         <v>0</v>
@@ -14896,13 +14998,13 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AH174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
@@ -15011,7 +15113,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG175" t="b">
         <v>0</v>
@@ -15126,7 +15228,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG176" t="b">
         <v>0</v>
@@ -15241,7 +15343,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG177" t="b">
         <v>0</v>
@@ -15356,10 +15458,10 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH178" t="b">
         <v>0</v>
@@ -15582,7 +15684,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG180" t="b">
         <v>0</v>
@@ -15697,7 +15799,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG181" t="b">
         <v>0</v>
@@ -15812,7 +15914,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG182" t="b">
         <v>0</v>
@@ -15927,7 +16029,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG183" t="b">
         <v>0</v>
@@ -16042,10 +16144,10 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH184" t="b">
         <v>0</v>
@@ -16157,7 +16259,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG185" t="b">
         <v>0</v>
@@ -16272,7 +16374,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG186" t="b">
         <v>0</v>
@@ -16387,7 +16489,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG187" t="b">
         <v>0</v>
@@ -16502,7 +16604,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG188" t="b">
         <v>0</v>
@@ -16617,7 +16719,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG189" t="b">
         <v>0</v>
@@ -16732,7 +16834,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG190" t="b">
         <v>0</v>
@@ -16847,7 +16949,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG191" t="b">
         <v>0</v>
@@ -16962,7 +17064,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG192" t="b">
         <v>0</v>
@@ -17077,7 +17179,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG193" t="b">
         <v>0</v>
@@ -17192,7 +17294,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG194" t="b">
         <v>0</v>
@@ -17307,7 +17409,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG195" t="b">
         <v>0</v>
@@ -17422,10 +17524,10 @@
         </is>
       </c>
       <c r="Z196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG196" t="b">
         <v>1</v>
-      </c>
-      <c r="AG196" t="b">
-        <v>0</v>
       </c>
       <c r="AH196" t="b">
         <v>0</v>
@@ -17537,7 +17639,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG197" t="b">
         <v>0</v>
@@ -17874,7 +17976,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG200" t="b">
         <v>0</v>
@@ -17989,7 +18091,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG201" t="b">
         <v>0</v>
@@ -18104,7 +18206,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG202" t="b">
         <v>0</v>
@@ -18219,7 +18321,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG203" t="b">
         <v>0</v>
@@ -18334,7 +18436,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG204" t="b">
         <v>0</v>
@@ -18449,7 +18551,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG205" t="b">
         <v>0</v>
@@ -18564,7 +18666,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG206" t="b">
         <v>0</v>
@@ -18679,7 +18781,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG207" t="b">
         <v>0</v>
@@ -18794,7 +18896,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG208" t="b">
         <v>0</v>
@@ -18909,7 +19011,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG209" t="b">
         <v>0</v>
@@ -19024,7 +19126,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG210" t="b">
         <v>0</v>
@@ -19139,7 +19241,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG211" t="b">
         <v>0</v>
@@ -19254,7 +19356,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG212" t="b">
         <v>0</v>
@@ -19480,7 +19582,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG214" t="b">
         <v>0</v>
@@ -19595,7 +19697,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG215" t="b">
         <v>0</v>
@@ -19710,7 +19812,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG216" t="b">
         <v>0</v>
@@ -19825,7 +19927,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG217" t="b">
         <v>0</v>
@@ -19839,8 +19941,2871 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>77.64</v>
+      </c>
+      <c r="F218" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I218" t="b">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>10</v>
+      </c>
+      <c r="K218" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M218" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N218" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>70.47</v>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S218" t="n">
+        <v>7</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V218" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="W218" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="X218" t="n">
+        <v>58.683</v>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>82.47</v>
+      </c>
+      <c r="F219" t="n">
+        <v>68.93000000000001</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I219" t="b">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>10</v>
+      </c>
+      <c r="K219" t="n">
+        <v>80.73999999999999</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M219" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N219" t="n">
+        <v>10</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>52.88</v>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S219" t="n">
+        <v>5.3801</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V219" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="W219" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="X219" t="n">
+        <v>69.45099999999999</v>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>78.06</v>
+      </c>
+      <c r="F220" t="n">
+        <v>52.28</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I220" t="b">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>10</v>
+      </c>
+      <c r="K220" t="n">
+        <v>847</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M220" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N220" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>737</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>65.17</v>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S220" t="n">
+        <v>7</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="V220" t="n">
+        <v>770</v>
+      </c>
+      <c r="W220" t="n">
+        <v>924</v>
+      </c>
+      <c r="X220" t="n">
+        <v>716.1</v>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="F221" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I221" t="b">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>10</v>
+      </c>
+      <c r="K221" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M221" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N221" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S221" t="n">
+        <v>7</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V221" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="W221" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="X221" t="n">
+        <v>36.177</v>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="F222" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I222" t="b">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>10</v>
+      </c>
+      <c r="K222" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M222" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N222" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S222" t="n">
+        <v>7</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V222" t="n">
+        <v>301</v>
+      </c>
+      <c r="W222" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="X222" t="n">
+        <v>279.93</v>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>70.34</v>
+      </c>
+      <c r="F223" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I223" t="b">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K223" t="n">
+        <v>43.73</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M223" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N223" t="n">
+        <v>8</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S223" t="n">
+        <v>5.1308</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V223" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="W223" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="X223" t="n">
+        <v>37.7105</v>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>74.48999999999999</v>
+      </c>
+      <c r="F224" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I224" t="b">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>10</v>
+      </c>
+      <c r="K224" t="n">
+        <v>1064.8</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M224" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N224" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>928</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>62.78</v>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S224" t="n">
+        <v>7</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V224" t="n">
+        <v>968</v>
+      </c>
+      <c r="W224" t="n">
+        <v>1161.6</v>
+      </c>
+      <c r="X224" t="n">
+        <v>900.24</v>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>70.28</v>
+      </c>
+      <c r="F225" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I225" t="b">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>10</v>
+      </c>
+      <c r="K225" t="n">
+        <v>1133</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M225" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N225" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>1012.5</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S225" t="n">
+        <v>7</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V225" t="n">
+        <v>1030</v>
+      </c>
+      <c r="W225" t="n">
+        <v>1236</v>
+      </c>
+      <c r="X225" t="n">
+        <v>957.9</v>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>74.45</v>
+      </c>
+      <c r="F226" t="n">
+        <v>72.36</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I226" t="b">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>10</v>
+      </c>
+      <c r="K226" t="n">
+        <v>742.5</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M226" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N226" t="n">
+        <v>10</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>676</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S226" t="n">
+        <v>5.217</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V226" t="n">
+        <v>675</v>
+      </c>
+      <c r="W226" t="n">
+        <v>810</v>
+      </c>
+      <c r="X226" t="n">
+        <v>639.785</v>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="F227" t="n">
+        <v>53.62</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I227" t="b">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>10</v>
+      </c>
+      <c r="K227" t="n">
+        <v>595.1</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M227" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N227" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>517.5</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>60.82</v>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S227" t="n">
+        <v>7</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V227" t="n">
+        <v>541</v>
+      </c>
+      <c r="W227" t="n">
+        <v>649.2</v>
+      </c>
+      <c r="X227" t="n">
+        <v>503.13</v>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="F228" t="n">
+        <v>37.36</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I228" t="b">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="K228" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M228" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N228" t="n">
+        <v>5</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S228" t="n">
+        <v>7</v>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V228" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="W228" t="n">
+        <v>169.8</v>
+      </c>
+      <c r="X228" t="n">
+        <v>131.595</v>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>晶豪科</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>70.48999999999999</v>
+      </c>
+      <c r="F229" t="n">
+        <v>53.81</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I229" t="b">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>10</v>
+      </c>
+      <c r="K229" t="n">
+        <v>301.4</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M229" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N229" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>260.75</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S229" t="n">
+        <v>7</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V229" t="n">
+        <v>274</v>
+      </c>
+      <c r="W229" t="n">
+        <v>328.8</v>
+      </c>
+      <c r="X229" t="n">
+        <v>254.82</v>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>76.76000000000001</v>
+      </c>
+      <c r="F230" t="n">
+        <v>43.67</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I230" t="b">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>10</v>
+      </c>
+      <c r="K230" t="n">
+        <v>3674</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M230" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N230" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>3089.38</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>54.48</v>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S230" t="n">
+        <v>7</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V230" t="n">
+        <v>3340</v>
+      </c>
+      <c r="W230" t="n">
+        <v>4008</v>
+      </c>
+      <c r="X230" t="n">
+        <v>3106.2</v>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>79.27</v>
+      </c>
+      <c r="F231" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I231" t="b">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>10</v>
+      </c>
+      <c r="K231" t="n">
+        <v>1298</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M231" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N231" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>1090.5</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>61.09</v>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S231" t="n">
+        <v>7</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V231" t="n">
+        <v>1180</v>
+      </c>
+      <c r="W231" t="n">
+        <v>1416</v>
+      </c>
+      <c r="X231" t="n">
+        <v>1097.4</v>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>79.44</v>
+      </c>
+      <c r="F232" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I232" t="b">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>10</v>
+      </c>
+      <c r="K232" t="n">
+        <v>3707</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M232" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N232" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>2990</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>54.05</v>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S232" t="n">
+        <v>7</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V232" t="n">
+        <v>3370</v>
+      </c>
+      <c r="W232" t="n">
+        <v>4044</v>
+      </c>
+      <c r="X232" t="n">
+        <v>3134.1</v>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="F233" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I233" t="b">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>10</v>
+      </c>
+      <c r="K233" t="n">
+        <v>1005.4</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M233" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N233" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>863</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S233" t="n">
+        <v>7</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V233" t="n">
+        <v>914</v>
+      </c>
+      <c r="W233" t="n">
+        <v>1096.8</v>
+      </c>
+      <c r="X233" t="n">
+        <v>850.02</v>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>76.39</v>
+      </c>
+      <c r="F234" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I234" t="b">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K234" t="n">
+        <v>1105</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M234" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N234" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>1037.5</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S234" t="n">
+        <v>7</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V234" t="n">
+        <v>1060</v>
+      </c>
+      <c r="W234" t="n">
+        <v>1272</v>
+      </c>
+      <c r="X234" t="n">
+        <v>985.8</v>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>75.38</v>
+      </c>
+      <c r="F235" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I235" t="b">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>10</v>
+      </c>
+      <c r="K235" t="n">
+        <v>386.1</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M235" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N235" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>325.25</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S235" t="n">
+        <v>7</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V235" t="n">
+        <v>351</v>
+      </c>
+      <c r="W235" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="X235" t="n">
+        <v>326.43</v>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>78.63</v>
+      </c>
+      <c r="F236" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I236" t="b">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>10</v>
+      </c>
+      <c r="K236" t="n">
+        <v>6512</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M236" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N236" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>5657.5</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>60.47</v>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S236" t="n">
+        <v>7</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V236" t="n">
+        <v>5920</v>
+      </c>
+      <c r="W236" t="n">
+        <v>7104</v>
+      </c>
+      <c r="X236" t="n">
+        <v>5505.6</v>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>74.05</v>
+      </c>
+      <c r="F237" t="n">
+        <v>41.97</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I237" t="b">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>10</v>
+      </c>
+      <c r="K237" t="n">
+        <v>433.4</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M237" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N237" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S237" t="n">
+        <v>7</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V237" t="n">
+        <v>394</v>
+      </c>
+      <c r="W237" t="n">
+        <v>472.8</v>
+      </c>
+      <c r="X237" t="n">
+        <v>366.42</v>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>辛耘</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="F238" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I238" t="b">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>10</v>
+      </c>
+      <c r="K238" t="n">
+        <v>836</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M238" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N238" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>714.5</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S238" t="n">
+        <v>7</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V238" t="n">
+        <v>760</v>
+      </c>
+      <c r="W238" t="n">
+        <v>912</v>
+      </c>
+      <c r="X238" t="n">
+        <v>706.8</v>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>藥華藥</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="F239" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I239" t="b">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>10</v>
+      </c>
+      <c r="K239" t="n">
+        <v>1716</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M239" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N239" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>1492.5</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S239" t="n">
+        <v>7</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V239" t="n">
+        <v>1560</v>
+      </c>
+      <c r="W239" t="n">
+        <v>1872</v>
+      </c>
+      <c r="X239" t="n">
+        <v>1450.8</v>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>6472</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>保瑞</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="F240" t="n">
+        <v>53.41</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I240" t="b">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
+        <v>10</v>
+      </c>
+      <c r="K240" t="n">
+        <v>483.45</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M240" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N240" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P240" t="n">
+        <v>438</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S240" t="n">
+        <v>7</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V240" t="n">
+        <v>439.5</v>
+      </c>
+      <c r="W240" t="n">
+        <v>527.4</v>
+      </c>
+      <c r="X240" t="n">
+        <v>408.735</v>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>81.37</v>
+      </c>
+      <c r="F241" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I241" t="b">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
+        <v>10</v>
+      </c>
+      <c r="K241" t="n">
+        <v>7496.5</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M241" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N241" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>6430</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S241" t="n">
+        <v>7</v>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V241" t="n">
+        <v>6815</v>
+      </c>
+      <c r="W241" t="n">
+        <v>8178</v>
+      </c>
+      <c r="X241" t="n">
+        <v>6337.95</v>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>9921</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>巨大</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="F242" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I242" t="b">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>10</v>
+      </c>
+      <c r="K242" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M242" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N242" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>102.53</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S242" t="n">
+        <v>7</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V242" t="n">
+        <v>105</v>
+      </c>
+      <c r="W242" t="n">
+        <v>126</v>
+      </c>
+      <c r="X242" t="n">
+        <v>97.65000000000001</v>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ217"/>
+  <autoFilter ref="A1:AJ242"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20090,7 +23055,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26 14:24:03</t>
+          <t>2026-08-27 14:24:27</t>
         </is>
       </c>
     </row>
@@ -20137,7 +23102,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>216</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7">
@@ -20157,7 +23122,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>216</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$268</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ242"/>
+  <dimension ref="A1:AJ268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
@@ -739,6 +739,9 @@
       <c r="AB2" t="n">
         <v>10.36</v>
       </c>
+      <c r="AC2" t="n">
+        <v>2.18</v>
+      </c>
       <c r="AG2" t="b">
         <v>1</v>
       </c>
@@ -803,7 +806,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
@@ -811,6 +814,9 @@
       <c r="AB3" t="n">
         <v>-7.12</v>
       </c>
+      <c r="AC3" t="n">
+        <v>-8.41</v>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -875,7 +881,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
@@ -883,6 +889,9 @@
       <c r="AB4" t="n">
         <v>12.73</v>
       </c>
+      <c r="AC4" t="n">
+        <v>18.12</v>
+      </c>
       <c r="AG4" t="b">
         <v>1</v>
       </c>
@@ -947,7 +956,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
@@ -955,6 +964,9 @@
       <c r="AB5" t="n">
         <v>-7.52</v>
       </c>
+      <c r="AC5" t="n">
+        <v>-5.23</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1019,7 +1031,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
@@ -1027,6 +1039,9 @@
       <c r="AB6" t="n">
         <v>2.37</v>
       </c>
+      <c r="AC6" t="n">
+        <v>5.52</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1091,7 +1106,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
@@ -1099,6 +1114,9 @@
       <c r="AB7" t="n">
         <v>21.2</v>
       </c>
+      <c r="AC7" t="n">
+        <v>11.57</v>
+      </c>
       <c r="AG7" t="b">
         <v>1</v>
       </c>
@@ -1163,7 +1181,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
@@ -1171,6 +1189,9 @@
       <c r="AB8" t="n">
         <v>-9.33</v>
       </c>
+      <c r="AC8" t="n">
+        <v>-9.56</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1235,7 +1256,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
@@ -1243,6 +1264,9 @@
       <c r="AB9" t="n">
         <v>-4.05</v>
       </c>
+      <c r="AC9" t="n">
+        <v>-5.86</v>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1307,7 +1331,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
@@ -1315,6 +1339,9 @@
       <c r="AB10" t="n">
         <v>-10.81</v>
       </c>
+      <c r="AC10" t="n">
+        <v>-9.35</v>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1379,7 +1406,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
@@ -1387,6 +1414,9 @@
       <c r="AB11" t="n">
         <v>-7.76</v>
       </c>
+      <c r="AC11" t="n">
+        <v>-5.3</v>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1451,7 +1481,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
@@ -1459,6 +1489,9 @@
       <c r="AB12" t="n">
         <v>27.94</v>
       </c>
+      <c r="AC12" t="n">
+        <v>61.12</v>
+      </c>
       <c r="AG12" t="b">
         <v>1</v>
       </c>
@@ -1523,7 +1556,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
@@ -1531,6 +1564,9 @@
       <c r="AB13" t="n">
         <v>-2.21</v>
       </c>
+      <c r="AC13" t="n">
+        <v>0.55</v>
+      </c>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1657,7 +1693,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
@@ -1665,6 +1701,9 @@
       <c r="AB15" t="n">
         <v>8.66</v>
       </c>
+      <c r="AC15" t="n">
+        <v>2.85</v>
+      </c>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -1729,7 +1768,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
@@ -1737,6 +1776,9 @@
       <c r="AB16" t="n">
         <v>16.34</v>
       </c>
+      <c r="AC16" t="n">
+        <v>11.47</v>
+      </c>
       <c r="AG16" t="b">
         <v>1</v>
       </c>
@@ -1801,7 +1843,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1873,7 +1915,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -1945,7 +1987,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -2017,7 +2059,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -2089,7 +2131,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2161,7 +2203,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2233,7 +2275,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2305,7 +2347,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2377,7 +2419,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
@@ -2449,7 +2491,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
@@ -2521,7 +2563,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2593,7 +2635,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2665,7 +2707,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2737,7 +2779,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2809,7 +2851,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -2881,7 +2923,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -2953,7 +2995,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3149,7 +3191,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3221,7 +3263,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA37" t="n">
         <v>10.15</v>
@@ -3230,7 +3272,7 @@
         <v>4.83</v>
       </c>
       <c r="AG37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH37" t="b">
         <v>0</v>
@@ -3293,7 +3335,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3365,7 +3407,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3437,7 +3479,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3509,7 +3551,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3581,7 +3623,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3653,7 +3695,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3725,7 +3767,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -3797,7 +3839,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -3869,7 +3911,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -3941,7 +3983,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -4013,7 +4055,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -4085,7 +4127,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4157,7 +4199,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4229,7 +4271,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4301,7 +4343,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4373,7 +4415,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4445,7 +4487,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4579,7 +4621,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4651,7 +4693,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -4723,7 +4765,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -4795,7 +4837,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -4867,7 +4909,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -4939,7 +4981,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -5011,7 +5053,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -5083,7 +5125,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -5155,7 +5197,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5227,7 +5269,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5299,7 +5341,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5371,7 +5413,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5443,7 +5485,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -5515,7 +5557,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -5649,7 +5691,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -5721,7 +5763,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -5793,7 +5835,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA73" t="n">
         <v>5.81</v>
@@ -5802,7 +5844,7 @@
         <v>12.61</v>
       </c>
       <c r="AG73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH73" t="b">
         <v>0</v>
@@ -5865,7 +5907,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -5937,7 +5979,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -6009,7 +6051,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -6081,7 +6123,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -6153,7 +6195,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6225,7 +6267,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6297,7 +6339,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6369,7 +6411,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -6441,7 +6483,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -6513,7 +6555,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -6585,7 +6627,7 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -6657,7 +6699,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -6729,7 +6771,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -6801,7 +6843,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -6873,7 +6915,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -6945,7 +6987,7 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA89" t="n">
         <v>4.2</v>
@@ -7079,7 +7121,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -7151,11 +7193,14 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
       </c>
+      <c r="AB92" t="n">
+        <v>6.34</v>
+      </c>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -7220,11 +7265,14 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
       </c>
+      <c r="AB93" t="n">
+        <v>-3.08</v>
+      </c>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -7289,13 +7337,16 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
       </c>
+      <c r="AB94" t="n">
+        <v>18.91</v>
+      </c>
       <c r="AG94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH94" t="b">
         <v>0</v>
@@ -7358,11 +7409,14 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
       </c>
+      <c r="AB95" t="n">
+        <v>-12.2</v>
+      </c>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -7427,11 +7481,14 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
       </c>
+      <c r="AB96" t="n">
+        <v>-8.81</v>
+      </c>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -7496,11 +7553,14 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
       </c>
+      <c r="AB97" t="n">
+        <v>-10.95</v>
+      </c>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -7565,11 +7625,14 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
       </c>
+      <c r="AB98" t="n">
+        <v>5.47</v>
+      </c>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -7634,11 +7697,14 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
       </c>
+      <c r="AB99" t="n">
+        <v>-5.34</v>
+      </c>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -7703,11 +7769,14 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
       </c>
+      <c r="AB100" t="n">
+        <v>5.71</v>
+      </c>
       <c r="AG100" t="b">
         <v>1</v>
       </c>
@@ -7772,11 +7841,14 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
       </c>
+      <c r="AB101" t="n">
+        <v>8.91</v>
+      </c>
       <c r="AG101" t="b">
         <v>1</v>
       </c>
@@ -7841,11 +7913,14 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
       </c>
+      <c r="AB102" t="n">
+        <v>23.07</v>
+      </c>
       <c r="AG102" t="b">
         <v>1</v>
       </c>
@@ -7910,11 +7985,14 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
       </c>
+      <c r="AB103" t="n">
+        <v>3.48</v>
+      </c>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -7979,11 +8057,14 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
       </c>
+      <c r="AB104" t="n">
+        <v>-0.66</v>
+      </c>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -8048,11 +8129,14 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
       </c>
+      <c r="AB105" t="n">
+        <v>53.25</v>
+      </c>
       <c r="AG105" t="b">
         <v>1</v>
       </c>
@@ -8117,11 +8201,14 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
       </c>
+      <c r="AB106" t="n">
+        <v>3.86</v>
+      </c>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -8186,13 +8273,16 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
       </c>
+      <c r="AB107" t="n">
+        <v>8.82</v>
+      </c>
       <c r="AG107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH107" t="b">
         <v>0</v>
@@ -8255,11 +8345,14 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
       </c>
+      <c r="AB108" t="n">
+        <v>4.29</v>
+      </c>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -8324,11 +8417,14 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
       </c>
+      <c r="AB109" t="n">
+        <v>-8.01</v>
+      </c>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -8393,11 +8489,14 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
       </c>
+      <c r="AB110" t="n">
+        <v>10.06</v>
+      </c>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -8462,11 +8561,14 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
       </c>
+      <c r="AB111" t="n">
+        <v>3</v>
+      </c>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -8531,11 +8633,14 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA112" t="n">
         <v>-2.8</v>
       </c>
+      <c r="AB112" t="n">
+        <v>11.89</v>
+      </c>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -8600,7 +8705,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
@@ -8669,7 +8774,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
@@ -8738,7 +8843,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
@@ -8807,13 +8912,13 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
       </c>
       <c r="AG116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH116" t="b">
         <v>0</v>
@@ -8876,7 +8981,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
@@ -8945,7 +9050,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
@@ -9014,7 +9119,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
@@ -9083,7 +9188,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
@@ -9152,7 +9257,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
@@ -9221,7 +9326,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
@@ -9290,7 +9395,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
@@ -9359,7 +9464,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
@@ -9428,7 +9533,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
@@ -9497,7 +9602,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
@@ -9566,7 +9671,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
@@ -9635,7 +9740,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
@@ -9704,7 +9809,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA129" t="n">
         <v>-4.83</v>
@@ -9822,7 +9927,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
@@ -9940,7 +10045,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
@@ -10058,7 +10163,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
@@ -10176,7 +10281,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
@@ -10294,7 +10399,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
@@ -10412,7 +10517,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
@@ -10530,7 +10635,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
@@ -10645,7 +10750,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
@@ -10763,7 +10868,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
@@ -10881,7 +10986,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
@@ -10999,7 +11104,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
@@ -11117,7 +11222,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
@@ -11235,7 +11340,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
@@ -11353,7 +11458,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
@@ -11471,7 +11576,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
@@ -11589,7 +11694,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA145" t="n">
         <v>0.63</v>
@@ -11707,7 +11812,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
@@ -11825,7 +11930,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
@@ -11943,7 +12048,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
@@ -12061,7 +12166,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
@@ -12179,7 +12284,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
@@ -12297,7 +12402,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
@@ -12415,7 +12520,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
@@ -12533,7 +12638,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
@@ -12651,7 +12756,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
@@ -12769,7 +12874,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
@@ -12887,7 +12992,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
@@ -13005,7 +13110,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
@@ -13123,7 +13228,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
@@ -13241,7 +13346,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
@@ -13359,7 +13464,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
@@ -13477,7 +13582,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
@@ -13595,7 +13700,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
@@ -13713,7 +13818,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
@@ -13831,7 +13936,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
@@ -13949,7 +14054,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
@@ -14067,7 +14172,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
@@ -14185,7 +14290,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
@@ -14414,7 +14519,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
@@ -14532,7 +14637,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
@@ -14650,7 +14755,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA171" t="n">
         <v>7.75</v>
@@ -14768,7 +14873,10 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>-2.21</v>
       </c>
       <c r="AG172" t="b">
         <v>0</v>
@@ -14883,7 +14991,10 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>-1.14</v>
       </c>
       <c r="AG173" t="b">
         <v>0</v>
@@ -14998,7 +15109,10 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>-7.41</v>
       </c>
       <c r="AG174" t="b">
         <v>0</v>
@@ -15113,7 +15227,10 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>2.27</v>
       </c>
       <c r="AG175" t="b">
         <v>0</v>
@@ -15228,7 +15345,10 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>7.46</v>
       </c>
       <c r="AG176" t="b">
         <v>0</v>
@@ -15343,7 +15463,10 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>0.67</v>
       </c>
       <c r="AG177" t="b">
         <v>0</v>
@@ -15458,7 +15581,10 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>25.94</v>
       </c>
       <c r="AG178" t="b">
         <v>1</v>
@@ -15684,7 +15810,10 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>7.41</v>
       </c>
       <c r="AG180" t="b">
         <v>0</v>
@@ -15799,7 +15928,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG181" t="b">
         <v>0</v>
@@ -15914,7 +16043,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG182" t="b">
         <v>0</v>
@@ -16029,7 +16158,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG183" t="b">
         <v>0</v>
@@ -16144,7 +16273,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG184" t="b">
         <v>1</v>
@@ -16259,7 +16388,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG185" t="b">
         <v>0</v>
@@ -16374,7 +16503,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG186" t="b">
         <v>0</v>
@@ -16489,7 +16618,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG187" t="b">
         <v>0</v>
@@ -16604,7 +16733,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG188" t="b">
         <v>0</v>
@@ -16719,7 +16848,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG189" t="b">
         <v>0</v>
@@ -16834,7 +16963,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG190" t="b">
         <v>0</v>
@@ -16949,7 +17078,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG191" t="b">
         <v>0</v>
@@ -17064,7 +17193,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG192" t="b">
         <v>0</v>
@@ -17179,7 +17308,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG193" t="b">
         <v>0</v>
@@ -17294,7 +17423,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG194" t="b">
         <v>0</v>
@@ -17409,7 +17538,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG195" t="b">
         <v>0</v>
@@ -17524,7 +17653,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG196" t="b">
         <v>1</v>
@@ -17639,7 +17768,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG197" t="b">
         <v>0</v>
@@ -17976,7 +18105,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG200" t="b">
         <v>0</v>
@@ -18091,7 +18220,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG201" t="b">
         <v>0</v>
@@ -18206,7 +18335,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG202" t="b">
         <v>0</v>
@@ -18321,7 +18450,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG203" t="b">
         <v>0</v>
@@ -18436,7 +18565,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG204" t="b">
         <v>0</v>
@@ -18551,7 +18680,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG205" t="b">
         <v>0</v>
@@ -18666,7 +18795,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG206" t="b">
         <v>0</v>
@@ -18781,7 +18910,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG207" t="b">
         <v>0</v>
@@ -18896,7 +19025,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG208" t="b">
         <v>0</v>
@@ -19011,7 +19140,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG209" t="b">
         <v>0</v>
@@ -19126,7 +19255,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG210" t="b">
         <v>0</v>
@@ -19241,13 +19370,13 @@
         </is>
       </c>
       <c r="Z211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH211" t="b">
         <v>1</v>
-      </c>
-      <c r="AG211" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH211" t="b">
-        <v>0</v>
       </c>
       <c r="AI211" t="inlineStr">
         <is>
@@ -19356,7 +19485,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG212" t="b">
         <v>0</v>
@@ -19582,7 +19711,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG214" t="b">
         <v>0</v>
@@ -19697,7 +19826,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG215" t="b">
         <v>0</v>
@@ -19812,7 +19941,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG216" t="b">
         <v>0</v>
@@ -19927,7 +20056,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG217" t="b">
         <v>0</v>
@@ -20042,7 +20171,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG218" t="b">
         <v>0</v>
@@ -20157,7 +20286,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG219" t="b">
         <v>0</v>
@@ -20272,7 +20401,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG220" t="b">
         <v>0</v>
@@ -20387,7 +20516,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG221" t="b">
         <v>0</v>
@@ -20502,7 +20631,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG222" t="b">
         <v>0</v>
@@ -20617,7 +20746,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG223" t="b">
         <v>0</v>
@@ -20732,7 +20861,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG224" t="b">
         <v>0</v>
@@ -20847,7 +20976,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG225" t="b">
         <v>0</v>
@@ -20962,7 +21091,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG226" t="b">
         <v>0</v>
@@ -21077,7 +21206,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG227" t="b">
         <v>0</v>
@@ -21192,7 +21321,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG228" t="b">
         <v>0</v>
@@ -21307,7 +21436,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG229" t="b">
         <v>0</v>
@@ -21422,7 +21551,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG230" t="b">
         <v>0</v>
@@ -21537,13 +21666,13 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
       <c r="AH231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
@@ -21763,7 +21892,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG233" t="b">
         <v>0</v>
@@ -22100,7 +22229,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG236" t="b">
         <v>0</v>
@@ -22215,7 +22344,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG237" t="b">
         <v>0</v>
@@ -22330,7 +22459,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG238" t="b">
         <v>0</v>
@@ -22445,7 +22574,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG239" t="b">
         <v>0</v>
@@ -22560,7 +22689,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG240" t="b">
         <v>0</v>
@@ -22675,7 +22804,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG241" t="b">
         <v>0</v>
@@ -22790,7 +22919,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG242" t="b">
         <v>0</v>
@@ -22804,8 +22933,2978 @@
         </is>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>75.87</v>
+      </c>
+      <c r="F243" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I243" t="b">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>10</v>
+      </c>
+      <c r="K243" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M243" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N243" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P243" t="n">
+        <v>60.35</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>60.36</v>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S243" t="n">
+        <v>7</v>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V243" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="W243" t="n">
+        <v>75.23999999999999</v>
+      </c>
+      <c r="X243" t="n">
+        <v>58.311</v>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>76.31</v>
+      </c>
+      <c r="F244" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I244" t="b">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>10</v>
+      </c>
+      <c r="K244" t="n">
+        <v>242.55</v>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M244" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N244" t="n">
+        <v>1</v>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>206.25</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>63.91</v>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S244" t="n">
+        <v>7</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V244" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="W244" t="n">
+        <v>264.6</v>
+      </c>
+      <c r="X244" t="n">
+        <v>205.065</v>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="F245" t="n">
+        <v>72.84999999999999</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I245" t="b">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>10</v>
+      </c>
+      <c r="K245" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M245" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="N245" t="n">
+        <v>10</v>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P245" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S245" t="n">
+        <v>4.3375</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V245" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="W245" t="n">
+        <v>84.34780000000001</v>
+      </c>
+      <c r="X245" t="n">
+        <v>69.45099999999999</v>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>82.58</v>
+      </c>
+      <c r="F246" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I246" t="b">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>10</v>
+      </c>
+      <c r="K246" t="n">
+        <v>830.5</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M246" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N246" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>737</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>69.33</v>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S246" t="n">
+        <v>7</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="V246" t="n">
+        <v>755</v>
+      </c>
+      <c r="W246" t="n">
+        <v>906</v>
+      </c>
+      <c r="X246" t="n">
+        <v>702.15</v>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="F247" t="n">
+        <v>25.23</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I247" t="b">
+        <v>0</v>
+      </c>
+      <c r="J247" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="K247" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M247" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N247" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P247" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>78.19</v>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S247" t="n">
+        <v>7</v>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V247" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="W247" t="n">
+        <v>381</v>
+      </c>
+      <c r="X247" t="n">
+        <v>295.275</v>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>70.54000000000001</v>
+      </c>
+      <c r="F248" t="n">
+        <v>50.74</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I248" t="b">
+        <v>0</v>
+      </c>
+      <c r="J248" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="K248" t="n">
+        <v>353.5</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M248" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N248" t="n">
+        <v>10</v>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P248" t="n">
+        <v>328.25</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S248" t="n">
+        <v>4.9887</v>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V248" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="W248" t="n">
+        <v>390.655</v>
+      </c>
+      <c r="X248" t="n">
+        <v>315.9125</v>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="F249" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I249" t="b">
+        <v>0</v>
+      </c>
+      <c r="J249" t="n">
+        <v>10</v>
+      </c>
+      <c r="K249" t="n">
+        <v>735.9</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M249" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="N249" t="n">
+        <v>10</v>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>676</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S249" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V249" t="n">
+        <v>669</v>
+      </c>
+      <c r="W249" t="n">
+        <v>802.8</v>
+      </c>
+      <c r="X249" t="n">
+        <v>639.785</v>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>76</v>
+      </c>
+      <c r="F250" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I250" t="b">
+        <v>0</v>
+      </c>
+      <c r="J250" t="n">
+        <v>10</v>
+      </c>
+      <c r="K250" t="n">
+        <v>594</v>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M250" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N250" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P250" t="n">
+        <v>524.5</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>57.26</v>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S250" t="n">
+        <v>7</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V250" t="n">
+        <v>540</v>
+      </c>
+      <c r="W250" t="n">
+        <v>648</v>
+      </c>
+      <c r="X250" t="n">
+        <v>502.2</v>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>79.09</v>
+      </c>
+      <c r="F251" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I251" t="b">
+        <v>0</v>
+      </c>
+      <c r="J251" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="K251" t="n">
+        <v>154.01</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M251" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="N251" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P251" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>70.73999999999999</v>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S251" t="n">
+        <v>7</v>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V251" t="n">
+        <v>144</v>
+      </c>
+      <c r="W251" t="n">
+        <v>171.9409</v>
+      </c>
+      <c r="X251" t="n">
+        <v>133.92</v>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="F252" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I252" t="b">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>10</v>
+      </c>
+      <c r="K252" t="n">
+        <v>7771.5</v>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M252" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N252" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P252" t="n">
+        <v>5907.5</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>85.53</v>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S252" t="n">
+        <v>7</v>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V252" t="n">
+        <v>7065</v>
+      </c>
+      <c r="W252" t="n">
+        <v>8478</v>
+      </c>
+      <c r="X252" t="n">
+        <v>6570.45</v>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>75.76000000000001</v>
+      </c>
+      <c r="F253" t="n">
+        <v>44.27</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I253" t="b">
+        <v>0</v>
+      </c>
+      <c r="J253" t="n">
+        <v>10</v>
+      </c>
+      <c r="K253" t="n">
+        <v>3696</v>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M253" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N253" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P253" t="n">
+        <v>3095</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S253" t="n">
+        <v>7</v>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V253" t="n">
+        <v>3360</v>
+      </c>
+      <c r="W253" t="n">
+        <v>4032</v>
+      </c>
+      <c r="X253" t="n">
+        <v>3124.8</v>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>智原</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="F254" t="n">
+        <v>53.76</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I254" t="b">
+        <v>0</v>
+      </c>
+      <c r="J254" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K254" t="n">
+        <v>198</v>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M254" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="N254" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P254" t="n">
+        <v>175.25</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S254" t="n">
+        <v>7</v>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V254" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="W254" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="X254" t="n">
+        <v>167.865</v>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="F255" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I255" t="b">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>10</v>
+      </c>
+      <c r="K255" t="n">
+        <v>1221</v>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M255" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N255" t="n">
+        <v>5</v>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P255" t="n">
+        <v>1103</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>62.88</v>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S255" t="n">
+        <v>7</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V255" t="n">
+        <v>1110</v>
+      </c>
+      <c r="W255" t="n">
+        <v>1332</v>
+      </c>
+      <c r="X255" t="n">
+        <v>1032.3</v>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>76.16</v>
+      </c>
+      <c r="F256" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I256" t="b">
+        <v>0</v>
+      </c>
+      <c r="J256" t="n">
+        <v>10</v>
+      </c>
+      <c r="K256" t="n">
+        <v>3635.5</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M256" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N256" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>2990</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>51.56</v>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S256" t="n">
+        <v>7</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V256" t="n">
+        <v>3305</v>
+      </c>
+      <c r="W256" t="n">
+        <v>3966</v>
+      </c>
+      <c r="X256" t="n">
+        <v>3073.65</v>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>71.37</v>
+      </c>
+      <c r="F257" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I257" t="b">
+        <v>0</v>
+      </c>
+      <c r="J257" t="n">
+        <v>10</v>
+      </c>
+      <c r="K257" t="n">
+        <v>482.9</v>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M257" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N257" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P257" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S257" t="n">
+        <v>7</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V257" t="n">
+        <v>439</v>
+      </c>
+      <c r="W257" t="n">
+        <v>526.8</v>
+      </c>
+      <c r="X257" t="n">
+        <v>408.27</v>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="F258" t="n">
+        <v>54.01</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I258" t="b">
+        <v>0</v>
+      </c>
+      <c r="J258" t="n">
+        <v>10</v>
+      </c>
+      <c r="K258" t="n">
+        <v>988.9</v>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M258" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N258" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P258" t="n">
+        <v>863</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S258" t="n">
+        <v>7</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V258" t="n">
+        <v>899</v>
+      </c>
+      <c r="W258" t="n">
+        <v>1078.8</v>
+      </c>
+      <c r="X258" t="n">
+        <v>836.0700000000001</v>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>72.86</v>
+      </c>
+      <c r="F259" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I259" t="b">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>10</v>
+      </c>
+      <c r="K259" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M259" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N259" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>63.77</v>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S259" t="n">
+        <v>7</v>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V259" t="n">
+        <v>235</v>
+      </c>
+      <c r="W259" t="n">
+        <v>282</v>
+      </c>
+      <c r="X259" t="n">
+        <v>218.55</v>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="F260" t="n">
+        <v>44.08</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I260" t="b">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>10</v>
+      </c>
+      <c r="K260" t="n">
+        <v>1254</v>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M260" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N260" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>1055</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>70.52</v>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S260" t="n">
+        <v>7</v>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V260" t="n">
+        <v>1140</v>
+      </c>
+      <c r="W260" t="n">
+        <v>1368</v>
+      </c>
+      <c r="X260" t="n">
+        <v>1060.2</v>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="F261" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I261" t="b">
+        <v>0</v>
+      </c>
+      <c r="J261" t="n">
+        <v>10</v>
+      </c>
+      <c r="K261" t="n">
+        <v>6616.5</v>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M261" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N261" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>5787.5</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S261" t="n">
+        <v>7</v>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V261" t="n">
+        <v>6015</v>
+      </c>
+      <c r="W261" t="n">
+        <v>7218</v>
+      </c>
+      <c r="X261" t="n">
+        <v>5593.95</v>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>辛耘</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="F262" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I262" t="b">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>10</v>
+      </c>
+      <c r="K262" t="n">
+        <v>823.9</v>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M262" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N262" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>739.5</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S262" t="n">
+        <v>7</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V262" t="n">
+        <v>749</v>
+      </c>
+      <c r="W262" t="n">
+        <v>898.8</v>
+      </c>
+      <c r="X262" t="n">
+        <v>696.5700000000001</v>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="F263" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I263" t="b">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>10</v>
+      </c>
+      <c r="K263" t="n">
+        <v>4471.5</v>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M263" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N263" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P263" t="n">
+        <v>4057.5</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>65.44</v>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S263" t="n">
+        <v>7</v>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V263" t="n">
+        <v>4065</v>
+      </c>
+      <c r="W263" t="n">
+        <v>4878</v>
+      </c>
+      <c r="X263" t="n">
+        <v>3780.45</v>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>73.81</v>
+      </c>
+      <c r="F264" t="n">
+        <v>61.68</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I264" t="b">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>10</v>
+      </c>
+      <c r="K264" t="n">
+        <v>683.1</v>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M264" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N264" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>603.5</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S264" t="n">
+        <v>7</v>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V264" t="n">
+        <v>621</v>
+      </c>
+      <c r="W264" t="n">
+        <v>730.8255</v>
+      </c>
+      <c r="X264" t="n">
+        <v>577.53</v>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="F265" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I265" t="b">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K265" t="n">
+        <v>187</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M265" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N265" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P265" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S265" t="n">
+        <v>7</v>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V265" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="W265" t="n">
+        <v>219</v>
+      </c>
+      <c r="X265" t="n">
+        <v>169.725</v>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>藥華藥</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>74.47</v>
+      </c>
+      <c r="F266" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I266" t="b">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>10</v>
+      </c>
+      <c r="K266" t="n">
+        <v>1699.5</v>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M266" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N266" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>1492.5</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S266" t="n">
+        <v>7</v>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V266" t="n">
+        <v>1545</v>
+      </c>
+      <c r="W266" t="n">
+        <v>1854</v>
+      </c>
+      <c r="X266" t="n">
+        <v>1436.85</v>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>84.83</v>
+      </c>
+      <c r="F267" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I267" t="b">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>10</v>
+      </c>
+      <c r="K267" t="n">
+        <v>7920</v>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M267" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N267" t="n">
+        <v>1</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>6632.5</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>81.06999999999999</v>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S267" t="n">
+        <v>7</v>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V267" t="n">
+        <v>7200</v>
+      </c>
+      <c r="W267" t="n">
+        <v>8640</v>
+      </c>
+      <c r="X267" t="n">
+        <v>6696</v>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>9921</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>巨大</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="F268" t="n">
+        <v>55.24</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I268" t="b">
+        <v>0</v>
+      </c>
+      <c r="J268" t="n">
+        <v>10</v>
+      </c>
+      <c r="K268" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M268" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N268" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>44.93</v>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S268" t="n">
+        <v>7</v>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V268" t="n">
+        <v>103</v>
+      </c>
+      <c r="W268" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="X268" t="n">
+        <v>95.79000000000001</v>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI268" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ242"/>
+  <autoFilter ref="A1:AJ268"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23055,7 +26154,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27 14:24:27</t>
+          <t>2026-08-28 14:23:43</t>
         </is>
       </c>
     </row>
@@ -23102,7 +26201,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>241</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7">
@@ -23122,7 +26221,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>241</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$268</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$300</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ268"/>
+  <dimension ref="A1:AJ300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1851,6 +1851,9 @@
       <c r="AB17" t="n">
         <v>0.61</v>
       </c>
+      <c r="AC17" t="n">
+        <v>-0.61</v>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -1915,7 +1918,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -1923,6 +1926,9 @@
       <c r="AB18" t="n">
         <v>-8.6</v>
       </c>
+      <c r="AC18" t="n">
+        <v>-9.24</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -1987,7 +1993,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -1995,6 +2001,9 @@
       <c r="AB19" t="n">
         <v>-2.29</v>
       </c>
+      <c r="AC19" t="n">
+        <v>-3.56</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2059,7 +2068,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -2067,6 +2076,9 @@
       <c r="AB20" t="n">
         <v>-11.24</v>
       </c>
+      <c r="AC20" t="n">
+        <v>-9.56</v>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2131,7 +2143,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2139,6 +2151,9 @@
       <c r="AB21" t="n">
         <v>-7.94</v>
       </c>
+      <c r="AC21" t="n">
+        <v>-5.48</v>
+      </c>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2203,7 +2218,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2211,6 +2226,9 @@
       <c r="AB22" t="n">
         <v>12.84</v>
       </c>
+      <c r="AC22" t="n">
+        <v>22.13</v>
+      </c>
       <c r="AG22" t="b">
         <v>1</v>
       </c>
@@ -2275,7 +2293,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2283,6 +2301,9 @@
       <c r="AB23" t="n">
         <v>-2.43</v>
       </c>
+      <c r="AC23" t="n">
+        <v>2.43</v>
+      </c>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2347,7 +2368,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2355,6 +2376,9 @@
       <c r="AB24" t="n">
         <v>-1.35</v>
       </c>
+      <c r="AC24" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2419,7 +2443,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
@@ -2427,6 +2451,9 @@
       <c r="AB25" t="n">
         <v>17.06</v>
       </c>
+      <c r="AC25" t="n">
+        <v>9.109999999999999</v>
+      </c>
       <c r="AG25" t="b">
         <v>1</v>
       </c>
@@ -2491,7 +2518,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
@@ -2499,6 +2526,9 @@
       <c r="AB26" t="n">
         <v>25</v>
       </c>
+      <c r="AC26" t="n">
+        <v>15.31</v>
+      </c>
       <c r="AG26" t="b">
         <v>1</v>
       </c>
@@ -2563,7 +2593,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2571,6 +2601,9 @@
       <c r="AB27" t="n">
         <v>42.29</v>
       </c>
+      <c r="AC27" t="n">
+        <v>30.29</v>
+      </c>
       <c r="AG27" t="b">
         <v>1</v>
       </c>
@@ -2635,7 +2668,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2643,6 +2676,9 @@
       <c r="AB28" t="n">
         <v>-10.8</v>
       </c>
+      <c r="AC28" t="n">
+        <v>-6.02</v>
+      </c>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -2707,7 +2743,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2715,6 +2751,9 @@
       <c r="AB29" t="n">
         <v>-2.08</v>
       </c>
+      <c r="AC29" t="n">
+        <v>9.41</v>
+      </c>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -2779,7 +2818,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2787,6 +2826,9 @@
       <c r="AB30" t="n">
         <v>-8.140000000000001</v>
       </c>
+      <c r="AC30" t="n">
+        <v>-4.8</v>
+      </c>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -2851,7 +2893,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -2859,6 +2901,9 @@
       <c r="AB31" t="n">
         <v>2.36</v>
       </c>
+      <c r="AC31" t="n">
+        <v>6.17</v>
+      </c>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -2923,7 +2968,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -2931,6 +2976,9 @@
       <c r="AB32" t="n">
         <v>-0.37</v>
       </c>
+      <c r="AC32" t="n">
+        <v>-0.74</v>
+      </c>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -2995,7 +3043,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3003,6 +3051,9 @@
       <c r="AB33" t="n">
         <v>-9.07</v>
       </c>
+      <c r="AC33" t="n">
+        <v>-7.77</v>
+      </c>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3191,7 +3242,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3199,6 +3250,9 @@
       <c r="AB36" t="n">
         <v>5.1</v>
       </c>
+      <c r="AC36" t="n">
+        <v>0.46</v>
+      </c>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -3263,7 +3317,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA37" t="n">
         <v>10.15</v>
@@ -3271,6 +3325,9 @@
       <c r="AB37" t="n">
         <v>4.83</v>
       </c>
+      <c r="AC37" t="n">
+        <v>18.05</v>
+      </c>
       <c r="AG37" t="b">
         <v>1</v>
       </c>
@@ -3335,7 +3392,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3343,6 +3400,9 @@
       <c r="AB38" t="n">
         <v>-1.74</v>
       </c>
+      <c r="AC38" t="n">
+        <v>-4.77</v>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -3407,7 +3467,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3479,7 +3539,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3551,7 +3611,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3623,7 +3683,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3695,7 +3755,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3767,7 +3827,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -3839,7 +3899,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -3911,7 +3971,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -3983,7 +4043,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -4055,7 +4115,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -4127,7 +4187,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4199,7 +4259,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4271,7 +4331,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4343,7 +4403,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4415,7 +4475,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4487,7 +4547,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4621,7 +4681,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4693,7 +4753,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -4765,7 +4825,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -4837,7 +4897,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -4909,7 +4969,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -4981,7 +5041,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -5053,7 +5113,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -5125,7 +5185,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -5197,7 +5257,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5269,7 +5329,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5341,7 +5401,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5413,7 +5473,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5485,7 +5545,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -5557,7 +5617,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -5691,7 +5751,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -5763,7 +5823,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -5835,7 +5895,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA73" t="n">
         <v>5.81</v>
@@ -5907,7 +5967,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -5979,7 +6039,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -6051,7 +6111,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -6063,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="AH76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
@@ -6123,7 +6183,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -6195,7 +6255,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6267,7 +6327,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6339,7 +6399,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6411,7 +6471,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -6483,7 +6543,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -6555,7 +6615,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -6627,7 +6687,7 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -6699,7 +6759,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -6771,7 +6831,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -6843,7 +6903,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -6915,7 +6975,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -6987,7 +7047,7 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA89" t="n">
         <v>4.2</v>
@@ -6996,7 +7056,7 @@
         <v>12.27</v>
       </c>
       <c r="AG89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH89" t="b">
         <v>0</v>
@@ -7121,7 +7181,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -7193,7 +7253,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -7265,7 +7325,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -7337,7 +7397,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -7409,7 +7469,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -7481,7 +7541,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -7553,7 +7613,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -7625,7 +7685,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -7697,7 +7757,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -7769,7 +7829,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -7841,7 +7901,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -7913,7 +7973,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -7985,7 +8045,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -8057,7 +8117,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -8129,7 +8189,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -8201,7 +8261,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -8273,7 +8333,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -8345,7 +8405,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -8417,7 +8477,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -8489,7 +8549,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -8561,7 +8621,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -8633,7 +8693,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA112" t="n">
         <v>-2.8</v>
@@ -8705,11 +8765,14 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
       </c>
+      <c r="AB113" t="n">
+        <v>1.25</v>
+      </c>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -8774,16 +8837,19 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
       </c>
+      <c r="AB114" t="n">
+        <v>-2.73</v>
+      </c>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AH114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
@@ -8843,11 +8909,14 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
       </c>
+      <c r="AB115" t="n">
+        <v>-8.26</v>
+      </c>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -8912,11 +8981,14 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
       </c>
+      <c r="AB116" t="n">
+        <v>15.75</v>
+      </c>
       <c r="AG116" t="b">
         <v>1</v>
       </c>
@@ -8981,11 +9053,14 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
       </c>
+      <c r="AB117" t="n">
+        <v>6.5</v>
+      </c>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -9050,11 +9125,14 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
       </c>
+      <c r="AB118" t="n">
+        <v>-16.95</v>
+      </c>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -9119,11 +9197,14 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
       </c>
+      <c r="AB119" t="n">
+        <v>-13.62</v>
+      </c>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -9188,11 +9269,14 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
       </c>
+      <c r="AB120" t="n">
+        <v>3.63</v>
+      </c>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -9257,11 +9341,14 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
       </c>
+      <c r="AB121" t="n">
+        <v>0.86</v>
+      </c>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -9326,11 +9413,14 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
       </c>
+      <c r="AB122" t="n">
+        <v>8.779999999999999</v>
+      </c>
       <c r="AG122" t="b">
         <v>1</v>
       </c>
@@ -9395,11 +9485,14 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
       </c>
+      <c r="AB123" t="n">
+        <v>7.8</v>
+      </c>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -9464,11 +9557,14 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
       </c>
+      <c r="AB124" t="n">
+        <v>-4.25</v>
+      </c>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -9533,11 +9629,14 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
       </c>
+      <c r="AB125" t="n">
+        <v>3.77</v>
+      </c>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -9602,11 +9701,14 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
       </c>
+      <c r="AB126" t="n">
+        <v>8.73</v>
+      </c>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -9671,11 +9773,14 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
       </c>
+      <c r="AB127" t="n">
+        <v>-4.81</v>
+      </c>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -9740,11 +9845,14 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
       </c>
+      <c r="AB128" t="n">
+        <v>4.27</v>
+      </c>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -9809,11 +9917,14 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA129" t="n">
         <v>-4.83</v>
       </c>
+      <c r="AB129" t="n">
+        <v>7.18</v>
+      </c>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -9927,7 +10038,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
@@ -10045,7 +10156,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
@@ -10163,7 +10274,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
@@ -10281,7 +10392,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
@@ -10399,7 +10510,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
@@ -10517,7 +10628,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
@@ -10635,7 +10746,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
@@ -10750,13 +10861,13 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
       </c>
       <c r="AG137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH137" t="b">
         <v>0</v>
@@ -10868,7 +10979,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
@@ -10986,7 +11097,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
@@ -11104,7 +11215,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
@@ -11222,7 +11333,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
@@ -11340,7 +11451,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
@@ -11458,7 +11569,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
@@ -11576,7 +11687,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
@@ -11694,7 +11805,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA145" t="n">
         <v>0.63</v>
@@ -11812,7 +11923,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
@@ -11930,7 +12041,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
@@ -12048,7 +12159,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
@@ -12166,7 +12277,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
@@ -12284,7 +12395,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
@@ -12402,7 +12513,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
@@ -12520,7 +12631,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
@@ -12638,7 +12749,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
@@ -12756,7 +12867,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
@@ -12874,7 +12985,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
@@ -12992,7 +13103,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
@@ -13110,7 +13221,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
@@ -13228,7 +13339,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
@@ -13346,7 +13457,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
@@ -13464,7 +13575,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
@@ -13582,7 +13693,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
@@ -13700,7 +13811,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
@@ -13818,7 +13929,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
@@ -13936,7 +14047,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
@@ -14054,7 +14165,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
@@ -14172,7 +14283,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
@@ -14290,7 +14401,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
@@ -14519,7 +14630,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
@@ -14637,7 +14748,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
@@ -14755,7 +14866,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA171" t="n">
         <v>7.75</v>
@@ -14873,7 +14984,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
@@ -14991,7 +15102,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
@@ -15109,7 +15220,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
@@ -15227,7 +15338,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
@@ -15345,7 +15456,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
@@ -15463,7 +15574,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
@@ -15581,7 +15692,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
@@ -15810,7 +15921,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
@@ -15928,7 +16039,10 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>-3.74</v>
       </c>
       <c r="AG181" t="b">
         <v>0</v>
@@ -16043,7 +16157,10 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>-3</v>
       </c>
       <c r="AG182" t="b">
         <v>0</v>
@@ -16158,7 +16275,10 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>-6.79</v>
       </c>
       <c r="AG183" t="b">
         <v>0</v>
@@ -16273,7 +16393,10 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>42.06</v>
       </c>
       <c r="AG184" t="b">
         <v>1</v>
@@ -16388,7 +16511,10 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA185" t="n">
+        <v>-4.42</v>
       </c>
       <c r="AG185" t="b">
         <v>0</v>
@@ -16503,7 +16629,10 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>12.62</v>
       </c>
       <c r="AG186" t="b">
         <v>0</v>
@@ -16618,7 +16747,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG187" t="b">
         <v>0</v>
@@ -16733,7 +16862,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG188" t="b">
         <v>0</v>
@@ -16848,7 +16977,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG189" t="b">
         <v>0</v>
@@ -16963,7 +17092,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG190" t="b">
         <v>0</v>
@@ -17078,7 +17207,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG191" t="b">
         <v>0</v>
@@ -17193,7 +17322,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG192" t="b">
         <v>0</v>
@@ -17308,7 +17437,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG193" t="b">
         <v>0</v>
@@ -17423,7 +17552,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG194" t="b">
         <v>0</v>
@@ -17538,7 +17667,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG195" t="b">
         <v>0</v>
@@ -17653,7 +17782,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG196" t="b">
         <v>1</v>
@@ -17768,7 +17897,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG197" t="b">
         <v>0</v>
@@ -18105,7 +18234,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG200" t="b">
         <v>0</v>
@@ -18220,7 +18349,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG201" t="b">
         <v>0</v>
@@ -18335,7 +18464,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG202" t="b">
         <v>0</v>
@@ -18450,7 +18579,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG203" t="b">
         <v>0</v>
@@ -18565,7 +18694,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG204" t="b">
         <v>0</v>
@@ -18680,7 +18809,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG205" t="b">
         <v>0</v>
@@ -18795,7 +18924,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG206" t="b">
         <v>0</v>
@@ -18910,7 +19039,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG207" t="b">
         <v>0</v>
@@ -19025,7 +19154,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG208" t="b">
         <v>0</v>
@@ -19140,7 +19269,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG209" t="b">
         <v>0</v>
@@ -19255,7 +19384,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG210" t="b">
         <v>0</v>
@@ -19370,7 +19499,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG211" t="b">
         <v>0</v>
@@ -19485,13 +19614,13 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AH212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI212" t="inlineStr">
         <is>
@@ -19711,7 +19840,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG214" t="b">
         <v>0</v>
@@ -19826,13 +19955,13 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
       <c r="AH215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI215" t="inlineStr">
         <is>
@@ -19941,7 +20070,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG216" t="b">
         <v>0</v>
@@ -20056,7 +20185,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG217" t="b">
         <v>0</v>
@@ -20171,7 +20300,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG218" t="b">
         <v>0</v>
@@ -20286,7 +20415,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG219" t="b">
         <v>0</v>
@@ -20401,7 +20530,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG220" t="b">
         <v>0</v>
@@ -20516,7 +20645,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG221" t="b">
         <v>0</v>
@@ -20631,7 +20760,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG222" t="b">
         <v>0</v>
@@ -20746,7 +20875,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG223" t="b">
         <v>0</v>
@@ -20861,7 +20990,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG224" t="b">
         <v>0</v>
@@ -20976,10 +21105,10 @@
         </is>
       </c>
       <c r="Z225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG225" t="b">
         <v>1</v>
-      </c>
-      <c r="AG225" t="b">
-        <v>0</v>
       </c>
       <c r="AH225" t="b">
         <v>0</v>
@@ -21091,7 +21220,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG226" t="b">
         <v>0</v>
@@ -21206,7 +21335,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG227" t="b">
         <v>0</v>
@@ -21321,7 +21450,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG228" t="b">
         <v>0</v>
@@ -21436,7 +21565,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG229" t="b">
         <v>0</v>
@@ -21551,7 +21680,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG230" t="b">
         <v>0</v>
@@ -21666,7 +21795,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG231" t="b">
         <v>0</v>
@@ -21892,13 +22021,13 @@
         </is>
       </c>
       <c r="Z233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH233" t="b">
         <v>1</v>
-      </c>
-      <c r="AG233" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH233" t="b">
-        <v>0</v>
       </c>
       <c r="AI233" t="inlineStr">
         <is>
@@ -22229,7 +22358,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG236" t="b">
         <v>0</v>
@@ -22344,7 +22473,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG237" t="b">
         <v>0</v>
@@ -22459,13 +22588,13 @@
         </is>
       </c>
       <c r="Z238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH238" t="b">
         <v>1</v>
-      </c>
-      <c r="AG238" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH238" t="b">
-        <v>0</v>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
@@ -22574,13 +22703,13 @@
         </is>
       </c>
       <c r="Z239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH239" t="b">
         <v>1</v>
-      </c>
-      <c r="AG239" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH239" t="b">
-        <v>0</v>
       </c>
       <c r="AI239" t="inlineStr">
         <is>
@@ -22689,7 +22818,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG240" t="b">
         <v>0</v>
@@ -22804,7 +22933,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG241" t="b">
         <v>0</v>
@@ -22919,7 +23048,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG242" t="b">
         <v>0</v>
@@ -23034,7 +23163,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG243" t="b">
         <v>0</v>
@@ -23149,7 +23278,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG244" t="b">
         <v>0</v>
@@ -23264,7 +23393,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG245" t="b">
         <v>0</v>
@@ -23379,7 +23508,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG246" t="b">
         <v>0</v>
@@ -23494,7 +23623,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG247" t="b">
         <v>0</v>
@@ -23609,7 +23738,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG248" t="b">
         <v>0</v>
@@ -23724,7 +23853,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG249" t="b">
         <v>0</v>
@@ -23839,7 +23968,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG250" t="b">
         <v>0</v>
@@ -23954,7 +24083,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG251" t="b">
         <v>0</v>
@@ -24069,7 +24198,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG252" t="b">
         <v>0</v>
@@ -24184,7 +24313,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG253" t="b">
         <v>0</v>
@@ -24299,7 +24428,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG254" t="b">
         <v>0</v>
@@ -24414,13 +24543,13 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG255" t="b">
         <v>0</v>
       </c>
       <c r="AH255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI255" t="inlineStr">
         <is>
@@ -24751,13 +24880,13 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG258" t="b">
         <v>0</v>
       </c>
       <c r="AH258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI258" t="inlineStr">
         <is>
@@ -25088,7 +25217,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG261" t="b">
         <v>0</v>
@@ -25203,7 +25332,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG262" t="b">
         <v>0</v>
@@ -25318,7 +25447,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG263" t="b">
         <v>0</v>
@@ -25433,13 +25562,13 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
       <c r="AH264" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI264" t="inlineStr">
         <is>
@@ -25659,13 +25788,13 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
       <c r="AH266" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI266" t="inlineStr">
         <is>
@@ -25774,7 +25903,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG267" t="b">
         <v>0</v>
@@ -25889,7 +26018,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG268" t="b">
         <v>0</v>
@@ -25903,8 +26032,3672 @@
         </is>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>85.27</v>
+      </c>
+      <c r="F269" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I269" t="b">
+        <v>0</v>
+      </c>
+      <c r="J269" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K269" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M269" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N269" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>61.05</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S269" t="n">
+        <v>7</v>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V269" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="W269" t="n">
+        <v>79.44</v>
+      </c>
+      <c r="X269" t="n">
+        <v>61.566</v>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>85.83</v>
+      </c>
+      <c r="F270" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I270" t="b">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>10</v>
+      </c>
+      <c r="K270" t="n">
+        <v>801.9</v>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M270" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="N270" t="n">
+        <v>8</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P270" t="n">
+        <v>737</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>60.33</v>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S270" t="n">
+        <v>4.3217</v>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="V270" t="n">
+        <v>729</v>
+      </c>
+      <c r="W270" t="n">
+        <v>872.6168</v>
+      </c>
+      <c r="X270" t="n">
+        <v>697.495</v>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="F271" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I271" t="b">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>10</v>
+      </c>
+      <c r="K271" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M271" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N271" t="n">
+        <v>7</v>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S271" t="n">
+        <v>7</v>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V271" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="W271" t="n">
+        <v>47.04</v>
+      </c>
+      <c r="X271" t="n">
+        <v>36.456</v>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>72.43000000000001</v>
+      </c>
+      <c r="F272" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I272" t="b">
+        <v>0</v>
+      </c>
+      <c r="J272" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="K272" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M272" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="N272" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S272" t="n">
+        <v>7</v>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V272" t="n">
+        <v>305</v>
+      </c>
+      <c r="W272" t="n">
+        <v>366</v>
+      </c>
+      <c r="X272" t="n">
+        <v>283.65</v>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>78.84</v>
+      </c>
+      <c r="F273" t="n">
+        <v>42.98</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I273" t="b">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="K273" t="n">
+        <v>132</v>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M273" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N273" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>69.86</v>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S273" t="n">
+        <v>7</v>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V273" t="n">
+        <v>129</v>
+      </c>
+      <c r="W273" t="n">
+        <v>154.8</v>
+      </c>
+      <c r="X273" t="n">
+        <v>119.97</v>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>76.64</v>
+      </c>
+      <c r="F274" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I274" t="b">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>10</v>
+      </c>
+      <c r="K274" t="n">
+        <v>273.35</v>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M274" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N274" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P274" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S274" t="n">
+        <v>7</v>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V274" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="W274" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="X274" t="n">
+        <v>231.105</v>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="F275" t="n">
+        <v>52.84</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I275" t="b">
+        <v>0</v>
+      </c>
+      <c r="J275" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K275" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M275" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="N275" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P275" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S275" t="n">
+        <v>6.5415</v>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V275" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="W275" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="X275" t="n">
+        <v>37.7105</v>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>宏碁</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>75.54000000000001</v>
+      </c>
+      <c r="F276" t="n">
+        <v>70.38</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I276" t="b">
+        <v>0</v>
+      </c>
+      <c r="J276" t="n">
+        <v>10</v>
+      </c>
+      <c r="K276" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M276" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="N276" t="n">
+        <v>10</v>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S276" t="n">
+        <v>5.0802</v>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V276" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="W276" t="n">
+        <v>35.8339</v>
+      </c>
+      <c r="X276" t="n">
+        <v>29.8997</v>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>83.38</v>
+      </c>
+      <c r="F277" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I277" t="b">
+        <v>0</v>
+      </c>
+      <c r="J277" t="n">
+        <v>10</v>
+      </c>
+      <c r="K277" t="n">
+        <v>1098.9</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M277" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N277" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>958</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>73.23</v>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S277" t="n">
+        <v>7</v>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V277" t="n">
+        <v>999</v>
+      </c>
+      <c r="W277" t="n">
+        <v>1198.8</v>
+      </c>
+      <c r="X277" t="n">
+        <v>929.0700000000001</v>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>71.63</v>
+      </c>
+      <c r="F278" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I278" t="b">
+        <v>0</v>
+      </c>
+      <c r="J278" t="n">
+        <v>10</v>
+      </c>
+      <c r="K278" t="n">
+        <v>1281.5</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M278" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N278" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>1077.5</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>57.97</v>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S278" t="n">
+        <v>7</v>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V278" t="n">
+        <v>1165</v>
+      </c>
+      <c r="W278" t="n">
+        <v>1398</v>
+      </c>
+      <c r="X278" t="n">
+        <v>1083.45</v>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>微星</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="F279" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I279" t="b">
+        <v>0</v>
+      </c>
+      <c r="J279" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="K279" t="n">
+        <v>164.17</v>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M279" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N279" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>152.3</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>68.73999999999999</v>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S279" t="n">
+        <v>7</v>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V279" t="n">
+        <v>155</v>
+      </c>
+      <c r="W279" t="n">
+        <v>186</v>
+      </c>
+      <c r="X279" t="n">
+        <v>144.15</v>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>76.23999999999999</v>
+      </c>
+      <c r="F280" t="n">
+        <v>42.03</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I280" t="b">
+        <v>0</v>
+      </c>
+      <c r="J280" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="K280" t="n">
+        <v>353.5</v>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M280" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="N280" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P280" t="n">
+        <v>328.25</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S280" t="n">
+        <v>6.6728</v>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V280" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="W280" t="n">
+        <v>399.6671</v>
+      </c>
+      <c r="X280" t="n">
+        <v>315.9125</v>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>85.95</v>
+      </c>
+      <c r="F281" t="n">
+        <v>71.98</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I281" t="b">
+        <v>0</v>
+      </c>
+      <c r="J281" t="n">
+        <v>10</v>
+      </c>
+      <c r="K281" t="n">
+        <v>744.7</v>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M281" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="N281" t="n">
+        <v>10</v>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P281" t="n">
+        <v>673.5</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="S281" t="n">
+        <v>5.497</v>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V281" t="n">
+        <v>677</v>
+      </c>
+      <c r="W281" t="n">
+        <v>812.4</v>
+      </c>
+      <c r="X281" t="n">
+        <v>639.785</v>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>78.69</v>
+      </c>
+      <c r="F282" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I282" t="b">
+        <v>0</v>
+      </c>
+      <c r="J282" t="n">
+        <v>10</v>
+      </c>
+      <c r="K282" t="n">
+        <v>597.3</v>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M282" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N282" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>524.5</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S282" t="n">
+        <v>7</v>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V282" t="n">
+        <v>543</v>
+      </c>
+      <c r="W282" t="n">
+        <v>651.6</v>
+      </c>
+      <c r="X282" t="n">
+        <v>504.99</v>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>72.19</v>
+      </c>
+      <c r="F283" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I283" t="b">
+        <v>0</v>
+      </c>
+      <c r="J283" t="n">
+        <v>10</v>
+      </c>
+      <c r="K283" t="n">
+        <v>282.7</v>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M283" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N283" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P283" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S283" t="n">
+        <v>7</v>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V283" t="n">
+        <v>257</v>
+      </c>
+      <c r="W283" t="n">
+        <v>308.4</v>
+      </c>
+      <c r="X283" t="n">
+        <v>239.01</v>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>72.77</v>
+      </c>
+      <c r="F284" t="n">
+        <v>72.70999999999999</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I284" t="b">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>10</v>
+      </c>
+      <c r="K284" t="n">
+        <v>256.85</v>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M284" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N284" t="n">
+        <v>10</v>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P284" t="n">
+        <v>233.75</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S284" t="n">
+        <v>3.909</v>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V284" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="W284" t="n">
+        <v>270.5198</v>
+      </c>
+      <c r="X284" t="n">
+        <v>224.3725</v>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="F285" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I285" t="b">
+        <v>0</v>
+      </c>
+      <c r="J285" t="n">
+        <v>10</v>
+      </c>
+      <c r="K285" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M285" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N285" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P285" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S285" t="n">
+        <v>7</v>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V285" t="n">
+        <v>114</v>
+      </c>
+      <c r="W285" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="X285" t="n">
+        <v>106.02</v>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI285" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>84.53</v>
+      </c>
+      <c r="F286" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I286" t="b">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="K286" t="n">
+        <v>154.01</v>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M286" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="N286" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P286" t="n">
+        <v>134.25</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>79.34</v>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S286" t="n">
+        <v>7</v>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V286" t="n">
+        <v>144</v>
+      </c>
+      <c r="W286" t="n">
+        <v>172.8</v>
+      </c>
+      <c r="X286" t="n">
+        <v>133.92</v>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>74.77</v>
+      </c>
+      <c r="F287" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I287" t="b">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="K287" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M287" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="N287" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P287" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>68.33</v>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S287" t="n">
+        <v>7</v>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V287" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="W287" t="n">
+        <v>131.3166</v>
+      </c>
+      <c r="X287" t="n">
+        <v>102.765</v>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>82.16</v>
+      </c>
+      <c r="F288" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I288" t="b">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K288" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M288" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N288" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S288" t="n">
+        <v>7</v>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V288" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="W288" t="n">
+        <v>39.7782</v>
+      </c>
+      <c r="X288" t="n">
+        <v>31.4805</v>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>70.02</v>
+      </c>
+      <c r="F289" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I289" t="b">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="K289" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M289" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="N289" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>52.19</v>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S289" t="n">
+        <v>7</v>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V289" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="W289" t="n">
+        <v>43.967</v>
+      </c>
+      <c r="X289" t="n">
+        <v>36.9675</v>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>75.93000000000001</v>
+      </c>
+      <c r="F290" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I290" t="b">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K290" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M290" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N290" t="n">
+        <v>7</v>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S290" t="n">
+        <v>7</v>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V290" t="n">
+        <v>38.55</v>
+      </c>
+      <c r="W290" t="n">
+        <v>44.2145</v>
+      </c>
+      <c r="X290" t="n">
+        <v>35.8515</v>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI290" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>87.12</v>
+      </c>
+      <c r="F291" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I291" t="b">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>10</v>
+      </c>
+      <c r="K291" t="n">
+        <v>8415</v>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M291" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N291" t="n">
+        <v>1</v>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>6162.5</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>87.67</v>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S291" t="n">
+        <v>7</v>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V291" t="n">
+        <v>7650</v>
+      </c>
+      <c r="W291" t="n">
+        <v>9180</v>
+      </c>
+      <c r="X291" t="n">
+        <v>7114.5</v>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG291" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH291" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI291" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="F292" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I292" t="b">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
+        <v>10</v>
+      </c>
+      <c r="K292" t="n">
+        <v>3767.5</v>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M292" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N292" t="n">
+        <v>3</v>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P292" t="n">
+        <v>3095</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S292" t="n">
+        <v>7</v>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V292" t="n">
+        <v>3425</v>
+      </c>
+      <c r="W292" t="n">
+        <v>4110</v>
+      </c>
+      <c r="X292" t="n">
+        <v>3185.25</v>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG292" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH292" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI292" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>76.18000000000001</v>
+      </c>
+      <c r="F293" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I293" t="b">
+        <v>0</v>
+      </c>
+      <c r="J293" t="n">
+        <v>10</v>
+      </c>
+      <c r="K293" t="n">
+        <v>546.15</v>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M293" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N293" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>477.25</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>56.54</v>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S293" t="n">
+        <v>7</v>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V293" t="n">
+        <v>496.5</v>
+      </c>
+      <c r="W293" t="n">
+        <v>595.8</v>
+      </c>
+      <c r="X293" t="n">
+        <v>461.745</v>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG293" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH293" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI293" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>80.48</v>
+      </c>
+      <c r="F294" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I294" t="b">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
+        <v>10</v>
+      </c>
+      <c r="K294" t="n">
+        <v>3883</v>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M294" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N294" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>3010</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S294" t="n">
+        <v>7</v>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V294" t="n">
+        <v>3530</v>
+      </c>
+      <c r="W294" t="n">
+        <v>4236</v>
+      </c>
+      <c r="X294" t="n">
+        <v>3282.9</v>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI294" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ294" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>74.73999999999999</v>
+      </c>
+      <c r="F295" t="n">
+        <v>42.44</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I295" t="b">
+        <v>0</v>
+      </c>
+      <c r="J295" t="n">
+        <v>10</v>
+      </c>
+      <c r="K295" t="n">
+        <v>492.25</v>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M295" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N295" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>410.25</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S295" t="n">
+        <v>7</v>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V295" t="n">
+        <v>447.5</v>
+      </c>
+      <c r="W295" t="n">
+        <v>537</v>
+      </c>
+      <c r="X295" t="n">
+        <v>416.175</v>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI295" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ295" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="F296" t="n">
+        <v>52.55</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I296" t="b">
+        <v>0</v>
+      </c>
+      <c r="J296" t="n">
+        <v>10</v>
+      </c>
+      <c r="K296" t="n">
+        <v>250.8</v>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M296" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N296" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>219.75</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>60.32</v>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S296" t="n">
+        <v>7</v>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V296" t="n">
+        <v>228</v>
+      </c>
+      <c r="W296" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="X296" t="n">
+        <v>212.04</v>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI296" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ296" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="F297" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I297" t="b">
+        <v>0</v>
+      </c>
+      <c r="J297" t="n">
+        <v>10</v>
+      </c>
+      <c r="K297" t="n">
+        <v>6710</v>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M297" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N297" t="n">
+        <v>3</v>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P297" t="n">
+        <v>5787.5</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>65.68000000000001</v>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S297" t="n">
+        <v>7</v>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V297" t="n">
+        <v>6100</v>
+      </c>
+      <c r="W297" t="n">
+        <v>7320</v>
+      </c>
+      <c r="X297" t="n">
+        <v>5673</v>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI297" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>77.84999999999999</v>
+      </c>
+      <c r="F298" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I298" t="b">
+        <v>0</v>
+      </c>
+      <c r="J298" t="n">
+        <v>10</v>
+      </c>
+      <c r="K298" t="n">
+        <v>4482.5</v>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M298" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N298" t="n">
+        <v>7</v>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P298" t="n">
+        <v>4057.5</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S298" t="n">
+        <v>7</v>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V298" t="n">
+        <v>4075</v>
+      </c>
+      <c r="W298" t="n">
+        <v>4890</v>
+      </c>
+      <c r="X298" t="n">
+        <v>3789.75</v>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG298" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH298" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI298" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>81.89</v>
+      </c>
+      <c r="F299" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I299" t="b">
+        <v>0</v>
+      </c>
+      <c r="J299" t="n">
+        <v>10</v>
+      </c>
+      <c r="K299" t="n">
+        <v>7804.5</v>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M299" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N299" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>6742.5</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>68.47</v>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S299" t="n">
+        <v>7</v>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V299" t="n">
+        <v>7095</v>
+      </c>
+      <c r="W299" t="n">
+        <v>8514</v>
+      </c>
+      <c r="X299" t="n">
+        <v>6598.35</v>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG299" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH299" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI299" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>群聯</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="F300" t="n">
+        <v>60.05</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I300" t="b">
+        <v>0</v>
+      </c>
+      <c r="J300" t="n">
+        <v>10</v>
+      </c>
+      <c r="K300" t="n">
+        <v>2381.5</v>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M300" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N300" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>2115</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S300" t="n">
+        <v>7</v>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V300" t="n">
+        <v>2165</v>
+      </c>
+      <c r="W300" t="n">
+        <v>2598</v>
+      </c>
+      <c r="X300" t="n">
+        <v>2013.45</v>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI300" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ300" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ268"/>
+  <autoFilter ref="A1:AJ300"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26154,7 +29947,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28 14:23:43</t>
+          <t>2026-08-31 14:25:19</t>
         </is>
       </c>
     </row>
@@ -26201,7 +29994,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7">
@@ -26221,7 +30014,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$332</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ300"/>
+  <dimension ref="A1:AJ332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA37" t="n">
         <v>10.15</v>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3475,6 +3475,9 @@
       <c r="AB39" t="n">
         <v>-6.41</v>
       </c>
+      <c r="AC39" t="n">
+        <v>-7.37</v>
+      </c>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -3539,7 +3542,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3547,6 +3550,9 @@
       <c r="AB40" t="n">
         <v>0.39</v>
       </c>
+      <c r="AC40" t="n">
+        <v>1.17</v>
+      </c>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -3611,7 +3617,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3619,6 +3625,9 @@
       <c r="AB41" t="n">
         <v>-3.54</v>
       </c>
+      <c r="AC41" t="n">
+        <v>-3.54</v>
+      </c>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -3683,7 +3692,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3691,6 +3700,9 @@
       <c r="AB42" t="n">
         <v>10.24</v>
       </c>
+      <c r="AC42" t="n">
+        <v>11.92</v>
+      </c>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -3755,7 +3767,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3763,6 +3775,9 @@
       <c r="AB43" t="n">
         <v>10.25</v>
       </c>
+      <c r="AC43" t="n">
+        <v>20.38</v>
+      </c>
       <c r="AG43" t="b">
         <v>1</v>
       </c>
@@ -3827,7 +3842,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -3835,6 +3850,9 @@
       <c r="AB44" t="n">
         <v>-5.53</v>
       </c>
+      <c r="AC44" t="n">
+        <v>-2.4</v>
+      </c>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -3899,7 +3917,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -3907,6 +3925,9 @@
       <c r="AB45" t="n">
         <v>-0.86</v>
       </c>
+      <c r="AC45" t="n">
+        <v>2.43</v>
+      </c>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -3971,7 +3992,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -3979,6 +4000,9 @@
       <c r="AB46" t="n">
         <v>1.08</v>
       </c>
+      <c r="AC46" t="n">
+        <v>1.9</v>
+      </c>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -4043,7 +4067,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -4051,6 +4075,9 @@
       <c r="AB47" t="n">
         <v>1.36</v>
       </c>
+      <c r="AC47" t="n">
+        <v>7.56</v>
+      </c>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -4115,7 +4142,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -4123,6 +4150,9 @@
       <c r="AB48" t="n">
         <v>4.29</v>
       </c>
+      <c r="AC48" t="n">
+        <v>5.93</v>
+      </c>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -4187,7 +4217,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4195,6 +4225,9 @@
       <c r="AB49" t="n">
         <v>-7.09</v>
       </c>
+      <c r="AC49" t="n">
+        <v>7.34</v>
+      </c>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -4259,7 +4292,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4267,6 +4300,9 @@
       <c r="AB50" t="n">
         <v>12.84</v>
       </c>
+      <c r="AC50" t="n">
+        <v>9.17</v>
+      </c>
       <c r="AG50" t="b">
         <v>1</v>
       </c>
@@ -4331,7 +4367,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4339,6 +4375,9 @@
       <c r="AB51" t="n">
         <v>22.31</v>
       </c>
+      <c r="AC51" t="n">
+        <v>10.77</v>
+      </c>
       <c r="AG51" t="b">
         <v>1</v>
       </c>
@@ -4403,7 +4442,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4411,6 +4450,9 @@
       <c r="AB52" t="n">
         <v>45.24</v>
       </c>
+      <c r="AC52" t="n">
+        <v>31.46</v>
+      </c>
       <c r="AG52" t="b">
         <v>1</v>
       </c>
@@ -4475,7 +4517,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4483,6 +4525,9 @@
       <c r="AB53" t="n">
         <v>2.09</v>
       </c>
+      <c r="AC53" t="n">
+        <v>12.56</v>
+      </c>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -4547,7 +4592,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4555,6 +4600,9 @@
       <c r="AB54" t="n">
         <v>-6.54</v>
       </c>
+      <c r="AC54" t="n">
+        <v>-4.71</v>
+      </c>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -4681,7 +4729,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4689,6 +4737,9 @@
       <c r="AB56" t="n">
         <v>10.98</v>
       </c>
+      <c r="AC56" t="n">
+        <v>-0.83</v>
+      </c>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -4753,7 +4804,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -4825,7 +4876,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -4897,7 +4948,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -4969,7 +5020,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -5041,7 +5092,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -5113,7 +5164,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -5185,7 +5236,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -5257,7 +5308,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5329,7 +5380,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5401,7 +5452,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5473,7 +5524,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5545,7 +5596,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -5617,7 +5668,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -5751,7 +5802,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -5823,7 +5874,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -5835,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="AH72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
@@ -5895,7 +5946,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA73" t="n">
         <v>5.81</v>
@@ -5967,7 +6018,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -6039,7 +6090,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -6111,7 +6162,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -6183,7 +6234,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -6255,7 +6306,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6327,7 +6378,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6399,7 +6450,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6471,7 +6522,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -6543,7 +6594,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -6615,7 +6666,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -6687,7 +6738,7 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -6759,7 +6810,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -6831,7 +6882,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -6903,7 +6954,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -6975,7 +7026,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -6987,7 +7038,7 @@
         <v>0</v>
       </c>
       <c r="AH88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
@@ -7047,7 +7098,7 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA89" t="n">
         <v>4.2</v>
@@ -7181,7 +7232,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -7253,7 +7304,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -7325,7 +7376,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -7397,7 +7448,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -7469,7 +7520,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -7541,7 +7592,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -7613,7 +7664,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -7685,7 +7736,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -7757,7 +7808,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -7829,7 +7880,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -7901,7 +7952,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -7973,7 +8024,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -8045,7 +8096,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -8117,7 +8168,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -8189,7 +8240,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -8261,7 +8312,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -8333,7 +8384,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -8405,7 +8456,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -8477,7 +8528,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -8549,7 +8600,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -8621,7 +8672,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -8693,7 +8744,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA112" t="n">
         <v>-2.8</v>
@@ -8702,7 +8753,7 @@
         <v>11.89</v>
       </c>
       <c r="AG112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH112" t="b">
         <v>0</v>
@@ -8765,7 +8816,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
@@ -8837,7 +8888,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
@@ -8909,7 +8960,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
@@ -8981,7 +9032,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
@@ -9053,7 +9104,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
@@ -9125,7 +9176,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
@@ -9197,7 +9248,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
@@ -9269,7 +9320,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
@@ -9341,7 +9392,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
@@ -9413,7 +9464,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
@@ -9485,7 +9536,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
@@ -9557,7 +9608,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
@@ -9629,7 +9680,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
@@ -9701,7 +9752,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
@@ -9773,7 +9824,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
@@ -9845,7 +9896,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
@@ -9917,7 +9968,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA129" t="n">
         <v>-4.83</v>
@@ -10038,11 +10089,14 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
       </c>
+      <c r="AB130" t="n">
+        <v>6.58</v>
+      </c>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -10156,11 +10210,14 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
       </c>
+      <c r="AB131" t="n">
+        <v>9.869999999999999</v>
+      </c>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -10274,11 +10331,14 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
       </c>
+      <c r="AB132" t="n">
+        <v>-1.72</v>
+      </c>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -10392,11 +10452,14 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
       </c>
+      <c r="AB133" t="n">
+        <v>14.49</v>
+      </c>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -10510,11 +10573,14 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
       </c>
+      <c r="AB134" t="n">
+        <v>-9.109999999999999</v>
+      </c>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -10628,11 +10694,14 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
       </c>
+      <c r="AB135" t="n">
+        <v>0.58</v>
+      </c>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -10746,11 +10815,14 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
       </c>
+      <c r="AB136" t="n">
+        <v>2.49</v>
+      </c>
       <c r="AG136" t="b">
         <v>1</v>
       </c>
@@ -10861,11 +10933,14 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
       </c>
+      <c r="AB137" t="n">
+        <v>11.97</v>
+      </c>
       <c r="AG137" t="b">
         <v>1</v>
       </c>
@@ -10979,11 +11054,14 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
       </c>
+      <c r="AB138" t="n">
+        <v>4.72</v>
+      </c>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -11097,11 +11175,14 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
       </c>
+      <c r="AB139" t="n">
+        <v>9.210000000000001</v>
+      </c>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -11215,11 +11296,14 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
       </c>
+      <c r="AB140" t="n">
+        <v>43.29</v>
+      </c>
       <c r="AG140" t="b">
         <v>1</v>
       </c>
@@ -11333,11 +11417,14 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
       </c>
+      <c r="AB141" t="n">
+        <v>-15.2</v>
+      </c>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -11451,11 +11538,14 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
       </c>
+      <c r="AB142" t="n">
+        <v>1.04</v>
+      </c>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -11569,11 +11659,14 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
       </c>
+      <c r="AB143" t="n">
+        <v>8.31</v>
+      </c>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -11687,11 +11780,14 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
       </c>
+      <c r="AB144" t="n">
+        <v>-6.43</v>
+      </c>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -11805,13 +11901,16 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA145" t="n">
         <v>0.63</v>
       </c>
+      <c r="AB145" t="n">
+        <v>21.88</v>
+      </c>
       <c r="AG145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH145" t="b">
         <v>0</v>
@@ -11923,7 +12022,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
@@ -12041,7 +12140,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
@@ -12159,7 +12258,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
@@ -12277,7 +12376,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
@@ -12395,7 +12494,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
@@ -12513,7 +12612,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
@@ -12631,7 +12730,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
@@ -12749,7 +12848,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
@@ -12867,7 +12966,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
@@ -12985,7 +13084,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
@@ -13103,7 +13202,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
@@ -13221,7 +13320,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
@@ -13339,7 +13438,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
@@ -13457,7 +13556,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
@@ -13575,7 +13674,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
@@ -13693,7 +13792,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
@@ -13811,7 +13910,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
@@ -13929,7 +14028,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
@@ -14047,7 +14146,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
@@ -14165,7 +14264,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
@@ -14283,7 +14382,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
@@ -14401,7 +14500,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
@@ -14630,7 +14729,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
@@ -14748,7 +14847,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
@@ -14866,13 +14965,13 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA171" t="n">
         <v>7.75</v>
       </c>
       <c r="AG171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH171" t="b">
         <v>0</v>
@@ -14984,7 +15083,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
@@ -15102,7 +15201,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
@@ -15220,7 +15319,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
@@ -15338,7 +15437,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
@@ -15456,7 +15555,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
@@ -15574,7 +15673,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
@@ -15692,7 +15791,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
@@ -15921,7 +16020,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
@@ -16039,7 +16138,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
@@ -16157,7 +16256,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
@@ -16275,7 +16374,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
@@ -16393,7 +16492,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
@@ -16511,7 +16610,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
@@ -16520,7 +16619,7 @@
         <v>0</v>
       </c>
       <c r="AH185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI185" t="inlineStr">
         <is>
@@ -16629,13 +16728,13 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA186" t="n">
         <v>12.62</v>
       </c>
       <c r="AG186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH186" t="b">
         <v>0</v>
@@ -16747,7 +16846,10 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>6.14</v>
       </c>
       <c r="AG187" t="b">
         <v>0</v>
@@ -16862,7 +16964,10 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>1.52</v>
       </c>
       <c r="AG188" t="b">
         <v>0</v>
@@ -16977,7 +17082,10 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>-2.21</v>
       </c>
       <c r="AG189" t="b">
         <v>0</v>
@@ -17092,7 +17200,10 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>1.57</v>
       </c>
       <c r="AG190" t="b">
         <v>0</v>
@@ -17207,7 +17318,10 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>-3.25</v>
       </c>
       <c r="AG191" t="b">
         <v>0</v>
@@ -17322,7 +17436,10 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>2.47</v>
       </c>
       <c r="AG192" t="b">
         <v>0</v>
@@ -17437,7 +17554,10 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>7.77</v>
       </c>
       <c r="AG193" t="b">
         <v>0</v>
@@ -17552,7 +17672,10 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>8.48</v>
       </c>
       <c r="AG194" t="b">
         <v>0</v>
@@ -17667,7 +17790,10 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.15</v>
       </c>
       <c r="AG195" t="b">
         <v>0</v>
@@ -17782,7 +17908,10 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>32.52</v>
       </c>
       <c r="AG196" t="b">
         <v>1</v>
@@ -17897,7 +18026,10 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>-0.54</v>
       </c>
       <c r="AG197" t="b">
         <v>0</v>
@@ -18234,7 +18366,10 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>7.63</v>
       </c>
       <c r="AG200" t="b">
         <v>0</v>
@@ -18349,13 +18484,16 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>-12.08</v>
       </c>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
       <c r="AH201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI201" t="inlineStr">
         <is>
@@ -18464,10 +18602,13 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>21.12</v>
       </c>
       <c r="AG202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH202" t="b">
         <v>0</v>
@@ -18579,7 +18720,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG203" t="b">
         <v>0</v>
@@ -18694,7 +18835,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG204" t="b">
         <v>0</v>
@@ -18809,7 +18950,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG205" t="b">
         <v>0</v>
@@ -18924,7 +19065,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG206" t="b">
         <v>0</v>
@@ -19039,7 +19180,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG207" t="b">
         <v>0</v>
@@ -19154,7 +19295,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG208" t="b">
         <v>0</v>
@@ -19269,7 +19410,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG209" t="b">
         <v>0</v>
@@ -19384,7 +19525,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG210" t="b">
         <v>0</v>
@@ -19499,7 +19640,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG211" t="b">
         <v>0</v>
@@ -19614,7 +19755,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG212" t="b">
         <v>0</v>
@@ -19840,7 +19981,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG214" t="b">
         <v>0</v>
@@ -19955,7 +20096,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG215" t="b">
         <v>0</v>
@@ -20070,13 +20211,13 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
       <c r="AH216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI216" t="inlineStr">
         <is>
@@ -20185,7 +20326,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG217" t="b">
         <v>0</v>
@@ -20300,7 +20441,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG218" t="b">
         <v>0</v>
@@ -20415,7 +20556,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG219" t="b">
         <v>0</v>
@@ -20530,7 +20671,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG220" t="b">
         <v>0</v>
@@ -20645,7 +20786,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG221" t="b">
         <v>0</v>
@@ -20760,7 +20901,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG222" t="b">
         <v>0</v>
@@ -20875,7 +21016,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG223" t="b">
         <v>0</v>
@@ -20990,7 +21131,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG224" t="b">
         <v>0</v>
@@ -21105,7 +21246,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG225" t="b">
         <v>1</v>
@@ -21220,7 +21361,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG226" t="b">
         <v>0</v>
@@ -21335,7 +21476,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG227" t="b">
         <v>0</v>
@@ -21450,7 +21591,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG228" t="b">
         <v>0</v>
@@ -21565,7 +21706,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG229" t="b">
         <v>0</v>
@@ -21680,7 +21821,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG230" t="b">
         <v>0</v>
@@ -21795,7 +21936,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG231" t="b">
         <v>0</v>
@@ -22021,7 +22162,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG233" t="b">
         <v>0</v>
@@ -22358,7 +22499,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG236" t="b">
         <v>0</v>
@@ -22473,7 +22614,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG237" t="b">
         <v>0</v>
@@ -22588,7 +22729,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG238" t="b">
         <v>0</v>
@@ -22703,7 +22844,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG239" t="b">
         <v>0</v>
@@ -22818,7 +22959,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG240" t="b">
         <v>0</v>
@@ -22933,7 +23074,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG241" t="b">
         <v>0</v>
@@ -23048,7 +23189,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG242" t="b">
         <v>0</v>
@@ -23163,7 +23304,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG243" t="b">
         <v>0</v>
@@ -23278,7 +23419,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG244" t="b">
         <v>0</v>
@@ -23393,7 +23534,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG245" t="b">
         <v>0</v>
@@ -23508,7 +23649,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG246" t="b">
         <v>0</v>
@@ -23623,7 +23764,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG247" t="b">
         <v>0</v>
@@ -23738,7 +23879,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG248" t="b">
         <v>0</v>
@@ -23853,7 +23994,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG249" t="b">
         <v>0</v>
@@ -23968,7 +24109,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG250" t="b">
         <v>0</v>
@@ -24083,7 +24224,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG251" t="b">
         <v>0</v>
@@ -24198,7 +24339,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG252" t="b">
         <v>0</v>
@@ -24313,7 +24454,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG253" t="b">
         <v>0</v>
@@ -24428,7 +24569,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG254" t="b">
         <v>0</v>
@@ -24543,7 +24684,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG255" t="b">
         <v>0</v>
@@ -24880,7 +25021,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG258" t="b">
         <v>0</v>
@@ -25217,7 +25358,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG261" t="b">
         <v>0</v>
@@ -25332,7 +25473,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG262" t="b">
         <v>0</v>
@@ -25447,7 +25588,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG263" t="b">
         <v>0</v>
@@ -25562,7 +25703,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG264" t="b">
         <v>0</v>
@@ -25788,7 +25929,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG266" t="b">
         <v>0</v>
@@ -25903,7 +26044,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG267" t="b">
         <v>0</v>
@@ -26018,7 +26159,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG268" t="b">
         <v>0</v>
@@ -26133,7 +26274,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG269" t="b">
         <v>0</v>
@@ -26248,7 +26389,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG270" t="b">
         <v>0</v>
@@ -26363,7 +26504,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG271" t="b">
         <v>0</v>
@@ -26478,7 +26619,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG272" t="b">
         <v>0</v>
@@ -26593,7 +26734,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG273" t="b">
         <v>0</v>
@@ -26708,7 +26849,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG274" t="b">
         <v>0</v>
@@ -26823,7 +26964,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG275" t="b">
         <v>0</v>
@@ -26938,7 +27079,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG276" t="b">
         <v>0</v>
@@ -27053,7 +27194,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG277" t="b">
         <v>0</v>
@@ -27168,7 +27309,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG278" t="b">
         <v>0</v>
@@ -27283,7 +27424,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG279" t="b">
         <v>0</v>
@@ -27398,7 +27539,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG280" t="b">
         <v>0</v>
@@ -27513,7 +27654,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG281" t="b">
         <v>0</v>
@@ -27628,7 +27769,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG282" t="b">
         <v>0</v>
@@ -27743,7 +27884,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG283" t="b">
         <v>0</v>
@@ -27858,7 +27999,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG284" t="b">
         <v>0</v>
@@ -27973,7 +28114,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG285" t="b">
         <v>0</v>
@@ -28088,7 +28229,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG286" t="b">
         <v>0</v>
@@ -28203,7 +28344,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG287" t="b">
         <v>0</v>
@@ -28318,7 +28459,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG288" t="b">
         <v>0</v>
@@ -28433,7 +28574,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG289" t="b">
         <v>0</v>
@@ -28548,7 +28689,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG290" t="b">
         <v>0</v>
@@ -28663,7 +28804,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG291" t="b">
         <v>0</v>
@@ -28778,7 +28919,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG292" t="b">
         <v>0</v>
@@ -28893,7 +29034,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG293" t="b">
         <v>0</v>
@@ -29341,7 +29482,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG297" t="b">
         <v>0</v>
@@ -29456,7 +29597,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG298" t="b">
         <v>0</v>
@@ -29571,7 +29712,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG299" t="b">
         <v>0</v>
@@ -29696,8 +29837,3672 @@
         </is>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="F301" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I301" t="b">
+        <v>0</v>
+      </c>
+      <c r="J301" t="n">
+        <v>10</v>
+      </c>
+      <c r="K301" t="n">
+        <v>74.58</v>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M301" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N301" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P301" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>73.52</v>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S301" t="n">
+        <v>7</v>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V301" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="W301" t="n">
+        <v>81.36</v>
+      </c>
+      <c r="X301" t="n">
+        <v>63.054</v>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG301" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH301" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI301" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>77.33</v>
+      </c>
+      <c r="F302" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I302" t="b">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
+        <v>10</v>
+      </c>
+      <c r="K302" t="n">
+        <v>257.95</v>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M302" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N302" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>67.06999999999999</v>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S302" t="n">
+        <v>7</v>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V302" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="W302" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="X302" t="n">
+        <v>218.085</v>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG302" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH302" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI302" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>75.09</v>
+      </c>
+      <c r="F303" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I303" t="b">
+        <v>0</v>
+      </c>
+      <c r="J303" t="n">
+        <v>10</v>
+      </c>
+      <c r="K303" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M303" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="N303" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>55.16</v>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S303" t="n">
+        <v>5.5088</v>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V303" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="W303" t="n">
+        <v>86.1965</v>
+      </c>
+      <c r="X303" t="n">
+        <v>69.45099999999999</v>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG303" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH303" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI303" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>87.14</v>
+      </c>
+      <c r="F304" t="n">
+        <v>59.43</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I304" t="b">
+        <v>0</v>
+      </c>
+      <c r="J304" t="n">
+        <v>10</v>
+      </c>
+      <c r="K304" t="n">
+        <v>837.1</v>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M304" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N304" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P304" t="n">
+        <v>737</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>72.84</v>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S304" t="n">
+        <v>7</v>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="V304" t="n">
+        <v>761</v>
+      </c>
+      <c r="W304" t="n">
+        <v>913.2</v>
+      </c>
+      <c r="X304" t="n">
+        <v>707.73</v>
+      </c>
+      <c r="Y304" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG304" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH304" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI304" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>76.43000000000001</v>
+      </c>
+      <c r="F305" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I305" t="b">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>10</v>
+      </c>
+      <c r="K305" t="n">
+        <v>330.55</v>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M305" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N305" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>62.46</v>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S305" t="n">
+        <v>7</v>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V305" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="W305" t="n">
+        <v>360.6</v>
+      </c>
+      <c r="X305" t="n">
+        <v>279.465</v>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG305" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH305" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI305" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>74.28</v>
+      </c>
+      <c r="F306" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I306" t="b">
+        <v>0</v>
+      </c>
+      <c r="J306" t="n">
+        <v>10</v>
+      </c>
+      <c r="K306" t="n">
+        <v>145.75</v>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M306" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N306" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>124.25</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>68.48999999999999</v>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S306" t="n">
+        <v>7</v>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V306" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="W306" t="n">
+        <v>159</v>
+      </c>
+      <c r="X306" t="n">
+        <v>123.225</v>
+      </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG306" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH306" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI306" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>70.34</v>
+      </c>
+      <c r="F307" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I307" t="b">
+        <v>0</v>
+      </c>
+      <c r="J307" t="n">
+        <v>10</v>
+      </c>
+      <c r="K307" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M307" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N307" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>61.66</v>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S307" t="n">
+        <v>7</v>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V307" t="n">
+        <v>252</v>
+      </c>
+      <c r="W307" t="n">
+        <v>302.4</v>
+      </c>
+      <c r="X307" t="n">
+        <v>234.36</v>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG307" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH307" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>宏碁</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>70.73999999999999</v>
+      </c>
+      <c r="F308" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I308" t="b">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="K308" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M308" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="N308" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S308" t="n">
+        <v>5.8276</v>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V308" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="W308" t="n">
+        <v>36.3086</v>
+      </c>
+      <c r="X308" t="n">
+        <v>29.8997</v>
+      </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG308" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH308" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI308" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>82.23999999999999</v>
+      </c>
+      <c r="F309" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I309" t="b">
+        <v>0</v>
+      </c>
+      <c r="J309" t="n">
+        <v>10</v>
+      </c>
+      <c r="K309" t="n">
+        <v>1111</v>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M309" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N309" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>958</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S309" t="n">
+        <v>7</v>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V309" t="n">
+        <v>1010</v>
+      </c>
+      <c r="W309" t="n">
+        <v>1212</v>
+      </c>
+      <c r="X309" t="n">
+        <v>939.3</v>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG309" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH309" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>74.81999999999999</v>
+      </c>
+      <c r="F310" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I310" t="b">
+        <v>0</v>
+      </c>
+      <c r="J310" t="n">
+        <v>10</v>
+      </c>
+      <c r="K310" t="n">
+        <v>1347.5</v>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M310" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N310" t="n">
+        <v>1</v>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>1080</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S310" t="n">
+        <v>7</v>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V310" t="n">
+        <v>1225</v>
+      </c>
+      <c r="W310" t="n">
+        <v>1470</v>
+      </c>
+      <c r="X310" t="n">
+        <v>1139.25</v>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG310" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH310" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI310" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>73.56999999999999</v>
+      </c>
+      <c r="F311" t="n">
+        <v>60.72</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I311" t="b">
+        <v>0</v>
+      </c>
+      <c r="J311" t="n">
+        <v>10</v>
+      </c>
+      <c r="K311" t="n">
+        <v>394.9</v>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M311" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N311" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P311" t="n">
+        <v>358.5</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S311" t="n">
+        <v>6.8822</v>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V311" t="n">
+        <v>359</v>
+      </c>
+      <c r="W311" t="n">
+        <v>417.8578</v>
+      </c>
+      <c r="X311" t="n">
+        <v>334.2929</v>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG311" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH311" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI311" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="F312" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I312" t="b">
+        <v>0</v>
+      </c>
+      <c r="J312" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K312" t="n">
+        <v>353.5</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M312" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N312" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>67.27</v>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S312" t="n">
+        <v>7</v>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V312" t="n">
+        <v>342</v>
+      </c>
+      <c r="W312" t="n">
+        <v>403.526</v>
+      </c>
+      <c r="X312" t="n">
+        <v>318.06</v>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG312" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH312" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI312" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>86.92</v>
+      </c>
+      <c r="F313" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I313" t="b">
+        <v>0</v>
+      </c>
+      <c r="J313" t="n">
+        <v>10</v>
+      </c>
+      <c r="K313" t="n">
+        <v>782.1</v>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M313" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N313" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>679</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="S313" t="n">
+        <v>7</v>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V313" t="n">
+        <v>711</v>
+      </c>
+      <c r="W313" t="n">
+        <v>853.2</v>
+      </c>
+      <c r="X313" t="n">
+        <v>661.23</v>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG313" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH313" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI313" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>75.79000000000001</v>
+      </c>
+      <c r="F314" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I314" t="b">
+        <v>0</v>
+      </c>
+      <c r="J314" t="n">
+        <v>10</v>
+      </c>
+      <c r="K314" t="n">
+        <v>569.8</v>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M314" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N314" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>524.5</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S314" t="n">
+        <v>7</v>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V314" t="n">
+        <v>518</v>
+      </c>
+      <c r="W314" t="n">
+        <v>621.6</v>
+      </c>
+      <c r="X314" t="n">
+        <v>481.74</v>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG314" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH314" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>75.77</v>
+      </c>
+      <c r="F315" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I315" t="b">
+        <v>0</v>
+      </c>
+      <c r="J315" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="K315" t="n">
+        <v>125.68</v>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M315" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="N315" t="n">
+        <v>3</v>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P315" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S315" t="n">
+        <v>7</v>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V315" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="W315" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="X315" t="n">
+        <v>106.485</v>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG315" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH315" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="F316" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I316" t="b">
+        <v>0</v>
+      </c>
+      <c r="J316" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="K316" t="n">
+        <v>154.01</v>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M316" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="N316" t="n">
+        <v>5</v>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>134.25</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>78.93000000000001</v>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S316" t="n">
+        <v>7</v>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V316" t="n">
+        <v>145</v>
+      </c>
+      <c r="W316" t="n">
+        <v>173.721</v>
+      </c>
+      <c r="X316" t="n">
+        <v>134.85</v>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG316" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH316" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI316" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="F317" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I317" t="b">
+        <v>0</v>
+      </c>
+      <c r="J317" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="K317" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M317" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N317" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>75.94</v>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S317" t="n">
+        <v>7</v>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V317" t="n">
+        <v>111</v>
+      </c>
+      <c r="W317" t="n">
+        <v>132.2077</v>
+      </c>
+      <c r="X317" t="n">
+        <v>103.23</v>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG317" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH317" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>83.48999999999999</v>
+      </c>
+      <c r="F318" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I318" t="b">
+        <v>0</v>
+      </c>
+      <c r="J318" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="K318" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M318" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N318" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S318" t="n">
+        <v>7</v>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V318" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="W318" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="X318" t="n">
+        <v>32.5035</v>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG318" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH318" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>88.16</v>
+      </c>
+      <c r="F319" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I319" t="b">
+        <v>0</v>
+      </c>
+      <c r="J319" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="K319" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M319" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N319" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P319" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>85.62</v>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S319" t="n">
+        <v>7</v>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V319" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="W319" t="n">
+        <v>47.9905</v>
+      </c>
+      <c r="X319" t="n">
+        <v>37.479</v>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG319" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH319" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>晶豪科</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>76.89</v>
+      </c>
+      <c r="F320" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I320" t="b">
+        <v>0</v>
+      </c>
+      <c r="J320" t="n">
+        <v>10</v>
+      </c>
+      <c r="K320" t="n">
+        <v>306.35</v>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M320" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N320" t="n">
+        <v>5</v>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P320" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S320" t="n">
+        <v>7</v>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V320" t="n">
+        <v>278.5</v>
+      </c>
+      <c r="W320" t="n">
+        <v>334.2</v>
+      </c>
+      <c r="X320" t="n">
+        <v>259.005</v>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG320" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH320" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI320" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>82.33</v>
+      </c>
+      <c r="F321" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I321" t="b">
+        <v>0</v>
+      </c>
+      <c r="J321" t="n">
+        <v>10</v>
+      </c>
+      <c r="K321" t="n">
+        <v>8338</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M321" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N321" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>6332.5</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>71.34</v>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S321" t="n">
+        <v>7</v>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V321" t="n">
+        <v>7580</v>
+      </c>
+      <c r="W321" t="n">
+        <v>9096</v>
+      </c>
+      <c r="X321" t="n">
+        <v>7049.4</v>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG321" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH321" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>76.43000000000001</v>
+      </c>
+      <c r="F322" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I322" t="b">
+        <v>0</v>
+      </c>
+      <c r="J322" t="n">
+        <v>10</v>
+      </c>
+      <c r="K322" t="n">
+        <v>3751</v>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M322" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N322" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>3102.5</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>62.59</v>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S322" t="n">
+        <v>7</v>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V322" t="n">
+        <v>3410</v>
+      </c>
+      <c r="W322" t="n">
+        <v>4092</v>
+      </c>
+      <c r="X322" t="n">
+        <v>3171.3</v>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG322" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH322" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI322" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>智原</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="F323" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I323" t="b">
+        <v>0</v>
+      </c>
+      <c r="J323" t="n">
+        <v>10</v>
+      </c>
+      <c r="K323" t="n">
+        <v>201.85</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M323" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N323" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P323" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>65.98999999999999</v>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S323" t="n">
+        <v>7</v>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V323" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="W323" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="X323" t="n">
+        <v>170.655</v>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG323" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH323" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI323" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="F324" t="n">
+        <v>53.39</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I324" t="b">
+        <v>0</v>
+      </c>
+      <c r="J324" t="n">
+        <v>10</v>
+      </c>
+      <c r="K324" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M324" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N324" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>477.25</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>59.29</v>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S324" t="n">
+        <v>7</v>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V324" t="n">
+        <v>503</v>
+      </c>
+      <c r="W324" t="n">
+        <v>603.6</v>
+      </c>
+      <c r="X324" t="n">
+        <v>467.79</v>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG324" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH324" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="F325" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I325" t="b">
+        <v>0</v>
+      </c>
+      <c r="J325" t="n">
+        <v>10</v>
+      </c>
+      <c r="K325" t="n">
+        <v>261.25</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M325" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N325" t="n">
+        <v>5</v>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S325" t="n">
+        <v>7</v>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V325" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="W325" t="n">
+        <v>285</v>
+      </c>
+      <c r="X325" t="n">
+        <v>220.875</v>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI325" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ325" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>82.70999999999999</v>
+      </c>
+      <c r="F326" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I326" t="b">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="K326" t="n">
+        <v>448</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M326" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N326" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>73.06</v>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S326" t="n">
+        <v>7</v>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V326" t="n">
+        <v>421.5</v>
+      </c>
+      <c r="W326" t="n">
+        <v>505.8</v>
+      </c>
+      <c r="X326" t="n">
+        <v>391.995</v>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI326" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ326" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>75.54000000000001</v>
+      </c>
+      <c r="F327" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I327" t="b">
+        <v>0</v>
+      </c>
+      <c r="J327" t="n">
+        <v>10</v>
+      </c>
+      <c r="K327" t="n">
+        <v>6594.5</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M327" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N327" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P327" t="n">
+        <v>5847.5</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S327" t="n">
+        <v>7</v>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V327" t="n">
+        <v>5995</v>
+      </c>
+      <c r="W327" t="n">
+        <v>7194</v>
+      </c>
+      <c r="X327" t="n">
+        <v>5575.35</v>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG327" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH327" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="F328" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I328" t="b">
+        <v>0</v>
+      </c>
+      <c r="J328" t="n">
+        <v>10</v>
+      </c>
+      <c r="K328" t="n">
+        <v>442.2</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M328" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N328" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P328" t="n">
+        <v>375</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S328" t="n">
+        <v>7</v>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V328" t="n">
+        <v>402</v>
+      </c>
+      <c r="W328" t="n">
+        <v>482.4</v>
+      </c>
+      <c r="X328" t="n">
+        <v>373.86</v>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG328" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH328" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI328" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>73.93000000000001</v>
+      </c>
+      <c r="F329" t="n">
+        <v>52.19</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I329" t="b">
+        <v>0</v>
+      </c>
+      <c r="J329" t="n">
+        <v>10</v>
+      </c>
+      <c r="K329" t="n">
+        <v>4702.5</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M329" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N329" t="n">
+        <v>5</v>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>4037.5</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>74.59</v>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S329" t="n">
+        <v>7</v>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V329" t="n">
+        <v>4275</v>
+      </c>
+      <c r="W329" t="n">
+        <v>5130</v>
+      </c>
+      <c r="X329" t="n">
+        <v>3975.75</v>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG329" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH329" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>6121</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>新普</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>72</v>
+      </c>
+      <c r="F330" t="n">
+        <v>63.05</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I330" t="b">
+        <v>0</v>
+      </c>
+      <c r="J330" t="n">
+        <v>10</v>
+      </c>
+      <c r="K330" t="n">
+        <v>449.35</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M330" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="N330" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P330" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S330" t="n">
+        <v>5.7368</v>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V330" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="W330" t="n">
+        <v>469.6344</v>
+      </c>
+      <c r="X330" t="n">
+        <v>385.065</v>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI330" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ330" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="F331" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I331" t="b">
+        <v>0</v>
+      </c>
+      <c r="J331" t="n">
+        <v>10</v>
+      </c>
+      <c r="K331" t="n">
+        <v>201.85</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M331" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N331" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S331" t="n">
+        <v>7</v>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V331" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="W331" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="X331" t="n">
+        <v>170.655</v>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ331" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="F332" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I332" t="b">
+        <v>0</v>
+      </c>
+      <c r="J332" t="n">
+        <v>10</v>
+      </c>
+      <c r="K332" t="n">
+        <v>1347.5</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M332" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N332" t="n">
+        <v>7</v>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P332" t="n">
+        <v>1225</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S332" t="n">
+        <v>7</v>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V332" t="n">
+        <v>1225</v>
+      </c>
+      <c r="W332" t="n">
+        <v>1470</v>
+      </c>
+      <c r="X332" t="n">
+        <v>1139.25</v>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z332" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG332" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH332" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI332" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ300"/>
+  <autoFilter ref="A1:AJ332"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -29947,7 +33752,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31 14:25:19</t>
+          <t>2026-09-01 14:23:29</t>
         </is>
       </c>
     </row>
@@ -29994,7 +33799,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>299</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7">
@@ -30014,7 +33819,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>299</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$332</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$359</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ332"/>
+  <dimension ref="A1:AJ359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3317,22 +3317,22 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA37" t="n">
-        <v>10.15</v>
+        <v>-63.07</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.83</v>
+        <v>-64.86</v>
       </c>
       <c r="AC37" t="n">
-        <v>18.05</v>
+        <v>-60.42</v>
       </c>
       <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="b">
         <v>1</v>
-      </c>
-      <c r="AH37" t="b">
-        <v>0</v>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3704,7 +3704,7 @@
         <v>11.92</v>
       </c>
       <c r="AG42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH42" t="b">
         <v>0</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4529,7 +4529,7 @@
         <v>12.56</v>
       </c>
       <c r="AG53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH53" t="b">
         <v>0</v>
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -4812,6 +4812,9 @@
       <c r="AB57" t="n">
         <v>-0.42</v>
       </c>
+      <c r="AC57" t="n">
+        <v>2.92</v>
+      </c>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -4876,7 +4879,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -4884,6 +4887,9 @@
       <c r="AB58" t="n">
         <v>-7.84</v>
       </c>
+      <c r="AC58" t="n">
+        <v>-12.54</v>
+      </c>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -4948,7 +4954,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -4956,6 +4962,9 @@
       <c r="AB59" t="n">
         <v>-2.03</v>
       </c>
+      <c r="AC59" t="n">
+        <v>-3.54</v>
+      </c>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -5020,7 +5029,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -5028,6 +5037,9 @@
       <c r="AB60" t="n">
         <v>-8.699999999999999</v>
       </c>
+      <c r="AC60" t="n">
+        <v>-7.04</v>
+      </c>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -5092,7 +5104,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -5100,6 +5112,9 @@
       <c r="AB61" t="n">
         <v>13.97</v>
       </c>
+      <c r="AC61" t="n">
+        <v>18.54</v>
+      </c>
       <c r="AG61" t="b">
         <v>1</v>
       </c>
@@ -5164,7 +5179,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -5172,6 +5187,9 @@
       <c r="AB62" t="n">
         <v>-9.789999999999999</v>
       </c>
+      <c r="AC62" t="n">
+        <v>-10.02</v>
+      </c>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -5236,7 +5254,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -5244,6 +5262,9 @@
       <c r="AB63" t="n">
         <v>2.88</v>
       </c>
+      <c r="AC63" t="n">
+        <v>-4.97</v>
+      </c>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -5308,7 +5329,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5316,6 +5337,9 @@
       <c r="AB64" t="n">
         <v>0.29</v>
       </c>
+      <c r="AC64" t="n">
+        <v>0.87</v>
+      </c>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -5380,7 +5404,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5388,6 +5412,9 @@
       <c r="AB65" t="n">
         <v>7.69</v>
       </c>
+      <c r="AC65" t="n">
+        <v>9.32</v>
+      </c>
       <c r="AG65" t="b">
         <v>1</v>
       </c>
@@ -5452,7 +5479,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5460,6 +5487,9 @@
       <c r="AB66" t="n">
         <v>-1.76</v>
       </c>
+      <c r="AC66" t="n">
+        <v>5.77</v>
+      </c>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -5524,7 +5554,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5532,6 +5562,9 @@
       <c r="AB67" t="n">
         <v>37.19</v>
       </c>
+      <c r="AC67" t="n">
+        <v>70.34</v>
+      </c>
       <c r="AG67" t="b">
         <v>1</v>
       </c>
@@ -5596,7 +5629,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -5604,6 +5637,9 @@
       <c r="AB68" t="n">
         <v>8.42</v>
       </c>
+      <c r="AC68" t="n">
+        <v>13.75</v>
+      </c>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -5668,7 +5704,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -5676,6 +5712,9 @@
       <c r="AB69" t="n">
         <v>-5.94</v>
       </c>
+      <c r="AC69" t="n">
+        <v>-4.13</v>
+      </c>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -5802,7 +5841,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -5810,6 +5849,9 @@
       <c r="AB71" t="n">
         <v>19.4</v>
       </c>
+      <c r="AC71" t="n">
+        <v>14.91</v>
+      </c>
       <c r="AG71" t="b">
         <v>1</v>
       </c>
@@ -5874,7 +5916,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -5882,6 +5924,9 @@
       <c r="AB72" t="n">
         <v>10.07</v>
       </c>
+      <c r="AC72" t="n">
+        <v>-9.380000000000001</v>
+      </c>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -5946,19 +5991,22 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA73" t="n">
-        <v>5.81</v>
+        <v>-64.53</v>
       </c>
       <c r="AB73" t="n">
-        <v>12.61</v>
+        <v>-62.25</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>-56.68</v>
       </c>
       <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="b">
         <v>1</v>
-      </c>
-      <c r="AH73" t="b">
-        <v>0</v>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
@@ -6018,7 +6066,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -6026,6 +6074,9 @@
       <c r="AB74" t="n">
         <v>-9</v>
       </c>
+      <c r="AC74" t="n">
+        <v>-13.18</v>
+      </c>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -6090,7 +6141,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -6162,7 +6213,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -6234,7 +6285,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -6243,7 +6294,7 @@
         <v>11.69</v>
       </c>
       <c r="AG77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH77" t="b">
         <v>0</v>
@@ -6306,7 +6357,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6378,7 +6429,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6450,7 +6501,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6522,7 +6573,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -6594,7 +6645,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -6666,7 +6717,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -6738,7 +6789,7 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -6810,7 +6861,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -6882,7 +6933,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -6954,7 +7005,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -7026,7 +7077,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -7098,19 +7149,19 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA89" t="n">
-        <v>4.2</v>
+        <v>-65.06999999999999</v>
       </c>
       <c r="AB89" t="n">
-        <v>12.27</v>
+        <v>-62.36</v>
       </c>
       <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="b">
         <v>1</v>
-      </c>
-      <c r="AH89" t="b">
-        <v>0</v>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
@@ -7232,7 +7283,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -7304,7 +7355,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -7376,7 +7427,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -7448,7 +7499,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -7520,7 +7571,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -7592,7 +7643,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -7664,7 +7715,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -7736,7 +7787,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -7808,7 +7859,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -7880,7 +7931,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -7952,7 +8003,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -8024,7 +8075,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -8096,7 +8147,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -8168,7 +8219,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -8240,7 +8291,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -8312,7 +8363,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -8384,7 +8435,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -8456,7 +8507,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -8528,7 +8579,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -8600,7 +8651,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -8672,7 +8723,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -8744,19 +8795,19 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA112" t="n">
-        <v>-2.8</v>
+        <v>-67.41</v>
       </c>
       <c r="AB112" t="n">
-        <v>11.89</v>
+        <v>-62.49</v>
       </c>
       <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="b">
         <v>1</v>
-      </c>
-      <c r="AH112" t="b">
-        <v>0</v>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
@@ -8816,7 +8867,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
@@ -8888,7 +8939,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
@@ -8960,7 +9011,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
@@ -9032,7 +9083,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
@@ -9104,7 +9155,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
@@ -9176,7 +9227,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
@@ -9248,7 +9299,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
@@ -9320,7 +9371,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
@@ -9392,7 +9443,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
@@ -9464,7 +9515,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
@@ -9536,7 +9587,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
@@ -9608,7 +9659,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
@@ -9680,7 +9731,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
@@ -9752,7 +9803,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
@@ -9824,7 +9875,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
@@ -9896,7 +9947,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
@@ -9968,13 +10019,13 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA129" t="n">
-        <v>-4.83</v>
+        <v>-68.09</v>
       </c>
       <c r="AB129" t="n">
-        <v>7.18</v>
+        <v>-64.06999999999999</v>
       </c>
       <c r="AG129" t="b">
         <v>0</v>
@@ -10089,7 +10140,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
@@ -10210,7 +10261,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
@@ -10331,7 +10382,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
@@ -10452,7 +10503,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
@@ -10573,7 +10624,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
@@ -10694,7 +10745,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
@@ -10815,7 +10866,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
@@ -10933,7 +10984,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
@@ -11054,7 +11105,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
@@ -11175,7 +11226,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
@@ -11296,7 +11347,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
@@ -11417,7 +11468,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
@@ -11538,7 +11589,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
@@ -11659,7 +11710,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
@@ -11780,7 +11831,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
@@ -11792,7 +11843,7 @@
         <v>0</v>
       </c>
       <c r="AH144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
@@ -11901,19 +11952,19 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA145" t="n">
-        <v>0.63</v>
+        <v>-66.26000000000001</v>
       </c>
       <c r="AB145" t="n">
-        <v>21.88</v>
+        <v>-59.14</v>
       </c>
       <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH145" t="b">
         <v>1</v>
-      </c>
-      <c r="AH145" t="b">
-        <v>0</v>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
@@ -12022,11 +12073,14 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
       </c>
+      <c r="AB146" t="n">
+        <v>3.55</v>
+      </c>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -12140,11 +12194,14 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
       </c>
+      <c r="AB147" t="n">
+        <v>-1.16</v>
+      </c>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -12258,11 +12315,14 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
       </c>
+      <c r="AB148" t="n">
+        <v>3.2</v>
+      </c>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -12376,11 +12436,14 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
       </c>
+      <c r="AB149" t="n">
+        <v>15.17</v>
+      </c>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -12494,11 +12557,14 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
       </c>
+      <c r="AB150" t="n">
+        <v>-2.49</v>
+      </c>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -12612,11 +12678,14 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
       </c>
+      <c r="AB151" t="n">
+        <v>40.72</v>
+      </c>
       <c r="AG151" t="b">
         <v>1</v>
       </c>
@@ -12730,11 +12799,14 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
       </c>
+      <c r="AB152" t="n">
+        <v>-13.89</v>
+      </c>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -12848,7 +12920,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
@@ -12966,7 +13038,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
@@ -13084,7 +13156,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
@@ -13202,7 +13274,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
@@ -13320,7 +13392,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
@@ -13438,7 +13510,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
@@ -13556,13 +13628,13 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
       </c>
       <c r="AG159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH159" t="b">
         <v>1</v>
@@ -13674,7 +13746,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
@@ -13792,7 +13864,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
@@ -13910,7 +13982,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
@@ -14028,7 +14100,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
@@ -14146,7 +14218,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
@@ -14264,7 +14336,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
@@ -14382,7 +14454,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
@@ -14500,7 +14572,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
@@ -14729,7 +14801,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
@@ -14847,7 +14919,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
@@ -14965,16 +15037,16 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA171" t="n">
-        <v>7.75</v>
+        <v>-63.88</v>
       </c>
       <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH171" t="b">
         <v>1</v>
-      </c>
-      <c r="AH171" t="b">
-        <v>0</v>
       </c>
       <c r="AI171" t="inlineStr">
         <is>
@@ -15083,7 +15155,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
@@ -15201,7 +15273,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
@@ -15319,7 +15391,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
@@ -15437,7 +15509,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
@@ -15555,7 +15627,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
@@ -15673,7 +15745,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
@@ -15791,7 +15863,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
@@ -16020,7 +16092,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
@@ -16138,7 +16210,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
@@ -16256,7 +16328,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
@@ -16374,7 +16446,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
@@ -16492,7 +16564,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
@@ -16610,7 +16682,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
@@ -16728,16 +16800,16 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA186" t="n">
-        <v>12.62</v>
+        <v>-62.24</v>
       </c>
       <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH186" t="b">
         <v>1</v>
-      </c>
-      <c r="AH186" t="b">
-        <v>0</v>
       </c>
       <c r="AI186" t="inlineStr">
         <is>
@@ -16846,7 +16918,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
@@ -16964,7 +17036,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
@@ -17082,7 +17154,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
@@ -17200,7 +17272,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
@@ -17318,7 +17390,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
@@ -17436,7 +17508,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
@@ -17554,7 +17626,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
@@ -17672,7 +17744,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
@@ -17790,7 +17862,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
@@ -17908,7 +17980,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
@@ -18026,7 +18098,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
@@ -18366,7 +18438,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
@@ -18484,7 +18556,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
@@ -18602,16 +18674,16 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA202" t="n">
-        <v>21.12</v>
+        <v>-59.39</v>
       </c>
       <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH202" t="b">
         <v>1</v>
-      </c>
-      <c r="AH202" t="b">
-        <v>0</v>
       </c>
       <c r="AI202" t="inlineStr">
         <is>
@@ -18720,7 +18792,10 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>-3.05</v>
       </c>
       <c r="AG203" t="b">
         <v>0</v>
@@ -18835,7 +18910,10 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>2.61</v>
       </c>
       <c r="AG204" t="b">
         <v>0</v>
@@ -18950,7 +19028,10 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>12.16</v>
       </c>
       <c r="AG205" t="b">
         <v>0</v>
@@ -19065,7 +19146,10 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>-3.05</v>
       </c>
       <c r="AG206" t="b">
         <v>0</v>
@@ -19180,7 +19264,10 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>4.02</v>
       </c>
       <c r="AG207" t="b">
         <v>0</v>
@@ -19295,7 +19382,10 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>0.58</v>
       </c>
       <c r="AG208" t="b">
         <v>0</v>
@@ -19410,7 +19500,10 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>0.19</v>
       </c>
       <c r="AG209" t="b">
         <v>0</v>
@@ -19525,7 +19618,10 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>9.869999999999999</v>
       </c>
       <c r="AG210" t="b">
         <v>0</v>
@@ -19640,7 +19736,10 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>-16.12</v>
       </c>
       <c r="AG211" t="b">
         <v>0</v>
@@ -19755,7 +19854,10 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>-3.86</v>
       </c>
       <c r="AG212" t="b">
         <v>0</v>
@@ -19981,7 +20083,10 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>6.06</v>
       </c>
       <c r="AG214" t="b">
         <v>0</v>
@@ -20096,7 +20201,10 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>-17.67</v>
       </c>
       <c r="AG215" t="b">
         <v>0</v>
@@ -20211,7 +20319,10 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>-7.55</v>
       </c>
       <c r="AG216" t="b">
         <v>0</v>
@@ -20326,13 +20437,16 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>-61.53</v>
       </c>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
       <c r="AH217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
@@ -20441,7 +20555,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG218" t="b">
         <v>0</v>
@@ -20556,7 +20670,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG219" t="b">
         <v>0</v>
@@ -20671,7 +20785,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG220" t="b">
         <v>0</v>
@@ -20786,7 +20900,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG221" t="b">
         <v>0</v>
@@ -20901,7 +21015,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG222" t="b">
         <v>0</v>
@@ -21016,7 +21130,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG223" t="b">
         <v>0</v>
@@ -21131,7 +21245,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG224" t="b">
         <v>0</v>
@@ -21246,7 +21360,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG225" t="b">
         <v>1</v>
@@ -21361,7 +21475,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG226" t="b">
         <v>0</v>
@@ -21476,13 +21590,13 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
       <c r="AH227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
@@ -21591,7 +21705,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG228" t="b">
         <v>0</v>
@@ -21706,7 +21820,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG229" t="b">
         <v>0</v>
@@ -21821,7 +21935,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG230" t="b">
         <v>0</v>
@@ -21936,7 +22050,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG231" t="b">
         <v>0</v>
@@ -22162,7 +22276,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG233" t="b">
         <v>0</v>
@@ -22499,7 +22613,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG236" t="b">
         <v>0</v>
@@ -22614,7 +22728,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG237" t="b">
         <v>0</v>
@@ -22729,7 +22843,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG238" t="b">
         <v>0</v>
@@ -22844,7 +22958,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG239" t="b">
         <v>0</v>
@@ -22959,7 +23073,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG240" t="b">
         <v>0</v>
@@ -23074,13 +23188,13 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG241" t="b">
         <v>0</v>
       </c>
       <c r="AH241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI241" t="inlineStr">
         <is>
@@ -23189,7 +23303,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG242" t="b">
         <v>0</v>
@@ -23304,7 +23418,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG243" t="b">
         <v>0</v>
@@ -23419,7 +23533,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG244" t="b">
         <v>0</v>
@@ -23534,7 +23648,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG245" t="b">
         <v>0</v>
@@ -23649,7 +23763,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG246" t="b">
         <v>0</v>
@@ -23764,7 +23878,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG247" t="b">
         <v>0</v>
@@ -23879,7 +23993,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG248" t="b">
         <v>0</v>
@@ -23994,7 +24108,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG249" t="b">
         <v>0</v>
@@ -24109,13 +24223,13 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG250" t="b">
         <v>0</v>
       </c>
       <c r="AH250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI250" t="inlineStr">
         <is>
@@ -24224,7 +24338,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG251" t="b">
         <v>0</v>
@@ -24339,7 +24453,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG252" t="b">
         <v>0</v>
@@ -24454,7 +24568,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG253" t="b">
         <v>0</v>
@@ -24569,7 +24683,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG254" t="b">
         <v>0</v>
@@ -24684,7 +24798,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG255" t="b">
         <v>0</v>
@@ -25021,7 +25135,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG258" t="b">
         <v>0</v>
@@ -25358,7 +25472,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG261" t="b">
         <v>0</v>
@@ -25473,7 +25587,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG262" t="b">
         <v>0</v>
@@ -25588,7 +25702,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG263" t="b">
         <v>0</v>
@@ -25703,7 +25817,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG264" t="b">
         <v>0</v>
@@ -25929,7 +26043,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG266" t="b">
         <v>0</v>
@@ -26044,13 +26158,13 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG267" t="b">
         <v>0</v>
       </c>
       <c r="AH267" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI267" t="inlineStr">
         <is>
@@ -26159,7 +26273,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG268" t="b">
         <v>0</v>
@@ -26274,7 +26388,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG269" t="b">
         <v>0</v>
@@ -26389,7 +26503,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG270" t="b">
         <v>0</v>
@@ -26504,7 +26618,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG271" t="b">
         <v>0</v>
@@ -26619,7 +26733,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG272" t="b">
         <v>0</v>
@@ -26734,7 +26848,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG273" t="b">
         <v>0</v>
@@ -26849,7 +26963,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG274" t="b">
         <v>0</v>
@@ -26964,7 +27078,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG275" t="b">
         <v>0</v>
@@ -27079,7 +27193,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG276" t="b">
         <v>0</v>
@@ -27194,7 +27308,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG277" t="b">
         <v>0</v>
@@ -27309,7 +27423,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG278" t="b">
         <v>0</v>
@@ -27424,7 +27538,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG279" t="b">
         <v>0</v>
@@ -27539,7 +27653,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG280" t="b">
         <v>0</v>
@@ -27654,7 +27768,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG281" t="b">
         <v>0</v>
@@ -27769,13 +27883,13 @@
         </is>
       </c>
       <c r="Z282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH282" t="b">
         <v>1</v>
-      </c>
-      <c r="AG282" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH282" t="b">
-        <v>0</v>
       </c>
       <c r="AI282" t="inlineStr">
         <is>
@@ -27884,7 +27998,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG283" t="b">
         <v>0</v>
@@ -27999,7 +28113,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG284" t="b">
         <v>0</v>
@@ -28114,7 +28228,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG285" t="b">
         <v>0</v>
@@ -28229,7 +28343,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG286" t="b">
         <v>0</v>
@@ -28344,7 +28458,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG287" t="b">
         <v>0</v>
@@ -28459,7 +28573,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG288" t="b">
         <v>0</v>
@@ -28574,7 +28688,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG289" t="b">
         <v>0</v>
@@ -28689,7 +28803,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG290" t="b">
         <v>0</v>
@@ -28804,7 +28918,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG291" t="b">
         <v>0</v>
@@ -28919,7 +29033,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG292" t="b">
         <v>0</v>
@@ -29034,7 +29148,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG293" t="b">
         <v>0</v>
@@ -29482,7 +29596,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG297" t="b">
         <v>0</v>
@@ -29597,7 +29711,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG298" t="b">
         <v>0</v>
@@ -29712,13 +29826,13 @@
         </is>
       </c>
       <c r="Z299" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG299" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH299" t="b">
         <v>1</v>
-      </c>
-      <c r="AG299" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH299" t="b">
-        <v>0</v>
       </c>
       <c r="AI299" t="inlineStr">
         <is>
@@ -29938,7 +30052,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG301" t="b">
         <v>0</v>
@@ -30053,7 +30167,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG302" t="b">
         <v>0</v>
@@ -30168,7 +30282,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG303" t="b">
         <v>0</v>
@@ -30283,7 +30397,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG304" t="b">
         <v>0</v>
@@ -30398,7 +30512,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG305" t="b">
         <v>0</v>
@@ -30513,7 +30627,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG306" t="b">
         <v>0</v>
@@ -30628,7 +30742,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG307" t="b">
         <v>0</v>
@@ -30743,7 +30857,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG308" t="b">
         <v>0</v>
@@ -30858,7 +30972,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG309" t="b">
         <v>0</v>
@@ -30973,7 +31087,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG310" t="b">
         <v>0</v>
@@ -31088,7 +31202,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG311" t="b">
         <v>0</v>
@@ -31203,7 +31317,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG312" t="b">
         <v>0</v>
@@ -31318,7 +31432,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG313" t="b">
         <v>0</v>
@@ -31433,7 +31547,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG314" t="b">
         <v>0</v>
@@ -31548,7 +31662,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG315" t="b">
         <v>0</v>
@@ -31663,7 +31777,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG316" t="b">
         <v>0</v>
@@ -31778,7 +31892,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG317" t="b">
         <v>0</v>
@@ -31893,7 +32007,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG318" t="b">
         <v>0</v>
@@ -32008,7 +32122,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG319" t="b">
         <v>0</v>
@@ -32123,7 +32237,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG320" t="b">
         <v>0</v>
@@ -32238,7 +32352,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG321" t="b">
         <v>0</v>
@@ -32353,7 +32467,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG322" t="b">
         <v>0</v>
@@ -32468,7 +32582,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG323" t="b">
         <v>0</v>
@@ -32583,7 +32697,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG324" t="b">
         <v>0</v>
@@ -32920,7 +33034,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG327" t="b">
         <v>0</v>
@@ -33035,7 +33149,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG328" t="b">
         <v>0</v>
@@ -33150,7 +33264,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG329" t="b">
         <v>0</v>
@@ -33487,7 +33601,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG332" t="b">
         <v>0</v>
@@ -33501,8 +33615,3097 @@
         </is>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>82.33</v>
+      </c>
+      <c r="F333" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I333" t="b">
+        <v>0</v>
+      </c>
+      <c r="J333" t="n">
+        <v>10</v>
+      </c>
+      <c r="K333" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M333" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N333" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>72.67</v>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S333" t="n">
+        <v>7</v>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V333" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="W333" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="X333" t="n">
+        <v>62.124</v>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z333" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG333" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH333" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI333" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="F334" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I334" t="b">
+        <v>0</v>
+      </c>
+      <c r="J334" t="n">
+        <v>10</v>
+      </c>
+      <c r="K334" t="n">
+        <v>261.25</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M334" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N334" t="n">
+        <v>3</v>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P334" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S334" t="n">
+        <v>7</v>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V334" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="W334" t="n">
+        <v>285</v>
+      </c>
+      <c r="X334" t="n">
+        <v>220.875</v>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG334" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH334" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI334" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>台化</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>84.70999999999999</v>
+      </c>
+      <c r="F335" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I335" t="b">
+        <v>0</v>
+      </c>
+      <c r="J335" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K335" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M335" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N335" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P335" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>82.06</v>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S335" t="n">
+        <v>7</v>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V335" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="W335" t="n">
+        <v>87.36</v>
+      </c>
+      <c r="X335" t="n">
+        <v>67.70399999999999</v>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG335" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH335" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI335" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>72.64</v>
+      </c>
+      <c r="F336" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I336" t="b">
+        <v>0</v>
+      </c>
+      <c r="J336" t="n">
+        <v>10</v>
+      </c>
+      <c r="K336" t="n">
+        <v>815.1</v>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M336" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="N336" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P336" t="n">
+        <v>739</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S336" t="n">
+        <v>5.6026</v>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="V336" t="n">
+        <v>741</v>
+      </c>
+      <c r="W336" t="n">
+        <v>879.8008</v>
+      </c>
+      <c r="X336" t="n">
+        <v>699.485</v>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z336" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG336" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH336" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI336" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>80.29000000000001</v>
+      </c>
+      <c r="F337" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I337" t="b">
+        <v>0</v>
+      </c>
+      <c r="J337" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="K337" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M337" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="N337" t="n">
+        <v>3</v>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P337" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S337" t="n">
+        <v>7</v>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V337" t="n">
+        <v>315</v>
+      </c>
+      <c r="W337" t="n">
+        <v>378</v>
+      </c>
+      <c r="X337" t="n">
+        <v>292.95</v>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z337" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG337" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH337" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI337" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>82.41</v>
+      </c>
+      <c r="F338" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I338" t="b">
+        <v>0</v>
+      </c>
+      <c r="J338" t="n">
+        <v>10</v>
+      </c>
+      <c r="K338" t="n">
+        <v>1111</v>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M338" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N338" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>958</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>69.31999999999999</v>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S338" t="n">
+        <v>7</v>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V338" t="n">
+        <v>1010</v>
+      </c>
+      <c r="W338" t="n">
+        <v>1212</v>
+      </c>
+      <c r="X338" t="n">
+        <v>939.3</v>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z338" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG338" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH338" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI338" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="F339" t="n">
+        <v>58.12</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I339" t="b">
+        <v>0</v>
+      </c>
+      <c r="J339" t="n">
+        <v>10</v>
+      </c>
+      <c r="K339" t="n">
+        <v>397.65</v>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M339" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N339" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>349.25</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S339" t="n">
+        <v>6.9008</v>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V339" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="W339" t="n">
+        <v>414.1896</v>
+      </c>
+      <c r="X339" t="n">
+        <v>336.5536</v>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z339" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG339" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH339" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI339" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="F340" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I340" t="b">
+        <v>0</v>
+      </c>
+      <c r="J340" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K340" t="n">
+        <v>353.5</v>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M340" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N340" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P340" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S340" t="n">
+        <v>5.6669</v>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V340" t="n">
+        <v>337</v>
+      </c>
+      <c r="W340" t="n">
+        <v>388.4138</v>
+      </c>
+      <c r="X340" t="n">
+        <v>317.9025</v>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z340" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG340" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH340" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI340" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>79.64</v>
+      </c>
+      <c r="F341" t="n">
+        <v>60.91</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I341" t="b">
+        <v>0</v>
+      </c>
+      <c r="J341" t="n">
+        <v>10</v>
+      </c>
+      <c r="K341" t="n">
+        <v>569.8</v>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M341" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N341" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P341" t="n">
+        <v>524.5</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S341" t="n">
+        <v>7</v>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V341" t="n">
+        <v>518</v>
+      </c>
+      <c r="W341" t="n">
+        <v>621.6</v>
+      </c>
+      <c r="X341" t="n">
+        <v>481.74</v>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z341" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG341" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH341" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI341" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>72.79000000000001</v>
+      </c>
+      <c r="F342" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I342" t="b">
+        <v>0</v>
+      </c>
+      <c r="J342" t="n">
+        <v>10</v>
+      </c>
+      <c r="K342" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M342" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="N342" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S342" t="n">
+        <v>6.2746</v>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V342" t="n">
+        <v>112</v>
+      </c>
+      <c r="W342" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="X342" t="n">
+        <v>104.9725</v>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z342" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG342" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH342" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>74.81999999999999</v>
+      </c>
+      <c r="F343" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I343" t="b">
+        <v>0</v>
+      </c>
+      <c r="J343" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="K343" t="n">
+        <v>152.08</v>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M343" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N343" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P343" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S343" t="n">
+        <v>7</v>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V343" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="W343" t="n">
+        <v>171.0027</v>
+      </c>
+      <c r="X343" t="n">
+        <v>133.455</v>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z343" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG343" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH343" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI343" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>78.22</v>
+      </c>
+      <c r="F344" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I344" t="b">
+        <v>0</v>
+      </c>
+      <c r="J344" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="K344" t="n">
+        <v>116</v>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M344" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N344" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>73.63</v>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S344" t="n">
+        <v>7</v>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V344" t="n">
+        <v>109</v>
+      </c>
+      <c r="W344" t="n">
+        <v>127.7798</v>
+      </c>
+      <c r="X344" t="n">
+        <v>101.37</v>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z344" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG344" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH344" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI344" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="F345" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I345" t="b">
+        <v>0</v>
+      </c>
+      <c r="J345" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K345" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M345" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N345" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P345" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S345" t="n">
+        <v>7</v>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V345" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="W345" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="X345" t="n">
+        <v>33.015</v>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z345" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG345" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH345" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI345" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>74.78</v>
+      </c>
+      <c r="F346" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I346" t="b">
+        <v>0</v>
+      </c>
+      <c r="J346" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="K346" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M346" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N346" t="n">
+        <v>7</v>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P346" t="n">
+        <v>38.82</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S346" t="n">
+        <v>7</v>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V346" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="W346" t="n">
+        <v>45.6263</v>
+      </c>
+      <c r="X346" t="n">
+        <v>37.665</v>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z346" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG346" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH346" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI346" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>90.23999999999999</v>
+      </c>
+      <c r="F347" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I347" t="b">
+        <v>0</v>
+      </c>
+      <c r="J347" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K347" t="n">
+        <v>42</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M347" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N347" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P347" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S347" t="n">
+        <v>7</v>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V347" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="W347" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="X347" t="n">
+        <v>38.316</v>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG347" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH347" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI347" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>76.93000000000001</v>
+      </c>
+      <c r="F348" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I348" t="b">
+        <v>0</v>
+      </c>
+      <c r="J348" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K348" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M348" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N348" t="n">
+        <v>7</v>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S348" t="n">
+        <v>7</v>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V348" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="W348" t="n">
+        <v>47.7599</v>
+      </c>
+      <c r="X348" t="n">
+        <v>39.1995</v>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG348" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH348" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI348" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="F349" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I349" t="b">
+        <v>0</v>
+      </c>
+      <c r="J349" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="K349" t="n">
+        <v>37.74</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M349" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N349" t="n">
+        <v>7</v>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P349" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S349" t="n">
+        <v>7</v>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V349" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="W349" t="n">
+        <v>40.7029</v>
+      </c>
+      <c r="X349" t="n">
+        <v>33.7125</v>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z349" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG349" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH349" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI349" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>晶豪科</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>79.87</v>
+      </c>
+      <c r="F350" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I350" t="b">
+        <v>0</v>
+      </c>
+      <c r="J350" t="n">
+        <v>10</v>
+      </c>
+      <c r="K350" t="n">
+        <v>309.65</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M350" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N350" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P350" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>61.36</v>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S350" t="n">
+        <v>7</v>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V350" t="n">
+        <v>281.5</v>
+      </c>
+      <c r="W350" t="n">
+        <v>337.8</v>
+      </c>
+      <c r="X350" t="n">
+        <v>261.795</v>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z350" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG350" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH350" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI350" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>85.97</v>
+      </c>
+      <c r="F351" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I351" t="b">
+        <v>0</v>
+      </c>
+      <c r="J351" t="n">
+        <v>10</v>
+      </c>
+      <c r="K351" t="n">
+        <v>8591</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M351" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N351" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P351" t="n">
+        <v>6525</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>80.28</v>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S351" t="n">
+        <v>7</v>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V351" t="n">
+        <v>7810</v>
+      </c>
+      <c r="W351" t="n">
+        <v>9372</v>
+      </c>
+      <c r="X351" t="n">
+        <v>7263.3</v>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG351" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH351" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI351" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>智原</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>72.41</v>
+      </c>
+      <c r="F352" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I352" t="b">
+        <v>0</v>
+      </c>
+      <c r="J352" t="n">
+        <v>10</v>
+      </c>
+      <c r="K352" t="n">
+        <v>202.95</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M352" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N352" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P352" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S352" t="n">
+        <v>7</v>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V352" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="W352" t="n">
+        <v>218.71</v>
+      </c>
+      <c r="X352" t="n">
+        <v>171.585</v>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z352" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG352" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH352" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI352" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="F353" t="n">
+        <v>55.73</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I353" t="b">
+        <v>0</v>
+      </c>
+      <c r="J353" t="n">
+        <v>10</v>
+      </c>
+      <c r="K353" t="n">
+        <v>552.2</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M353" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N353" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P353" t="n">
+        <v>477.25</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S353" t="n">
+        <v>7</v>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V353" t="n">
+        <v>502</v>
+      </c>
+      <c r="W353" t="n">
+        <v>602.4</v>
+      </c>
+      <c r="X353" t="n">
+        <v>466.86</v>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z353" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG353" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH353" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI353" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>75.76000000000001</v>
+      </c>
+      <c r="F354" t="n">
+        <v>48.23</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I354" t="b">
+        <v>0</v>
+      </c>
+      <c r="J354" t="n">
+        <v>10</v>
+      </c>
+      <c r="K354" t="n">
+        <v>3734.5</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M354" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N354" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P354" t="n">
+        <v>3117.5</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S354" t="n">
+        <v>7</v>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V354" t="n">
+        <v>3395</v>
+      </c>
+      <c r="W354" t="n">
+        <v>4074</v>
+      </c>
+      <c r="X354" t="n">
+        <v>3157.35</v>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI354" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ354" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>70.20999999999999</v>
+      </c>
+      <c r="F355" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I355" t="b">
+        <v>0</v>
+      </c>
+      <c r="J355" t="n">
+        <v>10</v>
+      </c>
+      <c r="K355" t="n">
+        <v>516.45</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M355" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N355" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P355" t="n">
+        <v>420.75</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>60.91</v>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S355" t="n">
+        <v>7</v>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V355" t="n">
+        <v>469.5</v>
+      </c>
+      <c r="W355" t="n">
+        <v>563.4</v>
+      </c>
+      <c r="X355" t="n">
+        <v>436.635</v>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI355" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ355" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>72.84</v>
+      </c>
+      <c r="F356" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I356" t="b">
+        <v>0</v>
+      </c>
+      <c r="J356" t="n">
+        <v>10</v>
+      </c>
+      <c r="K356" t="n">
+        <v>256.85</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M356" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N356" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P356" t="n">
+        <v>220.75</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>58.26</v>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S356" t="n">
+        <v>7</v>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V356" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="W356" t="n">
+        <v>280.2</v>
+      </c>
+      <c r="X356" t="n">
+        <v>217.155</v>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI356" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ356" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>74.01000000000001</v>
+      </c>
+      <c r="F357" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I357" t="b">
+        <v>0</v>
+      </c>
+      <c r="J357" t="n">
+        <v>10</v>
+      </c>
+      <c r="K357" t="n">
+        <v>461.45</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M357" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N357" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P357" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>60.37</v>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S357" t="n">
+        <v>7</v>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V357" t="n">
+        <v>419.5</v>
+      </c>
+      <c r="W357" t="n">
+        <v>503.4</v>
+      </c>
+      <c r="X357" t="n">
+        <v>390.135</v>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI357" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ357" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="F358" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I358" t="b">
+        <v>0</v>
+      </c>
+      <c r="J358" t="n">
+        <v>10</v>
+      </c>
+      <c r="K358" t="n">
+        <v>4620</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M358" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N358" t="n">
+        <v>5</v>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P358" t="n">
+        <v>3967.5</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S358" t="n">
+        <v>7</v>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V358" t="n">
+        <v>4200</v>
+      </c>
+      <c r="W358" t="n">
+        <v>5040</v>
+      </c>
+      <c r="X358" t="n">
+        <v>3906</v>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z358" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG358" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH358" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI358" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>81.41</v>
+      </c>
+      <c r="F359" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I359" t="b">
+        <v>0</v>
+      </c>
+      <c r="J359" t="n">
+        <v>10</v>
+      </c>
+      <c r="K359" t="n">
+        <v>2871</v>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M359" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N359" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P359" t="n">
+        <v>2464.22</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S359" t="n">
+        <v>7</v>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V359" t="n">
+        <v>2610</v>
+      </c>
+      <c r="W359" t="n">
+        <v>3132</v>
+      </c>
+      <c r="X359" t="n">
+        <v>2427.3</v>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG359" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH359" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI359" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ332"/>
+  <autoFilter ref="A1:AJ359"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33752,7 +36955,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23:29</t>
+          <t>2026-09-02 14:24:01</t>
         </is>
       </c>
     </row>
@@ -33799,7 +37002,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>331</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7">
@@ -33819,7 +37022,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>331</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$359</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$383</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ359"/>
+  <dimension ref="A1:AJ383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2755,7 +2755,7 @@
         <v>9.41</v>
       </c>
       <c r="AG29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH29" t="b">
         <v>0</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA37" t="n">
         <v>-63.07</v>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -5641,7 +5641,7 @@
         <v>13.75</v>
       </c>
       <c r="AG68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH68" t="b">
         <v>0</v>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA73" t="n">
         <v>-64.53</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -6141,7 +6141,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -6149,6 +6149,9 @@
       <c r="AB75" t="n">
         <v>6.94</v>
       </c>
+      <c r="AC75" t="n">
+        <v>0.28</v>
+      </c>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -6213,7 +6216,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -6221,6 +6224,9 @@
       <c r="AB76" t="n">
         <v>0.68</v>
       </c>
+      <c r="AC76" t="n">
+        <v>-6.46</v>
+      </c>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -6285,7 +6291,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -6293,6 +6299,9 @@
       <c r="AB77" t="n">
         <v>11.69</v>
       </c>
+      <c r="AC77" t="n">
+        <v>10.95</v>
+      </c>
       <c r="AG77" t="b">
         <v>1</v>
       </c>
@@ -6357,7 +6366,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6365,6 +6374,9 @@
       <c r="AB78" t="n">
         <v>-12.33</v>
       </c>
+      <c r="AC78" t="n">
+        <v>-10.93</v>
+      </c>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -6429,7 +6441,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6437,6 +6449,9 @@
       <c r="AB79" t="n">
         <v>-3.3</v>
       </c>
+      <c r="AC79" t="n">
+        <v>-3.44</v>
+      </c>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -6501,7 +6516,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6509,11 +6524,14 @@
       <c r="AB80" t="n">
         <v>5.25</v>
       </c>
+      <c r="AC80" t="n">
+        <v>-7.1</v>
+      </c>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AH80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
@@ -6573,7 +6591,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -6581,6 +6599,9 @@
       <c r="AB81" t="n">
         <v>7.89</v>
       </c>
+      <c r="AC81" t="n">
+        <v>10.9</v>
+      </c>
       <c r="AG81" t="b">
         <v>1</v>
       </c>
@@ -6645,7 +6666,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -6653,6 +6674,9 @@
       <c r="AB82" t="n">
         <v>29.71</v>
       </c>
+      <c r="AC82" t="n">
+        <v>32</v>
+      </c>
       <c r="AG82" t="b">
         <v>1</v>
       </c>
@@ -6717,7 +6741,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -6725,6 +6749,9 @@
       <c r="AB83" t="n">
         <v>-1.5</v>
       </c>
+      <c r="AC83" t="n">
+        <v>6.63</v>
+      </c>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -6789,7 +6816,7 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -6797,6 +6824,9 @@
       <c r="AB84" t="n">
         <v>48.39</v>
       </c>
+      <c r="AC84" t="n">
+        <v>53.43</v>
+      </c>
       <c r="AG84" t="b">
         <v>1</v>
       </c>
@@ -6861,7 +6891,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -6869,6 +6899,9 @@
       <c r="AB85" t="n">
         <v>-8.880000000000001</v>
       </c>
+      <c r="AC85" t="n">
+        <v>-4.31</v>
+      </c>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -6933,7 +6966,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -6941,6 +6974,9 @@
       <c r="AB86" t="n">
         <v>6.86</v>
       </c>
+      <c r="AC86" t="n">
+        <v>4.69</v>
+      </c>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -7005,7 +7041,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -7013,6 +7049,9 @@
       <c r="AB87" t="n">
         <v>-7.64</v>
       </c>
+      <c r="AC87" t="n">
+        <v>-3.34</v>
+      </c>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -7077,7 +7116,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -7085,6 +7124,9 @@
       <c r="AB88" t="n">
         <v>7.96</v>
       </c>
+      <c r="AC88" t="n">
+        <v>-6.57</v>
+      </c>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -7149,7 +7191,7 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA89" t="n">
         <v>-65.06999999999999</v>
@@ -7157,6 +7199,9 @@
       <c r="AB89" t="n">
         <v>-62.36</v>
       </c>
+      <c r="AC89" t="n">
+        <v>-59.23</v>
+      </c>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -7283,7 +7328,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -7291,6 +7336,9 @@
       <c r="AB91" t="n">
         <v>0</v>
       </c>
+      <c r="AC91" t="n">
+        <v>-4.29</v>
+      </c>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -7355,7 +7403,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -7427,7 +7475,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -7499,7 +7547,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -7571,7 +7619,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -7643,7 +7691,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -7715,7 +7763,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -7787,7 +7835,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -7859,7 +7907,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -7931,7 +7979,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -8003,7 +8051,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -8075,7 +8123,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -8147,7 +8195,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -8156,7 +8204,7 @@
         <v>3.48</v>
       </c>
       <c r="AG103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH103" t="b">
         <v>0</v>
@@ -8219,7 +8267,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -8291,7 +8339,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -8363,7 +8411,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -8435,7 +8483,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -8507,7 +8555,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -8579,7 +8627,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -8651,7 +8699,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -8723,7 +8771,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -8795,7 +8843,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA112" t="n">
         <v>-67.41</v>
@@ -8867,7 +8915,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
@@ -8939,7 +8987,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
@@ -9011,7 +9059,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
@@ -9083,7 +9131,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
@@ -9155,7 +9203,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
@@ -9227,7 +9275,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
@@ -9299,7 +9347,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
@@ -9371,7 +9419,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
@@ -9443,7 +9491,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
@@ -9515,7 +9563,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
@@ -9587,7 +9635,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
@@ -9596,7 +9644,7 @@
         <v>7.8</v>
       </c>
       <c r="AG123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH123" t="b">
         <v>0</v>
@@ -9659,7 +9707,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
@@ -9731,7 +9779,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
@@ -9803,7 +9851,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
@@ -9875,7 +9923,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
@@ -9947,7 +9995,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
@@ -10019,7 +10067,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA129" t="n">
         <v>-68.09</v>
@@ -10140,7 +10188,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
@@ -10261,7 +10309,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
@@ -10382,7 +10430,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
@@ -10503,7 +10551,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
@@ -10624,7 +10672,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
@@ -10745,7 +10793,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
@@ -10757,7 +10805,7 @@
         <v>0</v>
       </c>
       <c r="AH135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
@@ -10866,7 +10914,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
@@ -10984,7 +11032,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
@@ -11105,7 +11153,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
@@ -11114,7 +11162,7 @@
         <v>4.72</v>
       </c>
       <c r="AG138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH138" t="b">
         <v>0</v>
@@ -11226,7 +11274,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
@@ -11235,7 +11283,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="AG139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH139" t="b">
         <v>0</v>
@@ -11347,7 +11395,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
@@ -11468,7 +11516,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
@@ -11589,7 +11637,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
@@ -11710,7 +11758,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
@@ -11831,7 +11879,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
@@ -11952,7 +12000,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA145" t="n">
         <v>-66.26000000000001</v>
@@ -12073,7 +12121,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
@@ -12194,7 +12242,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
@@ -12315,7 +12363,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
@@ -12436,7 +12484,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
@@ -12557,7 +12605,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
@@ -12678,7 +12726,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
@@ -12799,7 +12847,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
@@ -12920,11 +12968,14 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
       </c>
+      <c r="AB153" t="n">
+        <v>-1.41</v>
+      </c>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -13038,11 +13089,14 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
       </c>
+      <c r="AB154" t="n">
+        <v>1.44</v>
+      </c>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -13156,11 +13210,14 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
       </c>
+      <c r="AB155" t="n">
+        <v>-3.32</v>
+      </c>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -13274,11 +13331,14 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
       </c>
+      <c r="AB156" t="n">
+        <v>-0.34</v>
+      </c>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -13392,11 +13452,14 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
       </c>
+      <c r="AB157" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -13510,11 +13573,14 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
       </c>
+      <c r="AB158" t="n">
+        <v>-6</v>
+      </c>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -13628,11 +13694,14 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
       </c>
+      <c r="AB159" t="n">
+        <v>10.33</v>
+      </c>
       <c r="AG159" t="b">
         <v>1</v>
       </c>
@@ -13746,11 +13815,14 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
       </c>
+      <c r="AB160" t="n">
+        <v>-11.61</v>
+      </c>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -13864,11 +13936,14 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
       </c>
+      <c r="AB161" t="n">
+        <v>-1.17</v>
+      </c>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -13982,11 +14057,14 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
       </c>
+      <c r="AB162" t="n">
+        <v>-7.64</v>
+      </c>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -14100,11 +14178,14 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
       </c>
+      <c r="AB163" t="n">
+        <v>-1.85</v>
+      </c>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -14218,11 +14299,14 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
       </c>
+      <c r="AB164" t="n">
+        <v>-3.18</v>
+      </c>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -14336,11 +14420,14 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
       </c>
+      <c r="AB165" t="n">
+        <v>6.94</v>
+      </c>
       <c r="AG165" t="b">
         <v>1</v>
       </c>
@@ -14454,11 +14541,14 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
       </c>
+      <c r="AB166" t="n">
+        <v>29.65</v>
+      </c>
       <c r="AG166" t="b">
         <v>1</v>
       </c>
@@ -14572,11 +14662,14 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
       </c>
+      <c r="AB167" t="n">
+        <v>-19.04</v>
+      </c>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -14801,11 +14894,14 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
       </c>
+      <c r="AB169" t="n">
+        <v>-8.93</v>
+      </c>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -14919,11 +15015,14 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
       </c>
+      <c r="AB170" t="n">
+        <v>3.02</v>
+      </c>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -15037,11 +15136,14 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA171" t="n">
         <v>-63.88</v>
       </c>
+      <c r="AB171" t="n">
+        <v>-60.87</v>
+      </c>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -15155,7 +15257,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
@@ -15273,7 +15375,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
@@ -15391,7 +15493,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
@@ -15509,7 +15611,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
@@ -15627,7 +15729,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
@@ -15745,7 +15847,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
@@ -15863,7 +15965,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
@@ -16092,7 +16194,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
@@ -16210,7 +16312,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
@@ -16328,7 +16430,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
@@ -16446,7 +16548,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
@@ -16564,7 +16666,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
@@ -16682,7 +16784,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
@@ -16800,7 +16902,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA186" t="n">
         <v>-62.24</v>
@@ -16918,7 +17020,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
@@ -17036,7 +17138,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
@@ -17154,7 +17256,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
@@ -17272,7 +17374,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
@@ -17281,7 +17383,7 @@
         <v>0</v>
       </c>
       <c r="AH190" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI190" t="inlineStr">
         <is>
@@ -17390,7 +17492,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
@@ -17508,7 +17610,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
@@ -17626,7 +17728,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
@@ -17744,13 +17846,13 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
       </c>
       <c r="AG194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH194" t="b">
         <v>0</v>
@@ -17862,7 +17964,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
@@ -17980,7 +18082,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
@@ -18098,7 +18200,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
@@ -18438,7 +18540,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
@@ -18556,7 +18658,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
@@ -18674,7 +18776,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
@@ -18792,7 +18894,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
@@ -18910,7 +19012,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
@@ -19028,7 +19130,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
@@ -19146,7 +19248,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
@@ -19264,7 +19366,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
@@ -19382,7 +19484,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
@@ -19500,7 +19602,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
@@ -19509,7 +19611,7 @@
         <v>0</v>
       </c>
       <c r="AH209" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI209" t="inlineStr">
         <is>
@@ -19618,7 +19720,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -19736,7 +19838,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
@@ -19854,7 +19956,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
@@ -20083,7 +20185,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
@@ -20201,7 +20303,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
@@ -20319,7 +20421,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
@@ -20437,7 +20539,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
@@ -20555,7 +20657,10 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>4.12</v>
       </c>
       <c r="AG218" t="b">
         <v>0</v>
@@ -20670,7 +20775,10 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>-3.27</v>
       </c>
       <c r="AG219" t="b">
         <v>0</v>
@@ -20785,7 +20893,10 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>-6.23</v>
       </c>
       <c r="AG220" t="b">
         <v>0</v>
@@ -20900,7 +21011,10 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>-3.34</v>
       </c>
       <c r="AG221" t="b">
         <v>0</v>
@@ -21015,7 +21129,10 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>-0.66</v>
       </c>
       <c r="AG222" t="b">
         <v>0</v>
@@ -21130,7 +21247,10 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>-2.52</v>
       </c>
       <c r="AG223" t="b">
         <v>0</v>
@@ -21245,7 +21365,10 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>0.31</v>
       </c>
       <c r="AG224" t="b">
         <v>0</v>
@@ -21360,7 +21483,10 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>6.8</v>
       </c>
       <c r="AG225" t="b">
         <v>1</v>
@@ -21475,7 +21601,10 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AG226" t="b">
         <v>0</v>
@@ -21590,7 +21719,10 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>-11.74</v>
       </c>
       <c r="AG227" t="b">
         <v>0</v>
@@ -21705,7 +21837,10 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>3.89</v>
       </c>
       <c r="AG228" t="b">
         <v>0</v>
@@ -21820,7 +21955,10 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>1.09</v>
       </c>
       <c r="AG229" t="b">
         <v>0</v>
@@ -21935,7 +22073,10 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>-1.2</v>
       </c>
       <c r="AG230" t="b">
         <v>0</v>
@@ -22050,7 +22191,10 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>-21.78</v>
       </c>
       <c r="AG231" t="b">
         <v>0</v>
@@ -22276,7 +22420,10 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>-15.21</v>
       </c>
       <c r="AG233" t="b">
         <v>0</v>
@@ -22613,7 +22760,10 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>-2.03</v>
       </c>
       <c r="AG236" t="b">
         <v>0</v>
@@ -22728,7 +22878,10 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>-3.3</v>
       </c>
       <c r="AG237" t="b">
         <v>0</v>
@@ -22843,7 +22996,10 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>-2.37</v>
       </c>
       <c r="AG238" t="b">
         <v>0</v>
@@ -22958,7 +23114,10 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>-13.46</v>
       </c>
       <c r="AG239" t="b">
         <v>0</v>
@@ -23073,7 +23232,10 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>-6.37</v>
       </c>
       <c r="AG240" t="b">
         <v>0</v>
@@ -23188,7 +23350,10 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>-63.68</v>
       </c>
       <c r="AG241" t="b">
         <v>0</v>
@@ -23303,7 +23468,10 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>-4.29</v>
       </c>
       <c r="AG242" t="b">
         <v>0</v>
@@ -23418,7 +23586,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG243" t="b">
         <v>0</v>
@@ -23533,7 +23701,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG244" t="b">
         <v>0</v>
@@ -23648,7 +23816,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG245" t="b">
         <v>0</v>
@@ -23763,7 +23931,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG246" t="b">
         <v>0</v>
@@ -23878,7 +24046,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG247" t="b">
         <v>0</v>
@@ -23993,7 +24161,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG248" t="b">
         <v>0</v>
@@ -24108,7 +24276,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG249" t="b">
         <v>0</v>
@@ -24223,7 +24391,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG250" t="b">
         <v>0</v>
@@ -24338,7 +24506,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG251" t="b">
         <v>0</v>
@@ -24453,7 +24621,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG252" t="b">
         <v>0</v>
@@ -24568,7 +24736,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG253" t="b">
         <v>0</v>
@@ -24683,7 +24851,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG254" t="b">
         <v>0</v>
@@ -24798,7 +24966,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG255" t="b">
         <v>0</v>
@@ -25135,7 +25303,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG258" t="b">
         <v>0</v>
@@ -25472,7 +25640,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG261" t="b">
         <v>0</v>
@@ -25587,7 +25755,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG262" t="b">
         <v>0</v>
@@ -25702,7 +25870,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG263" t="b">
         <v>0</v>
@@ -25817,7 +25985,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG264" t="b">
         <v>0</v>
@@ -26043,7 +26211,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG266" t="b">
         <v>0</v>
@@ -26158,7 +26326,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG267" t="b">
         <v>0</v>
@@ -26273,7 +26441,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG268" t="b">
         <v>0</v>
@@ -26388,7 +26556,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG269" t="b">
         <v>0</v>
@@ -26503,7 +26671,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG270" t="b">
         <v>0</v>
@@ -26618,7 +26786,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG271" t="b">
         <v>0</v>
@@ -26733,7 +26901,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG272" t="b">
         <v>0</v>
@@ -26848,7 +27016,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG273" t="b">
         <v>0</v>
@@ -26963,7 +27131,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG274" t="b">
         <v>0</v>
@@ -27078,7 +27246,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG275" t="b">
         <v>0</v>
@@ -27193,7 +27361,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG276" t="b">
         <v>0</v>
@@ -27308,7 +27476,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG277" t="b">
         <v>0</v>
@@ -27423,7 +27591,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG278" t="b">
         <v>0</v>
@@ -27538,7 +27706,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG279" t="b">
         <v>0</v>
@@ -27653,7 +27821,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG280" t="b">
         <v>0</v>
@@ -27768,7 +27936,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG281" t="b">
         <v>0</v>
@@ -27883,7 +28051,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG282" t="b">
         <v>0</v>
@@ -27998,7 +28166,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG283" t="b">
         <v>0</v>
@@ -28113,7 +28281,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG284" t="b">
         <v>0</v>
@@ -28228,7 +28396,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG285" t="b">
         <v>0</v>
@@ -28343,7 +28511,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG286" t="b">
         <v>0</v>
@@ -28458,7 +28626,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG287" t="b">
         <v>0</v>
@@ -28573,7 +28741,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG288" t="b">
         <v>0</v>
@@ -28688,7 +28856,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG289" t="b">
         <v>0</v>
@@ -28803,7 +28971,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG290" t="b">
         <v>0</v>
@@ -28918,13 +29086,13 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG291" t="b">
         <v>0</v>
       </c>
       <c r="AH291" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI291" t="inlineStr">
         <is>
@@ -29033,7 +29201,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG292" t="b">
         <v>0</v>
@@ -29148,7 +29316,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG293" t="b">
         <v>0</v>
@@ -29596,7 +29764,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG297" t="b">
         <v>0</v>
@@ -29711,7 +29879,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG298" t="b">
         <v>0</v>
@@ -29826,7 +29994,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG299" t="b">
         <v>0</v>
@@ -30052,7 +30220,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG301" t="b">
         <v>0</v>
@@ -30167,7 +30335,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG302" t="b">
         <v>0</v>
@@ -30282,7 +30450,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG303" t="b">
         <v>0</v>
@@ -30397,7 +30565,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG304" t="b">
         <v>0</v>
@@ -30512,7 +30680,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG305" t="b">
         <v>0</v>
@@ -30627,13 +30795,13 @@
         </is>
       </c>
       <c r="Z306" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG306" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH306" t="b">
         <v>1</v>
-      </c>
-      <c r="AG306" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH306" t="b">
-        <v>0</v>
       </c>
       <c r="AI306" t="inlineStr">
         <is>
@@ -30742,7 +30910,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG307" t="b">
         <v>0</v>
@@ -30857,7 +31025,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG308" t="b">
         <v>0</v>
@@ -30972,7 +31140,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG309" t="b">
         <v>0</v>
@@ -31087,13 +31255,13 @@
         </is>
       </c>
       <c r="Z310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG310" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH310" t="b">
         <v>1</v>
-      </c>
-      <c r="AG310" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH310" t="b">
-        <v>0</v>
       </c>
       <c r="AI310" t="inlineStr">
         <is>
@@ -31202,7 +31370,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG311" t="b">
         <v>0</v>
@@ -31317,7 +31485,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG312" t="b">
         <v>0</v>
@@ -31432,7 +31600,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG313" t="b">
         <v>0</v>
@@ -31547,13 +31715,13 @@
         </is>
       </c>
       <c r="Z314" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG314" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH314" t="b">
         <v>1</v>
-      </c>
-      <c r="AG314" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH314" t="b">
-        <v>0</v>
       </c>
       <c r="AI314" t="inlineStr">
         <is>
@@ -31662,7 +31830,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG315" t="b">
         <v>0</v>
@@ -31777,7 +31945,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG316" t="b">
         <v>0</v>
@@ -31892,7 +32060,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG317" t="b">
         <v>0</v>
@@ -32007,7 +32175,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG318" t="b">
         <v>0</v>
@@ -32122,7 +32290,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG319" t="b">
         <v>0</v>
@@ -32237,7 +32405,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG320" t="b">
         <v>0</v>
@@ -32352,7 +32520,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG321" t="b">
         <v>0</v>
@@ -32467,7 +32635,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG322" t="b">
         <v>0</v>
@@ -32582,7 +32750,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG323" t="b">
         <v>0</v>
@@ -32697,7 +32865,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG324" t="b">
         <v>0</v>
@@ -33034,7 +33202,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG327" t="b">
         <v>0</v>
@@ -33149,7 +33317,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG328" t="b">
         <v>0</v>
@@ -33264,7 +33432,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG329" t="b">
         <v>0</v>
@@ -33601,13 +33769,13 @@
         </is>
       </c>
       <c r="Z332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG332" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH332" t="b">
         <v>1</v>
-      </c>
-      <c r="AG332" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH332" t="b">
-        <v>0</v>
       </c>
       <c r="AI332" t="inlineStr">
         <is>
@@ -33716,7 +33884,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG333" t="b">
         <v>0</v>
@@ -33831,13 +33999,13 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG334" t="b">
         <v>0</v>
       </c>
       <c r="AH334" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI334" t="inlineStr">
         <is>
@@ -33946,7 +34114,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG335" t="b">
         <v>0</v>
@@ -34061,7 +34229,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG336" t="b">
         <v>0</v>
@@ -34176,7 +34344,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG337" t="b">
         <v>0</v>
@@ -34291,7 +34459,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG338" t="b">
         <v>0</v>
@@ -34406,7 +34574,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG339" t="b">
         <v>0</v>
@@ -34521,7 +34689,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG340" t="b">
         <v>0</v>
@@ -34636,13 +34804,13 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG341" t="b">
         <v>0</v>
       </c>
       <c r="AH341" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI341" t="inlineStr">
         <is>
@@ -34751,7 +34919,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG342" t="b">
         <v>0</v>
@@ -34866,7 +35034,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG343" t="b">
         <v>0</v>
@@ -34981,7 +35149,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG344" t="b">
         <v>0</v>
@@ -35096,7 +35264,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG345" t="b">
         <v>0</v>
@@ -35211,7 +35379,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG346" t="b">
         <v>0</v>
@@ -35326,7 +35494,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG347" t="b">
         <v>0</v>
@@ -35441,7 +35609,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG348" t="b">
         <v>0</v>
@@ -35556,7 +35724,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG349" t="b">
         <v>0</v>
@@ -35671,7 +35839,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG350" t="b">
         <v>0</v>
@@ -35786,13 +35954,13 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG351" t="b">
         <v>0</v>
       </c>
       <c r="AH351" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI351" t="inlineStr">
         <is>
@@ -35901,7 +36069,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG352" t="b">
         <v>0</v>
@@ -36016,7 +36184,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG353" t="b">
         <v>0</v>
@@ -36575,7 +36743,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG358" t="b">
         <v>0</v>
@@ -36690,7 +36858,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG359" t="b">
         <v>0</v>
@@ -36704,8 +36872,2756 @@
         </is>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="F360" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I360" t="b">
+        <v>0</v>
+      </c>
+      <c r="J360" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K360" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M360" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N360" t="n">
+        <v>10</v>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P360" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S360" t="n">
+        <v>3.044</v>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V360" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="W360" t="n">
+        <v>38.2045</v>
+      </c>
+      <c r="X360" t="n">
+        <v>34.1285</v>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z360" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG360" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH360" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI360" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="F361" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I361" t="b">
+        <v>0</v>
+      </c>
+      <c r="J361" t="n">
+        <v>10</v>
+      </c>
+      <c r="K361" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M361" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N361" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P361" t="n">
+        <v>63.55</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S361" t="n">
+        <v>7</v>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V361" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="W361" t="n">
+        <v>78.84</v>
+      </c>
+      <c r="X361" t="n">
+        <v>61.101</v>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z361" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG361" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH361" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI361" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>72.95</v>
+      </c>
+      <c r="F362" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I362" t="b">
+        <v>0</v>
+      </c>
+      <c r="J362" t="n">
+        <v>10</v>
+      </c>
+      <c r="K362" t="n">
+        <v>243.1</v>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M362" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N362" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P362" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>61.22</v>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S362" t="n">
+        <v>7</v>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V362" t="n">
+        <v>221</v>
+      </c>
+      <c r="W362" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="X362" t="n">
+        <v>205.53</v>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG362" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH362" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI362" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>72.94</v>
+      </c>
+      <c r="F363" t="n">
+        <v>49.96</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I363" t="b">
+        <v>0</v>
+      </c>
+      <c r="J363" t="n">
+        <v>10</v>
+      </c>
+      <c r="K363" t="n">
+        <v>328.9</v>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M363" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N363" t="n">
+        <v>5</v>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P363" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S363" t="n">
+        <v>7</v>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V363" t="n">
+        <v>299</v>
+      </c>
+      <c r="W363" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="X363" t="n">
+        <v>278.07</v>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG363" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH363" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI363" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="F364" t="n">
+        <v>57</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I364" t="b">
+        <v>0</v>
+      </c>
+      <c r="J364" t="n">
+        <v>10</v>
+      </c>
+      <c r="K364" t="n">
+        <v>1068.1</v>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M364" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N364" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P364" t="n">
+        <v>958</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S364" t="n">
+        <v>7</v>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V364" t="n">
+        <v>971</v>
+      </c>
+      <c r="W364" t="n">
+        <v>1165.2</v>
+      </c>
+      <c r="X364" t="n">
+        <v>903.03</v>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG364" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH364" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI364" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>77.12</v>
+      </c>
+      <c r="F365" t="n">
+        <v>44.95</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I365" t="b">
+        <v>0</v>
+      </c>
+      <c r="J365" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="K365" t="n">
+        <v>353.5</v>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M365" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N365" t="n">
+        <v>10</v>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P365" t="n">
+        <v>330</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S365" t="n">
+        <v>5.1037</v>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V365" t="n">
+        <v>335</v>
+      </c>
+      <c r="W365" t="n">
+        <v>386.042</v>
+      </c>
+      <c r="X365" t="n">
+        <v>317.9025</v>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z365" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG365" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH365" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI365" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="F366" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I366" t="b">
+        <v>0</v>
+      </c>
+      <c r="J366" t="n">
+        <v>10</v>
+      </c>
+      <c r="K366" t="n">
+        <v>4774</v>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M366" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N366" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P366" t="n">
+        <v>4110</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>61.08</v>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S366" t="n">
+        <v>7</v>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V366" t="n">
+        <v>4340</v>
+      </c>
+      <c r="W366" t="n">
+        <v>5208</v>
+      </c>
+      <c r="X366" t="n">
+        <v>4036.2</v>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z366" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG366" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH366" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI366" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>78.69</v>
+      </c>
+      <c r="F367" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I367" t="b">
+        <v>0</v>
+      </c>
+      <c r="J367" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="K367" t="n">
+        <v>125.68</v>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M367" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N367" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P367" t="n">
+        <v>117.15</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S367" t="n">
+        <v>6.5303</v>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V367" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="W367" t="n">
+        <v>138.6</v>
+      </c>
+      <c r="X367" t="n">
+        <v>107.9575</v>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z367" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG367" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH367" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI367" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="F368" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I368" t="b">
+        <v>0</v>
+      </c>
+      <c r="J368" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="K368" t="n">
+        <v>150.14</v>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M368" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N368" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P368" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>74</v>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S368" t="n">
+        <v>7</v>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V368" t="n">
+        <v>147</v>
+      </c>
+      <c r="W368" t="n">
+        <v>176.4</v>
+      </c>
+      <c r="X368" t="n">
+        <v>136.71</v>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z368" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG368" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH368" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI368" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>82.23999999999999</v>
+      </c>
+      <c r="F369" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I369" t="b">
+        <v>0</v>
+      </c>
+      <c r="J369" t="n">
+        <v>10</v>
+      </c>
+      <c r="K369" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M369" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N369" t="n">
+        <v>5</v>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P369" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>72.02</v>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S369" t="n">
+        <v>7</v>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V369" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="W369" t="n">
+        <v>135</v>
+      </c>
+      <c r="X369" t="n">
+        <v>104.625</v>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z369" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG369" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH369" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI369" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="F370" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I370" t="b">
+        <v>0</v>
+      </c>
+      <c r="J370" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="K370" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M370" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N370" t="n">
+        <v>3</v>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P370" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>82.87</v>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S370" t="n">
+        <v>7</v>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V370" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="W370" t="n">
+        <v>43.08</v>
+      </c>
+      <c r="X370" t="n">
+        <v>33.387</v>
+      </c>
+      <c r="Y370" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z370" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG370" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH370" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI370" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="F371" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I371" t="b">
+        <v>0</v>
+      </c>
+      <c r="J371" t="n">
+        <v>10</v>
+      </c>
+      <c r="K371" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M371" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N371" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P371" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>70.38</v>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S371" t="n">
+        <v>7</v>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V371" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="W371" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="X371" t="n">
+        <v>40.176</v>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z371" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG371" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH371" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI371" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="F372" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I372" t="b">
+        <v>0</v>
+      </c>
+      <c r="J372" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K372" t="n">
+        <v>70</v>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M372" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N372" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P372" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S372" t="n">
+        <v>7</v>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V372" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="W372" t="n">
+        <v>78.2897</v>
+      </c>
+      <c r="X372" t="n">
+        <v>63.705</v>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z372" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG372" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH372" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI372" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>84.88</v>
+      </c>
+      <c r="F373" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I373" t="b">
+        <v>0</v>
+      </c>
+      <c r="J373" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="K373" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M373" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N373" t="n">
+        <v>3</v>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P373" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S373" t="n">
+        <v>7</v>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V373" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="W373" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="X373" t="n">
+        <v>38.5485</v>
+      </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z373" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG373" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH373" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI373" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>78.53</v>
+      </c>
+      <c r="F374" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I374" t="b">
+        <v>0</v>
+      </c>
+      <c r="J374" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K374" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M374" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N374" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P374" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S374" t="n">
+        <v>7</v>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V374" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="W374" t="n">
+        <v>49.2852</v>
+      </c>
+      <c r="X374" t="n">
+        <v>39.618</v>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z374" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG374" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH374" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI374" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>74.26000000000001</v>
+      </c>
+      <c r="F375" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I375" t="b">
+        <v>0</v>
+      </c>
+      <c r="J375" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="K375" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M375" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N375" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P375" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S375" t="n">
+        <v>7</v>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V375" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="W375" t="n">
+        <v>42.3729</v>
+      </c>
+      <c r="X375" t="n">
+        <v>34.2705</v>
+      </c>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z375" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG375" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH375" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI375" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>72.78</v>
+      </c>
+      <c r="F376" t="n">
+        <v>46.64</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I376" t="b">
+        <v>0</v>
+      </c>
+      <c r="J376" t="n">
+        <v>10</v>
+      </c>
+      <c r="K376" t="n">
+        <v>7865</v>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M376" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N376" t="n">
+        <v>1</v>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P376" t="n">
+        <v>6552.5</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S376" t="n">
+        <v>7</v>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V376" t="n">
+        <v>7150</v>
+      </c>
+      <c r="W376" t="n">
+        <v>8580</v>
+      </c>
+      <c r="X376" t="n">
+        <v>6649.5</v>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z376" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG376" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH376" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI376" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>83.43000000000001</v>
+      </c>
+      <c r="F377" t="n">
+        <v>52.91</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I377" t="b">
+        <v>0</v>
+      </c>
+      <c r="J377" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="K377" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M377" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N377" t="n">
+        <v>10</v>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P377" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>66.09</v>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S377" t="n">
+        <v>4.2945</v>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V377" t="n">
+        <v>118</v>
+      </c>
+      <c r="W377" t="n">
+        <v>128.8671</v>
+      </c>
+      <c r="X377" t="n">
+        <v>112.9325</v>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z377" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG377" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH377" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI377" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>76.14</v>
+      </c>
+      <c r="F378" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I378" t="b">
+        <v>0</v>
+      </c>
+      <c r="J378" t="n">
+        <v>10</v>
+      </c>
+      <c r="K378" t="n">
+        <v>3432</v>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M378" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N378" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P378" t="n">
+        <v>3117.5</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S378" t="n">
+        <v>7</v>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V378" t="n">
+        <v>3120</v>
+      </c>
+      <c r="W378" t="n">
+        <v>3744</v>
+      </c>
+      <c r="X378" t="n">
+        <v>2901.6</v>
+      </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI378" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ378" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>70.48999999999999</v>
+      </c>
+      <c r="F379" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I379" t="b">
+        <v>0</v>
+      </c>
+      <c r="J379" t="n">
+        <v>10</v>
+      </c>
+      <c r="K379" t="n">
+        <v>1485</v>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M379" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N379" t="n">
+        <v>1</v>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P379" t="n">
+        <v>1210</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S379" t="n">
+        <v>7</v>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V379" t="n">
+        <v>1350</v>
+      </c>
+      <c r="W379" t="n">
+        <v>1620</v>
+      </c>
+      <c r="X379" t="n">
+        <v>1255.5</v>
+      </c>
+      <c r="Y379" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI379" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ379" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="F380" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I380" t="b">
+        <v>0</v>
+      </c>
+      <c r="J380" t="n">
+        <v>10</v>
+      </c>
+      <c r="K380" t="n">
+        <v>4455</v>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M380" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N380" t="n">
+        <v>5</v>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P380" t="n">
+        <v>3936.75</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>64.73999999999999</v>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S380" t="n">
+        <v>7</v>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V380" t="n">
+        <v>4050</v>
+      </c>
+      <c r="W380" t="n">
+        <v>4860</v>
+      </c>
+      <c r="X380" t="n">
+        <v>3766.5</v>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z380" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG380" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH380" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI380" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>81.97</v>
+      </c>
+      <c r="F381" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I381" t="b">
+        <v>0</v>
+      </c>
+      <c r="J381" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K381" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M381" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N381" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P381" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>74.94</v>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S381" t="n">
+        <v>7</v>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V381" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="W381" t="n">
+        <v>30.0708</v>
+      </c>
+      <c r="X381" t="n">
+        <v>24.831</v>
+      </c>
+      <c r="Y381" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z381" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG381" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH381" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI381" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>73.56</v>
+      </c>
+      <c r="F382" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I382" t="b">
+        <v>0</v>
+      </c>
+      <c r="J382" t="n">
+        <v>10</v>
+      </c>
+      <c r="K382" t="n">
+        <v>207.9</v>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M382" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N382" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P382" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>54.06</v>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S382" t="n">
+        <v>7</v>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V382" t="n">
+        <v>189</v>
+      </c>
+      <c r="W382" t="n">
+        <v>226.8</v>
+      </c>
+      <c r="X382" t="n">
+        <v>175.77</v>
+      </c>
+      <c r="Y382" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI382" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ382" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>75.67</v>
+      </c>
+      <c r="F383" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I383" t="b">
+        <v>0</v>
+      </c>
+      <c r="J383" t="n">
+        <v>10</v>
+      </c>
+      <c r="K383" t="n">
+        <v>2722.5</v>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M383" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N383" t="n">
+        <v>1</v>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P383" t="n">
+        <v>2464.22</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S383" t="n">
+        <v>7</v>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V383" t="n">
+        <v>2475</v>
+      </c>
+      <c r="W383" t="n">
+        <v>2970</v>
+      </c>
+      <c r="X383" t="n">
+        <v>2301.75</v>
+      </c>
+      <c r="Y383" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z383" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG383" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH383" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI383" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ359"/>
+  <autoFilter ref="A1:AJ383"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36955,7 +39871,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 14:24:01</t>
+          <t>2026-09-03 14:23:40</t>
         </is>
       </c>
     </row>
@@ -37002,7 +39918,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>358</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7">
@@ -37022,7 +39938,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>358</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$383</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$414</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ383"/>
+  <dimension ref="A1:AJ414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
         <v>-1.45</v>
@@ -742,6 +742,15 @@
       <c r="AC2" t="n">
         <v>2.18</v>
       </c>
+      <c r="AD2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-3.09</v>
+      </c>
       <c r="AG2" t="b">
         <v>1</v>
       </c>
@@ -750,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -802,11 +811,11 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA3" t="n">
         <v>-5.5</v>
@@ -817,6 +826,15 @@
       <c r="AC3" t="n">
         <v>-8.41</v>
       </c>
+      <c r="AD3" t="n">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-11.65</v>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -825,7 +843,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -877,11 +895,11 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
         <v>21.91</v>
@@ -892,6 +910,15 @@
       <c r="AC4" t="n">
         <v>18.12</v>
       </c>
+      <c r="AD4" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-1.1</v>
+      </c>
       <c r="AG4" t="b">
         <v>1</v>
       </c>
@@ -900,7 +927,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -952,11 +979,11 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA5" t="n">
         <v>3.92</v>
@@ -967,6 +994,15 @@
       <c r="AC5" t="n">
         <v>-5.23</v>
       </c>
+      <c r="AD5" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-9.48</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -975,7 +1011,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1063,11 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA6" t="n">
         <v>7.73</v>
@@ -1042,6 +1078,15 @@
       <c r="AC6" t="n">
         <v>5.52</v>
       </c>
+      <c r="AD6" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1050,7 +1095,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -1102,11 +1147,11 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
         <v>5.54</v>
@@ -1117,6 +1162,15 @@
       <c r="AC7" t="n">
         <v>11.57</v>
       </c>
+      <c r="AD7" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
       <c r="AG7" t="b">
         <v>1</v>
       </c>
@@ -1125,7 +1179,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -1177,11 +1231,11 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
         <v>-11.56</v>
@@ -1192,6 +1246,15 @@
       <c r="AC8" t="n">
         <v>-9.56</v>
       </c>
+      <c r="AD8" t="n">
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-4.89</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-11.78</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1200,7 +1263,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -1252,11 +1315,11 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
         <v>-10.14</v>
@@ -1267,6 +1330,15 @@
       <c r="AC9" t="n">
         <v>-5.86</v>
       </c>
+      <c r="AD9" t="n">
+        <v>-4.28</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-11.71</v>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1275,7 +1347,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -1327,11 +1399,11 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
         <v>-12.27</v>
@@ -1342,6 +1414,15 @@
       <c r="AC10" t="n">
         <v>-9.35</v>
       </c>
+      <c r="AD10" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-14.41</v>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1350,7 +1431,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -1402,11 +1483,11 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA11" t="n">
         <v>-6.97</v>
@@ -1417,6 +1498,15 @@
       <c r="AC11" t="n">
         <v>-5.3</v>
       </c>
+      <c r="AD11" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-11.69</v>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1425,7 +1515,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -1477,11 +1567,11 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
         <v>5.13</v>
@@ -1492,6 +1582,15 @@
       <c r="AC12" t="n">
         <v>61.12</v>
       </c>
+      <c r="AD12" t="n">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>82.33</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-3.53</v>
+      </c>
       <c r="AG12" t="b">
         <v>1</v>
       </c>
@@ -1500,7 +1599,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -1552,11 +1651,11 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA13" t="n">
         <v>-5.54</v>
@@ -1567,6 +1666,15 @@
       <c r="AC13" t="n">
         <v>0.55</v>
       </c>
+      <c r="AD13" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-8.029999999999999</v>
+      </c>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1575,7 +1683,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -1689,11 +1797,11 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
         <v>3.09</v>
@@ -1704,6 +1812,15 @@
       <c r="AC15" t="n">
         <v>2.85</v>
       </c>
+      <c r="AD15" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-2.35</v>
+      </c>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -1712,7 +1829,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -1764,11 +1881,11 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
         <v>9.31</v>
@@ -1779,6 +1896,15 @@
       <c r="AC16" t="n">
         <v>11.47</v>
       </c>
+      <c r="AD16" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
       <c r="AG16" t="b">
         <v>1</v>
       </c>
@@ -1787,7 +1913,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1969,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1918,7 +2044,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -1993,7 +2119,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -2068,7 +2194,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -2143,7 +2269,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2218,7 +2344,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2293,7 +2419,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2368,7 +2494,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2443,7 +2569,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
@@ -2518,7 +2644,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
@@ -2593,7 +2719,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2668,7 +2794,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2743,7 +2869,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2818,7 +2944,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2893,7 +3019,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -2968,7 +3094,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -3043,7 +3169,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3242,7 +3368,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3317,7 +3443,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA37" t="n">
         <v>-63.07</v>
@@ -3392,7 +3518,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3467,7 +3593,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3542,7 +3668,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3617,7 +3743,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3692,7 +3818,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3767,7 +3893,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3842,7 +3968,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -3917,7 +4043,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -3992,7 +4118,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -4067,7 +4193,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -4142,7 +4268,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -4217,7 +4343,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4292,7 +4418,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4367,7 +4493,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4442,7 +4568,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4517,7 +4643,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4592,7 +4718,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4729,7 +4855,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4804,7 +4930,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -4879,7 +5005,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -4954,7 +5080,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -5029,7 +5155,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -5104,7 +5230,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -5179,7 +5305,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -5254,7 +5380,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -5329,7 +5455,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5404,7 +5530,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5479,7 +5605,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5554,7 +5680,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5629,7 +5755,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -5704,7 +5830,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -5841,7 +5967,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -5916,7 +6042,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -5991,7 +6117,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA73" t="n">
         <v>-64.53</v>
@@ -6066,7 +6192,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -6141,7 +6267,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -6216,7 +6342,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -6291,7 +6417,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -6366,7 +6492,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6441,7 +6567,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6516,7 +6642,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6591,7 +6717,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -6666,7 +6792,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -6741,7 +6867,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -6816,7 +6942,7 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -6891,7 +7017,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -6966,7 +7092,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -7041,7 +7167,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -7116,7 +7242,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -7191,7 +7317,7 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA89" t="n">
         <v>-65.06999999999999</v>
@@ -7328,7 +7454,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -7403,7 +7529,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -7411,6 +7537,9 @@
       <c r="AB92" t="n">
         <v>6.34</v>
       </c>
+      <c r="AC92" t="n">
+        <v>5.07</v>
+      </c>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -7475,7 +7604,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -7483,6 +7612,9 @@
       <c r="AB93" t="n">
         <v>-3.08</v>
       </c>
+      <c r="AC93" t="n">
+        <v>-4.45</v>
+      </c>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -7547,7 +7679,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -7555,6 +7687,9 @@
       <c r="AB94" t="n">
         <v>18.91</v>
       </c>
+      <c r="AC94" t="n">
+        <v>15.36</v>
+      </c>
       <c r="AG94" t="b">
         <v>1</v>
       </c>
@@ -7619,7 +7754,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -7627,6 +7762,9 @@
       <c r="AB95" t="n">
         <v>-12.2</v>
       </c>
+      <c r="AC95" t="n">
+        <v>-9.18</v>
+      </c>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -7691,7 +7829,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -7699,6 +7837,9 @@
       <c r="AB96" t="n">
         <v>-8.81</v>
       </c>
+      <c r="AC96" t="n">
+        <v>1.57</v>
+      </c>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -7763,7 +7904,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -7771,6 +7912,9 @@
       <c r="AB97" t="n">
         <v>-10.95</v>
       </c>
+      <c r="AC97" t="n">
+        <v>-12.17</v>
+      </c>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -7835,7 +7979,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -7843,11 +7987,14 @@
       <c r="AB98" t="n">
         <v>5.47</v>
       </c>
+      <c r="AC98" t="n">
+        <v>-3.12</v>
+      </c>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AH98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
@@ -7907,7 +8054,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -7915,6 +8062,9 @@
       <c r="AB99" t="n">
         <v>-5.34</v>
       </c>
+      <c r="AC99" t="n">
+        <v>4.87</v>
+      </c>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -7979,7 +8129,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -7987,6 +8137,9 @@
       <c r="AB100" t="n">
         <v>5.71</v>
       </c>
+      <c r="AC100" t="n">
+        <v>6.39</v>
+      </c>
       <c r="AG100" t="b">
         <v>1</v>
       </c>
@@ -8051,7 +8204,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -8059,6 +8212,9 @@
       <c r="AB101" t="n">
         <v>8.91</v>
       </c>
+      <c r="AC101" t="n">
+        <v>12.79</v>
+      </c>
       <c r="AG101" t="b">
         <v>1</v>
       </c>
@@ -8123,7 +8279,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -8131,6 +8287,9 @@
       <c r="AB102" t="n">
         <v>23.07</v>
       </c>
+      <c r="AC102" t="n">
+        <v>26.93</v>
+      </c>
       <c r="AG102" t="b">
         <v>1</v>
       </c>
@@ -8195,7 +8354,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -8203,6 +8362,9 @@
       <c r="AB103" t="n">
         <v>3.48</v>
       </c>
+      <c r="AC103" t="n">
+        <v>15.96</v>
+      </c>
       <c r="AG103" t="b">
         <v>1</v>
       </c>
@@ -8267,7 +8429,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -8275,6 +8437,9 @@
       <c r="AB104" t="n">
         <v>-0.66</v>
       </c>
+      <c r="AC104" t="n">
+        <v>9.93</v>
+      </c>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -8339,7 +8504,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -8347,6 +8512,9 @@
       <c r="AB105" t="n">
         <v>53.25</v>
       </c>
+      <c r="AC105" t="n">
+        <v>60.52</v>
+      </c>
       <c r="AG105" t="b">
         <v>1</v>
       </c>
@@ -8411,7 +8579,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -8419,6 +8587,9 @@
       <c r="AB106" t="n">
         <v>3.86</v>
       </c>
+      <c r="AC106" t="n">
+        <v>10.36</v>
+      </c>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -8483,7 +8654,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -8491,6 +8662,9 @@
       <c r="AB107" t="n">
         <v>8.82</v>
       </c>
+      <c r="AC107" t="n">
+        <v>-11.57</v>
+      </c>
       <c r="AG107" t="b">
         <v>1</v>
       </c>
@@ -8555,7 +8729,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -8563,6 +8737,9 @@
       <c r="AB108" t="n">
         <v>4.29</v>
       </c>
+      <c r="AC108" t="n">
+        <v>-4.99</v>
+      </c>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -8627,7 +8804,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -8635,6 +8812,9 @@
       <c r="AB109" t="n">
         <v>-8.01</v>
       </c>
+      <c r="AC109" t="n">
+        <v>2.33</v>
+      </c>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -8699,7 +8879,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -8707,6 +8887,9 @@
       <c r="AB110" t="n">
         <v>10.06</v>
       </c>
+      <c r="AC110" t="n">
+        <v>6.31</v>
+      </c>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -8771,7 +8954,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -8779,6 +8962,9 @@
       <c r="AB111" t="n">
         <v>3</v>
       </c>
+      <c r="AC111" t="n">
+        <v>-12.67</v>
+      </c>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -8843,7 +9029,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA112" t="n">
         <v>-67.41</v>
@@ -8851,6 +9037,9 @@
       <c r="AB112" t="n">
         <v>-62.49</v>
       </c>
+      <c r="AC112" t="n">
+        <v>-60.14</v>
+      </c>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -8915,7 +9104,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
@@ -8987,7 +9176,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
@@ -9059,7 +9248,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
@@ -9131,7 +9320,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
@@ -9203,7 +9392,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
@@ -9275,7 +9464,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
@@ -9347,7 +9536,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
@@ -9419,7 +9608,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
@@ -9491,7 +9680,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
@@ -9563,7 +9752,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
@@ -9635,7 +9824,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
@@ -9707,7 +9896,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
@@ -9779,7 +9968,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
@@ -9851,7 +10040,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
@@ -9923,7 +10112,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
@@ -9995,7 +10184,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
@@ -10067,7 +10256,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA129" t="n">
         <v>-68.09</v>
@@ -10188,7 +10377,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
@@ -10309,7 +10498,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
@@ -10430,7 +10619,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
@@ -10551,7 +10740,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
@@ -10672,7 +10861,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
@@ -10793,7 +10982,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
@@ -10914,7 +11103,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
@@ -11032,7 +11221,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
@@ -11153,7 +11342,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
@@ -11274,7 +11463,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
@@ -11395,7 +11584,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
@@ -11516,7 +11705,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
@@ -11637,7 +11826,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
@@ -11758,7 +11947,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
@@ -11879,7 +12068,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
@@ -12000,7 +12189,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA145" t="n">
         <v>-66.26000000000001</v>
@@ -12121,7 +12310,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
@@ -12242,7 +12431,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
@@ -12363,7 +12552,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
@@ -12484,7 +12673,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
@@ -12605,7 +12794,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
@@ -12726,7 +12915,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
@@ -12847,7 +13036,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
@@ -12968,7 +13157,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
@@ -13089,7 +13278,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
@@ -13210,7 +13399,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
@@ -13331,7 +13520,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
@@ -13452,7 +13641,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
@@ -13573,7 +13762,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
@@ -13694,7 +13883,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
@@ -13815,7 +14004,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
@@ -13936,7 +14125,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
@@ -14057,7 +14246,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
@@ -14178,7 +14367,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
@@ -14299,7 +14488,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
@@ -14420,7 +14609,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
@@ -14541,7 +14730,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
@@ -14662,7 +14851,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
@@ -14894,7 +15083,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
@@ -15015,7 +15204,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
@@ -15136,7 +15325,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA171" t="n">
         <v>-63.88</v>
@@ -15257,11 +15446,14 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
       </c>
+      <c r="AB172" t="n">
+        <v>-1.01</v>
+      </c>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -15375,11 +15567,14 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
       </c>
+      <c r="AB173" t="n">
+        <v>0.43</v>
+      </c>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -15493,11 +15688,14 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
       </c>
+      <c r="AB174" t="n">
+        <v>-3.95</v>
+      </c>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -15611,11 +15809,14 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
       </c>
+      <c r="AB175" t="n">
+        <v>-6.06</v>
+      </c>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -15729,13 +15930,16 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
       </c>
+      <c r="AB176" t="n">
+        <v>12.31</v>
+      </c>
       <c r="AG176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH176" t="b">
         <v>0</v>
@@ -15847,11 +16051,14 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
       </c>
+      <c r="AB177" t="n">
+        <v>11.41</v>
+      </c>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -15965,11 +16172,14 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
       </c>
+      <c r="AB178" t="n">
+        <v>31.91</v>
+      </c>
       <c r="AG178" t="b">
         <v>1</v>
       </c>
@@ -16194,11 +16404,14 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
       </c>
+      <c r="AB180" t="n">
+        <v>3.75</v>
+      </c>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -16312,7 +16525,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
@@ -16430,7 +16643,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
@@ -16548,7 +16761,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
@@ -16666,7 +16879,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
@@ -16784,7 +16997,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
@@ -16902,7 +17115,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA186" t="n">
         <v>-62.24</v>
@@ -17020,7 +17233,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
@@ -17138,7 +17351,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
@@ -17256,7 +17469,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
@@ -17374,7 +17587,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
@@ -17492,7 +17705,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
@@ -17610,7 +17823,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
@@ -17728,7 +17941,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
@@ -17846,7 +18059,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
@@ -17964,7 +18177,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
@@ -18082,7 +18295,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
@@ -18200,7 +18413,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
@@ -18540,7 +18753,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
@@ -18658,7 +18871,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
@@ -18776,7 +18989,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
@@ -18894,7 +19107,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
@@ -19012,7 +19225,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
@@ -19130,7 +19343,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
@@ -19248,7 +19461,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
@@ -19366,7 +19579,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
@@ -19484,7 +19697,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
@@ -19602,7 +19815,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
@@ -19720,7 +19933,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -19838,7 +20051,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
@@ -19956,7 +20169,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
@@ -20185,7 +20398,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
@@ -20303,7 +20516,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
@@ -20421,7 +20634,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
@@ -20539,7 +20752,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
@@ -20657,7 +20870,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
@@ -20775,7 +20988,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
@@ -20893,7 +21106,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
@@ -21011,7 +21224,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
@@ -21129,7 +21342,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
@@ -21247,7 +21460,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
@@ -21365,7 +21578,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
@@ -21483,7 +21696,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
@@ -21601,7 +21814,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
@@ -21719,7 +21932,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
@@ -21837,7 +22050,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
@@ -21955,7 +22168,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
@@ -22073,7 +22286,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
@@ -22191,7 +22404,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
@@ -22420,7 +22633,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
@@ -22760,7 +22973,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
@@ -22878,7 +23091,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -22996,7 +23209,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
@@ -23114,7 +23327,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
@@ -23232,7 +23445,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
@@ -23350,7 +23563,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
@@ -23468,7 +23681,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
@@ -23586,7 +23799,10 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA243" t="n">
+        <v>5.26</v>
       </c>
       <c r="AG243" t="b">
         <v>0</v>
@@ -23701,7 +23917,10 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>2.27</v>
       </c>
       <c r="AG244" t="b">
         <v>0</v>
@@ -23816,7 +24035,10 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>-0.55</v>
       </c>
       <c r="AG245" t="b">
         <v>0</v>
@@ -23931,7 +24153,10 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>-1.19</v>
       </c>
       <c r="AG246" t="b">
         <v>0</v>
@@ -24046,7 +24271,10 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>-2.99</v>
       </c>
       <c r="AG247" t="b">
         <v>0</v>
@@ -24161,7 +24389,10 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>3.76</v>
       </c>
       <c r="AG248" t="b">
         <v>0</v>
@@ -24276,7 +24507,10 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>6.28</v>
       </c>
       <c r="AG249" t="b">
         <v>0</v>
@@ -24391,7 +24625,10 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>-8.15</v>
       </c>
       <c r="AG250" t="b">
         <v>0</v>
@@ -24506,7 +24743,10 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>4.51</v>
       </c>
       <c r="AG251" t="b">
         <v>0</v>
@@ -24621,7 +24861,10 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>4.74</v>
       </c>
       <c r="AG252" t="b">
         <v>0</v>
@@ -24736,7 +24979,10 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>6.25</v>
       </c>
       <c r="AG253" t="b">
         <v>0</v>
@@ -24851,7 +25097,10 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>-0.55</v>
       </c>
       <c r="AG254" t="b">
         <v>0</v>
@@ -24966,7 +25215,10 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>-18.74</v>
       </c>
       <c r="AG255" t="b">
         <v>0</v>
@@ -25303,7 +25555,10 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>-8.9</v>
       </c>
       <c r="AG258" t="b">
         <v>0</v>
@@ -25640,7 +25895,10 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>-3.41</v>
       </c>
       <c r="AG261" t="b">
         <v>0</v>
@@ -25755,7 +26013,10 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>-5.07</v>
       </c>
       <c r="AG262" t="b">
         <v>0</v>
@@ -25870,7 +26131,10 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>3.81</v>
       </c>
       <c r="AG263" t="b">
         <v>0</v>
@@ -25985,7 +26249,10 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>-5.31</v>
       </c>
       <c r="AG264" t="b">
         <v>0</v>
@@ -26211,7 +26478,10 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>-15.21</v>
       </c>
       <c r="AG266" t="b">
         <v>0</v>
@@ -26326,7 +26596,10 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>-64.38</v>
       </c>
       <c r="AG267" t="b">
         <v>0</v>
@@ -26441,7 +26714,10 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>-3.98</v>
       </c>
       <c r="AG268" t="b">
         <v>0</v>
@@ -26556,7 +26832,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG269" t="b">
         <v>0</v>
@@ -26671,7 +26947,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG270" t="b">
         <v>0</v>
@@ -26786,7 +27062,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG271" t="b">
         <v>0</v>
@@ -26901,7 +27177,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG272" t="b">
         <v>0</v>
@@ -27016,7 +27292,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG273" t="b">
         <v>0</v>
@@ -27131,7 +27407,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG274" t="b">
         <v>0</v>
@@ -27246,7 +27522,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG275" t="b">
         <v>0</v>
@@ -27361,7 +27637,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG276" t="b">
         <v>0</v>
@@ -27476,7 +27752,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG277" t="b">
         <v>0</v>
@@ -27591,13 +27867,13 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG278" t="b">
         <v>0</v>
       </c>
       <c r="AH278" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI278" t="inlineStr">
         <is>
@@ -27706,7 +27982,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG279" t="b">
         <v>0</v>
@@ -27821,7 +28097,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG280" t="b">
         <v>0</v>
@@ -27936,7 +28212,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG281" t="b">
         <v>0</v>
@@ -28051,7 +28327,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG282" t="b">
         <v>0</v>
@@ -28166,7 +28442,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG283" t="b">
         <v>0</v>
@@ -28281,7 +28557,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG284" t="b">
         <v>0</v>
@@ -28396,7 +28672,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG285" t="b">
         <v>0</v>
@@ -28511,7 +28787,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG286" t="b">
         <v>0</v>
@@ -28626,7 +28902,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG287" t="b">
         <v>0</v>
@@ -28741,7 +29017,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG288" t="b">
         <v>0</v>
@@ -28856,7 +29132,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG289" t="b">
         <v>0</v>
@@ -28971,7 +29247,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG290" t="b">
         <v>0</v>
@@ -29086,7 +29362,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG291" t="b">
         <v>0</v>
@@ -29201,7 +29477,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG292" t="b">
         <v>0</v>
@@ -29316,7 +29592,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG293" t="b">
         <v>0</v>
@@ -29764,7 +30040,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG297" t="b">
         <v>0</v>
@@ -29879,7 +30155,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG298" t="b">
         <v>0</v>
@@ -29994,7 +30270,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG299" t="b">
         <v>0</v>
@@ -30220,7 +30496,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG301" t="b">
         <v>0</v>
@@ -30335,13 +30611,13 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG302" t="b">
         <v>0</v>
       </c>
       <c r="AH302" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI302" t="inlineStr">
         <is>
@@ -30450,7 +30726,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG303" t="b">
         <v>0</v>
@@ -30565,7 +30841,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG304" t="b">
         <v>0</v>
@@ -30680,7 +30956,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG305" t="b">
         <v>0</v>
@@ -30795,7 +31071,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG306" t="b">
         <v>0</v>
@@ -30910,7 +31186,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG307" t="b">
         <v>0</v>
@@ -31025,7 +31301,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG308" t="b">
         <v>0</v>
@@ -31140,7 +31416,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG309" t="b">
         <v>0</v>
@@ -31255,7 +31531,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG310" t="b">
         <v>0</v>
@@ -31370,7 +31646,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG311" t="b">
         <v>0</v>
@@ -31485,7 +31761,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG312" t="b">
         <v>0</v>
@@ -31600,7 +31876,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG313" t="b">
         <v>0</v>
@@ -31715,7 +31991,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG314" t="b">
         <v>0</v>
@@ -31830,7 +32106,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG315" t="b">
         <v>0</v>
@@ -31945,7 +32221,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG316" t="b">
         <v>0</v>
@@ -32060,7 +32336,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG317" t="b">
         <v>0</v>
@@ -32175,7 +32451,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG318" t="b">
         <v>0</v>
@@ -32290,7 +32566,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG319" t="b">
         <v>0</v>
@@ -32405,7 +32681,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG320" t="b">
         <v>0</v>
@@ -32520,13 +32796,13 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
       <c r="AH321" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI321" t="inlineStr">
         <is>
@@ -32635,7 +32911,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG322" t="b">
         <v>0</v>
@@ -32750,7 +33026,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG323" t="b">
         <v>0</v>
@@ -32865,7 +33141,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG324" t="b">
         <v>0</v>
@@ -33202,7 +33478,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG327" t="b">
         <v>0</v>
@@ -33317,7 +33593,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG328" t="b">
         <v>0</v>
@@ -33432,7 +33708,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG329" t="b">
         <v>0</v>
@@ -33769,7 +34045,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG332" t="b">
         <v>0</v>
@@ -33884,7 +34160,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG333" t="b">
         <v>0</v>
@@ -33999,7 +34275,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG334" t="b">
         <v>0</v>
@@ -34114,13 +34390,13 @@
         </is>
       </c>
       <c r="Z335" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG335" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH335" t="b">
         <v>1</v>
-      </c>
-      <c r="AG335" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH335" t="b">
-        <v>0</v>
       </c>
       <c r="AI335" t="inlineStr">
         <is>
@@ -34229,7 +34505,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG336" t="b">
         <v>0</v>
@@ -34344,7 +34620,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG337" t="b">
         <v>0</v>
@@ -34459,7 +34735,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG338" t="b">
         <v>0</v>
@@ -34574,7 +34850,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG339" t="b">
         <v>0</v>
@@ -34689,7 +34965,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG340" t="b">
         <v>0</v>
@@ -34804,7 +35080,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG341" t="b">
         <v>0</v>
@@ -34919,7 +35195,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG342" t="b">
         <v>0</v>
@@ -35034,7 +35310,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG343" t="b">
         <v>0</v>
@@ -35149,7 +35425,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG344" t="b">
         <v>0</v>
@@ -35264,7 +35540,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG345" t="b">
         <v>0</v>
@@ -35379,7 +35655,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG346" t="b">
         <v>0</v>
@@ -35494,7 +35770,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG347" t="b">
         <v>0</v>
@@ -35609,7 +35885,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG348" t="b">
         <v>0</v>
@@ -35724,7 +36000,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG349" t="b">
         <v>0</v>
@@ -35839,7 +36115,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG350" t="b">
         <v>0</v>
@@ -35954,7 +36230,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG351" t="b">
         <v>0</v>
@@ -36069,7 +36345,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG352" t="b">
         <v>0</v>
@@ -36184,7 +36460,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG353" t="b">
         <v>0</v>
@@ -36743,7 +37019,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG358" t="b">
         <v>0</v>
@@ -36858,7 +37134,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG359" t="b">
         <v>0</v>
@@ -36973,7 +37249,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG360" t="b">
         <v>0</v>
@@ -37088,7 +37364,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG361" t="b">
         <v>0</v>
@@ -37203,7 +37479,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG362" t="b">
         <v>0</v>
@@ -37318,7 +37594,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG363" t="b">
         <v>0</v>
@@ -37433,7 +37709,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG364" t="b">
         <v>0</v>
@@ -37548,7 +37824,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG365" t="b">
         <v>0</v>
@@ -37663,7 +37939,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG366" t="b">
         <v>0</v>
@@ -37778,7 +38054,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG367" t="b">
         <v>0</v>
@@ -37893,7 +38169,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG368" t="b">
         <v>0</v>
@@ -38008,7 +38284,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG369" t="b">
         <v>0</v>
@@ -38123,7 +38399,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG370" t="b">
         <v>0</v>
@@ -38238,7 +38514,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG371" t="b">
         <v>0</v>
@@ -38353,7 +38629,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG372" t="b">
         <v>0</v>
@@ -38468,7 +38744,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG373" t="b">
         <v>0</v>
@@ -38583,7 +38859,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG374" t="b">
         <v>0</v>
@@ -38698,7 +38974,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG375" t="b">
         <v>0</v>
@@ -38813,7 +39089,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG376" t="b">
         <v>0</v>
@@ -38928,7 +39204,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG377" t="b">
         <v>0</v>
@@ -39265,7 +39541,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG380" t="b">
         <v>0</v>
@@ -39380,7 +39656,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG381" t="b">
         <v>0</v>
@@ -39606,7 +39882,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG383" t="b">
         <v>0</v>
@@ -39620,8 +39896,3558 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>81.04000000000001</v>
+      </c>
+      <c r="F384" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I384" t="b">
+        <v>0</v>
+      </c>
+      <c r="J384" t="n">
+        <v>10</v>
+      </c>
+      <c r="K384" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M384" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N384" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P384" t="n">
+        <v>63.55</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>68.98</v>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S384" t="n">
+        <v>7</v>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V384" t="n">
+        <v>66</v>
+      </c>
+      <c r="W384" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="X384" t="n">
+        <v>61.38</v>
+      </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z384" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG384" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH384" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI384" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>77.84</v>
+      </c>
+      <c r="F385" t="n">
+        <v>57.38</v>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I385" t="b">
+        <v>0</v>
+      </c>
+      <c r="J385" t="n">
+        <v>10</v>
+      </c>
+      <c r="K385" t="n">
+        <v>248.05</v>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M385" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N385" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P385" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S385" t="n">
+        <v>7</v>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V385" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="W385" t="n">
+        <v>270.6</v>
+      </c>
+      <c r="X385" t="n">
+        <v>209.715</v>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z385" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG385" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH385" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI385" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="F386" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I386" t="b">
+        <v>0</v>
+      </c>
+      <c r="J386" t="n">
+        <v>10</v>
+      </c>
+      <c r="K386" t="n">
+        <v>79.42</v>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M386" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N386" t="n">
+        <v>10</v>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P386" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>36.76</v>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S386" t="n">
+        <v>3.8075</v>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V386" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="W386" t="n">
+        <v>81.7171</v>
+      </c>
+      <c r="X386" t="n">
+        <v>69.45099999999999</v>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z386" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG386" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH386" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI386" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>80.64</v>
+      </c>
+      <c r="F387" t="n">
+        <v>58.61</v>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I387" t="b">
+        <v>0</v>
+      </c>
+      <c r="J387" t="n">
+        <v>10</v>
+      </c>
+      <c r="K387" t="n">
+        <v>820.6</v>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M387" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N387" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P387" t="n">
+        <v>740</v>
+      </c>
+      <c r="Q387" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S387" t="n">
+        <v>6.2353</v>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="V387" t="n">
+        <v>746</v>
+      </c>
+      <c r="W387" t="n">
+        <v>894.1063</v>
+      </c>
+      <c r="X387" t="n">
+        <v>699.485</v>
+      </c>
+      <c r="Y387" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z387" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG387" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH387" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI387" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>73.23999999999999</v>
+      </c>
+      <c r="F388" t="n">
+        <v>41.85</v>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I388" t="b">
+        <v>0</v>
+      </c>
+      <c r="J388" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="K388" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M388" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N388" t="n">
+        <v>5</v>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P388" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>59</v>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S388" t="n">
+        <v>7</v>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V388" t="n">
+        <v>308</v>
+      </c>
+      <c r="W388" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="X388" t="n">
+        <v>286.44</v>
+      </c>
+      <c r="Y388" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z388" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG388" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH388" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI388" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>86</v>
+      </c>
+      <c r="F389" t="n">
+        <v>62.26</v>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I389" t="b">
+        <v>0</v>
+      </c>
+      <c r="J389" t="n">
+        <v>10</v>
+      </c>
+      <c r="K389" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M389" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N389" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P389" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="Q389" t="n">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="S389" t="n">
+        <v>7</v>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V389" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="W389" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="X389" t="n">
+        <v>38.688</v>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z389" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG389" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH389" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI389" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>宏碁</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="F390" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I390" t="b">
+        <v>0</v>
+      </c>
+      <c r="J390" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K390" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M390" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N390" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q390" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S390" t="n">
+        <v>7</v>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V390" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="W390" t="n">
+        <v>37.4286</v>
+      </c>
+      <c r="X390" t="n">
+        <v>30.411</v>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z390" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG390" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH390" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI390" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>83.54000000000001</v>
+      </c>
+      <c r="F391" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I391" t="b">
+        <v>0</v>
+      </c>
+      <c r="J391" t="n">
+        <v>10</v>
+      </c>
+      <c r="K391" t="n">
+        <v>1127.5</v>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M391" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N391" t="n">
+        <v>3</v>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P391" t="n">
+        <v>965.5</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S391" t="n">
+        <v>7</v>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V391" t="n">
+        <v>1025</v>
+      </c>
+      <c r="W391" t="n">
+        <v>1230</v>
+      </c>
+      <c r="X391" t="n">
+        <v>953.25</v>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z391" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG391" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH391" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI391" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>微星</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>75.15000000000001</v>
+      </c>
+      <c r="F392" t="n">
+        <v>34.18</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I392" t="b">
+        <v>0</v>
+      </c>
+      <c r="J392" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="K392" t="n">
+        <v>164.17</v>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M392" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N392" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P392" t="n">
+        <v>150.75</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S392" t="n">
+        <v>7</v>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V392" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="W392" t="n">
+        <v>193.8</v>
+      </c>
+      <c r="X392" t="n">
+        <v>150.195</v>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z392" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG392" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH392" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI392" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>85.04000000000001</v>
+      </c>
+      <c r="F393" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I393" t="b">
+        <v>0</v>
+      </c>
+      <c r="J393" t="n">
+        <v>10</v>
+      </c>
+      <c r="K393" t="n">
+        <v>379.5</v>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M393" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N393" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P393" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>70.88</v>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S393" t="n">
+        <v>7</v>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V393" t="n">
+        <v>345</v>
+      </c>
+      <c r="W393" t="n">
+        <v>411.4335</v>
+      </c>
+      <c r="X393" t="n">
+        <v>320.85</v>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z393" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG393" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH393" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI393" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2385</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>群光</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>73.29000000000001</v>
+      </c>
+      <c r="F394" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I394" t="b">
+        <v>0</v>
+      </c>
+      <c r="J394" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K394" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M394" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="N394" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P394" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S394" t="n">
+        <v>5.9027</v>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V394" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="W394" t="n">
+        <v>123.9956</v>
+      </c>
+      <c r="X394" t="n">
+        <v>103.9775</v>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z394" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG394" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH394" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI394" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="F395" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I395" t="b">
+        <v>0</v>
+      </c>
+      <c r="J395" t="n">
+        <v>10</v>
+      </c>
+      <c r="K395" t="n">
+        <v>782.1</v>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M395" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N395" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P395" t="n">
+        <v>685</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S395" t="n">
+        <v>7</v>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V395" t="n">
+        <v>711</v>
+      </c>
+      <c r="W395" t="n">
+        <v>853.2</v>
+      </c>
+      <c r="X395" t="n">
+        <v>661.23</v>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z395" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG395" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH395" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI395" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="F396" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I396" t="b">
+        <v>0</v>
+      </c>
+      <c r="J396" t="n">
+        <v>10</v>
+      </c>
+      <c r="K396" t="n">
+        <v>4856.5</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M396" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N396" t="n">
+        <v>3</v>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P396" t="n">
+        <v>4110</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>65.72</v>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S396" t="n">
+        <v>7</v>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V396" t="n">
+        <v>4415</v>
+      </c>
+      <c r="W396" t="n">
+        <v>5298</v>
+      </c>
+      <c r="X396" t="n">
+        <v>4105.95</v>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z396" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG396" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH396" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI396" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2609</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>陽明</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>71.34</v>
+      </c>
+      <c r="F397" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I397" t="b">
+        <v>0</v>
+      </c>
+      <c r="J397" t="n">
+        <v>10</v>
+      </c>
+      <c r="K397" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M397" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N397" t="n">
+        <v>10</v>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P397" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S397" t="n">
+        <v>4.6031</v>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V397" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="W397" t="n">
+        <v>69.84</v>
+      </c>
+      <c r="X397" t="n">
+        <v>55.521</v>
+      </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z397" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG397" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH397" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI397" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="F398" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I398" t="b">
+        <v>0</v>
+      </c>
+      <c r="J398" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K398" t="n">
+        <v>125.68</v>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M398" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="N398" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P398" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S398" t="n">
+        <v>6.1239</v>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V398" t="n">
+        <v>115</v>
+      </c>
+      <c r="W398" t="n">
+        <v>138</v>
+      </c>
+      <c r="X398" t="n">
+        <v>107.9575</v>
+      </c>
+      <c r="Y398" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z398" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG398" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH398" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI398" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>84.20999999999999</v>
+      </c>
+      <c r="F399" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I399" t="b">
+        <v>0</v>
+      </c>
+      <c r="J399" t="n">
+        <v>10</v>
+      </c>
+      <c r="K399" t="n">
+        <v>165.55</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M399" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N399" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P399" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>77.95999999999999</v>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S399" t="n">
+        <v>7</v>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V399" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="W399" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="X399" t="n">
+        <v>139.965</v>
+      </c>
+      <c r="Y399" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z399" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG399" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH399" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI399" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>80.29000000000001</v>
+      </c>
+      <c r="F400" t="n">
+        <v>52.05</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I400" t="b">
+        <v>0</v>
+      </c>
+      <c r="J400" t="n">
+        <v>10</v>
+      </c>
+      <c r="K400" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M400" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N400" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P400" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>70.31</v>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S400" t="n">
+        <v>7</v>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V400" t="n">
+        <v>115</v>
+      </c>
+      <c r="W400" t="n">
+        <v>138</v>
+      </c>
+      <c r="X400" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="Y400" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z400" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG400" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH400" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI400" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>84.86</v>
+      </c>
+      <c r="F401" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I401" t="b">
+        <v>0</v>
+      </c>
+      <c r="J401" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K401" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M401" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N401" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P401" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="Q401" t="n">
+        <v>80.61</v>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S401" t="n">
+        <v>7</v>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V401" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="W401" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="X401" t="n">
+        <v>34.131</v>
+      </c>
+      <c r="Y401" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z401" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG401" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH401" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI401" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="F402" t="n">
+        <v>43</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I402" t="b">
+        <v>0</v>
+      </c>
+      <c r="J402" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K402" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M402" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N402" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P402" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>83.36</v>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S402" t="n">
+        <v>7</v>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V402" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="W402" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="X402" t="n">
+        <v>40.5015</v>
+      </c>
+      <c r="Y402" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z402" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG402" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH402" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI402" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>76.27</v>
+      </c>
+      <c r="F403" t="n">
+        <v>47.18</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I403" t="b">
+        <v>0</v>
+      </c>
+      <c r="J403" t="n">
+        <v>10</v>
+      </c>
+      <c r="K403" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M403" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N403" t="n">
+        <v>3</v>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P403" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>67.87</v>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S403" t="n">
+        <v>7</v>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V403" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="W403" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="X403" t="n">
+        <v>38.595</v>
+      </c>
+      <c r="Y403" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z403" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG403" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH403" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI403" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>78.87</v>
+      </c>
+      <c r="F404" t="n">
+        <v>44.95</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I404" t="b">
+        <v>0</v>
+      </c>
+      <c r="J404" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="K404" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M404" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N404" t="n">
+        <v>7</v>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P404" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>73.03</v>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S404" t="n">
+        <v>7</v>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V404" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="W404" t="n">
+        <v>49.1875</v>
+      </c>
+      <c r="X404" t="n">
+        <v>39.8505</v>
+      </c>
+      <c r="Y404" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z404" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG404" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH404" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI404" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="F405" t="n">
+        <v>42.28</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I405" t="b">
+        <v>0</v>
+      </c>
+      <c r="J405" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K405" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M405" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="N405" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P405" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S405" t="n">
+        <v>7</v>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V405" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="W405" t="n">
+        <v>42.9414</v>
+      </c>
+      <c r="X405" t="n">
+        <v>34.689</v>
+      </c>
+      <c r="Y405" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z405" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG405" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH405" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI405" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>晶豪科</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="F406" t="n">
+        <v>59.83</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I406" t="b">
+        <v>0</v>
+      </c>
+      <c r="J406" t="n">
+        <v>10</v>
+      </c>
+      <c r="K406" t="n">
+        <v>306.35</v>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M406" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N406" t="n">
+        <v>7</v>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P406" t="n">
+        <v>276</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>58.84</v>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S406" t="n">
+        <v>7</v>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V406" t="n">
+        <v>278.5</v>
+      </c>
+      <c r="W406" t="n">
+        <v>334.2</v>
+      </c>
+      <c r="X406" t="n">
+        <v>259.005</v>
+      </c>
+      <c r="Y406" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z406" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG406" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH406" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI406" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="F407" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I407" t="b">
+        <v>0</v>
+      </c>
+      <c r="J407" t="n">
+        <v>10</v>
+      </c>
+      <c r="K407" t="n">
+        <v>8140</v>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M407" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N407" t="n">
+        <v>3</v>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P407" t="n">
+        <v>6627.5</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S407" t="n">
+        <v>7</v>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V407" t="n">
+        <v>7400</v>
+      </c>
+      <c r="W407" t="n">
+        <v>8880</v>
+      </c>
+      <c r="X407" t="n">
+        <v>6882</v>
+      </c>
+      <c r="Y407" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z407" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG407" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH407" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI407" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>83.16</v>
+      </c>
+      <c r="F408" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I408" t="b">
+        <v>0</v>
+      </c>
+      <c r="J408" t="n">
+        <v>10</v>
+      </c>
+      <c r="K408" t="n">
+        <v>3927</v>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M408" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N408" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P408" t="n">
+        <v>3155</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>73.29000000000001</v>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S408" t="n">
+        <v>7</v>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V408" t="n">
+        <v>3570</v>
+      </c>
+      <c r="W408" t="n">
+        <v>4284</v>
+      </c>
+      <c r="X408" t="n">
+        <v>3320.1</v>
+      </c>
+      <c r="Y408" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z408" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG408" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH408" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI408" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="F409" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I409" t="b">
+        <v>0</v>
+      </c>
+      <c r="J409" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="K409" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M409" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N409" t="n">
+        <v>10</v>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P409" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S409" t="n">
+        <v>4.2945</v>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V409" t="n">
+        <v>118</v>
+      </c>
+      <c r="W409" t="n">
+        <v>127.544</v>
+      </c>
+      <c r="X409" t="n">
+        <v>112.9325</v>
+      </c>
+      <c r="Y409" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z409" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG409" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH409" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI409" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>79.84</v>
+      </c>
+      <c r="F410" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I410" t="b">
+        <v>0</v>
+      </c>
+      <c r="J410" t="n">
+        <v>10</v>
+      </c>
+      <c r="K410" t="n">
+        <v>3487</v>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M410" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N410" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P410" t="n">
+        <v>3117.5</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S410" t="n">
+        <v>7</v>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V410" t="n">
+        <v>3170</v>
+      </c>
+      <c r="W410" t="n">
+        <v>3804</v>
+      </c>
+      <c r="X410" t="n">
+        <v>2948.1</v>
+      </c>
+      <c r="Y410" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI410" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ410" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="F411" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I411" t="b">
+        <v>0</v>
+      </c>
+      <c r="J411" t="n">
+        <v>10</v>
+      </c>
+      <c r="K411" t="n">
+        <v>494.45</v>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M411" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N411" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P411" t="n">
+        <v>420.75</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>53.82</v>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S411" t="n">
+        <v>7</v>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V411" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="W411" t="n">
+        <v>539.4</v>
+      </c>
+      <c r="X411" t="n">
+        <v>418.035</v>
+      </c>
+      <c r="Y411" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI411" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ411" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>71.84</v>
+      </c>
+      <c r="F412" t="n">
+        <v>42.03</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I412" t="b">
+        <v>0</v>
+      </c>
+      <c r="J412" t="n">
+        <v>10</v>
+      </c>
+      <c r="K412" t="n">
+        <v>473</v>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M412" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N412" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P412" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S412" t="n">
+        <v>7</v>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V412" t="n">
+        <v>430</v>
+      </c>
+      <c r="W412" t="n">
+        <v>516</v>
+      </c>
+      <c r="X412" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="Y412" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI412" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ412" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="F413" t="n">
+        <v>59.84</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I413" t="b">
+        <v>0</v>
+      </c>
+      <c r="J413" t="n">
+        <v>10</v>
+      </c>
+      <c r="K413" t="n">
+        <v>4642</v>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M413" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N413" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P413" t="n">
+        <v>3971.48</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>7</v>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V413" t="n">
+        <v>4220</v>
+      </c>
+      <c r="W413" t="n">
+        <v>5064</v>
+      </c>
+      <c r="X413" t="n">
+        <v>3924.6</v>
+      </c>
+      <c r="Y413" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z413" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG413" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH413" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI413" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>73.87</v>
+      </c>
+      <c r="F414" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I414" t="b">
+        <v>0</v>
+      </c>
+      <c r="J414" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K414" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M414" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N414" t="n">
+        <v>7</v>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P414" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>71.56</v>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>7</v>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V414" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="W414" t="n">
+        <v>29.621</v>
+      </c>
+      <c r="X414" t="n">
+        <v>24.7845</v>
+      </c>
+      <c r="Y414" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z414" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG414" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH414" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI414" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ383"/>
+  <autoFilter ref="A1:AJ414"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39714,7 +43540,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-6.34</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -39830,7 +43674,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="E6" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-6.34</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -39871,7 +43733,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-03 14:23:40</t>
+          <t>2026-09-04 14:24:24</t>
         </is>
       </c>
     </row>
@@ -39918,7 +43780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>382</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7">
@@ -39928,7 +43790,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -39938,7 +43800,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>382</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$414</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$438</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ414"/>
+  <dimension ref="A1:AJ438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1965,11 +1965,11 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="n">
         <v>-1.43</v>
@@ -1980,6 +1980,15 @@
       <c r="AC17" t="n">
         <v>-0.61</v>
       </c>
+      <c r="AD17" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-2.85</v>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -1988,7 +1997,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -2040,11 +2049,11 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="n">
         <v>-6.69</v>
@@ -2055,6 +2064,15 @@
       <c r="AC18" t="n">
         <v>-9.24</v>
       </c>
+      <c r="AD18" t="n">
+        <v>-12.74</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-13.69</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2063,7 +2081,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -2115,11 +2133,11 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA19" t="n">
         <v>-4.07</v>
@@ -2130,6 +2148,15 @@
       <c r="AC19" t="n">
         <v>-3.56</v>
       </c>
+      <c r="AD19" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-4.58</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2138,7 +2165,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -2190,11 +2217,11 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
         <v>-1.42</v>
@@ -2205,6 +2232,15 @@
       <c r="AC20" t="n">
         <v>-9.56</v>
       </c>
+      <c r="AD20" t="n">
+        <v>-5.81</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-14.08</v>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2213,7 +2249,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -2265,11 +2301,11 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="n">
         <v>-3.59</v>
@@ -2280,6 +2316,15 @@
       <c r="AC21" t="n">
         <v>-5.48</v>
       </c>
+      <c r="AD21" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-10.02</v>
+      </c>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2288,7 +2333,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -2340,11 +2385,11 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA22" t="n">
         <v>14.67</v>
@@ -2355,6 +2400,15 @@
       <c r="AC22" t="n">
         <v>22.13</v>
       </c>
+      <c r="AD22" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-0.73</v>
+      </c>
       <c r="AG22" t="b">
         <v>1</v>
       </c>
@@ -2363,7 +2417,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -2415,11 +2469,11 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="n">
         <v>2.43</v>
@@ -2430,6 +2484,15 @@
       <c r="AC23" t="n">
         <v>2.43</v>
       </c>
+      <c r="AD23" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-4.01</v>
+      </c>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2438,7 +2501,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2490,11 +2553,11 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="n">
         <v>1.05</v>
@@ -2505,6 +2568,15 @@
       <c r="AC24" t="n">
         <v>1.5</v>
       </c>
+      <c r="AD24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-3.6</v>
+      </c>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2513,7 +2585,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2565,11 +2637,11 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="n">
         <v>8.18</v>
@@ -2580,6 +2652,15 @@
       <c r="AC25" t="n">
         <v>9.109999999999999</v>
       </c>
+      <c r="AD25" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="AG25" t="b">
         <v>1</v>
       </c>
@@ -2588,7 +2669,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -2640,11 +2721,11 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="n">
         <v>6.01</v>
@@ -2655,6 +2736,15 @@
       <c r="AC26" t="n">
         <v>15.31</v>
       </c>
+      <c r="AD26" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-1.74</v>
+      </c>
       <c r="AG26" t="b">
         <v>1</v>
       </c>
@@ -2663,7 +2753,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -2715,11 +2805,11 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="n">
         <v>13.83</v>
@@ -2730,6 +2820,15 @@
       <c r="AC27" t="n">
         <v>30.29</v>
       </c>
+      <c r="AD27" t="n">
+        <v>30.86</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-1.71</v>
+      </c>
       <c r="AG27" t="b">
         <v>1</v>
       </c>
@@ -2738,7 +2837,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -2790,11 +2889,11 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA28" t="n">
         <v>-10.91</v>
@@ -2805,6 +2904,15 @@
       <c r="AC28" t="n">
         <v>-6.02</v>
       </c>
+      <c r="AD28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-13.64</v>
+      </c>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -2813,7 +2921,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -2865,11 +2973,11 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="n">
         <v>-2.87</v>
@@ -2880,6 +2988,15 @@
       <c r="AC29" t="n">
         <v>9.41</v>
       </c>
+      <c r="AD29" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-3.96</v>
+      </c>
       <c r="AG29" t="b">
         <v>1</v>
       </c>
@@ -2888,7 +3005,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -2940,11 +3057,11 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA30" t="n">
         <v>-8.630000000000001</v>
@@ -2955,6 +3072,15 @@
       <c r="AC30" t="n">
         <v>-4.8</v>
       </c>
+      <c r="AD30" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>-11.86</v>
+      </c>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -2963,7 +3089,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -3015,11 +3141,11 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.91</v>
@@ -3030,6 +3156,15 @@
       <c r="AC31" t="n">
         <v>6.17</v>
       </c>
+      <c r="AD31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>-14.34</v>
+      </c>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3038,7 +3173,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -3090,11 +3225,11 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA32" t="n">
         <v>-6.43</v>
@@ -3105,6 +3240,15 @@
       <c r="AC32" t="n">
         <v>-0.74</v>
       </c>
+      <c r="AD32" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-8.359999999999999</v>
+      </c>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3113,7 +3257,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3309,11 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="n">
         <v>-3.11</v>
@@ -3180,6 +3324,15 @@
       <c r="AC33" t="n">
         <v>-7.77</v>
       </c>
+      <c r="AD33" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>-10.62</v>
+      </c>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3188,7 +3341,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -3364,11 +3517,11 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.48</v>
@@ -3379,6 +3532,15 @@
       <c r="AC36" t="n">
         <v>0.46</v>
       </c>
+      <c r="AD36" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>-7.19</v>
+      </c>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -3387,7 +3549,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -3439,11 +3601,11 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA37" t="n">
         <v>-63.07</v>
@@ -3454,6 +3616,15 @@
       <c r="AC37" t="n">
         <v>-60.42</v>
       </c>
+      <c r="AD37" t="n">
+        <v>-58.57</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>-52.16</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>-67.34</v>
+      </c>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -3462,7 +3633,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -3514,11 +3685,11 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA38" t="n">
         <v>-5.23</v>
@@ -3529,6 +3700,15 @@
       <c r="AC38" t="n">
         <v>-4.77</v>
       </c>
+      <c r="AD38" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>-9.529999999999999</v>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -3537,7 +3717,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3773,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3668,7 +3848,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3743,7 +3923,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3818,7 +3998,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -3893,7 +4073,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -3968,7 +4148,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -4043,7 +4223,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -4118,7 +4298,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -4193,7 +4373,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -4268,7 +4448,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -4343,7 +4523,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4355,7 +4535,7 @@
         <v>7.34</v>
       </c>
       <c r="AG49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH49" t="b">
         <v>1</v>
@@ -4418,7 +4598,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4493,7 +4673,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4568,7 +4748,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4643,7 +4823,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4718,7 +4898,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4855,7 +5035,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -4930,7 +5110,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -5005,7 +5185,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -5080,7 +5260,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -5155,7 +5335,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -5230,7 +5410,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -5305,7 +5485,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -5380,7 +5560,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -5455,7 +5635,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5530,7 +5710,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5605,7 +5785,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5680,7 +5860,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5755,7 +5935,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -5830,7 +6010,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -5967,7 +6147,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -6042,7 +6222,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -6117,7 +6297,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA73" t="n">
         <v>-64.53</v>
@@ -6192,7 +6372,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -6267,7 +6447,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -6342,7 +6522,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -6417,7 +6597,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -6492,7 +6672,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6567,7 +6747,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6642,7 +6822,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6717,7 +6897,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -6792,7 +6972,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -6867,7 +7047,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -6942,7 +7122,7 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -7017,7 +7197,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -7092,7 +7272,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -7167,7 +7347,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -7242,7 +7422,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -7317,7 +7497,7 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA89" t="n">
         <v>-65.06999999999999</v>
@@ -7454,7 +7634,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -7529,7 +7709,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -7604,7 +7784,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -7619,7 +7799,7 @@
         <v>0</v>
       </c>
       <c r="AH93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI93" t="inlineStr">
         <is>
@@ -7679,7 +7859,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -7754,7 +7934,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -7829,7 +8009,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -7904,7 +8084,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -7979,7 +8159,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -8054,7 +8234,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -8129,7 +8309,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -8204,7 +8384,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -8279,7 +8459,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -8354,7 +8534,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -8429,7 +8609,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -8504,7 +8684,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -8579,7 +8759,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -8654,7 +8834,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -8729,7 +8909,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -8804,7 +8984,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -8879,7 +9059,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -8954,7 +9134,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -9029,7 +9209,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA112" t="n">
         <v>-67.41</v>
@@ -9104,13 +9284,16 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
       </c>
       <c r="AB113" t="n">
         <v>1.25</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>2.64</v>
       </c>
       <c r="AG113" t="b">
         <v>0</v>
@@ -9176,13 +9359,16 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
       </c>
       <c r="AB114" t="n">
         <v>-2.73</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>-6.48</v>
       </c>
       <c r="AG114" t="b">
         <v>0</v>
@@ -9248,13 +9434,16 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
       </c>
       <c r="AB115" t="n">
         <v>-8.26</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>-4.46</v>
       </c>
       <c r="AG115" t="b">
         <v>0</v>
@@ -9320,13 +9509,16 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
       </c>
       <c r="AB116" t="n">
         <v>15.75</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>13.47</v>
       </c>
       <c r="AG116" t="b">
         <v>1</v>
@@ -9392,12 +9584,15 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
       </c>
       <c r="AB117" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC117" t="n">
         <v>6.5</v>
       </c>
       <c r="AG117" t="b">
@@ -9464,13 +9659,16 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
       </c>
       <c r="AB118" t="n">
         <v>-16.95</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>-5.51</v>
       </c>
       <c r="AG118" t="b">
         <v>0</v>
@@ -9536,13 +9734,16 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
       </c>
       <c r="AB119" t="n">
         <v>-13.62</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>-13.46</v>
       </c>
       <c r="AG119" t="b">
         <v>0</v>
@@ -9608,13 +9809,16 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
       </c>
       <c r="AB120" t="n">
         <v>3.63</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>-1.34</v>
       </c>
       <c r="AG120" t="b">
         <v>0</v>
@@ -9680,13 +9884,16 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
       </c>
       <c r="AB121" t="n">
         <v>0.86</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.65</v>
       </c>
       <c r="AG121" t="b">
         <v>0</v>
@@ -9752,13 +9959,16 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
       </c>
       <c r="AB122" t="n">
         <v>8.779999999999999</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>6.22</v>
       </c>
       <c r="AG122" t="b">
         <v>1</v>
@@ -9824,13 +10034,16 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
       </c>
       <c r="AB123" t="n">
         <v>7.8</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>17.68</v>
       </c>
       <c r="AG123" t="b">
         <v>1</v>
@@ -9896,13 +10109,16 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
       </c>
       <c r="AB124" t="n">
         <v>-4.25</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>2.78</v>
       </c>
       <c r="AG124" t="b">
         <v>0</v>
@@ -9968,13 +10184,16 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
       </c>
       <c r="AB125" t="n">
         <v>3.77</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>10.63</v>
       </c>
       <c r="AG125" t="b">
         <v>0</v>
@@ -10040,13 +10259,16 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
       </c>
       <c r="AB126" t="n">
         <v>8.73</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>8.57</v>
       </c>
       <c r="AG126" t="b">
         <v>0</v>
@@ -10112,13 +10334,16 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
       </c>
       <c r="AB127" t="n">
         <v>-4.81</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>5.35</v>
       </c>
       <c r="AG127" t="b">
         <v>0</v>
@@ -10184,13 +10409,16 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
       </c>
       <c r="AB128" t="n">
         <v>4.27</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1.45</v>
       </c>
       <c r="AG128" t="b">
         <v>0</v>
@@ -10256,13 +10484,16 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA129" t="n">
         <v>-68.09</v>
       </c>
       <c r="AB129" t="n">
         <v>-64.06999999999999</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>-62.39</v>
       </c>
       <c r="AG129" t="b">
         <v>0</v>
@@ -10377,7 +10608,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
@@ -10498,7 +10729,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
@@ -10619,7 +10850,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
@@ -10740,7 +10971,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
@@ -10861,7 +11092,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
@@ -10982,7 +11213,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
@@ -11103,7 +11334,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
@@ -11221,7 +11452,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
@@ -11342,7 +11573,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
@@ -11463,7 +11694,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
@@ -11584,7 +11815,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
@@ -11705,7 +11936,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
@@ -11826,7 +12057,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
@@ -11947,7 +12178,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
@@ -12068,7 +12299,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
@@ -12189,7 +12420,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA145" t="n">
         <v>-66.26000000000001</v>
@@ -12310,7 +12541,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
@@ -12431,7 +12662,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
@@ -12552,7 +12783,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
@@ -12673,7 +12904,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
@@ -12794,7 +13025,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
@@ -12915,7 +13146,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
@@ -13036,7 +13267,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
@@ -13157,7 +13388,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
@@ -13278,7 +13509,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
@@ -13399,7 +13630,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
@@ -13520,7 +13751,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
@@ -13641,7 +13872,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
@@ -13762,7 +13993,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
@@ -13883,7 +14114,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
@@ -14004,7 +14235,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
@@ -14125,7 +14356,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
@@ -14246,7 +14477,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
@@ -14367,7 +14598,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
@@ -14488,7 +14719,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
@@ -14609,7 +14840,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
@@ -14730,7 +14961,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
@@ -14851,7 +15082,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
@@ -15083,7 +15314,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
@@ -15204,7 +15435,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
@@ -15325,7 +15556,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA171" t="n">
         <v>-63.88</v>
@@ -15446,7 +15677,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
@@ -15567,7 +15798,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
@@ -15688,7 +15919,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
@@ -15809,7 +16040,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
@@ -15930,7 +16161,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
@@ -16051,7 +16282,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
@@ -16172,7 +16403,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
@@ -16404,7 +16635,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
@@ -16525,10 +16756,13 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>-2.55</v>
       </c>
       <c r="AG181" t="b">
         <v>0</v>
@@ -16643,10 +16877,13 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>-3.73</v>
       </c>
       <c r="AG182" t="b">
         <v>0</v>
@@ -16761,10 +16998,13 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>-6.99</v>
       </c>
       <c r="AG183" t="b">
         <v>0</v>
@@ -16879,10 +17119,13 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>23.68</v>
       </c>
       <c r="AG184" t="b">
         <v>1</v>
@@ -16997,10 +17240,13 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>-8.17</v>
       </c>
       <c r="AG185" t="b">
         <v>0</v>
@@ -17115,10 +17361,13 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA186" t="n">
         <v>-62.24</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>-60.48</v>
       </c>
       <c r="AG186" t="b">
         <v>0</v>
@@ -17233,7 +17482,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
@@ -17351,7 +17600,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
@@ -17469,7 +17718,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
@@ -17587,7 +17836,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
@@ -17705,7 +17954,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
@@ -17823,7 +18072,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
@@ -17941,13 +18190,13 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
       </c>
       <c r="AG193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH193" t="b">
         <v>0</v>
@@ -18059,7 +18308,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
@@ -18177,7 +18426,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
@@ -18295,7 +18544,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
@@ -18413,7 +18662,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
@@ -18753,7 +19002,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
@@ -18871,7 +19120,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
@@ -18989,7 +19238,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
@@ -19107,7 +19356,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
@@ -19225,7 +19474,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
@@ -19343,7 +19592,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
@@ -19461,7 +19710,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
@@ -19579,7 +19828,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
@@ -19697,7 +19946,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
@@ -19815,7 +20064,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
@@ -19933,7 +20182,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -20051,7 +20300,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
@@ -20169,7 +20418,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
@@ -20398,7 +20647,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
@@ -20516,7 +20765,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
@@ -20634,7 +20883,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
@@ -20752,7 +21001,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
@@ -20870,7 +21119,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
@@ -20988,7 +21237,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
@@ -21106,7 +21355,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
@@ -21224,7 +21473,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
@@ -21342,7 +21591,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
@@ -21460,7 +21709,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
@@ -21578,7 +21827,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
@@ -21696,7 +21945,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
@@ -21814,7 +22063,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
@@ -21932,7 +22181,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
@@ -22050,7 +22299,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
@@ -22168,7 +22417,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
@@ -22286,7 +22535,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
@@ -22404,7 +22653,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
@@ -22633,7 +22882,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
@@ -22973,7 +23222,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
@@ -23091,7 +23340,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -23209,7 +23458,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
@@ -23327,7 +23576,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
@@ -23445,7 +23694,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
@@ -23563,7 +23812,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
@@ -23681,7 +23930,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
@@ -23690,7 +23939,7 @@
         <v>0</v>
       </c>
       <c r="AH242" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI242" t="inlineStr">
         <is>
@@ -23799,7 +24048,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
@@ -23917,7 +24166,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
@@ -24035,7 +24284,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
@@ -24153,7 +24402,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
@@ -24271,7 +24520,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
@@ -24389,7 +24638,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
@@ -24507,7 +24756,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
@@ -24625,7 +24874,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
@@ -24743,7 +24992,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
@@ -24861,7 +25110,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
@@ -24979,7 +25228,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
@@ -25097,7 +25346,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
@@ -25215,7 +25464,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
@@ -25555,7 +25804,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
@@ -25895,7 +26144,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
@@ -26013,7 +26262,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
@@ -26131,7 +26380,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
@@ -26249,7 +26498,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
@@ -26478,7 +26727,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
@@ -26596,7 +26845,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
@@ -26714,7 +26963,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
@@ -26832,7 +27081,10 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>0.6</v>
       </c>
       <c r="AG269" t="b">
         <v>0</v>
@@ -26947,7 +27199,10 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>1.37</v>
       </c>
       <c r="AG270" t="b">
         <v>0</v>
@@ -27062,7 +27317,10 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>-3.32</v>
       </c>
       <c r="AG271" t="b">
         <v>0</v>
@@ -27177,7 +27435,10 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>-1.97</v>
       </c>
       <c r="AG272" t="b">
         <v>0</v>
@@ -27292,7 +27553,10 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>10.85</v>
       </c>
       <c r="AG273" t="b">
         <v>0</v>
@@ -27407,7 +27671,10 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>-3.42</v>
       </c>
       <c r="AG274" t="b">
         <v>0</v>
@@ -27522,7 +27789,10 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>-0.74</v>
       </c>
       <c r="AG275" t="b">
         <v>0</v>
@@ -27637,7 +27907,10 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>2.54</v>
       </c>
       <c r="AG276" t="b">
         <v>0</v>
@@ -27752,7 +28025,10 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>0</v>
       </c>
       <c r="AG277" t="b">
         <v>0</v>
@@ -27867,7 +28143,10 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA278" t="n">
+        <v>-3.86</v>
       </c>
       <c r="AG278" t="b">
         <v>0</v>
@@ -27982,7 +28261,10 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA279" t="n">
+        <v>2.26</v>
       </c>
       <c r="AG279" t="b">
         <v>0</v>
@@ -28097,7 +28379,10 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA280" t="n">
+        <v>2.66</v>
       </c>
       <c r="AG280" t="b">
         <v>0</v>
@@ -28212,7 +28497,10 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA281" t="n">
+        <v>0.44</v>
       </c>
       <c r="AG281" t="b">
         <v>0</v>
@@ -28327,7 +28615,10 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA282" t="n">
+        <v>-4.79</v>
       </c>
       <c r="AG282" t="b">
         <v>0</v>
@@ -28442,7 +28733,10 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA283" t="n">
+        <v>6.23</v>
       </c>
       <c r="AG283" t="b">
         <v>0</v>
@@ -28557,7 +28851,10 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA284" t="n">
+        <v>-0.21</v>
       </c>
       <c r="AG284" t="b">
         <v>0</v>
@@ -28672,7 +28969,10 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA285" t="n">
+        <v>0.44</v>
       </c>
       <c r="AG285" t="b">
         <v>0</v>
@@ -28787,7 +29087,10 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA286" t="n">
+        <v>3.82</v>
       </c>
       <c r="AG286" t="b">
         <v>0</v>
@@ -28902,7 +29205,10 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA287" t="n">
+        <v>3.62</v>
       </c>
       <c r="AG287" t="b">
         <v>0</v>
@@ -29017,7 +29323,10 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>9.16</v>
       </c>
       <c r="AG288" t="b">
         <v>0</v>
@@ -29132,10 +29441,13 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA289" t="n">
+        <v>9.56</v>
       </c>
       <c r="AG289" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH289" t="b">
         <v>0</v>
@@ -29247,7 +29559,10 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>6.61</v>
       </c>
       <c r="AG290" t="b">
         <v>0</v>
@@ -29362,7 +29677,10 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>-12.94</v>
       </c>
       <c r="AG291" t="b">
         <v>0</v>
@@ -29477,7 +29795,10 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AG292" t="b">
         <v>0</v>
@@ -29592,7 +29913,10 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA293" t="n">
+        <v>-0.7</v>
       </c>
       <c r="AG293" t="b">
         <v>0</v>
@@ -30040,7 +30364,10 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA297" t="n">
+        <v>-2.7</v>
       </c>
       <c r="AG297" t="b">
         <v>0</v>
@@ -30155,7 +30482,10 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA298" t="n">
+        <v>-0.86</v>
       </c>
       <c r="AG298" t="b">
         <v>0</v>
@@ -30270,7 +30600,10 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>-64.90000000000001</v>
       </c>
       <c r="AG299" t="b">
         <v>0</v>
@@ -30496,7 +30829,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG301" t="b">
         <v>0</v>
@@ -30611,7 +30944,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG302" t="b">
         <v>0</v>
@@ -30726,7 +31059,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG303" t="b">
         <v>0</v>
@@ -30841,7 +31174,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG304" t="b">
         <v>0</v>
@@ -30956,7 +31289,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG305" t="b">
         <v>0</v>
@@ -31071,7 +31404,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG306" t="b">
         <v>0</v>
@@ -31186,7 +31519,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG307" t="b">
         <v>0</v>
@@ -31301,7 +31634,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG308" t="b">
         <v>0</v>
@@ -31416,7 +31749,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG309" t="b">
         <v>0</v>
@@ -31531,7 +31864,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG310" t="b">
         <v>0</v>
@@ -31646,7 +31979,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG311" t="b">
         <v>0</v>
@@ -31761,7 +32094,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG312" t="b">
         <v>0</v>
@@ -31876,7 +32209,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG313" t="b">
         <v>0</v>
@@ -31991,7 +32324,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG314" t="b">
         <v>0</v>
@@ -32106,7 +32439,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG315" t="b">
         <v>0</v>
@@ -32221,7 +32554,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG316" t="b">
         <v>0</v>
@@ -32336,7 +32669,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG317" t="b">
         <v>0</v>
@@ -32451,7 +32784,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG318" t="b">
         <v>0</v>
@@ -32566,7 +32899,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG319" t="b">
         <v>0</v>
@@ -32681,7 +33014,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG320" t="b">
         <v>0</v>
@@ -32796,7 +33129,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG321" t="b">
         <v>0</v>
@@ -32911,7 +33244,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG322" t="b">
         <v>0</v>
@@ -33026,7 +33359,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG323" t="b">
         <v>0</v>
@@ -33141,7 +33474,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG324" t="b">
         <v>0</v>
@@ -33478,7 +33811,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG327" t="b">
         <v>0</v>
@@ -33593,7 +33926,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG328" t="b">
         <v>0</v>
@@ -33708,7 +34041,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG329" t="b">
         <v>0</v>
@@ -34045,7 +34378,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG332" t="b">
         <v>0</v>
@@ -34160,7 +34493,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG333" t="b">
         <v>0</v>
@@ -34275,7 +34608,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG334" t="b">
         <v>0</v>
@@ -34390,7 +34723,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG335" t="b">
         <v>0</v>
@@ -34505,7 +34838,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG336" t="b">
         <v>0</v>
@@ -34620,7 +34953,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG337" t="b">
         <v>0</v>
@@ -34735,7 +35068,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG338" t="b">
         <v>0</v>
@@ -34850,7 +35183,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG339" t="b">
         <v>0</v>
@@ -34965,7 +35298,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG340" t="b">
         <v>0</v>
@@ -35080,7 +35413,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG341" t="b">
         <v>0</v>
@@ -35195,7 +35528,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG342" t="b">
         <v>0</v>
@@ -35310,7 +35643,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG343" t="b">
         <v>0</v>
@@ -35425,7 +35758,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG344" t="b">
         <v>0</v>
@@ -35540,7 +35873,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG345" t="b">
         <v>0</v>
@@ -35655,7 +35988,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG346" t="b">
         <v>0</v>
@@ -35770,7 +36103,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG347" t="b">
         <v>0</v>
@@ -35885,7 +36218,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG348" t="b">
         <v>0</v>
@@ -36000,7 +36333,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG349" t="b">
         <v>0</v>
@@ -36115,7 +36448,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG350" t="b">
         <v>0</v>
@@ -36230,7 +36563,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG351" t="b">
         <v>0</v>
@@ -36345,7 +36678,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG352" t="b">
         <v>0</v>
@@ -36460,7 +36793,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG353" t="b">
         <v>0</v>
@@ -37019,7 +37352,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG358" t="b">
         <v>0</v>
@@ -37134,13 +37467,13 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG359" t="b">
         <v>0</v>
       </c>
       <c r="AH359" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI359" t="inlineStr">
         <is>
@@ -37249,7 +37582,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG360" t="b">
         <v>0</v>
@@ -37364,7 +37697,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG361" t="b">
         <v>0</v>
@@ -37479,7 +37812,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG362" t="b">
         <v>0</v>
@@ -37594,7 +37927,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG363" t="b">
         <v>0</v>
@@ -37709,7 +38042,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG364" t="b">
         <v>0</v>
@@ -37824,7 +38157,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG365" t="b">
         <v>0</v>
@@ -37939,7 +38272,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG366" t="b">
         <v>0</v>
@@ -38054,7 +38387,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG367" t="b">
         <v>0</v>
@@ -38169,7 +38502,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG368" t="b">
         <v>0</v>
@@ -38284,7 +38617,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG369" t="b">
         <v>0</v>
@@ -38399,7 +38732,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG370" t="b">
         <v>0</v>
@@ -38514,7 +38847,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG371" t="b">
         <v>0</v>
@@ -38629,7 +38962,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG372" t="b">
         <v>0</v>
@@ -38744,7 +39077,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG373" t="b">
         <v>0</v>
@@ -38859,7 +39192,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG374" t="b">
         <v>0</v>
@@ -38974,7 +39307,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG375" t="b">
         <v>0</v>
@@ -39089,7 +39422,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG376" t="b">
         <v>0</v>
@@ -39204,7 +39537,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG377" t="b">
         <v>0</v>
@@ -39541,7 +39874,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG380" t="b">
         <v>0</v>
@@ -39656,7 +39989,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG381" t="b">
         <v>0</v>
@@ -39882,7 +40215,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG383" t="b">
         <v>0</v>
@@ -39997,7 +40330,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG384" t="b">
         <v>0</v>
@@ -40112,7 +40445,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG385" t="b">
         <v>0</v>
@@ -40227,7 +40560,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG386" t="b">
         <v>0</v>
@@ -40342,7 +40675,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG387" t="b">
         <v>0</v>
@@ -40457,7 +40790,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG388" t="b">
         <v>0</v>
@@ -40572,7 +40905,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG389" t="b">
         <v>0</v>
@@ -40684,7 +41017,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG390" t="b">
         <v>0</v>
@@ -40799,7 +41132,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG391" t="b">
         <v>0</v>
@@ -40914,7 +41247,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG392" t="b">
         <v>0</v>
@@ -41029,7 +41362,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG393" t="b">
         <v>0</v>
@@ -41144,7 +41477,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG394" t="b">
         <v>0</v>
@@ -41259,7 +41592,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG395" t="b">
         <v>0</v>
@@ -41374,7 +41707,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG396" t="b">
         <v>0</v>
@@ -41489,7 +41822,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG397" t="b">
         <v>0</v>
@@ -41604,7 +41937,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG398" t="b">
         <v>0</v>
@@ -41719,7 +42052,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG399" t="b">
         <v>0</v>
@@ -41834,7 +42167,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG400" t="b">
         <v>0</v>
@@ -41949,7 +42282,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG401" t="b">
         <v>0</v>
@@ -42064,7 +42397,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG402" t="b">
         <v>0</v>
@@ -42179,7 +42512,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG403" t="b">
         <v>0</v>
@@ -42294,7 +42627,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG404" t="b">
         <v>0</v>
@@ -42409,7 +42742,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG405" t="b">
         <v>0</v>
@@ -42524,7 +42857,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG406" t="b">
         <v>0</v>
@@ -42639,13 +42972,13 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG407" t="b">
         <v>0</v>
       </c>
       <c r="AH407" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI407" t="inlineStr">
         <is>
@@ -42754,7 +43087,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG408" t="b">
         <v>0</v>
@@ -42869,7 +43202,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG409" t="b">
         <v>0</v>
@@ -43317,7 +43650,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG413" t="b">
         <v>0</v>
@@ -43432,7 +43765,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG414" t="b">
         <v>0</v>
@@ -43443,11 +43776,2759 @@
       <c r="AI414" t="inlineStr">
         <is>
           <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>76.73999999999999</v>
+      </c>
+      <c r="F415" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I415" t="b">
+        <v>0</v>
+      </c>
+      <c r="J415" t="n">
+        <v>10</v>
+      </c>
+      <c r="K415" t="n">
+        <v>73.26000000000001</v>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M415" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N415" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P415" t="n">
+        <v>63.55</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>7</v>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V415" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="W415" t="n">
+        <v>79.92</v>
+      </c>
+      <c r="X415" t="n">
+        <v>61.938</v>
+      </c>
+      <c r="Y415" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z415" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG415" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH415" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI415" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>72.39</v>
+      </c>
+      <c r="F416" t="n">
+        <v>47.59</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I416" t="b">
+        <v>0</v>
+      </c>
+      <c r="J416" t="n">
+        <v>10</v>
+      </c>
+      <c r="K416" t="n">
+        <v>253.55</v>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M416" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N416" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P416" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S416" t="n">
+        <v>7</v>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V416" t="n">
+        <v>230.5</v>
+      </c>
+      <c r="W416" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="X416" t="n">
+        <v>214.365</v>
+      </c>
+      <c r="Y416" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z416" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG416" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH416" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI416" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>台化</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="F417" t="n">
+        <v>51.37</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I417" t="b">
+        <v>0</v>
+      </c>
+      <c r="J417" t="n">
+        <v>10</v>
+      </c>
+      <c r="K417" t="n">
+        <v>79.09</v>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M417" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N417" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P417" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S417" t="n">
+        <v>7</v>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V417" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="W417" t="n">
+        <v>86.28</v>
+      </c>
+      <c r="X417" t="n">
+        <v>66.867</v>
+      </c>
+      <c r="Y417" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z417" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG417" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH417" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI417" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>79.59</v>
+      </c>
+      <c r="F418" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I418" t="b">
+        <v>0</v>
+      </c>
+      <c r="J418" t="n">
+        <v>10</v>
+      </c>
+      <c r="K418" t="n">
+        <v>812.9</v>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M418" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N418" t="n">
+        <v>10</v>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P418" t="n">
+        <v>744.5</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S418" t="n">
+        <v>5.3471</v>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="V418" t="n">
+        <v>739</v>
+      </c>
+      <c r="W418" t="n">
+        <v>875.7082</v>
+      </c>
+      <c r="X418" t="n">
+        <v>699.485</v>
+      </c>
+      <c r="Y418" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z418" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG418" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH418" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI418" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="F419" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I419" t="b">
+        <v>0</v>
+      </c>
+      <c r="J419" t="n">
+        <v>10</v>
+      </c>
+      <c r="K419" t="n">
+        <v>264</v>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M419" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N419" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P419" t="n">
+        <v>232.75</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S419" t="n">
+        <v>7</v>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V419" t="n">
+        <v>240</v>
+      </c>
+      <c r="W419" t="n">
+        <v>288</v>
+      </c>
+      <c r="X419" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="Y419" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z419" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG419" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH419" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI419" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>80.09</v>
+      </c>
+      <c r="F420" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I420" t="b">
+        <v>0</v>
+      </c>
+      <c r="J420" t="n">
+        <v>10</v>
+      </c>
+      <c r="K420" t="n">
+        <v>1098.9</v>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M420" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N420" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P420" t="n">
+        <v>965.5</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S420" t="n">
+        <v>7</v>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V420" t="n">
+        <v>999</v>
+      </c>
+      <c r="W420" t="n">
+        <v>1198.8</v>
+      </c>
+      <c r="X420" t="n">
+        <v>929.0700000000001</v>
+      </c>
+      <c r="Y420" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG420" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH420" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI420" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="F421" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I421" t="b">
+        <v>0</v>
+      </c>
+      <c r="J421" t="n">
+        <v>10</v>
+      </c>
+      <c r="K421" t="n">
+        <v>382.25</v>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M421" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N421" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P421" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S421" t="n">
+        <v>7</v>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V421" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="W421" t="n">
+        <v>404.0524</v>
+      </c>
+      <c r="X421" t="n">
+        <v>323.175</v>
+      </c>
+      <c r="Y421" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG421" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH421" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI421" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="F422" t="n">
+        <v>53.62</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I422" t="b">
+        <v>0</v>
+      </c>
+      <c r="J422" t="n">
+        <v>10</v>
+      </c>
+      <c r="K422" t="n">
+        <v>300.3</v>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M422" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N422" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P422" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>60.82</v>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S422" t="n">
+        <v>7</v>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V422" t="n">
+        <v>273</v>
+      </c>
+      <c r="W422" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="X422" t="n">
+        <v>253.89</v>
+      </c>
+      <c r="Y422" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z422" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG422" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH422" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI422" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>80.58</v>
+      </c>
+      <c r="F423" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I423" t="b">
+        <v>0</v>
+      </c>
+      <c r="J423" t="n">
+        <v>10</v>
+      </c>
+      <c r="K423" t="n">
+        <v>5236</v>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M423" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N423" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P423" t="n">
+        <v>4255</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S423" t="n">
+        <v>7</v>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V423" t="n">
+        <v>4760</v>
+      </c>
+      <c r="W423" t="n">
+        <v>5712</v>
+      </c>
+      <c r="X423" t="n">
+        <v>4426.8</v>
+      </c>
+      <c r="Y423" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z423" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG423" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH423" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI423" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="F424" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I424" t="b">
+        <v>0</v>
+      </c>
+      <c r="J424" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="K424" t="n">
+        <v>125.68</v>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M424" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="N424" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P424" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S424" t="n">
+        <v>5.714</v>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V424" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="W424" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="X424" t="n">
+        <v>107.9575</v>
+      </c>
+      <c r="Y424" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z424" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG424" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH424" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI424" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>80.95999999999999</v>
+      </c>
+      <c r="F425" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I425" t="b">
+        <v>0</v>
+      </c>
+      <c r="J425" t="n">
+        <v>10</v>
+      </c>
+      <c r="K425" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M425" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N425" t="n">
+        <v>5</v>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P425" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>77.19</v>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S425" t="n">
+        <v>7</v>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V425" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="W425" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="X425" t="n">
+        <v>139.035</v>
+      </c>
+      <c r="Y425" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z425" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG425" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH425" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI425" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>80.98</v>
+      </c>
+      <c r="F426" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I426" t="b">
+        <v>0</v>
+      </c>
+      <c r="J426" t="n">
+        <v>10</v>
+      </c>
+      <c r="K426" t="n">
+        <v>125.95</v>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M426" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N426" t="n">
+        <v>3</v>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P426" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>70.13</v>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S426" t="n">
+        <v>7</v>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V426" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="W426" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="X426" t="n">
+        <v>106.485</v>
+      </c>
+      <c r="Y426" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z426" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG426" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH426" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI426" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="F427" t="n">
+        <v>51.27</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I427" t="b">
+        <v>0</v>
+      </c>
+      <c r="J427" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K427" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M427" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N427" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P427" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S427" t="n">
+        <v>7</v>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V427" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="W427" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="X427" t="n">
+        <v>34.3635</v>
+      </c>
+      <c r="Y427" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG427" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH427" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI427" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>85.55</v>
+      </c>
+      <c r="F428" t="n">
+        <v>35.53</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I428" t="b">
+        <v>0</v>
+      </c>
+      <c r="J428" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K428" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M428" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N428" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P428" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>80.22</v>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S428" t="n">
+        <v>7</v>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V428" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="W428" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="X428" t="n">
+        <v>40.5015</v>
+      </c>
+      <c r="Y428" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG428" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH428" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI428" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>78.89</v>
+      </c>
+      <c r="F429" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I429" t="b">
+        <v>0</v>
+      </c>
+      <c r="J429" t="n">
+        <v>10</v>
+      </c>
+      <c r="K429" t="n">
+        <v>45.21</v>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M429" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N429" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P429" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>68.44</v>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S429" t="n">
+        <v>7</v>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V429" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="W429" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="X429" t="n">
+        <v>38.223</v>
+      </c>
+      <c r="Y429" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z429" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG429" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH429" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI429" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="F430" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I430" t="b">
+        <v>0</v>
+      </c>
+      <c r="J430" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="K430" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M430" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N430" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P430" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S430" t="n">
+        <v>7</v>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V430" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="W430" t="n">
+        <v>48.732</v>
+      </c>
+      <c r="X430" t="n">
+        <v>39.618</v>
+      </c>
+      <c r="Y430" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG430" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH430" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI430" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>74.84</v>
+      </c>
+      <c r="F431" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I431" t="b">
+        <v>0</v>
+      </c>
+      <c r="J431" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="K431" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M431" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N431" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P431" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>71.66</v>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S431" t="n">
+        <v>7</v>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V431" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="W431" t="n">
+        <v>43.3547</v>
+      </c>
+      <c r="X431" t="n">
+        <v>34.689</v>
+      </c>
+      <c r="Y431" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG431" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH431" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI431" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>75.87</v>
+      </c>
+      <c r="F432" t="n">
+        <v>52.22</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I432" t="b">
+        <v>0</v>
+      </c>
+      <c r="J432" t="n">
+        <v>10</v>
+      </c>
+      <c r="K432" t="n">
+        <v>3762</v>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M432" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N432" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P432" t="n">
+        <v>3167.5</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>64.81999999999999</v>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S432" t="n">
+        <v>7</v>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V432" t="n">
+        <v>3420</v>
+      </c>
+      <c r="W432" t="n">
+        <v>4104</v>
+      </c>
+      <c r="X432" t="n">
+        <v>3180.6</v>
+      </c>
+      <c r="Y432" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG432" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH432" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI432" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>70.69</v>
+      </c>
+      <c r="F433" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I433" t="b">
+        <v>0</v>
+      </c>
+      <c r="J433" t="n">
+        <v>10</v>
+      </c>
+      <c r="K433" t="n">
+        <v>542.3</v>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M433" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N433" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P433" t="n">
+        <v>477.25</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S433" t="n">
+        <v>7</v>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V433" t="n">
+        <v>493</v>
+      </c>
+      <c r="W433" t="n">
+        <v>591.6</v>
+      </c>
+      <c r="X433" t="n">
+        <v>458.49</v>
+      </c>
+      <c r="Y433" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z433" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG433" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH433" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI433" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>73.02</v>
+      </c>
+      <c r="F434" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I434" t="b">
+        <v>0</v>
+      </c>
+      <c r="J434" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="K434" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M434" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="N434" t="n">
+        <v>10</v>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P434" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S434" t="n">
+        <v>3.4765</v>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V434" t="n">
+        <v>117</v>
+      </c>
+      <c r="W434" t="n">
+        <v>125.9384</v>
+      </c>
+      <c r="X434" t="n">
+        <v>112.9325</v>
+      </c>
+      <c r="Y434" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z434" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG434" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH434" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI434" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>71.54000000000001</v>
+      </c>
+      <c r="F435" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I435" t="b">
+        <v>0</v>
+      </c>
+      <c r="J435" t="n">
+        <v>10</v>
+      </c>
+      <c r="K435" t="n">
+        <v>3377</v>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M435" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N435" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P435" t="n">
+        <v>3122.5</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>52.32</v>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S435" t="n">
+        <v>7</v>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V435" t="n">
+        <v>3070</v>
+      </c>
+      <c r="W435" t="n">
+        <v>3684</v>
+      </c>
+      <c r="X435" t="n">
+        <v>2855.1</v>
+      </c>
+      <c r="Y435" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI435" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ435" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="F436" t="n">
+        <v>53.88</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I436" t="b">
+        <v>0</v>
+      </c>
+      <c r="J436" t="n">
+        <v>10</v>
+      </c>
+      <c r="K436" t="n">
+        <v>495.55</v>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M436" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N436" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P436" t="n">
+        <v>420.75</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S436" t="n">
+        <v>7</v>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V436" t="n">
+        <v>450.5</v>
+      </c>
+      <c r="W436" t="n">
+        <v>540.6</v>
+      </c>
+      <c r="X436" t="n">
+        <v>418.965</v>
+      </c>
+      <c r="Y436" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI436" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ436" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>79.73999999999999</v>
+      </c>
+      <c r="F437" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I437" t="b">
+        <v>0</v>
+      </c>
+      <c r="J437" t="n">
+        <v>10</v>
+      </c>
+      <c r="K437" t="n">
+        <v>6528.5</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M437" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N437" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P437" t="n">
+        <v>5847.5</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S437" t="n">
+        <v>7</v>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V437" t="n">
+        <v>5935</v>
+      </c>
+      <c r="W437" t="n">
+        <v>7122</v>
+      </c>
+      <c r="X437" t="n">
+        <v>5519.55</v>
+      </c>
+      <c r="Y437" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG437" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH437" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI437" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>70.04000000000001</v>
+      </c>
+      <c r="F438" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I438" t="b">
+        <v>0</v>
+      </c>
+      <c r="J438" t="n">
+        <v>10</v>
+      </c>
+      <c r="K438" t="n">
+        <v>210.1</v>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M438" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N438" t="n">
+        <v>3</v>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P438" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>65.38</v>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S438" t="n">
+        <v>7</v>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V438" t="n">
+        <v>191</v>
+      </c>
+      <c r="W438" t="n">
+        <v>229.2</v>
+      </c>
+      <c r="X438" t="n">
+        <v>177.63</v>
+      </c>
+      <c r="Y438" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI438" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ438" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ414"/>
+  <autoFilter ref="A1:AJ438"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43540,25 +46621,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C4" t="n">
         <v>0.5</v>
       </c>
       <c r="D4" t="n">
-        <v>7.53</v>
+        <v>3.24</v>
       </c>
       <c r="E4" t="n">
-        <v>15.61</v>
+        <v>11.84</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.34</v>
+        <v>-8.65</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3571</v>
+        <v>0.2941</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>0.5294</v>
       </c>
     </row>
   </sheetData>
@@ -43674,25 +46755,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
         <v>0.5</v>
       </c>
       <c r="D6" t="n">
-        <v>7.53</v>
+        <v>3.24</v>
       </c>
       <c r="E6" t="n">
-        <v>15.61</v>
+        <v>11.84</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.34</v>
+        <v>-8.65</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3571</v>
+        <v>0.2941</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5</v>
+        <v>0.5294</v>
       </c>
     </row>
   </sheetData>
@@ -43733,7 +46814,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 14:24:24</t>
+          <t>2026-09-07 14:24:50</t>
         </is>
       </c>
     </row>
@@ -43780,7 +46861,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>413</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7">
@@ -43790,7 +46871,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -43800,7 +46881,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -43877,7 +46958,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Swing Buy 20D完成樣本未達30筆，只可做結構檢查。</t>
+          <t>完成樣本已達最低觀察門檻，可開始初步比較分組績效。</t>
         </is>
       </c>
     </row>

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$438</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$462</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ438"/>
+  <dimension ref="A1:AJ462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="n">
         <v>-5.13</v>
@@ -3784,6 +3784,15 @@
       <c r="AC39" t="n">
         <v>-7.37</v>
       </c>
+      <c r="AD39" t="n">
+        <v>-14.42</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>-15.71</v>
+      </c>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -3792,7 +3801,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -3844,11 +3853,11 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA40" t="n">
         <v>-3.13</v>
@@ -3859,6 +3868,15 @@
       <c r="AC40" t="n">
         <v>1.17</v>
       </c>
+      <c r="AD40" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>-6.01</v>
+      </c>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -3867,7 +3885,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -3919,11 +3937,11 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="n">
         <v>-4.05</v>
@@ -3934,6 +3952,15 @@
       <c r="AC41" t="n">
         <v>-3.54</v>
       </c>
+      <c r="AD41" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>-5.06</v>
+      </c>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -3942,7 +3969,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -3994,11 +4021,11 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA42" t="n">
         <v>1.86</v>
@@ -4009,6 +4036,15 @@
       <c r="AC42" t="n">
         <v>11.92</v>
       </c>
+      <c r="AD42" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>-6.52</v>
+      </c>
       <c r="AG42" t="b">
         <v>1</v>
       </c>
@@ -4017,7 +4053,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -4069,11 +4105,11 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA43" t="n">
         <v>8.460000000000001</v>
@@ -4084,6 +4120,15 @@
       <c r="AC43" t="n">
         <v>20.38</v>
       </c>
+      <c r="AD43" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>-0.95</v>
+      </c>
       <c r="AG43" t="b">
         <v>1</v>
       </c>
@@ -4092,7 +4137,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -4144,11 +4189,11 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA44" t="n">
         <v>10.82</v>
@@ -4159,6 +4204,15 @@
       <c r="AC44" t="n">
         <v>-2.4</v>
       </c>
+      <c r="AD44" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>-9.859999999999999</v>
+      </c>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4167,7 +4221,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -4219,11 +4273,11 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.71</v>
@@ -4234,6 +4288,15 @@
       <c r="AC45" t="n">
         <v>2.43</v>
       </c>
+      <c r="AD45" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>-4.28</v>
+      </c>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -4242,7 +4305,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4294,11 +4357,11 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="n">
         <v>12.1</v>
@@ -4309,6 +4372,15 @@
       <c r="AC46" t="n">
         <v>1.9</v>
       </c>
+      <c r="AD46" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>-5.06</v>
+      </c>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -4317,7 +4389,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -4369,11 +4441,11 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA47" t="n">
         <v>2.72</v>
@@ -4384,6 +4456,15 @@
       <c r="AC47" t="n">
         <v>7.56</v>
       </c>
+      <c r="AD47" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>-2.72</v>
+      </c>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -4392,7 +4473,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -4444,11 +4525,11 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="n">
         <v>5.32</v>
@@ -4459,6 +4540,15 @@
       <c r="AC48" t="n">
         <v>5.93</v>
       </c>
+      <c r="AD48" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>-3.89</v>
+      </c>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -4467,7 +4557,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4519,11 +4609,11 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA49" t="n">
         <v>-3.36</v>
@@ -4534,6 +4624,15 @@
       <c r="AC49" t="n">
         <v>7.34</v>
       </c>
+      <c r="AD49" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>-9.08</v>
+      </c>
       <c r="AG49" t="b">
         <v>1</v>
       </c>
@@ -4542,7 +4641,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -4594,11 +4693,11 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA50" t="n">
         <v>9.17</v>
@@ -4609,6 +4708,15 @@
       <c r="AC50" t="n">
         <v>9.17</v>
       </c>
+      <c r="AD50" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>-3.21</v>
+      </c>
       <c r="AG50" t="b">
         <v>1</v>
       </c>
@@ -4617,7 +4725,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -4669,11 +4777,11 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA51" t="n">
         <v>8.08</v>
@@ -4684,6 +4792,15 @@
       <c r="AC51" t="n">
         <v>10.77</v>
       </c>
+      <c r="AD51" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>29.42</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="AG51" t="b">
         <v>1</v>
       </c>
@@ -4692,7 +4809,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -4744,11 +4861,11 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="n">
         <v>20.55</v>
@@ -4759,6 +4876,15 @@
       <c r="AC52" t="n">
         <v>31.46</v>
       </c>
+      <c r="AD52" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>54.42</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>-1.26</v>
+      </c>
       <c r="AG52" t="b">
         <v>1</v>
       </c>
@@ -4767,7 +4893,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -4819,11 +4945,11 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA53" t="n">
         <v>-0.32</v>
@@ -4834,6 +4960,15 @@
       <c r="AC53" t="n">
         <v>12.56</v>
       </c>
+      <c r="AD53" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>-3.22</v>
+      </c>
       <c r="AG53" t="b">
         <v>1</v>
       </c>
@@ -4842,7 +4977,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -4894,11 +5029,11 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA54" t="n">
         <v>-5.24</v>
@@ -4909,6 +5044,15 @@
       <c r="AC54" t="n">
         <v>-4.71</v>
       </c>
+      <c r="AD54" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>-9.69</v>
+      </c>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -4917,7 +5061,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -5031,11 +5175,11 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA56" t="n">
         <v>-4.49</v>
@@ -5046,6 +5190,15 @@
       <c r="AC56" t="n">
         <v>-0.83</v>
       </c>
+      <c r="AD56" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>-5.55</v>
+      </c>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -5054,7 +5207,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5263,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -5185,7 +5338,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -5260,7 +5413,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -5335,7 +5488,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -5410,7 +5563,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -5485,7 +5638,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -5560,7 +5713,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -5635,7 +5788,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5710,7 +5863,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5785,7 +5938,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5860,7 +6013,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -5935,7 +6088,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -6010,7 +6163,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -6147,7 +6300,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -6222,7 +6375,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -6297,7 +6450,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA73" t="n">
         <v>-64.53</v>
@@ -6372,7 +6525,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -6447,7 +6600,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -6522,7 +6675,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -6597,7 +6750,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -6672,7 +6825,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6747,7 +6900,7 @@
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6822,7 +6975,7 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6897,7 +7050,7 @@
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -6972,7 +7125,7 @@
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -7047,7 +7200,7 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -7122,7 +7275,7 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -7197,7 +7350,7 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -7272,7 +7425,7 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -7347,7 +7500,7 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -7422,7 +7575,7 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -7497,7 +7650,7 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA89" t="n">
         <v>-65.06999999999999</v>
@@ -7634,7 +7787,7 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -7709,7 +7862,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -7784,7 +7937,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -7859,7 +8012,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -7934,7 +8087,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -8009,7 +8162,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -8084,7 +8237,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -8159,7 +8312,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -8234,7 +8387,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -8309,7 +8462,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -8384,7 +8537,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -8459,7 +8612,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -8534,7 +8687,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -8609,7 +8762,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -8684,7 +8837,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -8759,7 +8912,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -8834,7 +8987,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -8909,7 +9062,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -8984,7 +9137,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -9059,7 +9212,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -9134,7 +9287,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -9209,7 +9362,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA112" t="n">
         <v>-67.41</v>
@@ -9284,7 +9437,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
@@ -9359,7 +9512,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
@@ -9434,7 +9587,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
@@ -9509,7 +9662,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
@@ -9584,7 +9737,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
@@ -9659,7 +9812,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
@@ -9734,7 +9887,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
@@ -9809,7 +9962,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
@@ -9884,7 +10037,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
@@ -9959,7 +10112,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
@@ -10034,7 +10187,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
@@ -10109,7 +10262,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
@@ -10184,7 +10337,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
@@ -10259,7 +10412,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
@@ -10334,7 +10487,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
@@ -10409,7 +10562,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
@@ -10484,7 +10637,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA129" t="n">
         <v>-68.09</v>
@@ -10608,13 +10761,16 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
       </c>
       <c r="AB130" t="n">
         <v>6.58</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1.96</v>
       </c>
       <c r="AG130" t="b">
         <v>0</v>
@@ -10729,13 +10885,16 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
       </c>
       <c r="AB131" t="n">
         <v>9.869999999999999</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>6.4</v>
       </c>
       <c r="AG131" t="b">
         <v>0</v>
@@ -10850,13 +11009,16 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
       </c>
       <c r="AB132" t="n">
         <v>-1.72</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>-3.82</v>
       </c>
       <c r="AG132" t="b">
         <v>0</v>
@@ -10971,13 +11133,16 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
       </c>
       <c r="AB133" t="n">
         <v>14.49</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.47</v>
       </c>
       <c r="AG133" t="b">
         <v>0</v>
@@ -11092,13 +11257,16 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
       </c>
       <c r="AB134" t="n">
         <v>-9.109999999999999</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>-13.94</v>
       </c>
       <c r="AG134" t="b">
         <v>0</v>
@@ -11213,13 +11381,16 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
       </c>
       <c r="AB135" t="n">
         <v>0.58</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>3.11</v>
       </c>
       <c r="AG135" t="b">
         <v>0</v>
@@ -11334,13 +11505,16 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
       </c>
       <c r="AB136" t="n">
         <v>2.49</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1.96</v>
       </c>
       <c r="AG136" t="b">
         <v>1</v>
@@ -11452,13 +11626,16 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
       </c>
       <c r="AB137" t="n">
         <v>11.97</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>15.06</v>
       </c>
       <c r="AG137" t="b">
         <v>1</v>
@@ -11573,13 +11750,16 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
       </c>
       <c r="AB138" t="n">
         <v>4.72</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>19.55</v>
       </c>
       <c r="AG138" t="b">
         <v>1</v>
@@ -11694,13 +11874,16 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
       </c>
       <c r="AB139" t="n">
         <v>9.210000000000001</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>15.99</v>
       </c>
       <c r="AG139" t="b">
         <v>1</v>
@@ -11815,13 +11998,16 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="AB140" t="n">
         <v>43.29</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>22.87</v>
       </c>
       <c r="AG140" t="b">
         <v>1</v>
@@ -11936,13 +12122,16 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
       </c>
       <c r="AB141" t="n">
         <v>-15.2</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>-16.68</v>
       </c>
       <c r="AG141" t="b">
         <v>0</v>
@@ -12057,13 +12246,16 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
       </c>
       <c r="AB142" t="n">
         <v>1.04</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>-7.51</v>
       </c>
       <c r="AG142" t="b">
         <v>0</v>
@@ -12178,13 +12370,16 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
       </c>
       <c r="AB143" t="n">
         <v>8.31</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>7.68</v>
       </c>
       <c r="AG143" t="b">
         <v>0</v>
@@ -12299,13 +12494,16 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
       </c>
       <c r="AB144" t="n">
         <v>-6.43</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>0.36</v>
       </c>
       <c r="AG144" t="b">
         <v>0</v>
@@ -12420,13 +12618,16 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA145" t="n">
         <v>-66.26000000000001</v>
       </c>
       <c r="AB145" t="n">
         <v>-59.14</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>-63.44</v>
       </c>
       <c r="AG145" t="b">
         <v>0</v>
@@ -12541,7 +12742,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
@@ -12662,7 +12863,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
@@ -12783,7 +12984,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
@@ -12904,7 +13105,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
@@ -13025,7 +13226,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
@@ -13146,7 +13347,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
@@ -13267,7 +13468,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
@@ -13388,7 +13589,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
@@ -13509,7 +13710,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
@@ -13630,7 +13831,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
@@ -13751,7 +13952,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
@@ -13872,7 +14073,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
@@ -13993,7 +14194,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
@@ -14114,7 +14315,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
@@ -14235,7 +14436,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
@@ -14356,7 +14557,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
@@ -14477,7 +14678,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
@@ -14598,7 +14799,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
@@ -14719,7 +14920,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
@@ -14840,7 +15041,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
@@ -14961,7 +15162,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
@@ -15082,7 +15283,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
@@ -15314,7 +15515,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
@@ -15435,7 +15636,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
@@ -15556,7 +15757,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA171" t="n">
         <v>-63.88</v>
@@ -15677,7 +15878,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
@@ -15798,7 +15999,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
@@ -15919,7 +16120,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
@@ -16040,7 +16241,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
@@ -16161,7 +16362,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
@@ -16282,7 +16483,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
@@ -16403,7 +16604,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
@@ -16635,7 +16836,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
@@ -16756,7 +16957,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
@@ -16877,7 +17078,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
@@ -16889,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="AH182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
@@ -16998,7 +17199,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
@@ -17119,7 +17320,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
@@ -17240,7 +17441,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
@@ -17361,7 +17562,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA186" t="n">
         <v>-62.24</v>
@@ -17482,10 +17683,13 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>1.53</v>
       </c>
       <c r="AG187" t="b">
         <v>0</v>
@@ -17600,10 +17804,13 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>-1.69</v>
       </c>
       <c r="AG188" t="b">
         <v>0</v>
@@ -17718,10 +17925,13 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>-4.29</v>
       </c>
       <c r="AG189" t="b">
         <v>0</v>
@@ -17836,10 +18046,13 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>4.12</v>
       </c>
       <c r="AG190" t="b">
         <v>0</v>
@@ -17954,10 +18167,13 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>-6.91</v>
       </c>
       <c r="AG191" t="b">
         <v>0</v>
@@ -18072,10 +18288,13 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>5.3</v>
       </c>
       <c r="AG192" t="b">
         <v>0</v>
@@ -18190,10 +18409,13 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>10.19</v>
       </c>
       <c r="AG193" t="b">
         <v>1</v>
@@ -18308,10 +18530,13 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>15.21</v>
       </c>
       <c r="AG194" t="b">
         <v>1</v>
@@ -18426,10 +18651,13 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>10.56</v>
       </c>
       <c r="AG195" t="b">
         <v>0</v>
@@ -18544,10 +18772,13 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>13.64</v>
       </c>
       <c r="AG196" t="b">
         <v>1</v>
@@ -18662,10 +18893,13 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>-3.78</v>
       </c>
       <c r="AG197" t="b">
         <v>0</v>
@@ -19002,10 +19236,13 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>7</v>
       </c>
       <c r="AG200" t="b">
         <v>0</v>
@@ -19120,10 +19357,13 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>-5.7</v>
       </c>
       <c r="AG201" t="b">
         <v>0</v>
@@ -19238,10 +19478,13 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>-63.66</v>
       </c>
       <c r="AG202" t="b">
         <v>0</v>
@@ -19356,7 +19599,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
@@ -19474,7 +19717,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
@@ -19592,7 +19835,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
@@ -19710,7 +19953,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
@@ -19828,7 +20071,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
@@ -19946,7 +20189,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
@@ -20064,7 +20307,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
@@ -20182,7 +20425,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -20300,7 +20543,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
@@ -20418,7 +20661,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
@@ -20647,7 +20890,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
@@ -20765,7 +21008,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
@@ -20883,7 +21126,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
@@ -21001,7 +21244,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
@@ -21119,7 +21362,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
@@ -21237,7 +21480,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
@@ -21355,7 +21598,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
@@ -21473,7 +21716,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
@@ -21591,7 +21834,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
@@ -21709,7 +21952,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
@@ -21827,7 +22070,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
@@ -21945,7 +22188,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
@@ -22063,7 +22306,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
@@ -22181,7 +22424,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
@@ -22299,7 +22542,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
@@ -22417,7 +22660,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
@@ -22535,7 +22778,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
@@ -22653,7 +22896,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
@@ -22882,7 +23125,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
@@ -23222,7 +23465,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
@@ -23340,7 +23583,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -23458,7 +23701,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
@@ -23576,7 +23819,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
@@ -23694,7 +23937,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
@@ -23812,7 +24055,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
@@ -23930,7 +24173,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
@@ -24048,7 +24291,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
@@ -24166,7 +24409,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
@@ -24284,7 +24527,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
@@ -24402,7 +24645,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
@@ -24520,7 +24763,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
@@ -24529,7 +24772,7 @@
         <v>0</v>
       </c>
       <c r="AH247" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI247" t="inlineStr">
         <is>
@@ -24638,7 +24881,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
@@ -24756,7 +24999,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
@@ -24874,7 +25117,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
@@ -24992,7 +25235,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
@@ -25110,7 +25353,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
@@ -25119,7 +25362,7 @@
         <v>0</v>
       </c>
       <c r="AH252" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI252" t="inlineStr">
         <is>
@@ -25228,7 +25471,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
@@ -25346,7 +25589,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
@@ -25464,7 +25707,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
@@ -25804,7 +26047,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
@@ -26144,7 +26387,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
@@ -26262,7 +26505,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
@@ -26380,7 +26623,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
@@ -26498,7 +26741,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
@@ -26727,7 +26970,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
@@ -26845,7 +27088,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
@@ -26963,7 +27206,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
@@ -26972,7 +27215,7 @@
         <v>0</v>
       </c>
       <c r="AH268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI268" t="inlineStr">
         <is>
@@ -27081,7 +27324,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
@@ -27199,7 +27442,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
@@ -27317,7 +27560,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
@@ -27435,7 +27678,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
@@ -27553,7 +27796,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
@@ -27671,7 +27914,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
@@ -27680,7 +27923,7 @@
         <v>0</v>
       </c>
       <c r="AH274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI274" t="inlineStr">
         <is>
@@ -27789,7 +28032,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
@@ -27907,7 +28150,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
@@ -28025,7 +28268,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -28143,7 +28386,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
@@ -28261,7 +28504,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
@@ -28379,7 +28622,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
@@ -28497,7 +28740,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
@@ -28615,7 +28858,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
@@ -28733,7 +28976,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -28851,7 +29094,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
@@ -28969,7 +29212,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
@@ -29087,7 +29330,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
@@ -29205,7 +29448,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
@@ -29323,7 +29566,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
@@ -29441,7 +29684,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
@@ -29559,7 +29802,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
@@ -29677,7 +29920,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
@@ -29795,7 +30038,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
@@ -29913,7 +30156,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
@@ -30364,7 +30607,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -30482,7 +30725,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
@@ -30600,7 +30843,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
@@ -30829,7 +31072,10 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA301" t="n">
+        <v>-3.98</v>
       </c>
       <c r="AG301" t="b">
         <v>0</v>
@@ -30944,7 +31190,10 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA302" t="n">
+        <v>0.21</v>
       </c>
       <c r="AG302" t="b">
         <v>0</v>
@@ -31059,7 +31308,10 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>-4.22</v>
       </c>
       <c r="AG303" t="b">
         <v>0</v>
@@ -31174,7 +31426,10 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>-4.34</v>
       </c>
       <c r="AG304" t="b">
         <v>0</v>
@@ -31289,7 +31544,10 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA305" t="n">
+        <v>-3.16</v>
       </c>
       <c r="AG305" t="b">
         <v>0</v>
@@ -31404,7 +31662,10 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>3.4</v>
       </c>
       <c r="AG306" t="b">
         <v>0</v>
@@ -31519,13 +31780,16 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>-8.33</v>
       </c>
       <c r="AG307" t="b">
         <v>0</v>
       </c>
       <c r="AH307" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI307" t="inlineStr">
         <is>
@@ -31634,7 +31898,10 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>-2.2</v>
       </c>
       <c r="AG308" t="b">
         <v>0</v>
@@ -31749,7 +32016,10 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>-4.16</v>
       </c>
       <c r="AG309" t="b">
         <v>0</v>
@@ -31864,7 +32134,10 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA310" t="n">
+        <v>-12.24</v>
       </c>
       <c r="AG310" t="b">
         <v>0</v>
@@ -31979,7 +32252,10 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA311" t="n">
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AG311" t="b">
         <v>0</v>
@@ -32094,7 +32370,10 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA312" t="n">
+        <v>-4.09</v>
       </c>
       <c r="AG312" t="b">
         <v>0</v>
@@ -32209,13 +32488,16 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA313" t="n">
+        <v>-7.59</v>
       </c>
       <c r="AG313" t="b">
         <v>0</v>
       </c>
       <c r="AH313" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI313" t="inlineStr">
         <is>
@@ -32324,7 +32606,10 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA314" t="n">
+        <v>2.51</v>
       </c>
       <c r="AG314" t="b">
         <v>0</v>
@@ -32439,7 +32724,10 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA315" t="n">
+        <v>-2.18</v>
       </c>
       <c r="AG315" t="b">
         <v>0</v>
@@ -32554,7 +32842,10 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA316" t="n">
+        <v>2.76</v>
       </c>
       <c r="AG316" t="b">
         <v>0</v>
@@ -32669,7 +32960,10 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>2.25</v>
       </c>
       <c r="AG317" t="b">
         <v>0</v>
@@ -32784,7 +33078,10 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>6.72</v>
       </c>
       <c r="AG318" t="b">
         <v>0</v>
@@ -32899,7 +33196,10 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA319" t="n">
+        <v>6.2</v>
       </c>
       <c r="AG319" t="b">
         <v>0</v>
@@ -33014,7 +33314,10 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA320" t="n">
+        <v>7.18</v>
       </c>
       <c r="AG320" t="b">
         <v>0</v>
@@ -33129,7 +33432,10 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA321" t="n">
+        <v>-14.25</v>
       </c>
       <c r="AG321" t="b">
         <v>0</v>
@@ -33244,7 +33550,10 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA322" t="n">
+        <v>-3.67</v>
       </c>
       <c r="AG322" t="b">
         <v>0</v>
@@ -33359,7 +33668,10 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>-4.63</v>
       </c>
       <c r="AG323" t="b">
         <v>0</v>
@@ -33474,7 +33786,10 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>-3.78</v>
       </c>
       <c r="AG324" t="b">
         <v>0</v>
@@ -33811,7 +34126,10 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>-0.58</v>
       </c>
       <c r="AG327" t="b">
         <v>0</v>
@@ -33926,7 +34244,10 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>-1</v>
       </c>
       <c r="AG328" t="b">
         <v>0</v>
@@ -34041,7 +34362,10 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>-5.73</v>
       </c>
       <c r="AG329" t="b">
         <v>0</v>
@@ -34378,7 +34702,10 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>-16.33</v>
       </c>
       <c r="AG332" t="b">
         <v>0</v>
@@ -34493,7 +34820,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG333" t="b">
         <v>0</v>
@@ -34608,7 +34935,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG334" t="b">
         <v>0</v>
@@ -34723,7 +35050,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG335" t="b">
         <v>0</v>
@@ -34838,7 +35165,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG336" t="b">
         <v>0</v>
@@ -34953,13 +35280,13 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG337" t="b">
         <v>0</v>
       </c>
       <c r="AH337" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI337" t="inlineStr">
         <is>
@@ -35068,7 +35395,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG338" t="b">
         <v>0</v>
@@ -35183,7 +35510,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG339" t="b">
         <v>0</v>
@@ -35298,7 +35625,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG340" t="b">
         <v>0</v>
@@ -35413,7 +35740,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG341" t="b">
         <v>0</v>
@@ -35528,7 +35855,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG342" t="b">
         <v>0</v>
@@ -35643,7 +35970,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG343" t="b">
         <v>0</v>
@@ -35758,7 +36085,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG344" t="b">
         <v>0</v>
@@ -35873,7 +36200,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG345" t="b">
         <v>0</v>
@@ -35988,10 +36315,10 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG346" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH346" t="b">
         <v>0</v>
@@ -36103,7 +36430,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG347" t="b">
         <v>0</v>
@@ -36218,7 +36545,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG348" t="b">
         <v>0</v>
@@ -36333,7 +36660,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG349" t="b">
         <v>0</v>
@@ -36448,7 +36775,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG350" t="b">
         <v>0</v>
@@ -36563,7 +36890,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG351" t="b">
         <v>0</v>
@@ -36678,7 +37005,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG352" t="b">
         <v>0</v>
@@ -36793,7 +37120,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG353" t="b">
         <v>0</v>
@@ -37352,7 +37679,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG358" t="b">
         <v>0</v>
@@ -37467,7 +37794,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG359" t="b">
         <v>0</v>
@@ -37582,7 +37909,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG360" t="b">
         <v>0</v>
@@ -37697,7 +38024,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG361" t="b">
         <v>0</v>
@@ -37812,7 +38139,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG362" t="b">
         <v>0</v>
@@ -37927,7 +38254,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG363" t="b">
         <v>0</v>
@@ -38042,7 +38369,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG364" t="b">
         <v>0</v>
@@ -38157,7 +38484,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG365" t="b">
         <v>0</v>
@@ -38272,7 +38599,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG366" t="b">
         <v>0</v>
@@ -38387,7 +38714,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG367" t="b">
         <v>0</v>
@@ -38502,7 +38829,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG368" t="b">
         <v>0</v>
@@ -38617,7 +38944,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG369" t="b">
         <v>0</v>
@@ -38732,7 +39059,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG370" t="b">
         <v>0</v>
@@ -38847,7 +39174,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG371" t="b">
         <v>0</v>
@@ -38962,7 +39289,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG372" t="b">
         <v>0</v>
@@ -39077,7 +39404,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG373" t="b">
         <v>0</v>
@@ -39192,7 +39519,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG374" t="b">
         <v>0</v>
@@ -39307,7 +39634,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG375" t="b">
         <v>0</v>
@@ -39422,13 +39749,13 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG376" t="b">
         <v>0</v>
       </c>
       <c r="AH376" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI376" t="inlineStr">
         <is>
@@ -39537,7 +39864,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG377" t="b">
         <v>0</v>
@@ -39874,7 +40201,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG380" t="b">
         <v>0</v>
@@ -39989,7 +40316,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG381" t="b">
         <v>0</v>
@@ -40215,7 +40542,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG383" t="b">
         <v>0</v>
@@ -40330,7 +40657,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG384" t="b">
         <v>0</v>
@@ -40445,7 +40772,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG385" t="b">
         <v>0</v>
@@ -40560,7 +40887,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG386" t="b">
         <v>0</v>
@@ -40675,7 +41002,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG387" t="b">
         <v>0</v>
@@ -40790,7 +41117,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG388" t="b">
         <v>0</v>
@@ -40905,13 +41232,13 @@
         </is>
       </c>
       <c r="Z389" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG389" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH389" t="b">
         <v>1</v>
-      </c>
-      <c r="AG389" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH389" t="b">
-        <v>0</v>
       </c>
       <c r="AI389" t="inlineStr">
         <is>
@@ -41017,7 +41344,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG390" t="b">
         <v>0</v>
@@ -41132,7 +41459,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG391" t="b">
         <v>0</v>
@@ -41247,7 +41574,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG392" t="b">
         <v>0</v>
@@ -41362,7 +41689,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG393" t="b">
         <v>0</v>
@@ -41477,7 +41804,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG394" t="b">
         <v>0</v>
@@ -41592,13 +41919,13 @@
         </is>
       </c>
       <c r="Z395" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG395" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH395" t="b">
         <v>1</v>
-      </c>
-      <c r="AG395" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH395" t="b">
-        <v>0</v>
       </c>
       <c r="AI395" t="inlineStr">
         <is>
@@ -41707,7 +42034,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG396" t="b">
         <v>0</v>
@@ -41822,7 +42149,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG397" t="b">
         <v>0</v>
@@ -41937,7 +42264,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG398" t="b">
         <v>0</v>
@@ -42052,7 +42379,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG399" t="b">
         <v>0</v>
@@ -42167,7 +42494,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG400" t="b">
         <v>0</v>
@@ -42282,7 +42609,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG401" t="b">
         <v>0</v>
@@ -42397,7 +42724,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG402" t="b">
         <v>0</v>
@@ -42512,7 +42839,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG403" t="b">
         <v>0</v>
@@ -42627,7 +42954,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG404" t="b">
         <v>0</v>
@@ -42742,7 +43069,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG405" t="b">
         <v>0</v>
@@ -42857,7 +43184,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG406" t="b">
         <v>0</v>
@@ -42972,7 +43299,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG407" t="b">
         <v>0</v>
@@ -43087,13 +43414,13 @@
         </is>
       </c>
       <c r="Z408" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG408" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH408" t="b">
         <v>1</v>
-      </c>
-      <c r="AG408" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH408" t="b">
-        <v>0</v>
       </c>
       <c r="AI408" t="inlineStr">
         <is>
@@ -43202,7 +43529,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG409" t="b">
         <v>0</v>
@@ -43650,7 +43977,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG413" t="b">
         <v>0</v>
@@ -43765,7 +44092,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG414" t="b">
         <v>0</v>
@@ -43880,7 +44207,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG415" t="b">
         <v>0</v>
@@ -43995,7 +44322,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG416" t="b">
         <v>0</v>
@@ -44110,7 +44437,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG417" t="b">
         <v>0</v>
@@ -44225,7 +44552,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG418" t="b">
         <v>0</v>
@@ -44340,7 +44667,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG419" t="b">
         <v>0</v>
@@ -44455,7 +44782,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG420" t="b">
         <v>0</v>
@@ -44570,7 +44897,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG421" t="b">
         <v>0</v>
@@ -44685,7 +45012,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG422" t="b">
         <v>0</v>
@@ -44800,7 +45127,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG423" t="b">
         <v>0</v>
@@ -44915,7 +45242,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG424" t="b">
         <v>0</v>
@@ -45030,7 +45357,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG425" t="b">
         <v>0</v>
@@ -45145,7 +45472,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG426" t="b">
         <v>0</v>
@@ -45260,7 +45587,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG427" t="b">
         <v>0</v>
@@ -45375,7 +45702,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG428" t="b">
         <v>0</v>
@@ -45490,7 +45817,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG429" t="b">
         <v>0</v>
@@ -45605,7 +45932,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG430" t="b">
         <v>0</v>
@@ -45720,7 +46047,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG431" t="b">
         <v>0</v>
@@ -45835,7 +46162,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG432" t="b">
         <v>0</v>
@@ -45950,7 +46277,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG433" t="b">
         <v>0</v>
@@ -46065,7 +46392,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG434" t="b">
         <v>0</v>
@@ -46402,7 +46729,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG437" t="b">
         <v>0</v>
@@ -46527,8 +46854,2760 @@
         </is>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>75.36</v>
+      </c>
+      <c r="F439" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I439" t="b">
+        <v>0</v>
+      </c>
+      <c r="J439" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K439" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M439" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N439" t="n">
+        <v>10</v>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P439" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S439" t="n">
+        <v>3.044</v>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V439" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="W439" t="n">
+        <v>38.5207</v>
+      </c>
+      <c r="X439" t="n">
+        <v>34.1285</v>
+      </c>
+      <c r="Y439" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG439" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH439" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI439" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="F440" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I440" t="b">
+        <v>0</v>
+      </c>
+      <c r="J440" t="n">
+        <v>10</v>
+      </c>
+      <c r="K440" t="n">
+        <v>71.61</v>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M440" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N440" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P440" t="n">
+        <v>63.55</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S440" t="n">
+        <v>7</v>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V440" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="W440" t="n">
+        <v>78.12</v>
+      </c>
+      <c r="X440" t="n">
+        <v>60.543</v>
+      </c>
+      <c r="Y440" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG440" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH440" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI440" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>75.09</v>
+      </c>
+      <c r="F441" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I441" t="b">
+        <v>0</v>
+      </c>
+      <c r="J441" t="n">
+        <v>10</v>
+      </c>
+      <c r="K441" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M441" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N441" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P441" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S441" t="n">
+        <v>7</v>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V441" t="n">
+        <v>235</v>
+      </c>
+      <c r="W441" t="n">
+        <v>282</v>
+      </c>
+      <c r="X441" t="n">
+        <v>218.55</v>
+      </c>
+      <c r="Y441" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG441" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH441" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI441" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>台化</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="F442" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I442" t="b">
+        <v>0</v>
+      </c>
+      <c r="J442" t="n">
+        <v>10</v>
+      </c>
+      <c r="K442" t="n">
+        <v>77.66</v>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M442" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N442" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P442" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S442" t="n">
+        <v>7</v>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V442" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="W442" t="n">
+        <v>84.72</v>
+      </c>
+      <c r="X442" t="n">
+        <v>65.658</v>
+      </c>
+      <c r="Y442" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG442" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH442" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI442" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>73.29000000000001</v>
+      </c>
+      <c r="F443" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I443" t="b">
+        <v>0</v>
+      </c>
+      <c r="J443" t="n">
+        <v>10</v>
+      </c>
+      <c r="K443" t="n">
+        <v>150.7</v>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M443" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N443" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P443" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>68.45</v>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S443" t="n">
+        <v>7</v>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V443" t="n">
+        <v>137</v>
+      </c>
+      <c r="W443" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="X443" t="n">
+        <v>127.41</v>
+      </c>
+      <c r="Y443" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG443" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH443" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI443" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>73.09</v>
+      </c>
+      <c r="F444" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I444" t="b">
+        <v>0</v>
+      </c>
+      <c r="J444" t="n">
+        <v>10</v>
+      </c>
+      <c r="K444" t="n">
+        <v>254.1</v>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M444" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N444" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P444" t="n">
+        <v>232.75</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S444" t="n">
+        <v>7</v>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V444" t="n">
+        <v>231</v>
+      </c>
+      <c r="W444" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="X444" t="n">
+        <v>214.83</v>
+      </c>
+      <c r="Y444" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG444" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH444" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI444" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="F445" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I445" t="b">
+        <v>0</v>
+      </c>
+      <c r="J445" t="n">
+        <v>10</v>
+      </c>
+      <c r="K445" t="n">
+        <v>2491.5</v>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M445" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N445" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P445" t="n">
+        <v>2107.5</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S445" t="n">
+        <v>7</v>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V445" t="n">
+        <v>2265</v>
+      </c>
+      <c r="W445" t="n">
+        <v>2718</v>
+      </c>
+      <c r="X445" t="n">
+        <v>2106.45</v>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG445" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH445" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI445" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="F446" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I446" t="b">
+        <v>0</v>
+      </c>
+      <c r="J446" t="n">
+        <v>10</v>
+      </c>
+      <c r="K446" t="n">
+        <v>5181</v>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M446" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N446" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P446" t="n">
+        <v>4255</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S446" t="n">
+        <v>7</v>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V446" t="n">
+        <v>4710</v>
+      </c>
+      <c r="W446" t="n">
+        <v>5652</v>
+      </c>
+      <c r="X446" t="n">
+        <v>4380.3</v>
+      </c>
+      <c r="Y446" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG446" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH446" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI446" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="F447" t="n">
+        <v>71.09</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I447" t="b">
+        <v>0</v>
+      </c>
+      <c r="J447" t="n">
+        <v>10</v>
+      </c>
+      <c r="K447" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M447" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N447" t="n">
+        <v>8</v>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P447" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>47.28</v>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S447" t="n">
+        <v>3.6094</v>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V447" t="n">
+        <v>112</v>
+      </c>
+      <c r="W447" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="X447" t="n">
+        <v>107.9575</v>
+      </c>
+      <c r="Y447" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG447" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH447" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI447" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>臺企銀</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>76.31</v>
+      </c>
+      <c r="F448" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I448" t="b">
+        <v>0</v>
+      </c>
+      <c r="J448" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="K448" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M448" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N448" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P448" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>67.56</v>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S448" t="n">
+        <v>7</v>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V448" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="W448" t="n">
+        <v>19.8182</v>
+      </c>
+      <c r="X448" t="n">
+        <v>16.461</v>
+      </c>
+      <c r="Y448" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z448" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG448" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH448" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI448" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>76.08</v>
+      </c>
+      <c r="F449" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I449" t="b">
+        <v>0</v>
+      </c>
+      <c r="J449" t="n">
+        <v>10</v>
+      </c>
+      <c r="K449" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M449" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N449" t="n">
+        <v>5</v>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P449" t="n">
+        <v>143.25</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S449" t="n">
+        <v>7</v>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V449" t="n">
+        <v>149</v>
+      </c>
+      <c r="W449" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="X449" t="n">
+        <v>138.57</v>
+      </c>
+      <c r="Y449" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z449" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG449" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH449" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI449" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="F450" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I450" t="b">
+        <v>0</v>
+      </c>
+      <c r="J450" t="n">
+        <v>10</v>
+      </c>
+      <c r="K450" t="n">
+        <v>124.85</v>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M450" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N450" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P450" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>59</v>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S450" t="n">
+        <v>7</v>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V450" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="W450" t="n">
+        <v>136.2</v>
+      </c>
+      <c r="X450" t="n">
+        <v>105.555</v>
+      </c>
+      <c r="Y450" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z450" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG450" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH450" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI450" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="F451" t="n">
+        <v>50.21</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I451" t="b">
+        <v>0</v>
+      </c>
+      <c r="J451" t="n">
+        <v>10</v>
+      </c>
+      <c r="K451" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M451" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N451" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P451" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S451" t="n">
+        <v>7</v>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V451" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="W451" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="X451" t="n">
+        <v>34.689</v>
+      </c>
+      <c r="Y451" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z451" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG451" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH451" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI451" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>87.33</v>
+      </c>
+      <c r="F452" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I452" t="b">
+        <v>0</v>
+      </c>
+      <c r="J452" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K452" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M452" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N452" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P452" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>77.79000000000001</v>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S452" t="n">
+        <v>7</v>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V452" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="W452" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="X452" t="n">
+        <v>42.3615</v>
+      </c>
+      <c r="Y452" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z452" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG452" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH452" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI452" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F453" t="n">
+        <v>51.79</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I453" t="b">
+        <v>0</v>
+      </c>
+      <c r="J453" t="n">
+        <v>10</v>
+      </c>
+      <c r="K453" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M453" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N453" t="n">
+        <v>3</v>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P453" t="n">
+        <v>39.62</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>78.63</v>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S453" t="n">
+        <v>7</v>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V453" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="W453" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="X453" t="n">
+        <v>39.804</v>
+      </c>
+      <c r="Y453" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z453" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG453" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH453" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI453" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="F454" t="n">
+        <v>59.17</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I454" t="b">
+        <v>0</v>
+      </c>
+      <c r="J454" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K454" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M454" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N454" t="n">
+        <v>5</v>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P454" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>74.47</v>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S454" t="n">
+        <v>7</v>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V454" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="W454" t="n">
+        <v>50.5234</v>
+      </c>
+      <c r="X454" t="n">
+        <v>40.4085</v>
+      </c>
+      <c r="Y454" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z454" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG454" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH454" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI454" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>81.31999999999999</v>
+      </c>
+      <c r="F455" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I455" t="b">
+        <v>0</v>
+      </c>
+      <c r="J455" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K455" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M455" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N455" t="n">
+        <v>5</v>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P455" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S455" t="n">
+        <v>7</v>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V455" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="W455" t="n">
+        <v>45.3307</v>
+      </c>
+      <c r="X455" t="n">
+        <v>35.2005</v>
+      </c>
+      <c r="Y455" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z455" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG455" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH455" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI455" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>晶豪科</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>74.02</v>
+      </c>
+      <c r="F456" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I456" t="b">
+        <v>0</v>
+      </c>
+      <c r="J456" t="n">
+        <v>10</v>
+      </c>
+      <c r="K456" t="n">
+        <v>328.35</v>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M456" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N456" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P456" t="n">
+        <v>281</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S456" t="n">
+        <v>7</v>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V456" t="n">
+        <v>298.5</v>
+      </c>
+      <c r="W456" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="X456" t="n">
+        <v>277.605</v>
+      </c>
+      <c r="Y456" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z456" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG456" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH456" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI456" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>77.34</v>
+      </c>
+      <c r="F457" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I457" t="b">
+        <v>0</v>
+      </c>
+      <c r="J457" t="n">
+        <v>10</v>
+      </c>
+      <c r="K457" t="n">
+        <v>3613.5</v>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M457" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N457" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P457" t="n">
+        <v>3167.5</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>62.96</v>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S457" t="n">
+        <v>7</v>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V457" t="n">
+        <v>3285</v>
+      </c>
+      <c r="W457" t="n">
+        <v>3942</v>
+      </c>
+      <c r="X457" t="n">
+        <v>3055.05</v>
+      </c>
+      <c r="Y457" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z457" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG457" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH457" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI457" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>75.65000000000001</v>
+      </c>
+      <c r="F458" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I458" t="b">
+        <v>0</v>
+      </c>
+      <c r="J458" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K458" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M458" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="N458" t="n">
+        <v>10</v>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P458" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>54</v>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S458" t="n">
+        <v>4.2945</v>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V458" t="n">
+        <v>118</v>
+      </c>
+      <c r="W458" t="n">
+        <v>128.4808</v>
+      </c>
+      <c r="X458" t="n">
+        <v>112.9325</v>
+      </c>
+      <c r="Y458" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z458" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG458" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH458" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI458" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>70.73999999999999</v>
+      </c>
+      <c r="F459" t="n">
+        <v>53.79</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I459" t="b">
+        <v>0</v>
+      </c>
+      <c r="J459" t="n">
+        <v>10</v>
+      </c>
+      <c r="K459" t="n">
+        <v>485.65</v>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M459" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N459" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P459" t="n">
+        <v>420.75</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S459" t="n">
+        <v>7</v>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V459" t="n">
+        <v>441.5</v>
+      </c>
+      <c r="W459" t="n">
+        <v>529.8</v>
+      </c>
+      <c r="X459" t="n">
+        <v>410.595</v>
+      </c>
+      <c r="Y459" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI459" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ459" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="F460" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I460" t="b">
+        <v>0</v>
+      </c>
+      <c r="J460" t="n">
+        <v>10</v>
+      </c>
+      <c r="K460" t="n">
+        <v>522.5</v>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M460" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N460" t="n">
+        <v>3</v>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P460" t="n">
+        <v>385.75</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>69.59</v>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S460" t="n">
+        <v>7</v>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V460" t="n">
+        <v>475</v>
+      </c>
+      <c r="W460" t="n">
+        <v>570</v>
+      </c>
+      <c r="X460" t="n">
+        <v>441.75</v>
+      </c>
+      <c r="Y460" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI460" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ460" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>78.84</v>
+      </c>
+      <c r="F461" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I461" t="b">
+        <v>0</v>
+      </c>
+      <c r="J461" t="n">
+        <v>10</v>
+      </c>
+      <c r="K461" t="n">
+        <v>6556</v>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M461" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N461" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P461" t="n">
+        <v>5847.5</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S461" t="n">
+        <v>7</v>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V461" t="n">
+        <v>5960</v>
+      </c>
+      <c r="W461" t="n">
+        <v>7152</v>
+      </c>
+      <c r="X461" t="n">
+        <v>5542.8</v>
+      </c>
+      <c r="Y461" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z461" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG461" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH461" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI461" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>80.52</v>
+      </c>
+      <c r="F462" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I462" t="b">
+        <v>0</v>
+      </c>
+      <c r="J462" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="K462" t="n">
+        <v>28.51</v>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M462" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N462" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P462" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>68.27</v>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S462" t="n">
+        <v>7</v>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V462" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="W462" t="n">
+        <v>30.6378</v>
+      </c>
+      <c r="X462" t="n">
+        <v>24.9705</v>
+      </c>
+      <c r="Y462" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z462" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG462" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH462" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI462" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ438"/>
+  <autoFilter ref="A1:AJ462"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46621,25 +49700,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5</v>
+        <v>0.5294</v>
       </c>
       <c r="D4" t="n">
-        <v>3.24</v>
+        <v>4.06</v>
       </c>
       <c r="E4" t="n">
-        <v>11.84</v>
+        <v>13.64</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.65</v>
+        <v>-7.62</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2941</v>
+        <v>0.3137</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5294</v>
+        <v>0.4314</v>
       </c>
     </row>
   </sheetData>
@@ -46755,25 +49834,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5</v>
+        <v>0.5294</v>
       </c>
       <c r="D6" t="n">
-        <v>3.24</v>
+        <v>4.06</v>
       </c>
       <c r="E6" t="n">
-        <v>11.84</v>
+        <v>13.64</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.65</v>
+        <v>-7.62</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2941</v>
+        <v>0.3137</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5294</v>
+        <v>0.4314</v>
       </c>
     </row>
   </sheetData>
@@ -46814,7 +49893,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-07 14:24:50</t>
+          <t>2026-09-08 14:23:11</t>
         </is>
       </c>
     </row>
@@ -46861,7 +49940,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>437</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7">
@@ -46871,7 +49950,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
@@ -46881,7 +49960,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$462</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$484</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ462"/>
+  <dimension ref="A1:AJ484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5259,11 +5259,11 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.28</v>
@@ -5274,6 +5274,15 @@
       <c r="AC57" t="n">
         <v>2.92</v>
       </c>
+      <c r="AD57" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>-3.19</v>
+      </c>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -5282,7 +5291,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -5334,11 +5343,11 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA58" t="n">
         <v>-8.779999999999999</v>
@@ -5349,6 +5358,15 @@
       <c r="AC58" t="n">
         <v>-12.54</v>
       </c>
+      <c r="AD58" t="n">
+        <v>-16.61</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>-19.44</v>
+      </c>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -5357,7 +5375,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5427,11 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA59" t="n">
         <v>-4.05</v>
@@ -5424,6 +5442,15 @@
       <c r="AC59" t="n">
         <v>-3.54</v>
       </c>
+      <c r="AD59" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>-5.06</v>
+      </c>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -5432,7 +5459,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -5484,11 +5511,11 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA60" t="n">
         <v>-9.26</v>
@@ -5499,6 +5526,15 @@
       <c r="AC60" t="n">
         <v>-7.04</v>
       </c>
+      <c r="AD60" t="n">
+        <v>-6.67</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>-11.85</v>
+      </c>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -5507,7 +5543,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -5559,11 +5595,11 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA61" t="n">
         <v>8.57</v>
@@ -5574,6 +5610,15 @@
       <c r="AC61" t="n">
         <v>18.54</v>
       </c>
+      <c r="AD61" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
       <c r="AG61" t="b">
         <v>1</v>
       </c>
@@ -5582,7 +5627,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -5634,11 +5679,11 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA62" t="n">
         <v>-3.42</v>
@@ -5649,6 +5694,15 @@
       <c r="AC62" t="n">
         <v>-10.02</v>
       </c>
+      <c r="AD62" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>-14.58</v>
+      </c>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -5657,7 +5711,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -5709,11 +5763,11 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA63" t="n">
         <v>2.62</v>
@@ -5724,6 +5778,15 @@
       <c r="AC63" t="n">
         <v>-4.97</v>
       </c>
+      <c r="AD63" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>-8.289999999999999</v>
+      </c>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -5732,7 +5795,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -5784,11 +5847,11 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA64" t="n">
         <v>1.17</v>
@@ -5799,6 +5862,15 @@
       <c r="AC64" t="n">
         <v>0.87</v>
       </c>
+      <c r="AD64" t="n">
+        <v>-4.81</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>-6.27</v>
+      </c>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -5807,7 +5879,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -5859,11 +5931,11 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA65" t="n">
         <v>12.12</v>
@@ -5874,6 +5946,15 @@
       <c r="AC65" t="n">
         <v>9.32</v>
       </c>
+      <c r="AD65" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>-1.63</v>
+      </c>
       <c r="AG65" t="b">
         <v>1</v>
       </c>
@@ -5882,7 +5963,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -5934,11 +6015,11 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA66" t="n">
         <v>-1.13</v>
@@ -5949,6 +6030,15 @@
       <c r="AC66" t="n">
         <v>5.77</v>
       </c>
+      <c r="AD66" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>-2.76</v>
+      </c>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -5957,7 +6047,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -6009,11 +6099,11 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA67" t="n">
         <v>21.05</v>
@@ -6024,6 +6114,15 @@
       <c r="AC67" t="n">
         <v>70.34</v>
       </c>
+      <c r="AD67" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>74.37</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>-0.87</v>
+      </c>
       <c r="AG67" t="b">
         <v>1</v>
       </c>
@@ -6032,7 +6131,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -6084,11 +6183,11 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA68" t="n">
         <v>6.36</v>
@@ -6099,6 +6198,15 @@
       <c r="AC68" t="n">
         <v>13.75</v>
       </c>
+      <c r="AD68" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>-5.84</v>
+      </c>
       <c r="AG68" t="b">
         <v>1</v>
       </c>
@@ -6107,7 +6215,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -6159,11 +6267,11 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA69" t="n">
         <v>-5.94</v>
@@ -6174,6 +6282,15 @@
       <c r="AC69" t="n">
         <v>-4.13</v>
       </c>
+      <c r="AD69" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>-10.85</v>
+      </c>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -6182,7 +6299,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -6296,11 +6413,11 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA71" t="n">
         <v>3.22</v>
@@ -6311,6 +6428,15 @@
       <c r="AC71" t="n">
         <v>14.91</v>
       </c>
+      <c r="AD71" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
       <c r="AG71" t="b">
         <v>1</v>
       </c>
@@ -6319,7 +6445,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -6371,11 +6497,11 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA72" t="n">
         <v>-2.78</v>
@@ -6386,6 +6512,15 @@
       <c r="AC72" t="n">
         <v>-9.380000000000001</v>
       </c>
+      <c r="AD72" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>-11.11</v>
+      </c>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -6394,7 +6529,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -6446,11 +6581,11 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA73" t="n">
         <v>-64.53</v>
@@ -6461,6 +6596,15 @@
       <c r="AC73" t="n">
         <v>-56.68</v>
       </c>
+      <c r="AD73" t="n">
+        <v>-61.41</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>-52.28</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>-66.5</v>
+      </c>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -6469,7 +6613,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -6521,11 +6665,11 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA74" t="n">
         <v>-5.04</v>
@@ -6536,6 +6680,15 @@
       <c r="AC74" t="n">
         <v>-13.18</v>
       </c>
+      <c r="AD74" t="n">
+        <v>-15.11</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>-18.44</v>
+      </c>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -6544,7 +6697,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -6596,11 +6749,11 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA75" t="n">
         <v>0.97</v>
@@ -6611,6 +6764,15 @@
       <c r="AC75" t="n">
         <v>0.28</v>
       </c>
+      <c r="AD75" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>-3.19</v>
+      </c>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -6619,7 +6781,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -6671,11 +6833,11 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA76" t="n">
         <v>-3.4</v>
@@ -6686,6 +6848,15 @@
       <c r="AC76" t="n">
         <v>-6.46</v>
       </c>
+      <c r="AD76" t="n">
+        <v>-11.22</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>-12.59</v>
+      </c>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -6694,7 +6865,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -6746,11 +6917,11 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.93</v>
@@ -6761,6 +6932,15 @@
       <c r="AC77" t="n">
         <v>10.95</v>
       </c>
+      <c r="AD77" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>-6.86</v>
+      </c>
       <c r="AG77" t="b">
         <v>1</v>
       </c>
@@ -6769,7 +6949,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -6821,11 +7001,11 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA78" t="n">
         <v>-12.58</v>
@@ -6836,6 +7016,15 @@
       <c r="AC78" t="n">
         <v>-10.93</v>
       </c>
+      <c r="AD78" t="n">
+        <v>-10.67</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>-14.74</v>
+      </c>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -6844,7 +7033,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -6896,11 +7085,11 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA79" t="n">
         <v>-3.58</v>
@@ -6911,6 +7100,15 @@
       <c r="AC79" t="n">
         <v>-3.44</v>
       </c>
+      <c r="AD79" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>-7.88</v>
+      </c>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -6919,7 +7117,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -6971,11 +7169,11 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA80" t="n">
         <v>0.58</v>
@@ -6986,6 +7184,15 @@
       <c r="AC80" t="n">
         <v>-7.1</v>
       </c>
+      <c r="AD80" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>-8.56</v>
+      </c>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -6994,7 +7201,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -7046,11 +7253,11 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA81" t="n">
         <v>14.15</v>
@@ -7061,6 +7268,15 @@
       <c r="AC81" t="n">
         <v>10.9</v>
       </c>
+      <c r="AD81" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>-2.09</v>
+      </c>
       <c r="AG81" t="b">
         <v>1</v>
       </c>
@@ -7069,7 +7285,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -7121,11 +7337,11 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA82" t="n">
         <v>29.71</v>
@@ -7136,6 +7352,15 @@
       <c r="AC82" t="n">
         <v>32</v>
       </c>
+      <c r="AD82" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>-0.57</v>
+      </c>
       <c r="AG82" t="b">
         <v>1</v>
       </c>
@@ -7144,7 +7369,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -7196,11 +7421,11 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA83" t="n">
         <v>-1.5</v>
@@ -7211,6 +7436,15 @@
       <c r="AC83" t="n">
         <v>6.63</v>
       </c>
+      <c r="AD83" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>-3</v>
+      </c>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -7219,7 +7453,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -7271,11 +7505,11 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA84" t="n">
         <v>18.35</v>
@@ -7286,6 +7520,15 @@
       <c r="AC84" t="n">
         <v>53.43</v>
       </c>
+      <c r="AD84" t="n">
+        <v>44.21</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="AG84" t="b">
         <v>1</v>
       </c>
@@ -7294,7 +7537,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -7346,11 +7589,11 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA85" t="n">
         <v>-8.630000000000001</v>
@@ -7361,6 +7604,15 @@
       <c r="AC85" t="n">
         <v>-4.31</v>
       </c>
+      <c r="AD85" t="n">
+        <v>-6.09</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>-12.44</v>
+      </c>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -7369,7 +7621,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -7421,11 +7673,11 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA86" t="n">
         <v>1.62</v>
@@ -7436,6 +7688,15 @@
       <c r="AC86" t="n">
         <v>4.69</v>
       </c>
+      <c r="AD86" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>-6.05</v>
+      </c>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -7444,7 +7705,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -7496,11 +7757,11 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA87" t="n">
         <v>-10.5</v>
@@ -7511,6 +7772,15 @@
       <c r="AC87" t="n">
         <v>-3.34</v>
       </c>
+      <c r="AD87" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>-14.44</v>
+      </c>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -7519,7 +7789,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -7571,11 +7841,11 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA88" t="n">
         <v>-4.84</v>
@@ -7586,6 +7856,15 @@
       <c r="AC88" t="n">
         <v>-6.57</v>
       </c>
+      <c r="AD88" t="n">
+        <v>-8.65</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>-11.42</v>
+      </c>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -7594,7 +7873,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -7646,11 +7925,11 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA89" t="n">
         <v>-65.06999999999999</v>
@@ -7661,6 +7940,15 @@
       <c r="AC89" t="n">
         <v>-59.23</v>
       </c>
+      <c r="AD89" t="n">
+        <v>-61.37</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>-52.64</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>-66.17</v>
+      </c>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -7669,7 +7957,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -7783,11 +8071,11 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA91" t="n">
         <v>0.95</v>
@@ -7798,6 +8086,15 @@
       <c r="AC91" t="n">
         <v>-4.29</v>
       </c>
+      <c r="AD91" t="n">
+        <v>-7.33</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>-10.76</v>
+      </c>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -7806,7 +8103,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -7862,7 +8159,7 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -7937,7 +8234,7 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -8012,7 +8309,7 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -8087,7 +8384,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -8162,7 +8459,7 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -8237,7 +8534,7 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -8312,7 +8609,7 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -8387,7 +8684,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -8462,7 +8759,7 @@
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -8537,7 +8834,7 @@
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -8612,7 +8909,7 @@
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -8687,7 +8984,7 @@
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -8762,7 +9059,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -8837,7 +9134,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -8912,7 +9209,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -8987,7 +9284,7 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -9062,7 +9359,7 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -9137,7 +9434,7 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -9212,7 +9509,7 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -9287,7 +9584,7 @@
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -9362,7 +9659,7 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA112" t="n">
         <v>-67.41</v>
@@ -9437,7 +9734,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
@@ -9512,7 +9809,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
@@ -9587,7 +9884,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
@@ -9662,7 +9959,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
@@ -9737,7 +10034,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
@@ -9812,7 +10109,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
@@ -9887,7 +10184,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
@@ -9962,7 +10259,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
@@ -10037,7 +10334,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
@@ -10112,7 +10409,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
@@ -10187,7 +10484,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
@@ -10262,7 +10559,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
@@ -10337,7 +10634,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
@@ -10412,7 +10709,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
@@ -10487,7 +10784,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
@@ -10562,7 +10859,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
@@ -10637,7 +10934,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA129" t="n">
         <v>-68.09</v>
@@ -10761,7 +11058,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
@@ -10885,7 +11182,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
@@ -11009,7 +11306,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
@@ -11133,7 +11430,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
@@ -11257,7 +11554,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
@@ -11381,7 +11678,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
@@ -11505,7 +11802,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
@@ -11626,7 +11923,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
@@ -11750,7 +12047,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
@@ -11874,7 +12171,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
@@ -11998,7 +12295,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
@@ -12122,7 +12419,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
@@ -12246,7 +12543,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
@@ -12370,7 +12667,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
@@ -12494,7 +12791,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
@@ -12618,7 +12915,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA145" t="n">
         <v>-66.26000000000001</v>
@@ -12742,13 +13039,16 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
       </c>
       <c r="AB146" t="n">
         <v>3.55</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>4.73</v>
       </c>
       <c r="AG146" t="b">
         <v>0</v>
@@ -12863,13 +13163,16 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
       </c>
       <c r="AB147" t="n">
         <v>-1.16</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>-1.94</v>
       </c>
       <c r="AG147" t="b">
         <v>0</v>
@@ -12984,13 +13287,16 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
       </c>
       <c r="AB148" t="n">
         <v>3.2</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>2.37</v>
       </c>
       <c r="AG148" t="b">
         <v>0</v>
@@ -13105,13 +13411,16 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
       </c>
       <c r="AB149" t="n">
         <v>15.17</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>6.95</v>
       </c>
       <c r="AG149" t="b">
         <v>0</v>
@@ -13226,13 +13535,16 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
       </c>
       <c r="AB150" t="n">
         <v>-2.49</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>-2.7</v>
       </c>
       <c r="AG150" t="b">
         <v>0</v>
@@ -13347,13 +13659,16 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
       </c>
       <c r="AB151" t="n">
         <v>40.72</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>23.78</v>
       </c>
       <c r="AG151" t="b">
         <v>1</v>
@@ -13468,13 +13783,16 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
       </c>
       <c r="AB152" t="n">
         <v>-13.89</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>-12.12</v>
       </c>
       <c r="AG152" t="b">
         <v>0</v>
@@ -13589,13 +13907,16 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
       </c>
       <c r="AB153" t="n">
         <v>-1.41</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>-0</v>
       </c>
       <c r="AG153" t="b">
         <v>0</v>
@@ -13710,13 +14031,16 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
       </c>
       <c r="AB154" t="n">
         <v>1.44</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>2.16</v>
       </c>
       <c r="AG154" t="b">
         <v>0</v>
@@ -13831,12 +14155,15 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
       </c>
       <c r="AB155" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="AC155" t="n">
         <v>-3.32</v>
       </c>
       <c r="AG155" t="b">
@@ -13952,13 +14279,16 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
       </c>
       <c r="AB156" t="n">
         <v>-0.34</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>-1.88</v>
       </c>
       <c r="AG156" t="b">
         <v>0</v>
@@ -14073,13 +14403,16 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
       </c>
       <c r="AB157" t="n">
         <v>-0.6899999999999999</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>-1.24</v>
       </c>
       <c r="AG157" t="b">
         <v>0</v>
@@ -14194,13 +14527,16 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
       </c>
       <c r="AB158" t="n">
         <v>-6</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>-0.95</v>
       </c>
       <c r="AG158" t="b">
         <v>0</v>
@@ -14315,13 +14651,16 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
       </c>
       <c r="AB159" t="n">
         <v>10.33</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>7.38</v>
       </c>
       <c r="AG159" t="b">
         <v>1</v>
@@ -14436,13 +14775,16 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
       </c>
       <c r="AB160" t="n">
         <v>-11.61</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>-10.19</v>
       </c>
       <c r="AG160" t="b">
         <v>0</v>
@@ -14557,13 +14899,16 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
       </c>
       <c r="AB161" t="n">
         <v>-1.17</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>-3.37</v>
       </c>
       <c r="AG161" t="b">
         <v>0</v>
@@ -14678,13 +15023,16 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
       </c>
       <c r="AB162" t="n">
         <v>-7.64</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>-0.39</v>
       </c>
       <c r="AG162" t="b">
         <v>0</v>
@@ -14799,13 +15147,16 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
       </c>
       <c r="AB163" t="n">
         <v>-1.85</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>-5.13</v>
       </c>
       <c r="AG163" t="b">
         <v>0</v>
@@ -14920,13 +15271,16 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
       </c>
       <c r="AB164" t="n">
         <v>-3.18</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>-2.85</v>
       </c>
       <c r="AG164" t="b">
         <v>0</v>
@@ -15041,13 +15395,16 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
       </c>
       <c r="AB165" t="n">
         <v>6.94</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>2.31</v>
       </c>
       <c r="AG165" t="b">
         <v>1</v>
@@ -15162,13 +15519,16 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
       </c>
       <c r="AB166" t="n">
         <v>29.65</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>21.85</v>
       </c>
       <c r="AG166" t="b">
         <v>1</v>
@@ -15283,13 +15643,16 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
       </c>
       <c r="AB167" t="n">
         <v>-19.04</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>-12.81</v>
       </c>
       <c r="AG167" t="b">
         <v>0</v>
@@ -15515,13 +15878,16 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
       </c>
       <c r="AB169" t="n">
         <v>-8.93</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>-2.82</v>
       </c>
       <c r="AG169" t="b">
         <v>0</v>
@@ -15636,13 +16002,16 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
       </c>
       <c r="AB170" t="n">
         <v>3.02</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>10.57</v>
       </c>
       <c r="AG170" t="b">
         <v>0</v>
@@ -15757,13 +16126,16 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA171" t="n">
         <v>-63.88</v>
       </c>
       <c r="AB171" t="n">
         <v>-60.87</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>-62.92</v>
       </c>
       <c r="AG171" t="b">
         <v>0</v>
@@ -15878,7 +16250,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
@@ -15999,7 +16371,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
@@ -16120,7 +16492,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
@@ -16241,7 +16613,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
@@ -16362,7 +16734,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
@@ -16483,7 +16855,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
@@ -16492,7 +16864,7 @@
         <v>11.41</v>
       </c>
       <c r="AG177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH177" t="b">
         <v>0</v>
@@ -16604,7 +16976,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
@@ -16836,7 +17208,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
@@ -16957,7 +17329,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
@@ -17078,7 +17450,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
@@ -17199,7 +17571,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
@@ -17320,7 +17692,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
@@ -17441,7 +17813,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
@@ -17562,7 +17934,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA186" t="n">
         <v>-62.24</v>
@@ -17683,7 +18055,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
@@ -17804,7 +18176,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
@@ -17925,7 +18297,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
@@ -18046,7 +18418,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
@@ -18167,7 +18539,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
@@ -18288,7 +18660,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
@@ -18409,7 +18781,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
@@ -18530,7 +18902,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
@@ -18651,7 +19023,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
@@ -18772,7 +19144,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
@@ -18893,7 +19265,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
@@ -19236,7 +19608,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
@@ -19357,7 +19729,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
@@ -19478,7 +19850,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
@@ -19599,10 +19971,13 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>-2.66</v>
       </c>
       <c r="AG203" t="b">
         <v>0</v>
@@ -19717,16 +20092,19 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
       </c>
+      <c r="AB204" t="n">
+        <v>-4.72</v>
+      </c>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
       <c r="AH204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI204" t="inlineStr">
         <is>
@@ -19835,10 +20213,13 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>2.7</v>
       </c>
       <c r="AG205" t="b">
         <v>0</v>
@@ -19953,16 +20334,19 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
       </c>
+      <c r="AB206" t="n">
+        <v>-5.01</v>
+      </c>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AH206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI206" t="inlineStr">
         <is>
@@ -20071,10 +20455,13 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>0.82</v>
       </c>
       <c r="AG207" t="b">
         <v>0</v>
@@ -20189,10 +20576,13 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>-5.09</v>
       </c>
       <c r="AG208" t="b">
         <v>0</v>
@@ -20307,10 +20697,13 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>1.16</v>
       </c>
       <c r="AG209" t="b">
         <v>0</v>
@@ -20425,10 +20818,13 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>13.07</v>
       </c>
       <c r="AG210" t="b">
         <v>0</v>
@@ -20543,10 +20939,13 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>-14.4</v>
       </c>
       <c r="AG211" t="b">
         <v>0</v>
@@ -20661,10 +21060,13 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>-7.83</v>
       </c>
       <c r="AG212" t="b">
         <v>0</v>
@@ -20890,10 +21292,13 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>-1.39</v>
       </c>
       <c r="AG214" t="b">
         <v>0</v>
@@ -21008,10 +21413,13 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>-15.14</v>
       </c>
       <c r="AG215" t="b">
         <v>0</v>
@@ -21126,10 +21534,13 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>-10.83</v>
       </c>
       <c r="AG216" t="b">
         <v>0</v>
@@ -21244,10 +21655,13 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>-65.73</v>
       </c>
       <c r="AG217" t="b">
         <v>0</v>
@@ -21362,10 +21776,13 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>3.96</v>
       </c>
       <c r="AG218" t="b">
         <v>0</v>
@@ -21480,10 +21897,13 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>-3.81</v>
       </c>
       <c r="AG219" t="b">
         <v>0</v>
@@ -21598,16 +22018,19 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
       </c>
+      <c r="AB220" t="n">
+        <v>-6.75</v>
+      </c>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
       <c r="AH220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI220" t="inlineStr">
         <is>
@@ -21716,10 +22139,13 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>-2.83</v>
       </c>
       <c r="AG221" t="b">
         <v>0</v>
@@ -21834,10 +22260,13 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>-3.32</v>
       </c>
       <c r="AG222" t="b">
         <v>0</v>
@@ -21952,10 +22381,13 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>-2.77</v>
       </c>
       <c r="AG223" t="b">
         <v>0</v>
@@ -22070,10 +22502,13 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>2.17</v>
       </c>
       <c r="AG224" t="b">
         <v>0</v>
@@ -22188,10 +22623,13 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>1.46</v>
       </c>
       <c r="AG225" t="b">
         <v>1</v>
@@ -22306,10 +22744,13 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>-2.37</v>
       </c>
       <c r="AG226" t="b">
         <v>0</v>
@@ -22424,10 +22865,13 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>-4.81</v>
       </c>
       <c r="AG227" t="b">
         <v>0</v>
@@ -22542,10 +22986,13 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>4.95</v>
       </c>
       <c r="AG228" t="b">
         <v>0</v>
@@ -22660,10 +23107,13 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>13.87</v>
       </c>
       <c r="AG229" t="b">
         <v>0</v>
@@ -22778,10 +23228,13 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>3.59</v>
       </c>
       <c r="AG230" t="b">
         <v>0</v>
@@ -22896,10 +23349,13 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>-15.76</v>
       </c>
       <c r="AG231" t="b">
         <v>0</v>
@@ -23125,10 +23581,13 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>-9.52</v>
       </c>
       <c r="AG233" t="b">
         <v>0</v>
@@ -23465,10 +23924,13 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>5.15</v>
       </c>
       <c r="AG236" t="b">
         <v>0</v>
@@ -23583,10 +24045,13 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
+      </c>
+      <c r="AB237" t="n">
+        <v>4.06</v>
       </c>
       <c r="AG237" t="b">
         <v>0</v>
@@ -23701,10 +24166,13 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>-6.18</v>
       </c>
       <c r="AG238" t="b">
         <v>0</v>
@@ -23819,10 +24287,13 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>-15.38</v>
       </c>
       <c r="AG239" t="b">
         <v>0</v>
@@ -23937,16 +24408,19 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
       </c>
+      <c r="AB240" t="n">
+        <v>-7.74</v>
+      </c>
       <c r="AG240" t="b">
         <v>0</v>
       </c>
       <c r="AH240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI240" t="inlineStr">
         <is>
@@ -24055,10 +24529,13 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>-65.59</v>
       </c>
       <c r="AG241" t="b">
         <v>0</v>
@@ -24173,10 +24650,13 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
+      </c>
+      <c r="AB242" t="n">
+        <v>-7.33</v>
       </c>
       <c r="AG242" t="b">
         <v>0</v>
@@ -24291,7 +24771,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
@@ -24409,7 +24889,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
@@ -24527,7 +25007,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
@@ -24645,7 +25125,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
@@ -24763,7 +25243,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
@@ -24881,7 +25361,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
@@ -24999,7 +25479,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
@@ -25117,7 +25597,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
@@ -25235,7 +25715,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
@@ -25353,7 +25833,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
@@ -25471,7 +25951,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
@@ -25589,7 +26069,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
@@ -25707,7 +26187,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
@@ -26047,7 +26527,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
@@ -26387,7 +26867,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
@@ -26505,7 +26985,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
@@ -26623,7 +27103,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
@@ -26741,7 +27221,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
@@ -26970,7 +27450,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
@@ -27088,7 +27568,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
@@ -27206,7 +27686,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
@@ -27324,7 +27804,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
@@ -27442,7 +27922,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
@@ -27560,7 +28040,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
@@ -27678,7 +28158,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
@@ -27796,7 +28276,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
@@ -27914,7 +28394,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
@@ -28032,7 +28512,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
@@ -28150,7 +28630,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
@@ -28268,7 +28748,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -28386,7 +28866,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
@@ -28504,7 +28984,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
@@ -28622,7 +29102,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
@@ -28740,7 +29220,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
@@ -28858,7 +29338,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
@@ -28976,7 +29456,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -29094,7 +29574,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
@@ -29212,7 +29692,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
@@ -29330,7 +29810,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
@@ -29448,7 +29928,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
@@ -29566,7 +30046,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
@@ -29684,7 +30164,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
@@ -29802,7 +30282,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
@@ -29920,7 +30400,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
@@ -30038,7 +30518,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
@@ -30156,7 +30636,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
@@ -30607,7 +31087,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -30725,7 +31205,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
@@ -30843,7 +31323,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
@@ -31072,7 +31552,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
@@ -31190,7 +31670,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
@@ -31308,7 +31788,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
@@ -31426,7 +31906,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
@@ -31544,7 +32024,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
@@ -31662,7 +32142,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
@@ -31780,7 +32260,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
@@ -31898,7 +32378,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
@@ -32016,7 +32496,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
@@ -32134,7 +32614,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
@@ -32252,7 +32732,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
@@ -32370,7 +32850,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
@@ -32488,7 +32968,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
@@ -32606,7 +33086,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
@@ -32724,7 +33204,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
@@ -32842,7 +33322,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
@@ -32960,7 +33440,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
@@ -33078,7 +33558,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
@@ -33196,7 +33676,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
@@ -33314,7 +33794,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
@@ -33432,7 +33912,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
@@ -33550,7 +34030,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
@@ -33668,7 +34148,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
@@ -33786,7 +34266,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
@@ -34126,7 +34606,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
@@ -34244,7 +34724,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
@@ -34362,7 +34842,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
@@ -34371,7 +34851,7 @@
         <v>0</v>
       </c>
       <c r="AH329" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI329" t="inlineStr">
         <is>
@@ -34702,7 +35182,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
@@ -34820,7 +35300,10 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AG333" t="b">
         <v>0</v>
@@ -34935,7 +35418,10 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>-0.42</v>
       </c>
       <c r="AG334" t="b">
         <v>0</v>
@@ -35050,7 +35536,10 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>-1.37</v>
       </c>
       <c r="AG335" t="b">
         <v>0</v>
@@ -35165,7 +35654,10 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA336" t="n">
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AG336" t="b">
         <v>0</v>
@@ -35280,7 +35772,10 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA337" t="n">
+        <v>-7.14</v>
       </c>
       <c r="AG337" t="b">
         <v>0</v>
@@ -35395,7 +35890,10 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA338" t="n">
+        <v>-3.07</v>
       </c>
       <c r="AG338" t="b">
         <v>0</v>
@@ -35510,7 +36008,10 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA339" t="n">
+        <v>-3.32</v>
       </c>
       <c r="AG339" t="b">
         <v>0</v>
@@ -35625,7 +36126,10 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA340" t="n">
+        <v>1.48</v>
       </c>
       <c r="AG340" t="b">
         <v>0</v>
@@ -35740,7 +36244,10 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA341" t="n">
+        <v>0.97</v>
       </c>
       <c r="AG341" t="b">
         <v>0</v>
@@ -35855,7 +36362,10 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA342" t="n">
+        <v>3.57</v>
       </c>
       <c r="AG342" t="b">
         <v>0</v>
@@ -35970,7 +36480,10 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA343" t="n">
+        <v>2.44</v>
       </c>
       <c r="AG343" t="b">
         <v>0</v>
@@ -36085,7 +36598,10 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA344" t="n">
+        <v>1.38</v>
       </c>
       <c r="AG344" t="b">
         <v>0</v>
@@ -36200,7 +36716,10 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA345" t="n">
+        <v>3.52</v>
       </c>
       <c r="AG345" t="b">
         <v>0</v>
@@ -36315,7 +36834,10 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA346" t="n">
+        <v>9.26</v>
       </c>
       <c r="AG346" t="b">
         <v>1</v>
@@ -36430,7 +36952,10 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA347" t="n">
+        <v>2.91</v>
       </c>
       <c r="AG347" t="b">
         <v>0</v>
@@ -36545,7 +37070,10 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA348" t="n">
+        <v>2.49</v>
       </c>
       <c r="AG348" t="b">
         <v>0</v>
@@ -36660,7 +37188,10 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA349" t="n">
+        <v>4.28</v>
       </c>
       <c r="AG349" t="b">
         <v>0</v>
@@ -36775,7 +37306,10 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA350" t="n">
+        <v>8.880000000000001</v>
       </c>
       <c r="AG350" t="b">
         <v>0</v>
@@ -36890,7 +37424,10 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA351" t="n">
+        <v>-12.04</v>
       </c>
       <c r="AG351" t="b">
         <v>0</v>
@@ -37005,7 +37542,10 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA352" t="n">
+        <v>-4.34</v>
       </c>
       <c r="AG352" t="b">
         <v>0</v>
@@ -37120,7 +37660,10 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA353" t="n">
+        <v>1.39</v>
       </c>
       <c r="AG353" t="b">
         <v>0</v>
@@ -37679,13 +38222,16 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA358" t="n">
+        <v>-7.02</v>
       </c>
       <c r="AG358" t="b">
         <v>0</v>
       </c>
       <c r="AH358" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI358" t="inlineStr">
         <is>
@@ -37794,7 +38340,10 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AA359" t="n">
+        <v>-10.92</v>
       </c>
       <c r="AG359" t="b">
         <v>0</v>
@@ -37909,7 +38458,10 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA360" t="n">
+        <v>0.71</v>
       </c>
       <c r="AG360" t="b">
         <v>0</v>
@@ -38024,7 +38576,10 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA361" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AG361" t="b">
         <v>0</v>
@@ -38139,7 +38694,10 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA362" t="n">
+        <v>10.41</v>
       </c>
       <c r="AG362" t="b">
         <v>0</v>
@@ -38254,7 +38812,10 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA363" t="n">
+        <v>-2.68</v>
       </c>
       <c r="AG363" t="b">
         <v>0</v>
@@ -38369,7 +38930,10 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>1.85</v>
       </c>
       <c r="AG364" t="b">
         <v>0</v>
@@ -38484,7 +39048,10 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA365" t="n">
+        <v>0.3</v>
       </c>
       <c r="AG365" t="b">
         <v>0</v>
@@ -38599,7 +39166,10 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA366" t="n">
+        <v>8.76</v>
       </c>
       <c r="AG366" t="b">
         <v>0</v>
@@ -38714,13 +39284,16 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA367" t="n">
+        <v>-4.33</v>
       </c>
       <c r="AG367" t="b">
         <v>0</v>
       </c>
       <c r="AH367" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI367" t="inlineStr">
         <is>
@@ -38829,7 +39402,10 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA368" t="n">
+        <v>1.02</v>
       </c>
       <c r="AG368" t="b">
         <v>0</v>
@@ -38944,7 +39520,10 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA369" t="n">
+        <v>-1.78</v>
       </c>
       <c r="AG369" t="b">
         <v>0</v>
@@ -39059,7 +39638,10 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA370" t="n">
+        <v>3.62</v>
       </c>
       <c r="AG370" t="b">
         <v>0</v>
@@ -39174,7 +39756,10 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA371" t="n">
+        <v>4.05</v>
       </c>
       <c r="AG371" t="b">
         <v>0</v>
@@ -39289,7 +39874,10 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA372" t="n">
+        <v>1.75</v>
       </c>
       <c r="AG372" t="b">
         <v>0</v>
@@ -39404,7 +39992,10 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA373" t="n">
+        <v>1.69</v>
       </c>
       <c r="AG373" t="b">
         <v>0</v>
@@ -39519,7 +40110,10 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA374" t="n">
+        <v>0.7</v>
       </c>
       <c r="AG374" t="b">
         <v>0</v>
@@ -39634,7 +40228,10 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA375" t="n">
+        <v>3.12</v>
       </c>
       <c r="AG375" t="b">
         <v>0</v>
@@ -39749,7 +40346,10 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA376" t="n">
+        <v>-6.01</v>
       </c>
       <c r="AG376" t="b">
         <v>0</v>
@@ -39864,7 +40464,10 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA377" t="n">
+        <v>1.69</v>
       </c>
       <c r="AG377" t="b">
         <v>0</v>
@@ -40201,7 +40804,10 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA380" t="n">
+        <v>0.12</v>
       </c>
       <c r="AG380" t="b">
         <v>0</v>
@@ -40316,7 +40922,10 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA381" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG381" t="b">
         <v>0</v>
@@ -40542,13 +41151,16 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA383" t="n">
+        <v>-5.25</v>
       </c>
       <c r="AG383" t="b">
         <v>0</v>
       </c>
       <c r="AH383" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI383" t="inlineStr">
         <is>
@@ -40657,7 +41269,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG384" t="b">
         <v>0</v>
@@ -40772,7 +41384,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG385" t="b">
         <v>0</v>
@@ -40887,7 +41499,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG386" t="b">
         <v>0</v>
@@ -41002,7 +41614,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG387" t="b">
         <v>0</v>
@@ -41117,13 +41729,13 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG388" t="b">
         <v>0</v>
       </c>
       <c r="AH388" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI388" t="inlineStr">
         <is>
@@ -41232,7 +41844,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG389" t="b">
         <v>0</v>
@@ -41344,7 +41956,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG390" t="b">
         <v>0</v>
@@ -41459,7 +42071,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG391" t="b">
         <v>0</v>
@@ -41574,13 +42186,13 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG392" t="b">
         <v>0</v>
       </c>
       <c r="AH392" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI392" t="inlineStr">
         <is>
@@ -41689,7 +42301,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG393" t="b">
         <v>0</v>
@@ -41804,13 +42416,13 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG394" t="b">
         <v>0</v>
       </c>
       <c r="AH394" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI394" t="inlineStr">
         <is>
@@ -41919,7 +42531,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG395" t="b">
         <v>0</v>
@@ -42034,7 +42646,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG396" t="b">
         <v>0</v>
@@ -42149,7 +42761,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG397" t="b">
         <v>0</v>
@@ -42264,13 +42876,13 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG398" t="b">
         <v>0</v>
       </c>
       <c r="AH398" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI398" t="inlineStr">
         <is>
@@ -42379,7 +42991,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG399" t="b">
         <v>0</v>
@@ -42494,7 +43106,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG400" t="b">
         <v>0</v>
@@ -42609,7 +43221,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG401" t="b">
         <v>0</v>
@@ -42724,7 +43336,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG402" t="b">
         <v>0</v>
@@ -42839,7 +43451,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG403" t="b">
         <v>0</v>
@@ -42954,7 +43566,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG404" t="b">
         <v>0</v>
@@ -43069,7 +43681,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG405" t="b">
         <v>0</v>
@@ -43184,7 +43796,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG406" t="b">
         <v>0</v>
@@ -43299,7 +43911,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG407" t="b">
         <v>0</v>
@@ -43414,7 +44026,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG408" t="b">
         <v>0</v>
@@ -43529,7 +44141,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG409" t="b">
         <v>0</v>
@@ -43977,13 +44589,13 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG413" t="b">
         <v>0</v>
       </c>
       <c r="AH413" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI413" t="inlineStr">
         <is>
@@ -44092,7 +44704,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG414" t="b">
         <v>0</v>
@@ -44207,7 +44819,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG415" t="b">
         <v>0</v>
@@ -44322,7 +44934,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG416" t="b">
         <v>0</v>
@@ -44437,7 +45049,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG417" t="b">
         <v>0</v>
@@ -44552,7 +45164,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG418" t="b">
         <v>0</v>
@@ -44667,13 +45279,13 @@
         </is>
       </c>
       <c r="Z419" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG419" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH419" t="b">
         <v>1</v>
-      </c>
-      <c r="AG419" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH419" t="b">
-        <v>0</v>
       </c>
       <c r="AI419" t="inlineStr">
         <is>
@@ -44782,7 +45394,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG420" t="b">
         <v>0</v>
@@ -44897,7 +45509,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG421" t="b">
         <v>0</v>
@@ -45012,7 +45624,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG422" t="b">
         <v>0</v>
@@ -45127,7 +45739,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG423" t="b">
         <v>0</v>
@@ -45242,13 +45854,13 @@
         </is>
       </c>
       <c r="Z424" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG424" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH424" t="b">
         <v>1</v>
-      </c>
-      <c r="AG424" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH424" t="b">
-        <v>0</v>
       </c>
       <c r="AI424" t="inlineStr">
         <is>
@@ -45357,7 +45969,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG425" t="b">
         <v>0</v>
@@ -45472,7 +46084,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG426" t="b">
         <v>0</v>
@@ -45587,7 +46199,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG427" t="b">
         <v>0</v>
@@ -45702,7 +46314,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG428" t="b">
         <v>0</v>
@@ -45817,7 +46429,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG429" t="b">
         <v>0</v>
@@ -45932,7 +46544,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG430" t="b">
         <v>0</v>
@@ -46047,7 +46659,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG431" t="b">
         <v>0</v>
@@ -46162,7 +46774,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG432" t="b">
         <v>0</v>
@@ -46277,7 +46889,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG433" t="b">
         <v>0</v>
@@ -46392,7 +47004,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG434" t="b">
         <v>0</v>
@@ -46729,7 +47341,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG437" t="b">
         <v>0</v>
@@ -46955,7 +47567,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG439" t="b">
         <v>0</v>
@@ -47070,7 +47682,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG440" t="b">
         <v>0</v>
@@ -47185,7 +47797,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG441" t="b">
         <v>0</v>
@@ -47300,7 +47912,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG442" t="b">
         <v>0</v>
@@ -47415,7 +48027,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG443" t="b">
         <v>0</v>
@@ -47530,7 +48142,7 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG444" t="b">
         <v>0</v>
@@ -47645,7 +48257,7 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG445" t="b">
         <v>0</v>
@@ -47760,7 +48372,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG446" t="b">
         <v>0</v>
@@ -47875,13 +48487,13 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG447" t="b">
         <v>0</v>
       </c>
       <c r="AH447" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI447" t="inlineStr">
         <is>
@@ -47990,7 +48602,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG448" t="b">
         <v>0</v>
@@ -48105,7 +48717,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG449" t="b">
         <v>0</v>
@@ -48220,7 +48832,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG450" t="b">
         <v>0</v>
@@ -48335,7 +48947,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG451" t="b">
         <v>0</v>
@@ -48450,7 +49062,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG452" t="b">
         <v>0</v>
@@ -48565,7 +49177,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG453" t="b">
         <v>0</v>
@@ -48680,7 +49292,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG454" t="b">
         <v>0</v>
@@ -48795,7 +49407,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG455" t="b">
         <v>0</v>
@@ -48910,7 +49522,7 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG456" t="b">
         <v>0</v>
@@ -49025,7 +49637,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG457" t="b">
         <v>0</v>
@@ -49140,7 +49752,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG458" t="b">
         <v>0</v>
@@ -49477,7 +50089,7 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG461" t="b">
         <v>0</v>
@@ -49592,7 +50204,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG462" t="b">
         <v>0</v>
@@ -49601,13 +50213,2531 @@
         <v>0</v>
       </c>
       <c r="AI462" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>86.23999999999999</v>
+      </c>
+      <c r="F463" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I463" t="b">
+        <v>0</v>
+      </c>
+      <c r="J463" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="K463" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M463" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N463" t="n">
+        <v>10</v>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P463" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>59.68</v>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S463" t="n">
+        <v>3.7278</v>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V463" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="W463" t="n">
+        <v>39.5299</v>
+      </c>
+      <c r="X463" t="n">
+        <v>34.1285</v>
+      </c>
+      <c r="Y463" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z463" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG463" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH463" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI463" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>77.84999999999999</v>
+      </c>
+      <c r="F464" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I464" t="b">
+        <v>0</v>
+      </c>
+      <c r="J464" t="n">
+        <v>10</v>
+      </c>
+      <c r="K464" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M464" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="N464" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P464" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S464" t="n">
+        <v>6.112</v>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V464" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="W464" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="X464" t="n">
+        <v>61.5905</v>
+      </c>
+      <c r="Y464" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z464" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG464" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH464" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI464" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="F465" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I465" t="b">
+        <v>0</v>
+      </c>
+      <c r="J465" t="n">
+        <v>10</v>
+      </c>
+      <c r="K465" t="n">
+        <v>268.4</v>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M465" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N465" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P465" t="n">
+        <v>218.25</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S465" t="n">
+        <v>7</v>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V465" t="n">
+        <v>244</v>
+      </c>
+      <c r="W465" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="X465" t="n">
+        <v>226.92</v>
+      </c>
+      <c r="Y465" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z465" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG465" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH465" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI465" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>台化</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>74.69</v>
+      </c>
+      <c r="F466" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I466" t="b">
+        <v>0</v>
+      </c>
+      <c r="J466" t="n">
+        <v>10</v>
+      </c>
+      <c r="K466" t="n">
+        <v>78.43000000000001</v>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M466" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N466" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P466" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S466" t="n">
+        <v>7</v>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V466" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="W466" t="n">
+        <v>85.56</v>
+      </c>
+      <c r="X466" t="n">
+        <v>66.309</v>
+      </c>
+      <c r="Y466" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z466" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG466" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH466" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI466" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>74.73999999999999</v>
+      </c>
+      <c r="F467" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I467" t="b">
+        <v>0</v>
+      </c>
+      <c r="J467" t="n">
+        <v>10</v>
+      </c>
+      <c r="K467" t="n">
+        <v>156.75</v>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M467" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N467" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P467" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>60</v>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S467" t="n">
+        <v>7</v>
+      </c>
+      <c r="T467" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V467" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="W467" t="n">
+        <v>171</v>
+      </c>
+      <c r="X467" t="n">
+        <v>132.525</v>
+      </c>
+      <c r="Y467" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z467" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG467" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH467" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI467" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F468" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I468" t="b">
+        <v>0</v>
+      </c>
+      <c r="J468" t="n">
+        <v>10</v>
+      </c>
+      <c r="K468" t="n">
+        <v>1087.9</v>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M468" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="N468" t="n">
+        <v>10</v>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P468" t="n">
+        <v>974.5</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S468" t="n">
+        <v>4.3231</v>
+      </c>
+      <c r="T468" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V468" t="n">
+        <v>989</v>
+      </c>
+      <c r="W468" t="n">
+        <v>1142.0001</v>
+      </c>
+      <c r="X468" t="n">
+        <v>946.245</v>
+      </c>
+      <c r="Y468" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z468" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG468" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH468" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI468" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>友達</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>77.69</v>
+      </c>
+      <c r="F469" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I469" t="b">
+        <v>0</v>
+      </c>
+      <c r="J469" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="K469" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M469" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="N469" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P469" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>64.64</v>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S469" t="n">
+        <v>7</v>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V469" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="W469" t="n">
+        <v>37.44</v>
+      </c>
+      <c r="X469" t="n">
+        <v>29.016</v>
+      </c>
+      <c r="Y469" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z469" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG469" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH469" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI469" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="F470" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I470" t="b">
+        <v>0</v>
+      </c>
+      <c r="J470" t="n">
+        <v>10</v>
+      </c>
+      <c r="K470" t="n">
+        <v>5192</v>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M470" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N470" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P470" t="n">
+        <v>4282.5</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>63.42</v>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S470" t="n">
+        <v>7</v>
+      </c>
+      <c r="T470" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V470" t="n">
+        <v>4720</v>
+      </c>
+      <c r="W470" t="n">
+        <v>5664</v>
+      </c>
+      <c r="X470" t="n">
+        <v>4389.6</v>
+      </c>
+      <c r="Y470" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z470" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG470" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH470" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI470" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>臺企銀</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>79.03</v>
+      </c>
+      <c r="F471" t="n">
+        <v>43.39</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I471" t="b">
+        <v>0</v>
+      </c>
+      <c r="J471" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="K471" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M471" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N471" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P471" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S471" t="n">
+        <v>7</v>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V471" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="W471" t="n">
+        <v>20.3115</v>
+      </c>
+      <c r="X471" t="n">
+        <v>16.647</v>
+      </c>
+      <c r="Y471" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z471" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG471" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH471" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI471" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="F472" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I472" t="b">
+        <v>0</v>
+      </c>
+      <c r="J472" t="n">
+        <v>10</v>
+      </c>
+      <c r="K472" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M472" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N472" t="n">
+        <v>5</v>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P472" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>61.11</v>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S472" t="n">
+        <v>7</v>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V472" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="W472" t="n">
+        <v>53.76</v>
+      </c>
+      <c r="X472" t="n">
+        <v>41.664</v>
+      </c>
+      <c r="Y472" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z472" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG472" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH472" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI472" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="F473" t="n">
+        <v>53.06</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I473" t="b">
+        <v>0</v>
+      </c>
+      <c r="J473" t="n">
+        <v>10</v>
+      </c>
+      <c r="K473" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M473" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N473" t="n">
+        <v>3</v>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P473" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>73.73</v>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S473" t="n">
+        <v>7</v>
+      </c>
+      <c r="T473" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V473" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="W473" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="X473" t="n">
+        <v>34.596</v>
+      </c>
+      <c r="Y473" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z473" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG473" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH473" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI473" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>82.91</v>
+      </c>
+      <c r="F474" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I474" t="b">
+        <v>0</v>
+      </c>
+      <c r="J474" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K474" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M474" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N474" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P474" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>77.33</v>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S474" t="n">
+        <v>7</v>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V474" t="n">
+        <v>44.95</v>
+      </c>
+      <c r="W474" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="X474" t="n">
+        <v>41.8035</v>
+      </c>
+      <c r="Y474" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z474" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG474" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH474" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI474" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>78.23999999999999</v>
+      </c>
+      <c r="F475" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I475" t="b">
+        <v>0</v>
+      </c>
+      <c r="J475" t="n">
+        <v>10</v>
+      </c>
+      <c r="K475" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M475" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N475" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P475" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S475" t="n">
+        <v>7</v>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V475" t="n">
+        <v>38</v>
+      </c>
+      <c r="W475" t="n">
+        <v>45.5079</v>
+      </c>
+      <c r="X475" t="n">
+        <v>35.34</v>
+      </c>
+      <c r="Y475" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z475" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG475" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH475" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI475" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>晶豪科</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="F476" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I476" t="b">
+        <v>0</v>
+      </c>
+      <c r="J476" t="n">
+        <v>10</v>
+      </c>
+      <c r="K476" t="n">
+        <v>343.2</v>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M476" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N476" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P476" t="n">
+        <v>291.25</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S476" t="n">
+        <v>7</v>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V476" t="n">
+        <v>312</v>
+      </c>
+      <c r="W476" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="X476" t="n">
+        <v>290.16</v>
+      </c>
+      <c r="Y476" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z476" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG476" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH476" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI476" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="F477" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I477" t="b">
+        <v>0</v>
+      </c>
+      <c r="J477" t="n">
+        <v>10</v>
+      </c>
+      <c r="K477" t="n">
+        <v>3806</v>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M477" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N477" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P477" t="n">
+        <v>3222.5</v>
+      </c>
+      <c r="Q477" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S477" t="n">
+        <v>6.6828</v>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V477" t="n">
+        <v>3460</v>
+      </c>
+      <c r="W477" t="n">
+        <v>4152</v>
+      </c>
+      <c r="X477" t="n">
+        <v>3228.775</v>
+      </c>
+      <c r="Y477" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z477" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG477" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH477" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI477" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F478" t="n">
+        <v>52.01</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I478" t="b">
+        <v>0</v>
+      </c>
+      <c r="J478" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="K478" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M478" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="N478" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P478" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="Q478" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S478" t="n">
+        <v>5.6875</v>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V478" t="n">
+        <v>120</v>
+      </c>
+      <c r="W478" t="n">
+        <v>133.3589</v>
+      </c>
+      <c r="X478" t="n">
+        <v>113.175</v>
+      </c>
+      <c r="Y478" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z478" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG478" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH478" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI478" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>75.14</v>
+      </c>
+      <c r="F479" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I479" t="b">
+        <v>0</v>
+      </c>
+      <c r="J479" t="n">
+        <v>10</v>
+      </c>
+      <c r="K479" t="n">
+        <v>507.65</v>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M479" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N479" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P479" t="n">
+        <v>433</v>
+      </c>
+      <c r="Q479" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S479" t="n">
+        <v>7</v>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V479" t="n">
+        <v>461.5</v>
+      </c>
+      <c r="W479" t="n">
+        <v>553.8</v>
+      </c>
+      <c r="X479" t="n">
+        <v>429.195</v>
+      </c>
+      <c r="Y479" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI479" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ479" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>75.89</v>
+      </c>
+      <c r="F480" t="n">
+        <v>46.58</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I480" t="b">
+        <v>0</v>
+      </c>
+      <c r="J480" t="n">
+        <v>10</v>
+      </c>
+      <c r="K480" t="n">
+        <v>1584</v>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M480" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N480" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P480" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>53.84</v>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S480" t="n">
+        <v>7</v>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V480" t="n">
+        <v>1440</v>
+      </c>
+      <c r="W480" t="n">
+        <v>1728</v>
+      </c>
+      <c r="X480" t="n">
+        <v>1339.2</v>
+      </c>
+      <c r="Y480" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI480" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ480" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>77.06</v>
+      </c>
+      <c r="F481" t="n">
+        <v>43.46</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I481" t="b">
+        <v>0</v>
+      </c>
+      <c r="J481" t="n">
+        <v>10</v>
+      </c>
+      <c r="K481" t="n">
+        <v>536.8</v>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M481" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N481" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P481" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="Q481" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S481" t="n">
+        <v>7</v>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V481" t="n">
+        <v>488</v>
+      </c>
+      <c r="W481" t="n">
+        <v>585.6</v>
+      </c>
+      <c r="X481" t="n">
+        <v>453.84</v>
+      </c>
+      <c r="Y481" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI481" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ481" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="F482" t="n">
+        <v>54.45</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I482" t="b">
+        <v>0</v>
+      </c>
+      <c r="J482" t="n">
+        <v>10</v>
+      </c>
+      <c r="K482" t="n">
+        <v>6847.5</v>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M482" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N482" t="n">
+        <v>3</v>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P482" t="n">
+        <v>6030</v>
+      </c>
+      <c r="Q482" t="n">
+        <v>69.68000000000001</v>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S482" t="n">
+        <v>7</v>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V482" t="n">
+        <v>6225</v>
+      </c>
+      <c r="W482" t="n">
+        <v>7470</v>
+      </c>
+      <c r="X482" t="n">
+        <v>5789.25</v>
+      </c>
+      <c r="Y482" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z482" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG482" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH482" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI482" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>73.04000000000001</v>
+      </c>
+      <c r="F483" t="n">
+        <v>53.41</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I483" t="b">
+        <v>0</v>
+      </c>
+      <c r="J483" t="n">
+        <v>10</v>
+      </c>
+      <c r="K483" t="n">
+        <v>451</v>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M483" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N483" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P483" t="n">
+        <v>403</v>
+      </c>
+      <c r="Q483" t="n">
+        <v>59.38</v>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S483" t="n">
+        <v>7</v>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V483" t="n">
+        <v>410</v>
+      </c>
+      <c r="W483" t="n">
+        <v>492</v>
+      </c>
+      <c r="X483" t="n">
+        <v>381.3</v>
+      </c>
+      <c r="Y483" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z483" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG483" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH483" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI483" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>81.28</v>
+      </c>
+      <c r="F484" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I484" t="b">
+        <v>0</v>
+      </c>
+      <c r="J484" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="K484" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M484" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N484" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P484" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="Q484" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S484" t="n">
+        <v>7</v>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V484" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="W484" t="n">
+        <v>30.3031</v>
+      </c>
+      <c r="X484" t="n">
+        <v>24.9705</v>
+      </c>
+      <c r="Y484" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z484" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG484" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH484" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI484" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ462"/>
+  <autoFilter ref="A1:AJ484"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49700,25 +52830,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5294</v>
+        <v>0.4881</v>
       </c>
       <c r="D4" t="n">
-        <v>4.06</v>
+        <v>2.36</v>
       </c>
       <c r="E4" t="n">
-        <v>13.64</v>
+        <v>12.94</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.62</v>
+        <v>-9.02</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3137</v>
+        <v>0.2976</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4314</v>
+        <v>0.4643</v>
       </c>
     </row>
   </sheetData>
@@ -49834,25 +52964,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5294</v>
+        <v>0.4881</v>
       </c>
       <c r="D6" t="n">
-        <v>4.06</v>
+        <v>2.36</v>
       </c>
       <c r="E6" t="n">
-        <v>13.64</v>
+        <v>12.94</v>
       </c>
       <c r="F6" t="n">
-        <v>-7.62</v>
+        <v>-9.02</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3137</v>
+        <v>0.2976</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4314</v>
+        <v>0.4643</v>
       </c>
     </row>
   </sheetData>
@@ -49893,7 +53023,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 14:23:11</t>
+          <t>2026-09-10 14:25:36</t>
         </is>
       </c>
     </row>
@@ -49940,7 +53070,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>461</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7">
@@ -49950,7 +53080,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -49960,7 +53090,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>410</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$484</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$504</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ484"/>
+  <dimension ref="A1:AJ504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8155,11 +8155,11 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA92" t="n">
         <v>1.83</v>
@@ -8170,6 +8170,15 @@
       <c r="AC92" t="n">
         <v>5.07</v>
       </c>
+      <c r="AD92" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>-1.83</v>
+      </c>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -8178,7 +8187,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -8230,11 +8239,11 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA93" t="n">
         <v>-1.71</v>
@@ -8245,6 +8254,15 @@
       <c r="AC93" t="n">
         <v>-4.45</v>
       </c>
+      <c r="AD93" t="n">
+        <v>-11.99</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>-14.38</v>
+      </c>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -8253,7 +8271,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -8305,11 +8323,11 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA94" t="n">
         <v>-2.25</v>
@@ -8320,6 +8338,15 @@
       <c r="AC94" t="n">
         <v>15.36</v>
       </c>
+      <c r="AD94" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>-5.99</v>
+      </c>
       <c r="AG94" t="b">
         <v>1</v>
       </c>
@@ -8328,7 +8355,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -8380,11 +8407,11 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA95" t="n">
         <v>-14.59</v>
@@ -8395,6 +8422,15 @@
       <c r="AC95" t="n">
         <v>-9.18</v>
       </c>
+      <c r="AD95" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>-15.6</v>
+      </c>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -8403,7 +8439,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -8455,11 +8491,11 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA96" t="n">
         <v>-11.01</v>
@@ -8470,6 +8506,15 @@
       <c r="AC96" t="n">
         <v>1.57</v>
       </c>
+      <c r="AD96" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>-12.89</v>
+      </c>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -8478,7 +8523,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -8530,11 +8575,11 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA97" t="n">
         <v>-7.87</v>
@@ -8545,6 +8590,15 @@
       <c r="AC97" t="n">
         <v>-12.17</v>
       </c>
+      <c r="AD97" t="n">
+        <v>-12.98</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>-15.49</v>
+      </c>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -8553,7 +8607,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -8605,11 +8659,11 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA98" t="n">
         <v>3.12</v>
@@ -8620,6 +8674,15 @@
       <c r="AC98" t="n">
         <v>-3.12</v>
       </c>
+      <c r="AD98" t="n">
+        <v>-3.71</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>-8.199999999999999</v>
+      </c>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -8628,7 +8691,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -8680,11 +8743,11 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA99" t="n">
         <v>-9.98</v>
@@ -8695,6 +8758,15 @@
       <c r="AC99" t="n">
         <v>4.87</v>
       </c>
+      <c r="AD99" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>-13.18</v>
+      </c>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -8703,7 +8775,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -8755,11 +8827,11 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA100" t="n">
         <v>14.84</v>
@@ -8770,6 +8842,15 @@
       <c r="AC100" t="n">
         <v>6.39</v>
       </c>
+      <c r="AD100" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>0</v>
+      </c>
       <c r="AG100" t="b">
         <v>1</v>
       </c>
@@ -8778,7 +8859,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -8830,11 +8911,11 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA101" t="n">
         <v>24.03</v>
@@ -8845,6 +8926,15 @@
       <c r="AC101" t="n">
         <v>12.79</v>
       </c>
+      <c r="AD101" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>0</v>
+      </c>
       <c r="AG101" t="b">
         <v>1</v>
       </c>
@@ -8853,7 +8943,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -8905,11 +8995,11 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA102" t="n">
         <v>37.42</v>
@@ -8920,6 +9010,15 @@
       <c r="AC102" t="n">
         <v>26.93</v>
       </c>
+      <c r="AD102" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>0</v>
+      </c>
       <c r="AG102" t="b">
         <v>1</v>
       </c>
@@ -8928,7 +9027,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -8980,11 +9079,11 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.32</v>
@@ -8995,6 +9094,15 @@
       <c r="AC103" t="n">
         <v>15.96</v>
       </c>
+      <c r="AD103" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>-5.06</v>
+      </c>
       <c r="AG103" t="b">
         <v>1</v>
       </c>
@@ -9003,7 +9111,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -9055,11 +9163,11 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA104" t="n">
         <v>-1.32</v>
@@ -9070,6 +9178,15 @@
       <c r="AC104" t="n">
         <v>9.93</v>
       </c>
+      <c r="AD104" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>-5.43</v>
+      </c>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -9078,7 +9195,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -9130,11 +9247,11 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA105" t="n">
         <v>21.69</v>
@@ -9145,6 +9262,15 @@
       <c r="AC105" t="n">
         <v>60.52</v>
       </c>
+      <c r="AD105" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>73.43000000000001</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>0</v>
+      </c>
       <c r="AG105" t="b">
         <v>1</v>
       </c>
@@ -9153,7 +9279,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -9205,11 +9331,11 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA106" t="n">
         <v>-11.44</v>
@@ -9220,6 +9346,15 @@
       <c r="AC106" t="n">
         <v>10.36</v>
       </c>
+      <c r="AD106" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>-15.3</v>
+      </c>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -9228,7 +9363,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -9280,11 +9415,11 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA107" t="n">
         <v>6.37</v>
@@ -9295,6 +9430,15 @@
       <c r="AC107" t="n">
         <v>-11.57</v>
       </c>
+      <c r="AD107" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>-14.41</v>
+      </c>
       <c r="AG107" t="b">
         <v>1</v>
       </c>
@@ -9303,7 +9447,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -9355,11 +9499,11 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA108" t="n">
         <v>-5.92</v>
@@ -9370,6 +9514,15 @@
       <c r="AC108" t="n">
         <v>-4.99</v>
       </c>
+      <c r="AD108" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>-11.14</v>
+      </c>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -9378,7 +9531,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -9430,11 +9583,11 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA109" t="n">
         <v>-9.300000000000001</v>
@@ -9445,6 +9598,15 @@
       <c r="AC109" t="n">
         <v>2.33</v>
       </c>
+      <c r="AD109" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>-10.85</v>
+      </c>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -9453,7 +9615,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -9505,11 +9667,11 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA110" t="n">
         <v>2.47</v>
@@ -9520,6 +9682,15 @@
       <c r="AC110" t="n">
         <v>6.31</v>
       </c>
+      <c r="AD110" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>-4.76</v>
+      </c>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -9528,7 +9699,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -9580,11 +9751,11 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z111" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA111" t="n">
         <v>-6.67</v>
@@ -9595,6 +9766,15 @@
       <c r="AC111" t="n">
         <v>-12.67</v>
       </c>
+      <c r="AD111" t="n">
+        <v>-14.67</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>-14.67</v>
+      </c>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -9603,7 +9783,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -9655,11 +9835,11 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA112" t="n">
         <v>-67.41</v>
@@ -9670,6 +9850,15 @@
       <c r="AC112" t="n">
         <v>-60.14</v>
       </c>
+      <c r="AD112" t="n">
+        <v>-64.09999999999999</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>-55.32</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>-68.09</v>
+      </c>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -9678,7 +9867,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -9734,7 +9923,7 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
@@ -9809,7 +9998,7 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
@@ -9884,7 +10073,7 @@
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
@@ -9959,7 +10148,7 @@
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
@@ -10034,7 +10223,7 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
@@ -10109,7 +10298,7 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
@@ -10184,7 +10373,7 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
@@ -10259,7 +10448,7 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
@@ -10334,7 +10523,7 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
@@ -10409,7 +10598,7 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
@@ -10484,7 +10673,7 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
@@ -10559,7 +10748,7 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
@@ -10634,7 +10823,7 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
@@ -10709,7 +10898,7 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
@@ -10784,7 +10973,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
@@ -10859,7 +11048,7 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
@@ -10934,7 +11123,7 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA129" t="n">
         <v>-68.09</v>
@@ -11058,7 +11247,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
@@ -11182,7 +11371,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
@@ -11306,7 +11495,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
@@ -11321,7 +11510,7 @@
         <v>0</v>
       </c>
       <c r="AH132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
@@ -11430,7 +11619,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
@@ -11554,7 +11743,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
@@ -11678,7 +11867,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
@@ -11802,7 +11991,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
@@ -11923,7 +12112,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
@@ -12047,7 +12236,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
@@ -12171,7 +12360,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
@@ -12295,7 +12484,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
@@ -12419,7 +12608,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
@@ -12543,7 +12732,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
@@ -12667,7 +12856,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
@@ -12791,7 +12980,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
@@ -12915,7 +13104,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA145" t="n">
         <v>-66.26000000000001</v>
@@ -13039,7 +13228,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
@@ -13163,7 +13352,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
@@ -13287,7 +13476,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
@@ -13411,7 +13600,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
@@ -13535,7 +13724,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
@@ -13659,7 +13848,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
@@ -13783,7 +13972,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
@@ -13907,7 +14096,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
@@ -14031,7 +14220,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
@@ -14155,7 +14344,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
@@ -14279,7 +14468,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
@@ -14403,7 +14592,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
@@ -14527,7 +14716,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
@@ -14651,7 +14840,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
@@ -14775,7 +14964,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
@@ -14899,7 +15088,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
@@ -15023,7 +15212,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
@@ -15147,7 +15336,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
@@ -15271,7 +15460,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
@@ -15395,7 +15584,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
@@ -15519,7 +15708,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
@@ -15643,7 +15832,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
@@ -15878,7 +16067,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
@@ -16002,7 +16191,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
@@ -16126,7 +16315,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA171" t="n">
         <v>-63.88</v>
@@ -16250,13 +16439,16 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
       </c>
       <c r="AB172" t="n">
         <v>-1.01</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>-1.41</v>
       </c>
       <c r="AG172" t="b">
         <v>0</v>
@@ -16371,13 +16563,16 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
       </c>
       <c r="AB173" t="n">
         <v>0.43</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>1</v>
       </c>
       <c r="AG173" t="b">
         <v>0</v>
@@ -16492,13 +16687,16 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
       </c>
       <c r="AB174" t="n">
         <v>-3.95</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>-5.6</v>
       </c>
       <c r="AG174" t="b">
         <v>0</v>
@@ -16613,13 +16811,16 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
       </c>
       <c r="AB175" t="n">
         <v>-6.06</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>-6.63</v>
       </c>
       <c r="AG175" t="b">
         <v>0</v>
@@ -16734,13 +16935,16 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
       </c>
       <c r="AB176" t="n">
         <v>12.31</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>10.82</v>
       </c>
       <c r="AG176" t="b">
         <v>1</v>
@@ -16855,13 +17059,16 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
       </c>
       <c r="AB177" t="n">
         <v>11.41</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>14.5</v>
       </c>
       <c r="AG177" t="b">
         <v>1</v>
@@ -16976,13 +17183,16 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
       </c>
       <c r="AB178" t="n">
         <v>31.91</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>18.72</v>
       </c>
       <c r="AG178" t="b">
         <v>1</v>
@@ -17208,13 +17418,16 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
       </c>
       <c r="AB180" t="n">
         <v>3.75</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>9.289999999999999</v>
       </c>
       <c r="AG180" t="b">
         <v>0</v>
@@ -17329,7 +17542,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
@@ -17450,7 +17663,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
@@ -17571,7 +17784,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
@@ -17692,7 +17905,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
@@ -17813,7 +18026,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
@@ -17934,7 +18147,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA186" t="n">
         <v>-62.24</v>
@@ -18055,7 +18268,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
@@ -18176,7 +18389,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
@@ -18188,7 +18401,7 @@
         <v>0</v>
       </c>
       <c r="AH188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI188" t="inlineStr">
         <is>
@@ -18297,7 +18510,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
@@ -18309,7 +18522,7 @@
         <v>0</v>
       </c>
       <c r="AH189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI189" t="inlineStr">
         <is>
@@ -18418,7 +18631,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
@@ -18539,7 +18752,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
@@ -18660,7 +18873,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
@@ -18781,7 +18994,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
@@ -18902,7 +19115,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
@@ -19023,7 +19236,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
@@ -19144,7 +19357,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
@@ -19265,7 +19478,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
@@ -19608,7 +19821,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
@@ -19729,7 +19942,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
@@ -19850,7 +20063,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
@@ -19971,7 +20184,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
@@ -20092,7 +20305,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
@@ -20213,7 +20426,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
@@ -20334,7 +20547,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
@@ -20455,7 +20668,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
@@ -20576,7 +20789,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
@@ -20697,7 +20910,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
@@ -20818,7 +21031,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -20939,7 +21152,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
@@ -21060,7 +21273,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
@@ -21292,7 +21505,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
@@ -21304,7 +21517,7 @@
         <v>0</v>
       </c>
       <c r="AH214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI214" t="inlineStr">
         <is>
@@ -21413,7 +21626,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
@@ -21534,7 +21747,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
@@ -21655,7 +21868,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
@@ -21776,7 +21989,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
@@ -21897,7 +22110,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
@@ -21909,7 +22122,7 @@
         <v>0</v>
       </c>
       <c r="AH219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI219" t="inlineStr">
         <is>
@@ -22018,7 +22231,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
@@ -22139,7 +22352,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
@@ -22260,7 +22473,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
@@ -22272,7 +22485,7 @@
         <v>0</v>
       </c>
       <c r="AH222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI222" t="inlineStr">
         <is>
@@ -22381,7 +22594,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
@@ -22393,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="AH223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
@@ -22502,7 +22715,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
@@ -22623,7 +22836,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
@@ -22744,7 +22957,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
@@ -22865,7 +23078,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
@@ -22986,7 +23199,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
@@ -23107,7 +23320,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
@@ -23228,7 +23441,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
@@ -23349,7 +23562,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
@@ -23581,7 +23794,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
@@ -23924,7 +24137,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
@@ -24045,7 +24258,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -24166,7 +24379,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
@@ -24287,7 +24500,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
@@ -24408,7 +24621,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
@@ -24529,7 +24742,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
@@ -24650,7 +24863,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
@@ -24771,10 +24984,13 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
+      </c>
+      <c r="AB243" t="n">
+        <v>3.03</v>
       </c>
       <c r="AG243" t="b">
         <v>0</v>
@@ -24889,10 +25105,13 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
+      </c>
+      <c r="AB244" t="n">
+        <v>6.35</v>
       </c>
       <c r="AG244" t="b">
         <v>0</v>
@@ -25007,16 +25226,19 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
       </c>
+      <c r="AB245" t="n">
+        <v>-4.27</v>
+      </c>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AH245" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
@@ -25125,10 +25347,13 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>-5.7</v>
       </c>
       <c r="AG246" t="b">
         <v>0</v>
@@ -25243,10 +25468,13 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>-12.76</v>
       </c>
       <c r="AG247" t="b">
         <v>0</v>
@@ -25361,10 +25589,13 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>1.2</v>
       </c>
       <c r="AG248" t="b">
         <v>0</v>
@@ -25479,10 +25710,13 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>0.75</v>
       </c>
       <c r="AG249" t="b">
         <v>0</v>
@@ -25597,10 +25831,13 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>-8.699999999999999</v>
       </c>
       <c r="AG250" t="b">
         <v>0</v>
@@ -25715,10 +25952,13 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>3.12</v>
       </c>
       <c r="AG251" t="b">
         <v>0</v>
@@ -25833,10 +26073,13 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
+      </c>
+      <c r="AB252" t="n">
+        <v>-5.73</v>
       </c>
       <c r="AG252" t="b">
         <v>0</v>
@@ -25951,10 +26194,13 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>0.3</v>
       </c>
       <c r="AG253" t="b">
         <v>0</v>
@@ -26069,10 +26315,13 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>-6.09</v>
       </c>
       <c r="AG254" t="b">
         <v>0</v>
@@ -26187,10 +26436,13 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>-11.98</v>
       </c>
       <c r="AG255" t="b">
         <v>0</v>
@@ -26527,10 +26779,13 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
+      </c>
+      <c r="AB258" t="n">
+        <v>-8.57</v>
       </c>
       <c r="AG258" t="b">
         <v>0</v>
@@ -26867,10 +27122,13 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>1.75</v>
       </c>
       <c r="AG261" t="b">
         <v>0</v>
@@ -26985,16 +27243,19 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
       </c>
+      <c r="AB262" t="n">
+        <v>-6.01</v>
+      </c>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
       <c r="AH262" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI262" t="inlineStr">
         <is>
@@ -27103,16 +27364,19 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
       </c>
+      <c r="AB263" t="n">
+        <v>-10.21</v>
+      </c>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
       <c r="AH263" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI263" t="inlineStr">
         <is>
@@ -27221,10 +27485,13 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>-0.48</v>
       </c>
       <c r="AG264" t="b">
         <v>0</v>
@@ -27450,10 +27717,13 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>-17.15</v>
       </c>
       <c r="AG266" t="b">
         <v>0</v>
@@ -27568,10 +27838,13 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>-67.92</v>
       </c>
       <c r="AG267" t="b">
         <v>0</v>
@@ -27686,10 +27959,13 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>-14.95</v>
       </c>
       <c r="AG268" t="b">
         <v>0</v>
@@ -27804,7 +28080,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
@@ -27922,7 +28198,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
@@ -28040,7 +28316,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
@@ -28158,7 +28434,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
@@ -28167,7 +28443,7 @@
         <v>0</v>
       </c>
       <c r="AH272" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI272" t="inlineStr">
         <is>
@@ -28276,7 +28552,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
@@ -28394,7 +28670,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
@@ -28512,7 +28788,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
@@ -28521,7 +28797,7 @@
         <v>0</v>
       </c>
       <c r="AH275" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI275" t="inlineStr">
         <is>
@@ -28630,7 +28906,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
@@ -28748,7 +29024,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -28757,7 +29033,7 @@
         <v>0</v>
       </c>
       <c r="AH277" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI277" t="inlineStr">
         <is>
@@ -28866,7 +29142,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
@@ -28984,7 +29260,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
@@ -29102,7 +29378,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
@@ -29220,7 +29496,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
@@ -29338,7 +29614,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
@@ -29456,7 +29732,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -29574,7 +29850,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
@@ -29692,7 +29968,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
@@ -29810,7 +30086,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
@@ -29928,7 +30204,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
@@ -30046,7 +30322,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
@@ -30164,7 +30440,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
@@ -30282,7 +30558,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
@@ -30400,7 +30676,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
@@ -30518,7 +30794,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
@@ -30636,7 +30912,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
@@ -31087,7 +31363,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -31205,7 +31481,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
@@ -31214,7 +31490,7 @@
         <v>0</v>
       </c>
       <c r="AH298" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI298" t="inlineStr">
         <is>
@@ -31323,7 +31599,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
@@ -31552,7 +31828,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
@@ -31670,7 +31946,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
@@ -31788,7 +32064,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
@@ -31797,7 +32073,7 @@
         <v>0</v>
       </c>
       <c r="AH303" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI303" t="inlineStr">
         <is>
@@ -31906,7 +32182,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
@@ -31915,7 +32191,7 @@
         <v>0</v>
       </c>
       <c r="AH304" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI304" t="inlineStr">
         <is>
@@ -32024,7 +32300,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
@@ -32033,7 +32309,7 @@
         <v>0</v>
       </c>
       <c r="AH305" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI305" t="inlineStr">
         <is>
@@ -32142,7 +32418,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
@@ -32260,7 +32536,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
@@ -32378,7 +32654,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
@@ -32496,7 +32772,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
@@ -32505,7 +32781,7 @@
         <v>0</v>
       </c>
       <c r="AH309" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI309" t="inlineStr">
         <is>
@@ -32614,7 +32890,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
@@ -32732,7 +33008,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
@@ -32850,7 +33126,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
@@ -32968,7 +33244,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
@@ -33086,7 +33362,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
@@ -33204,7 +33480,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
@@ -33322,7 +33598,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
@@ -33440,7 +33716,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
@@ -33558,7 +33834,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
@@ -33676,7 +33952,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
@@ -33794,7 +34070,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
@@ -33912,7 +34188,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
@@ -34030,7 +34306,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
@@ -34148,7 +34424,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
@@ -34157,7 +34433,7 @@
         <v>0</v>
       </c>
       <c r="AH323" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI323" t="inlineStr">
         <is>
@@ -34266,7 +34542,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
@@ -34606,7 +34882,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
@@ -34724,7 +35000,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
@@ -34842,7 +35118,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
@@ -35182,7 +35458,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
@@ -35300,7 +35576,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
@@ -35418,7 +35694,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
@@ -35536,7 +35812,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
@@ -35654,7 +35930,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
@@ -35772,7 +36048,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
@@ -35890,7 +36166,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
@@ -35899,7 +36175,7 @@
         <v>0</v>
       </c>
       <c r="AH338" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI338" t="inlineStr">
         <is>
@@ -36008,7 +36284,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
@@ -36126,7 +36402,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
@@ -36244,7 +36520,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
@@ -36362,7 +36638,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
@@ -36480,7 +36756,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
@@ -36598,7 +36874,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
@@ -36716,7 +36992,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
@@ -36834,7 +37110,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
@@ -36952,7 +37228,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
@@ -37070,7 +37346,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
@@ -37188,7 +37464,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
@@ -37306,7 +37582,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
@@ -37424,7 +37700,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
@@ -37542,7 +37818,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
@@ -37551,7 +37827,7 @@
         <v>0</v>
       </c>
       <c r="AH352" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI352" t="inlineStr">
         <is>
@@ -37660,7 +37936,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
@@ -38222,7 +38498,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
@@ -38340,7 +38616,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
@@ -38458,7 +38734,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
@@ -38576,7 +38852,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
@@ -38694,7 +38970,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
@@ -38812,7 +39088,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
@@ -38821,7 +39097,7 @@
         <v>0</v>
       </c>
       <c r="AH363" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI363" t="inlineStr">
         <is>
@@ -38930,7 +39206,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
@@ -39048,7 +39324,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
@@ -39166,7 +39442,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
@@ -39284,7 +39560,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
@@ -39402,7 +39678,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
@@ -39520,7 +39796,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
@@ -39638,7 +39914,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
@@ -39756,7 +40032,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
@@ -39874,7 +40150,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
@@ -39992,7 +40268,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
@@ -40110,7 +40386,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
@@ -40228,7 +40504,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
@@ -40346,7 +40622,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
@@ -40464,7 +40740,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
@@ -40804,7 +41080,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
@@ -40813,7 +41089,7 @@
         <v>0</v>
       </c>
       <c r="AH380" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI380" t="inlineStr">
         <is>
@@ -40922,7 +41198,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
@@ -41151,7 +41427,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
@@ -41269,7 +41545,10 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA384" t="n">
+        <v>-2.12</v>
       </c>
       <c r="AG384" t="b">
         <v>0</v>
@@ -41384,7 +41663,10 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA385" t="n">
+        <v>3.99</v>
       </c>
       <c r="AG385" t="b">
         <v>0</v>
@@ -41499,13 +41781,16 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA386" t="n">
+        <v>-3.74</v>
       </c>
       <c r="AG386" t="b">
         <v>0</v>
       </c>
       <c r="AH386" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI386" t="inlineStr">
         <is>
@@ -41614,7 +41899,10 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA387" t="n">
+        <v>-4.56</v>
       </c>
       <c r="AG387" t="b">
         <v>0</v>
@@ -41729,7 +42017,10 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA388" t="n">
+        <v>-10.06</v>
       </c>
       <c r="AG388" t="b">
         <v>0</v>
@@ -41844,7 +42135,10 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA389" t="n">
+        <v>-9.130000000000001</v>
       </c>
       <c r="AG389" t="b">
         <v>0</v>
@@ -41956,7 +42250,10 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA390" t="n">
+        <v>-4.89</v>
       </c>
       <c r="AG390" t="b">
         <v>0</v>
@@ -42071,13 +42368,16 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA391" t="n">
+        <v>-9.85</v>
       </c>
       <c r="AG391" t="b">
         <v>0</v>
       </c>
       <c r="AH391" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI391" t="inlineStr">
         <is>
@@ -42186,7 +42486,10 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA392" t="n">
+        <v>-7.74</v>
       </c>
       <c r="AG392" t="b">
         <v>0</v>
@@ -42301,7 +42604,10 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA393" t="n">
+        <v>-2.46</v>
       </c>
       <c r="AG393" t="b">
         <v>0</v>
@@ -42416,7 +42722,10 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA394" t="n">
+        <v>-4.98</v>
       </c>
       <c r="AG394" t="b">
         <v>0</v>
@@ -42531,7 +42840,10 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA395" t="n">
+        <v>-5.2</v>
       </c>
       <c r="AG395" t="b">
         <v>0</v>
@@ -42646,7 +42958,10 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA396" t="n">
+        <v>3.85</v>
       </c>
       <c r="AG396" t="b">
         <v>0</v>
@@ -42761,7 +43076,10 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA397" t="n">
+        <v>2.06</v>
       </c>
       <c r="AG397" t="b">
         <v>0</v>
@@ -42876,7 +43194,10 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA398" t="n">
+        <v>-2.61</v>
       </c>
       <c r="AG398" t="b">
         <v>0</v>
@@ -42991,7 +43312,10 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA399" t="n">
+        <v>-1.33</v>
       </c>
       <c r="AG399" t="b">
         <v>0</v>
@@ -43106,7 +43430,10 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA400" t="n">
+        <v>-3.91</v>
       </c>
       <c r="AG400" t="b">
         <v>0</v>
@@ -43221,7 +43548,10 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA401" t="n">
+        <v>3.13</v>
       </c>
       <c r="AG401" t="b">
         <v>0</v>
@@ -43336,7 +43666,10 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA402" t="n">
+        <v>6.31</v>
       </c>
       <c r="AG402" t="b">
         <v>0</v>
@@ -43451,7 +43784,10 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA403" t="n">
+        <v>2.77</v>
       </c>
       <c r="AG403" t="b">
         <v>0</v>
@@ -43566,7 +43902,10 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA404" t="n">
+        <v>1.98</v>
       </c>
       <c r="AG404" t="b">
         <v>0</v>
@@ -43681,7 +44020,10 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA405" t="n">
+        <v>4.29</v>
       </c>
       <c r="AG405" t="b">
         <v>0</v>
@@ -43796,7 +44138,10 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA406" t="n">
+        <v>4.31</v>
       </c>
       <c r="AG406" t="b">
         <v>0</v>
@@ -43911,7 +44256,10 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA407" t="n">
+        <v>-10</v>
       </c>
       <c r="AG407" t="b">
         <v>0</v>
@@ -44026,7 +44374,10 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA408" t="n">
+        <v>-5.6</v>
       </c>
       <c r="AG408" t="b">
         <v>0</v>
@@ -44141,7 +44492,10 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA409" t="n">
+        <v>2.54</v>
       </c>
       <c r="AG409" t="b">
         <v>0</v>
@@ -44589,7 +44943,10 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA413" t="n">
+        <v>-13.51</v>
       </c>
       <c r="AG413" t="b">
         <v>0</v>
@@ -44704,7 +45061,10 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA414" t="n">
+        <v>2.06</v>
       </c>
       <c r="AG414" t="b">
         <v>0</v>
@@ -44819,7 +45179,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG415" t="b">
         <v>0</v>
@@ -44934,7 +45294,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG416" t="b">
         <v>0</v>
@@ -45049,7 +45409,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG417" t="b">
         <v>0</v>
@@ -45164,7 +45524,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG418" t="b">
         <v>0</v>
@@ -45279,7 +45639,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG419" t="b">
         <v>0</v>
@@ -45394,13 +45754,13 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG420" t="b">
         <v>0</v>
       </c>
       <c r="AH420" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI420" t="inlineStr">
         <is>
@@ -45509,7 +45869,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG421" t="b">
         <v>0</v>
@@ -45624,7 +45984,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG422" t="b">
         <v>0</v>
@@ -45739,7 +46099,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG423" t="b">
         <v>0</v>
@@ -45854,7 +46214,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG424" t="b">
         <v>0</v>
@@ -45969,7 +46329,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG425" t="b">
         <v>0</v>
@@ -46084,7 +46444,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG426" t="b">
         <v>0</v>
@@ -46199,7 +46559,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG427" t="b">
         <v>0</v>
@@ -46314,7 +46674,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG428" t="b">
         <v>0</v>
@@ -46429,7 +46789,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG429" t="b">
         <v>0</v>
@@ -46544,7 +46904,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG430" t="b">
         <v>0</v>
@@ -46659,7 +47019,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG431" t="b">
         <v>0</v>
@@ -46774,7 +47134,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG432" t="b">
         <v>0</v>
@@ -46889,7 +47249,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG433" t="b">
         <v>0</v>
@@ -47004,7 +47364,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG434" t="b">
         <v>0</v>
@@ -47341,7 +47701,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG437" t="b">
         <v>0</v>
@@ -47567,7 +47927,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG439" t="b">
         <v>0</v>
@@ -47682,7 +48042,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG440" t="b">
         <v>0</v>
@@ -47797,7 +48157,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG441" t="b">
         <v>0</v>
@@ -47912,7 +48272,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG442" t="b">
         <v>0</v>
@@ -48027,7 +48387,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG443" t="b">
         <v>0</v>
@@ -48142,7 +48502,7 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG444" t="b">
         <v>0</v>
@@ -48257,7 +48617,7 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG445" t="b">
         <v>0</v>
@@ -48372,7 +48732,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG446" t="b">
         <v>0</v>
@@ -48487,7 +48847,7 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG447" t="b">
         <v>0</v>
@@ -48602,7 +48962,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG448" t="b">
         <v>0</v>
@@ -48717,7 +49077,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG449" t="b">
         <v>0</v>
@@ -48832,7 +49192,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG450" t="b">
         <v>0</v>
@@ -48947,7 +49307,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG451" t="b">
         <v>0</v>
@@ -49062,7 +49422,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG452" t="b">
         <v>0</v>
@@ -49177,7 +49537,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG453" t="b">
         <v>0</v>
@@ -49292,7 +49652,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG454" t="b">
         <v>0</v>
@@ -49407,7 +49767,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG455" t="b">
         <v>0</v>
@@ -49522,7 +49882,7 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG456" t="b">
         <v>0</v>
@@ -49637,7 +49997,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG457" t="b">
         <v>0</v>
@@ -49752,7 +50112,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG458" t="b">
         <v>0</v>
@@ -50089,7 +50449,7 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG461" t="b">
         <v>0</v>
@@ -50204,7 +50564,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG462" t="b">
         <v>0</v>
@@ -50319,7 +50679,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG463" t="b">
         <v>0</v>
@@ -50434,7 +50794,7 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG464" t="b">
         <v>0</v>
@@ -50549,7 +50909,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG465" t="b">
         <v>0</v>
@@ -50664,7 +51024,7 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG466" t="b">
         <v>0</v>
@@ -50779,7 +51139,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG467" t="b">
         <v>0</v>
@@ -50894,13 +51254,13 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG468" t="b">
         <v>0</v>
       </c>
       <c r="AH468" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI468" t="inlineStr">
         <is>
@@ -51009,13 +51369,13 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG469" t="b">
         <v>0</v>
       </c>
       <c r="AH469" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI469" t="inlineStr">
         <is>
@@ -51124,7 +51484,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG470" t="b">
         <v>0</v>
@@ -51239,7 +51599,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG471" t="b">
         <v>0</v>
@@ -51354,7 +51714,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG472" t="b">
         <v>0</v>
@@ -51469,7 +51829,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG473" t="b">
         <v>0</v>
@@ -51584,7 +51944,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG474" t="b">
         <v>0</v>
@@ -51699,7 +52059,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG475" t="b">
         <v>0</v>
@@ -51814,13 +52174,13 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG476" t="b">
         <v>0</v>
       </c>
       <c r="AH476" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI476" t="inlineStr">
         <is>
@@ -51929,7 +52289,7 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG477" t="b">
         <v>0</v>
@@ -52044,7 +52404,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG478" t="b">
         <v>0</v>
@@ -52492,7 +52852,7 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG482" t="b">
         <v>0</v>
@@ -52607,7 +52967,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG483" t="b">
         <v>0</v>
@@ -52722,7 +53082,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG484" t="b">
         <v>0</v>
@@ -52731,13 +53091,2313 @@
         <v>0</v>
       </c>
       <c r="AI484" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="F485" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I485" t="b">
+        <v>0</v>
+      </c>
+      <c r="J485" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K485" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M485" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N485" t="n">
+        <v>10</v>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P485" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S485" t="n">
+        <v>3.3187</v>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V485" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="W485" t="n">
+        <v>38.1865</v>
+      </c>
+      <c r="X485" t="n">
+        <v>34.1285</v>
+      </c>
+      <c r="Y485" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z485" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG485" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH485" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI485" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>73.45</v>
+      </c>
+      <c r="F486" t="n">
+        <v>53.84</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I486" t="b">
+        <v>0</v>
+      </c>
+      <c r="J486" t="n">
+        <v>10</v>
+      </c>
+      <c r="K486" t="n">
+        <v>257.95</v>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M486" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N486" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P486" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>62.28</v>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S486" t="n">
+        <v>7</v>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U486" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V486" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="W486" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="X486" t="n">
+        <v>218.085</v>
+      </c>
+      <c r="Y486" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z486" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG486" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH486" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI486" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>友達</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>78.48999999999999</v>
+      </c>
+      <c r="F487" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I487" t="b">
+        <v>0</v>
+      </c>
+      <c r="J487" t="n">
+        <v>10</v>
+      </c>
+      <c r="K487" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M487" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N487" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P487" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>69.73999999999999</v>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S487" t="n">
+        <v>7</v>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V487" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="W487" t="n">
+        <v>36.24</v>
+      </c>
+      <c r="X487" t="n">
+        <v>28.086</v>
+      </c>
+      <c r="Y487" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z487" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG487" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH487" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI487" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>81.20999999999999</v>
+      </c>
+      <c r="F488" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I488" t="b">
+        <v>0</v>
+      </c>
+      <c r="J488" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K488" t="n">
+        <v>143</v>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M488" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N488" t="n">
+        <v>10</v>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P488" t="n">
+        <v>137.75</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S488" t="n">
+        <v>3.8536</v>
+      </c>
+      <c r="T488" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U488" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V488" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="W488" t="n">
+        <v>149.3176</v>
+      </c>
+      <c r="X488" t="n">
+        <v>135.0857</v>
+      </c>
+      <c r="Y488" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z488" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG488" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH488" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI488" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F489" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I489" t="b">
+        <v>0</v>
+      </c>
+      <c r="J489" t="n">
+        <v>10</v>
+      </c>
+      <c r="K489" t="n">
+        <v>5043.5</v>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M489" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N489" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P489" t="n">
+        <v>4337.5</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>58.58</v>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S489" t="n">
+        <v>7</v>
+      </c>
+      <c r="T489" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V489" t="n">
+        <v>4585</v>
+      </c>
+      <c r="W489" t="n">
+        <v>5502</v>
+      </c>
+      <c r="X489" t="n">
+        <v>4264.05</v>
+      </c>
+      <c r="Y489" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z489" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG489" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH489" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI489" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>臺企銀</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="F490" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I490" t="b">
+        <v>0</v>
+      </c>
+      <c r="J490" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K490" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M490" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N490" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P490" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>70.98</v>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S490" t="n">
+        <v>7</v>
+      </c>
+      <c r="T490" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V490" t="n">
+        <v>18</v>
+      </c>
+      <c r="W490" t="n">
+        <v>20.6613</v>
+      </c>
+      <c r="X490" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="Y490" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z490" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG490" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH490" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI490" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>81.63</v>
+      </c>
+      <c r="F491" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I491" t="b">
+        <v>0</v>
+      </c>
+      <c r="J491" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K491" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M491" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N491" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P491" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>74.47</v>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S491" t="n">
+        <v>7</v>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V491" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="W491" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="X491" t="n">
+        <v>42.6405</v>
+      </c>
+      <c r="Y491" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z491" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG491" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH491" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI491" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>82.41</v>
+      </c>
+      <c r="F492" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I492" t="b">
+        <v>0</v>
+      </c>
+      <c r="J492" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K492" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M492" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N492" t="n">
+        <v>3</v>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P492" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>76.19</v>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S492" t="n">
+        <v>7</v>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V492" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="W492" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="X492" t="n">
+        <v>35.2005</v>
+      </c>
+      <c r="Y492" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z492" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG492" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH492" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI492" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>83.67</v>
+      </c>
+      <c r="F493" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I493" t="b">
+        <v>0</v>
+      </c>
+      <c r="J493" t="n">
+        <v>10</v>
+      </c>
+      <c r="K493" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M493" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N493" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P493" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S493" t="n">
+        <v>7</v>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V493" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="W493" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="X493" t="n">
+        <v>43.059</v>
+      </c>
+      <c r="Y493" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z493" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG493" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH493" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI493" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>兆豐金</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>86.54000000000001</v>
+      </c>
+      <c r="F494" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I494" t="b">
+        <v>0</v>
+      </c>
+      <c r="J494" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K494" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M494" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N494" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P494" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>73.36</v>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S494" t="n">
+        <v>7</v>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V494" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="W494" t="n">
+        <v>59.4873</v>
+      </c>
+      <c r="X494" t="n">
+        <v>48.081</v>
+      </c>
+      <c r="Y494" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z494" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG494" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH494" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI494" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>80.37</v>
+      </c>
+      <c r="F495" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I495" t="b">
+        <v>0</v>
+      </c>
+      <c r="J495" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K495" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M495" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N495" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P495" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>66.88</v>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S495" t="n">
+        <v>7</v>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V495" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="W495" t="n">
+        <v>51.18</v>
+      </c>
+      <c r="X495" t="n">
+        <v>39.6645</v>
+      </c>
+      <c r="Y495" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z495" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG495" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH495" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI495" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>78.91</v>
+      </c>
+      <c r="F496" t="n">
+        <v>60.78</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I496" t="b">
+        <v>0</v>
+      </c>
+      <c r="J496" t="n">
+        <v>10</v>
+      </c>
+      <c r="K496" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M496" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N496" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P496" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S496" t="n">
+        <v>7</v>
+      </c>
+      <c r="T496" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U496" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V496" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="W496" t="n">
+        <v>49.9959</v>
+      </c>
+      <c r="X496" t="n">
+        <v>40.641</v>
+      </c>
+      <c r="Y496" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z496" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG496" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH496" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI496" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>84.88</v>
+      </c>
+      <c r="F497" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I497" t="b">
+        <v>0</v>
+      </c>
+      <c r="J497" t="n">
+        <v>10</v>
+      </c>
+      <c r="K497" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M497" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N497" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P497" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>80.36</v>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S497" t="n">
+        <v>7</v>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V497" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="W497" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="X497" t="n">
+        <v>36.177</v>
+      </c>
+      <c r="Y497" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z497" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG497" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH497" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI497" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>3034</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>聯詠</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>74.15000000000001</v>
+      </c>
+      <c r="F498" t="n">
+        <v>64.19</v>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I498" t="b">
+        <v>0</v>
+      </c>
+      <c r="J498" t="n">
+        <v>10</v>
+      </c>
+      <c r="K498" t="n">
+        <v>601.7</v>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M498" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="N498" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P498" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S498" t="n">
+        <v>5.5932</v>
+      </c>
+      <c r="T498" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U498" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V498" t="n">
+        <v>547</v>
+      </c>
+      <c r="W498" t="n">
+        <v>622.8916</v>
+      </c>
+      <c r="X498" t="n">
+        <v>516.405</v>
+      </c>
+      <c r="Y498" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z498" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG498" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH498" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI498" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>72.69</v>
+      </c>
+      <c r="F499" t="n">
+        <v>61.22</v>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I499" t="b">
+        <v>0</v>
+      </c>
+      <c r="J499" t="n">
+        <v>10</v>
+      </c>
+      <c r="K499" t="n">
+        <v>558.8</v>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M499" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="N499" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P499" t="n">
+        <v>495.5</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>58.12</v>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S499" t="n">
+        <v>6.9636</v>
+      </c>
+      <c r="T499" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U499" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V499" t="n">
+        <v>508</v>
+      </c>
+      <c r="W499" t="n">
+        <v>582.8035</v>
+      </c>
+      <c r="X499" t="n">
+        <v>472.625</v>
+      </c>
+      <c r="Y499" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z499" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG499" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH499" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI499" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>87.05</v>
+      </c>
+      <c r="F500" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I500" t="b">
+        <v>0</v>
+      </c>
+      <c r="J500" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K500" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M500" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N500" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P500" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S500" t="n">
+        <v>6.0183</v>
+      </c>
+      <c r="T500" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U500" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V500" t="n">
+        <v>121</v>
+      </c>
+      <c r="W500" t="n">
+        <v>136.1995</v>
+      </c>
+      <c r="X500" t="n">
+        <v>113.7179</v>
+      </c>
+      <c r="Y500" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z500" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG500" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH500" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI500" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="F501" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I501" t="b">
+        <v>0</v>
+      </c>
+      <c r="J501" t="n">
+        <v>10</v>
+      </c>
+      <c r="K501" t="n">
+        <v>6732</v>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M501" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N501" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P501" t="n">
+        <v>6085</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S501" t="n">
+        <v>7</v>
+      </c>
+      <c r="T501" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V501" t="n">
+        <v>6120</v>
+      </c>
+      <c r="W501" t="n">
+        <v>7344</v>
+      </c>
+      <c r="X501" t="n">
+        <v>5691.6</v>
+      </c>
+      <c r="Y501" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z501" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG501" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH501" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI501" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="F502" t="n">
+        <v>54.05</v>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I502" t="b">
+        <v>0</v>
+      </c>
+      <c r="J502" t="n">
+        <v>10</v>
+      </c>
+      <c r="K502" t="n">
+        <v>465.3</v>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M502" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N502" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P502" t="n">
+        <v>403</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S502" t="n">
+        <v>7</v>
+      </c>
+      <c r="T502" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V502" t="n">
+        <v>423</v>
+      </c>
+      <c r="W502" t="n">
+        <v>507.6</v>
+      </c>
+      <c r="X502" t="n">
+        <v>393.39</v>
+      </c>
+      <c r="Y502" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z502" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI502" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>73.81</v>
+      </c>
+      <c r="F503" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I503" t="b">
+        <v>0</v>
+      </c>
+      <c r="J503" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="K503" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M503" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N503" t="n">
+        <v>10</v>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P503" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S503" t="n">
+        <v>5.4638</v>
+      </c>
+      <c r="T503" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V503" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="W503" t="n">
+        <v>116.0928</v>
+      </c>
+      <c r="X503" t="n">
+        <v>99.73569999999999</v>
+      </c>
+      <c r="Y503" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z503" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG503" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH503" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI503" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="F504" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I504" t="b">
+        <v>0</v>
+      </c>
+      <c r="J504" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K504" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M504" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N504" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P504" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S504" t="n">
+        <v>7</v>
+      </c>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V504" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W504" t="n">
+        <v>31.1489</v>
+      </c>
+      <c r="X504" t="n">
+        <v>25.296</v>
+      </c>
+      <c r="Y504" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z504" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG504" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH504" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI504" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ484"/>
+  <autoFilter ref="A1:AJ504"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -52830,25 +55490,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4881</v>
+        <v>0.4857</v>
       </c>
       <c r="D4" t="n">
-        <v>2.36</v>
+        <v>2.01</v>
       </c>
       <c r="E4" t="n">
-        <v>12.94</v>
+        <v>13.12</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.02</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2976</v>
+        <v>0.3048</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4643</v>
+        <v>0.4762</v>
       </c>
     </row>
   </sheetData>
@@ -52964,25 +55624,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4881</v>
+        <v>0.4857</v>
       </c>
       <c r="D6" t="n">
-        <v>2.36</v>
+        <v>2.01</v>
       </c>
       <c r="E6" t="n">
-        <v>12.94</v>
+        <v>13.12</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.02</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2976</v>
+        <v>0.3048</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4643</v>
+        <v>0.4762</v>
       </c>
     </row>
   </sheetData>
@@ -53023,7 +55683,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-10 14:25:36</t>
+          <t>2026-09-11 14:27:05</t>
         </is>
       </c>
     </row>
@@ -53070,7 +55730,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>483</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7">
@@ -53080,7 +55740,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
@@ -53090,7 +55750,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
